--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>171</v>
+        <v>171.9</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>499</v>
+        <v>458</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>870</v>
+        <v>918</v>
       </c>
       <c r="M2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~870u (435cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~918u (459cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>50.1</v>
+        <v>52</v>
       </c>
       <c r="I3" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>259</v>
+        <v>236</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,13 +643,13 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="I4" t="n">
         <v>6.3</v>
       </c>
       <c r="J4" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -658,13 +658,13 @@
         <v>46</v>
       </c>
       <c r="M4" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>21.3</v>
+        <v>21.9</v>
       </c>
       <c r="I5" t="n">
-        <v>11.7</v>
+        <v>10.8</v>
       </c>
       <c r="J5" t="n">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -716,13 +716,13 @@
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>17.8</v>
+        <v>18.5</v>
       </c>
       <c r="I6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J6" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -774,13 +774,13 @@
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="J7" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -838,7 +838,7 @@
         <v>42</v>
       </c>
       <c r="O7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -875,13 +875,13 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="J8" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -896,7 +896,7 @@
         <v>44</v>
       </c>
       <c r="O8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -933,13 +933,13 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="J9" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -954,7 +954,7 @@
         <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -975,55 +975,55 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.7</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>21.7</v>
+        <v>11.2</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>8.5</v>
+        <v>14.1</v>
       </c>
       <c r="I10" t="n">
-        <v>11.3</v>
+        <v>4.4</v>
       </c>
       <c r="J10" t="n">
-        <v>97</v>
+        <v>69</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O10" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>BUY ~48u (8cs) - sells in ~3 wks</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1033,55 +1033,55 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.5</v>
+        <v>25.7</v>
       </c>
       <c r="E11" t="n">
-        <v>9.06</v>
+        <v>21.7</v>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>21.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>7.2</v>
+        <v>10.4</v>
       </c>
       <c r="J11" t="n">
-        <v>154</v>
+        <v>92</v>
       </c>
       <c r="K11" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>29.6</v>
+        <v>0.2</v>
       </c>
       <c r="N11" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O11" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~30 wks (overstock); consider ~624u</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1091,55 +1091,55 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G12" t="n">
         <v>14</v>
       </c>
-      <c r="E12" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G12" t="n">
-        <v>20</v>
-      </c>
       <c r="H12" t="n">
-        <v>10.5</v>
+        <v>24</v>
       </c>
       <c r="I12" t="n">
-        <v>8.300000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
-        <v>96</v>
+        <v>130</v>
       </c>
       <c r="K12" t="n">
-        <v>24</v>
+        <v>624</v>
       </c>
       <c r="L12" t="n">
-        <v>24</v>
+        <v>624</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3</v>
+        <v>26</v>
       </c>
       <c r="N12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O12" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~2 wks</t>
+          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,55 +1149,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>25.7</v>
       </c>
       <c r="E13" t="n">
-        <v>9.9</v>
+        <v>21.7</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>11.4</v>
+        <v>6.7</v>
       </c>
       <c r="I13" t="n">
-        <v>3.2</v>
+        <v>8.1</v>
       </c>
       <c r="J13" t="n">
+        <v>55</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>50</v>
+      </c>
+      <c r="O13" t="n">
         <v>27</v>
       </c>
-      <c r="K13" t="n">
-        <v>6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>66</v>
-      </c>
-      <c r="M13" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="N13" t="n">
-        <v>45</v>
-      </c>
-      <c r="O13" t="n">
-        <v>24</v>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BUY ~66u (11cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,55 +1207,55 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25.7</v>
+        <v>10.5</v>
       </c>
       <c r="E14" t="n">
-        <v>21.7</v>
+        <v>9.06</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="G14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>5.9</v>
+        <v>15.7</v>
       </c>
       <c r="I14" t="n">
-        <v>9.6</v>
+        <v>11.4</v>
       </c>
       <c r="J14" t="n">
-        <v>57</v>
+        <v>181</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>39.7</v>
       </c>
       <c r="N14" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1281,39 +1281,39 @@
         <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>10.9</v>
+        <v>10.6</v>
       </c>
       <c r="I15" t="n">
-        <v>7.9</v>
+        <v>3.2</v>
       </c>
       <c r="J15" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="K15" t="n">
         <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="M15" t="n">
-        <v>2.8</v>
+        <v>6.2</v>
       </c>
       <c r="N15" t="n">
         <v>45</v>
       </c>
       <c r="O15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~66u (11cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1323,55 +1323,55 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>9.67</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>7.57</v>
+        <v>9.9</v>
       </c>
       <c r="F16" t="n">
         <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>8.5</v>
       </c>
       <c r="J16" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="K16" t="n">
         <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="M16" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="N16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O16" t="n">
         <v>21</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUY ~42u (7cs) - sells in ~4 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1381,38 +1381,38 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8.67</v>
+        <v>10.5</v>
       </c>
       <c r="E17" t="n">
-        <v>6.57</v>
+        <v>9.06</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>9.9</v>
+        <v>14.9</v>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="J17" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L17" t="n">
-        <v>42</v>
+        <v>624</v>
       </c>
       <c r="M17" t="n">
-        <v>4.2</v>
+        <v>41.7</v>
       </c>
       <c r="N17" t="n">
         <v>45</v>
@@ -1422,14 +1422,14 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BUY ~42u (7cs) - sells in ~4 wks</t>
+          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,55 +1439,55 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="E18" t="n">
-        <v>9.06</v>
+        <v>16.67</v>
       </c>
       <c r="F18" t="n">
-        <v>1.44</v>
+        <v>3.33</v>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>14.6</v>
+        <v>5.8</v>
       </c>
       <c r="I18" t="n">
-        <v>13.3</v>
+        <v>14.2</v>
       </c>
       <c r="J18" t="n">
-        <v>196</v>
+        <v>84</v>
       </c>
       <c r="K18" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="M18" t="n">
-        <v>42.7</v>
+        <v>0.5</v>
       </c>
       <c r="N18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,55 +1497,55 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>10.5</v>
       </c>
       <c r="E19" t="n">
-        <v>8.4</v>
+        <v>9.06</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>9.9</v>
+        <v>12.7</v>
       </c>
       <c r="I19" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="J19" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L19" t="n">
-        <v>42</v>
+        <v>624</v>
       </c>
       <c r="M19" t="n">
-        <v>4.2</v>
+        <v>49.2</v>
       </c>
       <c r="N19" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O19" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUY ~42u (7cs) - sells in ~4 wks</t>
+          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,55 +1555,55 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.5</v>
+        <v>8.67</v>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>6.57</v>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H20" t="n">
-        <v>14.1</v>
+        <v>8.6</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="K20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>624</v>
+        <v>30</v>
       </c>
       <c r="M20" t="n">
-        <v>44.4</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
         <v>45</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~44 wks (overstock); consider ~624u</t>
+          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,55 +1613,55 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>9.67</v>
       </c>
       <c r="E21" t="n">
-        <v>16.67</v>
+        <v>7.57</v>
       </c>
       <c r="F21" t="n">
-        <v>3.33</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H21" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="I21" t="n">
-        <v>15.5</v>
+        <v>4.6</v>
       </c>
       <c r="J21" t="n">
-        <v>88</v>
+        <v>40</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
         <v>46</v>
       </c>
       <c r="O21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks</t>
+          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,48 +1671,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.03</v>
+        <v>10.5</v>
       </c>
       <c r="E22" t="n">
-        <v>9.15</v>
+        <v>8.4</v>
       </c>
       <c r="F22" t="n">
-        <v>0.88</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>18.1</v>
+        <v>8.6</v>
       </c>
       <c r="I22" t="n">
-        <v>11</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>201</v>
+        <v>40</v>
       </c>
       <c r="K22" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>624</v>
+        <v>30</v>
       </c>
       <c r="M22" t="n">
-        <v>34.6</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~35 wks (overstock); consider ~624u</t>
+          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
@@ -1745,13 +1745,13 @@
         <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>18.6</v>
+        <v>19.3</v>
       </c>
       <c r="I23" t="n">
-        <v>9.9</v>
+        <v>8.6</v>
       </c>
       <c r="J23" t="n">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="K23" t="n">
         <v>624</v>
@@ -1760,24 +1760,24 @@
         <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>33.5</v>
+        <v>32.2</v>
       </c>
       <c r="N23" t="n">
         <v>46</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~34 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~32 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.5</v>
+        <v>9.33</v>
       </c>
       <c r="E24" t="n">
-        <v>9.06</v>
+        <v>8.01</v>
       </c>
       <c r="F24" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="G24" t="n">
         <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>10.9</v>
+        <v>12.1</v>
       </c>
       <c r="I24" t="n">
-        <v>6.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K24" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L24" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M24" t="n">
-        <v>57.5</v>
+        <v>12.3</v>
       </c>
       <c r="N24" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O24" t="n">
         <v>16</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~58 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~12 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1849,51 +1849,51 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9.33</v>
+        <v>10.5</v>
       </c>
       <c r="E25" t="n">
-        <v>8.01</v>
+        <v>9.06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="G25" t="n">
         <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="I25" t="n">
-        <v>10.6</v>
+        <v>14.5</v>
       </c>
       <c r="J25" t="n">
-        <v>73</v>
+        <v>167</v>
       </c>
       <c r="K25" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L25" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M25" t="n">
-        <v>13</v>
+        <v>54.6</v>
       </c>
       <c r="N25" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~55 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.67</v>
+        <v>10.03</v>
       </c>
       <c r="E26" t="n">
-        <v>13.34</v>
+        <v>9.15</v>
       </c>
       <c r="F26" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="I26" t="n">
-        <v>7.9</v>
+        <v>10.8</v>
       </c>
       <c r="J26" t="n">
-        <v>37</v>
+        <v>202</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="M26" t="n">
-        <v>0.6</v>
+        <v>33.7</v>
       </c>
       <c r="N26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~34 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.03</v>
+        <v>16.67</v>
       </c>
       <c r="E27" t="n">
-        <v>9.15</v>
+        <v>13.34</v>
       </c>
       <c r="F27" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G27" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>14.3</v>
+        <v>4.9</v>
       </c>
       <c r="I27" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>158</v>
+        <v>35</v>
       </c>
       <c r="K27" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
-        <v>43.7</v>
+        <v>1.2</v>
       </c>
       <c r="N27" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O27" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~44 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (2cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,55 +2019,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D28" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="E28" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G28" t="n">
+        <v>9</v>
+      </c>
+      <c r="H28" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J28" t="n">
+        <v>149</v>
+      </c>
+      <c r="K28" t="n">
+        <v>624</v>
+      </c>
+      <c r="L28" t="n">
+        <v>624</v>
+      </c>
+      <c r="M28" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="N28" t="n">
+        <v>46</v>
+      </c>
+      <c r="O28" t="n">
         <v>14</v>
       </c>
-      <c r="E28" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G28" t="n">
-        <v>20</v>
-      </c>
-      <c r="H28" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J28" t="n">
-        <v>30</v>
-      </c>
-      <c r="K28" t="n">
-        <v>24</v>
-      </c>
-      <c r="L28" t="n">
-        <v>24</v>
-      </c>
-      <c r="M28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N28" t="n">
-        <v>44</v>
-      </c>
-      <c r="O28" t="n">
-        <v>13</v>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~5 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~41 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="E29" t="n">
-        <v>9.06</v>
+        <v>11.2</v>
       </c>
       <c r="F29" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="G29" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>9.300000000000001</v>
+        <v>4.6</v>
       </c>
       <c r="I29" t="n">
-        <v>19.4</v>
+        <v>7.4</v>
       </c>
       <c r="J29" t="n">
-        <v>182</v>
+        <v>30</v>
       </c>
       <c r="K29" t="n">
-        <v>624</v>
+        <v>24</v>
       </c>
       <c r="L29" t="n">
-        <v>624</v>
+        <v>24</v>
       </c>
       <c r="M29" t="n">
-        <v>67.2</v>
+        <v>5.2</v>
       </c>
       <c r="N29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O29" t="n">
         <v>13</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~67 wks (overstock); consider ~624u</t>
+          <t>BUY ~24u (4cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,38 +2135,38 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>26.52</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>24.2</v>
+        <v>11.2</v>
       </c>
       <c r="F30" t="n">
-        <v>2.33</v>
+        <v>0.8</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>5.1</v>
+        <v>15.1</v>
       </c>
       <c r="I30" t="n">
-        <v>13.2</v>
+        <v>9.6</v>
       </c>
       <c r="J30" t="n">
-        <v>68</v>
+        <v>156</v>
       </c>
       <c r="K30" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="L30" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="M30" t="n">
-        <v>40.7</v>
+        <v>5.6</v>
       </c>
       <c r="N30" t="n">
         <v>44</v>
@@ -2176,14 +2176,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~41 wks (overstock); consider ~208u</t>
+          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2193,55 +2193,55 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>26.52</v>
       </c>
       <c r="E31" t="n">
-        <v>11.2</v>
+        <v>24.2</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8</v>
+        <v>2.33</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H31" t="n">
-        <v>13.6</v>
+        <v>5.2</v>
       </c>
       <c r="I31" t="n">
-        <v>9.800000000000001</v>
+        <v>12.8</v>
       </c>
       <c r="J31" t="n">
-        <v>143</v>
+        <v>68</v>
       </c>
       <c r="K31" t="n">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="L31" t="n">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="M31" t="n">
-        <v>6.2</v>
+        <v>39.6</v>
       </c>
       <c r="N31" t="n">
         <v>44</v>
       </c>
       <c r="O31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
+          <t>CAUTION - 208u = ~40 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,29 +2251,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.67</v>
+        <v>10.85</v>
       </c>
       <c r="E32" t="n">
-        <v>7.57</v>
+        <v>8.68</v>
       </c>
       <c r="F32" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="G32" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="J32" t="n">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="K32" t="n">
         <v>6</v>
@@ -2288,18 +2288,18 @@
         <v>46</v>
       </c>
       <c r="O32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,29 +2309,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E33" t="n">
-        <v>8.4</v>
+        <v>8.68</v>
       </c>
       <c r="F33" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="G33" t="n">
         <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I33" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="J33" t="n">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="K33" t="n">
         <v>6</v>
@@ -2343,14 +2343,14 @@
         <v>1.2</v>
       </c>
       <c r="N33" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2383,13 +2383,13 @@
         <v>20</v>
       </c>
       <c r="H34" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I34" t="n">
-        <v>22.2</v>
+        <v>21.4</v>
       </c>
       <c r="J34" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K34" t="n">
         <v>6</v>
@@ -2398,13 +2398,13 @@
         <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N34" t="n">
         <v>46</v>
       </c>
       <c r="O34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2425,17 +2425,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E35" t="n">
-        <v>8.68</v>
+        <v>8.4</v>
       </c>
       <c r="F35" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G35" t="n">
         <v>20</v>
@@ -2444,10 +2444,10 @@
         <v>4.6</v>
       </c>
       <c r="I35" t="n">
-        <v>22</v>
+        <v>13.4</v>
       </c>
       <c r="J35" t="n">
-        <v>143</v>
+        <v>62</v>
       </c>
       <c r="K35" t="n">
         <v>6</v>
@@ -2459,21 +2459,21 @@
         <v>1.3</v>
       </c>
       <c r="N35" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O35" t="n">
         <v>10</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2487,51 +2487,51 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="E36" t="n">
-        <v>18.02</v>
+        <v>9.06</v>
       </c>
       <c r="F36" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="G36" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H36" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
       <c r="I36" t="n">
-        <v>14.1</v>
+        <v>9.4</v>
       </c>
       <c r="J36" t="n">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="K36" t="n">
-        <v>40</v>
+        <v>624</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
+        <v>624</v>
       </c>
       <c r="M36" t="n">
-        <v>8.1</v>
+        <v>92.5</v>
       </c>
       <c r="N36" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O36" t="n">
         <v>10</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~8 wks (cooling)</t>
+          <t>CAUTION - 624u = ~92 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,55 +2541,55 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8.67</v>
+        <v>20</v>
       </c>
       <c r="E37" t="n">
-        <v>6.57</v>
+        <v>18.02</v>
       </c>
       <c r="F37" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="G37" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H37" t="n">
         <v>4.9</v>
       </c>
       <c r="I37" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="J37" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="K37" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L37" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="M37" t="n">
-        <v>1.2</v>
+        <v>8.1</v>
       </c>
       <c r="N37" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~40u (10cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2599,55 +2599,55 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>8.67</v>
       </c>
       <c r="E38" t="n">
-        <v>9.82</v>
+        <v>6.57</v>
       </c>
       <c r="F38" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="G38" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H38" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="I38" t="n">
-        <v>14.2</v>
+        <v>13.4</v>
       </c>
       <c r="J38" t="n">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="K38" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L38" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>20.7</v>
+        <v>1.3</v>
       </c>
       <c r="N38" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,29 +2657,29 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.85</v>
+        <v>9.67</v>
       </c>
       <c r="E39" t="n">
-        <v>8.68</v>
+        <v>7.57</v>
       </c>
       <c r="F39" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H39" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I39" t="n">
-        <v>19.7</v>
+        <v>13.4</v>
       </c>
       <c r="J39" t="n">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="K39" t="n">
         <v>6</v>
@@ -2688,24 +2688,24 @@
         <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N39" t="n">
         <v>46</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2715,55 +2715,55 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E40" t="n">
-        <v>9.06</v>
+        <v>11.2</v>
       </c>
       <c r="F40" t="n">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="G40" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>5.4</v>
+        <v>10</v>
       </c>
       <c r="I40" t="n">
-        <v>13</v>
+        <v>8.9</v>
       </c>
       <c r="J40" t="n">
-        <v>71</v>
+        <v>127</v>
       </c>
       <c r="K40" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="L40" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="M40" t="n">
-        <v>115.8</v>
+        <v>8.4</v>
       </c>
       <c r="N40" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O40" t="n">
         <v>8</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~116 wks (overstock); consider ~624u</t>
+          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,48 +2773,48 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>11.2</v>
+        <v>9.82</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="G41" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H41" t="n">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="I41" t="n">
-        <v>10.3</v>
+        <v>14.9</v>
       </c>
       <c r="J41" t="n">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="K41" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L41" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M41" t="n">
-        <v>10</v>
+        <v>21.1</v>
       </c>
       <c r="N41" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~10 wks (cooling)</t>
+          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2847,13 +2847,13 @@
         <v>7</v>
       </c>
       <c r="H42" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>16.1</v>
+        <v>13.6</v>
       </c>
       <c r="J42" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K42" t="n">
         <v>84</v>
@@ -2862,24 +2862,24 @@
         <v>84</v>
       </c>
       <c r="M42" t="n">
-        <v>12</v>
+        <v>10.2</v>
       </c>
       <c r="N42" t="n">
         <v>44</v>
       </c>
       <c r="O42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~12 wks (cooling)</t>
+          <t>BUY ~84u (14cs) - sells in ~10 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,48 +2889,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>10.85</v>
       </c>
       <c r="E43" t="n">
-        <v>9.82</v>
+        <v>8.68</v>
       </c>
       <c r="F43" t="n">
-        <v>1.18</v>
+        <v>2.17</v>
       </c>
       <c r="G43" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="I43" t="n">
-        <v>23.6</v>
+        <v>29.2</v>
       </c>
       <c r="J43" t="n">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="K43" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L43" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>31.1</v>
+        <v>2.3</v>
       </c>
       <c r="N43" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O43" t="n">
         <v>6</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~31 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2963,13 +2963,13 @@
         <v>11</v>
       </c>
       <c r="H44" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>23.6</v>
+        <v>21.6</v>
       </c>
       <c r="J44" t="n">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="K44" t="n">
         <v>150</v>
@@ -2978,7 +2978,7 @@
         <v>150</v>
       </c>
       <c r="M44" t="n">
-        <v>31.6</v>
+        <v>29.9</v>
       </c>
       <c r="N44" t="n">
         <v>45</v>
@@ -2988,14 +2988,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~32 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~30 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.85</v>
+        <v>10.03</v>
       </c>
       <c r="E45" t="n">
-        <v>8.68</v>
+        <v>9.15</v>
       </c>
       <c r="F45" t="n">
-        <v>2.17</v>
+        <v>0.88</v>
       </c>
       <c r="G45" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H45" t="n">
-        <v>2.8</v>
+        <v>6.5</v>
       </c>
       <c r="I45" t="n">
-        <v>27.9</v>
+        <v>16.2</v>
       </c>
       <c r="J45" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K45" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L45" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M45" t="n">
-        <v>2.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="N45" t="n">
         <v>46</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
+          <t>CAUTION - 624u = ~95 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,48 +3063,48 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F46" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="I46" t="n">
-        <v>18.9</v>
+        <v>20.2</v>
       </c>
       <c r="J46" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="K46" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L46" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M46" t="n">
-        <v>105.3</v>
+        <v>28</v>
       </c>
       <c r="N46" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~105 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 150u = ~28 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3140,10 +3140,10 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="J47" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K47" t="n">
         <v>150</v>
@@ -3195,10 +3195,10 @@
         <v>11</v>
       </c>
       <c r="H48" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>16.6</v>
       </c>
       <c r="J48" t="n">
         <v>85</v>
@@ -3210,7 +3210,7 @@
         <v>150</v>
       </c>
       <c r="M48" t="n">
-        <v>48</v>
+        <v>41.9</v>
       </c>
       <c r="N48" t="n">
         <v>45</v>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~48 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~42 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3253,13 +3253,13 @@
         <v>15</v>
       </c>
       <c r="H49" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="I49" t="n">
-        <v>23.5</v>
+        <v>20.1</v>
       </c>
       <c r="J49" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K49" t="n">
         <v>40</v>
@@ -3268,17 +3268,17 @@
         <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>23.2</v>
+        <v>20.8</v>
       </c>
       <c r="N49" t="n">
         <v>48</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~23 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 40u = ~21 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Stigma Berry Tea 10mg THC</t>
+          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3353,38 +3353,38 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.03</v>
+        <v>10.58</v>
       </c>
       <c r="E51" t="n">
-        <v>9.15</v>
+        <v>7.06</v>
       </c>
       <c r="F51" t="n">
-        <v>0.88</v>
+        <v>3.53</v>
       </c>
       <c r="G51" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H51" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="I51" t="n">
-        <v>13.1</v>
+        <v>35.6</v>
       </c>
       <c r="J51" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K51" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="L51" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M51" t="n">
-        <v>329.6</v>
+        <v>18.7</v>
       </c>
       <c r="N51" t="n">
         <v>46</v>
@@ -3394,14 +3394,14 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~330 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 12u = ~19 wks (overstock); consider ~12u</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
+          <t>Stigma Berry Tea 10mg THC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3411,48 +3411,48 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.58</v>
+        <v>10.03</v>
       </c>
       <c r="E52" t="n">
-        <v>7.06</v>
+        <v>9.15</v>
       </c>
       <c r="F52" t="n">
-        <v>3.53</v>
+        <v>0.88</v>
       </c>
       <c r="G52" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="I52" t="n">
-        <v>35.6</v>
+        <v>15.6</v>
       </c>
       <c r="J52" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
-        <v>12</v>
+        <v>624</v>
       </c>
       <c r="L52" t="n">
-        <v>12</v>
+        <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>18.7</v>
+        <v>393.6</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 12u = ~19 wks (overstock); consider ~12u</t>
+          <t>CAUTION - 624u = ~394 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3485,13 +3485,13 @@
         <v>11</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="I53" t="n">
-        <v>148.9</v>
+        <v>114.1</v>
       </c>
       <c r="J53" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K53" t="n">
         <v>150</v>
@@ -3500,7 +3500,7 @@
         <v>150</v>
       </c>
       <c r="M53" t="n">
-        <v>256.4</v>
+        <v>198.9</v>
       </c>
       <c r="N53" t="n">
         <v>55</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~256 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~199 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>171.9</v>
+        <v>171.5</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>918</v>
+        <v>932</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~918u (459cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~932u (466cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
         <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -643,10 +643,10 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>20.3</v>
+        <v>18.9</v>
       </c>
       <c r="I4" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="J4" t="n">
         <v>117</v>
@@ -655,20 +655,20 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="M4" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~46u (23cs) - sells in ~2 wks</t>
+          <t>BUY ~36u (18cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="I5" t="n">
         <v>10.8</v>
       </c>
       <c r="J5" t="n">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="I6" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J6" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -774,13 +774,13 @@
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I7" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="J7" t="n">
         <v>84</v>
@@ -875,10 +875,10 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="J8" t="n">
         <v>84</v>
@@ -933,10 +933,10 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I9" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="J9" t="n">
         <v>84</v>
@@ -991,10 +991,10 @@
         <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="I10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
         <v>69</v>
@@ -1003,20 +1003,20 @@
         <v>24</v>
       </c>
       <c r="L10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
         <v>44</v>
       </c>
       <c r="O10" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~48u (8cs) - sells in ~3 wks</t>
+          <t>BUY ~42u (7cs) - sells in ~3 wks</t>
         </is>
       </c>
     </row>
@@ -1049,10 +1049,10 @@
         <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>10.4</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
         <v>92</v>
@@ -1070,7 +1070,7 @@
         <v>50</v>
       </c>
       <c r="O11" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>24</v>
+        <v>23.1</v>
       </c>
       <c r="I12" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J12" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K12" t="n">
         <v>624</v>
@@ -1122,17 +1122,17 @@
         <v>624</v>
       </c>
       <c r="M12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="N12" t="n">
         <v>45</v>
       </c>
       <c r="O12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~27 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
         <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="I13" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="J13" t="n">
         <v>55</v>
@@ -1186,7 +1186,7 @@
         <v>50</v>
       </c>
       <c r="O13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1223,13 +1223,13 @@
         <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="I14" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="J14" t="n">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="K14" t="n">
         <v>624</v>
@@ -1238,13 +1238,13 @@
         <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>39.7</v>
+        <v>39.9</v>
       </c>
       <c r="N14" t="n">
         <v>45</v>
       </c>
       <c r="O14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1281,13 +1281,13 @@
         <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="I15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K15" t="n">
         <v>6</v>
@@ -1313,7 +1313,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1323,38 +1323,38 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E16" t="n">
-        <v>9.9</v>
+        <v>9.06</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>10</v>
+        <v>14.9</v>
       </c>
       <c r="I16" t="n">
-        <v>8.5</v>
+        <v>3.9</v>
       </c>
       <c r="J16" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L16" t="n">
-        <v>24</v>
+        <v>624</v>
       </c>
       <c r="M16" t="n">
-        <v>2.4</v>
+        <v>42</v>
       </c>
       <c r="N16" t="n">
         <v>45</v>
@@ -1364,14 +1364,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1381,55 +1381,55 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
-        <v>9.06</v>
+        <v>9.9</v>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H17" t="n">
-        <v>14.9</v>
+        <v>9.6</v>
       </c>
       <c r="I17" t="n">
-        <v>2.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K17" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>624</v>
+        <v>18</v>
       </c>
       <c r="M17" t="n">
-        <v>41.7</v>
+        <v>1.9</v>
       </c>
       <c r="N17" t="n">
         <v>45</v>
       </c>
       <c r="O17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
+          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,55 +1439,55 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="E18" t="n">
-        <v>16.67</v>
+        <v>9.06</v>
       </c>
       <c r="F18" t="n">
-        <v>3.33</v>
+        <v>1.44</v>
       </c>
       <c r="G18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>5.8</v>
+        <v>12.7</v>
       </c>
       <c r="I18" t="n">
-        <v>14.2</v>
+        <v>6.3</v>
       </c>
       <c r="J18" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L18" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5</v>
+        <v>49</v>
       </c>
       <c r="N18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,48 +1497,48 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.5</v>
+        <v>9.67</v>
       </c>
       <c r="E19" t="n">
-        <v>9.06</v>
+        <v>7.57</v>
       </c>
       <c r="F19" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H19" t="n">
-        <v>12.7</v>
+        <v>8.6</v>
       </c>
       <c r="I19" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="J19" t="n">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="K19" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>624</v>
+        <v>30</v>
       </c>
       <c r="M19" t="n">
-        <v>49.2</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O19" t="n">
         <v>18</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
+          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
@@ -1574,10 +1574,10 @@
         <v>8.6</v>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J20" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
@@ -1603,7 +1603,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,38 +1613,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9.67</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>7.57</v>
+        <v>16.67</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>3.33</v>
       </c>
       <c r="G21" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="I21" t="n">
-        <v>4.6</v>
+        <v>15.8</v>
       </c>
       <c r="J21" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="N21" t="n">
         <v>46</v>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
+          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1690,10 +1690,10 @@
         <v>8.6</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K22" t="n">
         <v>6</v>
@@ -1745,13 +1745,13 @@
         <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="I23" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="J23" t="n">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="K23" t="n">
         <v>624</v>
@@ -1760,7 +1760,7 @@
         <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="N23" t="n">
         <v>46</v>
@@ -1777,7 +1777,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9.33</v>
+        <v>10.5</v>
       </c>
       <c r="E24" t="n">
-        <v>8.01</v>
+        <v>9.06</v>
       </c>
       <c r="F24" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="G24" t="n">
         <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>12.1</v>
+        <v>11.6</v>
       </c>
       <c r="I24" t="n">
-        <v>9.699999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="J24" t="n">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="K24" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L24" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M24" t="n">
-        <v>12.3</v>
+        <v>53.8</v>
       </c>
       <c r="N24" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~12 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~54 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,29 +1845,29 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.5</v>
+        <v>10.03</v>
       </c>
       <c r="E25" t="n">
-        <v>9.06</v>
+        <v>9.15</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44</v>
+        <v>0.88</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>11.4</v>
+        <v>18</v>
       </c>
       <c r="I25" t="n">
-        <v>14.5</v>
+        <v>11.1</v>
       </c>
       <c r="J25" t="n">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="K25" t="n">
         <v>624</v>
@@ -1876,24 +1876,24 @@
         <v>624</v>
       </c>
       <c r="M25" t="n">
-        <v>54.6</v>
+        <v>34.7</v>
       </c>
       <c r="N25" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O25" t="n">
         <v>16</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~55 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~35 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.03</v>
+        <v>16.67</v>
       </c>
       <c r="E26" t="n">
-        <v>9.15</v>
+        <v>13.34</v>
       </c>
       <c r="F26" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H26" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>10.8</v>
+        <v>7.4</v>
       </c>
       <c r="J26" t="n">
-        <v>202</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>33.7</v>
+        <v>0.7</v>
       </c>
       <c r="N26" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~34 wks (overstock); consider ~624u</t>
+          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,48 +1961,48 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.67</v>
+        <v>9.33</v>
       </c>
       <c r="E27" t="n">
-        <v>13.34</v>
+        <v>8.01</v>
       </c>
       <c r="F27" t="n">
-        <v>3.33</v>
+        <v>1.32</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>10.1</v>
       </c>
       <c r="J27" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M27" t="n">
-        <v>1.2</v>
+        <v>13</v>
       </c>
       <c r="N27" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~6u (2cs) - sells in ~1 wks</t>
+          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2035,13 +2035,13 @@
         <v>9</v>
       </c>
       <c r="H28" t="n">
-        <v>15.3</v>
+        <v>14.9</v>
       </c>
       <c r="I28" t="n">
-        <v>9.6</v>
+        <v>10.7</v>
       </c>
       <c r="J28" t="n">
-        <v>149</v>
+        <v>161</v>
       </c>
       <c r="K28" t="n">
         <v>624</v>
@@ -2050,24 +2050,24 @@
         <v>624</v>
       </c>
       <c r="M28" t="n">
-        <v>40.7</v>
+        <v>41.8</v>
       </c>
       <c r="N28" t="n">
         <v>46</v>
       </c>
       <c r="O28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~41 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14</v>
+        <v>26.52</v>
       </c>
       <c r="E29" t="n">
-        <v>11.2</v>
+        <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="J29" t="n">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="K29" t="n">
-        <v>24</v>
+        <v>208</v>
       </c>
       <c r="L29" t="n">
-        <v>24</v>
+        <v>208</v>
       </c>
       <c r="M29" t="n">
-        <v>5.2</v>
+        <v>41.8</v>
       </c>
       <c r="N29" t="n">
         <v>44</v>
       </c>
       <c r="O29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~5 wks (rising into season)</t>
+          <t>CAUTION - 208u = ~42 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,38 +2135,38 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E30" t="n">
         <v>11.2</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H30" t="n">
-        <v>15.1</v>
+        <v>4.4</v>
       </c>
       <c r="I30" t="n">
-        <v>9.6</v>
+        <v>8</v>
       </c>
       <c r="J30" t="n">
-        <v>156</v>
+        <v>31</v>
       </c>
       <c r="K30" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="L30" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="M30" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="N30" t="n">
         <v>44</v>
@@ -2176,14 +2176,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2193,38 +2193,38 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.52</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>24.2</v>
+        <v>11.2</v>
       </c>
       <c r="F31" t="n">
-        <v>2.33</v>
+        <v>0.8</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>5.2</v>
+        <v>14.9</v>
       </c>
       <c r="I31" t="n">
-        <v>12.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>68</v>
+        <v>156</v>
       </c>
       <c r="K31" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="L31" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="M31" t="n">
-        <v>39.6</v>
+        <v>5.6</v>
       </c>
       <c r="N31" t="n">
         <v>44</v>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~40 wks (overstock); consider ~208u</t>
+          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2267,13 +2267,13 @@
         <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I32" t="n">
-        <v>19.5</v>
+        <v>21.2</v>
       </c>
       <c r="J32" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K32" t="n">
         <v>6</v>
@@ -2299,7 +2299,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,29 +2309,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E33" t="n">
-        <v>8.68</v>
+        <v>8.4</v>
       </c>
       <c r="F33" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G33" t="n">
         <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="I33" t="n">
-        <v>15.5</v>
+        <v>13.4</v>
       </c>
       <c r="J33" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="K33" t="n">
         <v>6</v>
@@ -2340,24 +2340,24 @@
         <v>6</v>
       </c>
       <c r="M33" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N33" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O33" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,55 +2367,55 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E34" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F34" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G34" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H34" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="I34" t="n">
-        <v>21.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>126</v>
+        <v>61</v>
       </c>
       <c r="K34" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L34" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2</v>
+        <v>89.5</v>
       </c>
       <c r="N34" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>CAUTION - 624u = ~90 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2425,17 +2425,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E35" t="n">
-        <v>8.4</v>
+        <v>8.68</v>
       </c>
       <c r="F35" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="G35" t="n">
         <v>20</v>
@@ -2444,10 +2444,10 @@
         <v>4.6</v>
       </c>
       <c r="I35" t="n">
-        <v>13.4</v>
+        <v>17.5</v>
       </c>
       <c r="J35" t="n">
-        <v>62</v>
+        <v>102</v>
       </c>
       <c r="K35" t="n">
         <v>6</v>
@@ -2459,21 +2459,21 @@
         <v>1.3</v>
       </c>
       <c r="N35" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O35" t="n">
         <v>10</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2487,51 +2487,51 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="E36" t="n">
-        <v>9.06</v>
+        <v>18.02</v>
       </c>
       <c r="F36" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="G36" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H36" t="n">
-        <v>6.7</v>
+        <v>5</v>
       </c>
       <c r="I36" t="n">
-        <v>9.4</v>
+        <v>13.1</v>
       </c>
       <c r="J36" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="K36" t="n">
-        <v>624</v>
+        <v>40</v>
       </c>
       <c r="L36" t="n">
-        <v>624</v>
+        <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>92.5</v>
+        <v>8</v>
       </c>
       <c r="N36" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O36" t="n">
         <v>10</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~92 wks (overstock); consider ~624u</t>
+          <t>BUY ~40u (10cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,48 +2541,48 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D37" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E37" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="F37" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G37" t="n">
         <v>20</v>
       </c>
-      <c r="E37" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G37" t="n">
-        <v>10</v>
-      </c>
       <c r="H37" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I37" t="n">
-        <v>13.5</v>
+        <v>20.1</v>
       </c>
       <c r="J37" t="n">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="K37" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L37" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>8.1</v>
+        <v>1.2</v>
       </c>
       <c r="N37" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~8 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2731,10 +2731,10 @@
         <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="I40" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
         <v>127</v>
@@ -2746,7 +2746,7 @@
         <v>84</v>
       </c>
       <c r="M40" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="N40" t="n">
         <v>44</v>
@@ -2789,10 +2789,10 @@
         <v>11</v>
       </c>
       <c r="H41" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="I41" t="n">
-        <v>14.9</v>
+        <v>15.2</v>
       </c>
       <c r="J41" t="n">
         <v>106</v>
@@ -2804,7 +2804,7 @@
         <v>150</v>
       </c>
       <c r="M41" t="n">
-        <v>21.1</v>
+        <v>21.6</v>
       </c>
       <c r="N41" t="n">
         <v>55</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~22 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2847,13 +2847,13 @@
         <v>7</v>
       </c>
       <c r="H42" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I42" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="J42" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K42" t="n">
         <v>84</v>
@@ -2862,13 +2862,13 @@
         <v>84</v>
       </c>
       <c r="M42" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="N42" t="n">
         <v>44</v>
       </c>
       <c r="O42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,48 +2889,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>8.68</v>
+        <v>9.82</v>
       </c>
       <c r="F43" t="n">
-        <v>2.17</v>
+        <v>1.18</v>
       </c>
       <c r="G43" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H43" t="n">
-        <v>2.6</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>29.2</v>
+        <v>21.5</v>
       </c>
       <c r="J43" t="n">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="K43" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L43" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M43" t="n">
-        <v>2.3</v>
+        <v>30</v>
       </c>
       <c r="N43" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O43" t="n">
         <v>6</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
+          <t>CAUTION - 150u = ~30 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2963,10 +2963,10 @@
         <v>11</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I44" t="n">
-        <v>21.6</v>
+        <v>22.3</v>
       </c>
       <c r="J44" t="n">
         <v>100</v>
@@ -2978,7 +2978,7 @@
         <v>150</v>
       </c>
       <c r="M44" t="n">
-        <v>29.9</v>
+        <v>30.9</v>
       </c>
       <c r="N44" t="n">
         <v>45</v>
@@ -2988,14 +2988,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~30 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~31 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.03</v>
+        <v>10.85</v>
       </c>
       <c r="E45" t="n">
-        <v>9.15</v>
+        <v>8.68</v>
       </c>
       <c r="F45" t="n">
-        <v>0.88</v>
+        <v>2.17</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="I45" t="n">
-        <v>16.2</v>
+        <v>27.1</v>
       </c>
       <c r="J45" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="K45" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>95.40000000000001</v>
+        <v>2.2</v>
       </c>
       <c r="N45" t="n">
         <v>46</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~95 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,48 +3063,48 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>10.03</v>
       </c>
       <c r="E46" t="n">
-        <v>9.82</v>
+        <v>9.15</v>
       </c>
       <c r="F46" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H46" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="I46" t="n">
-        <v>20.2</v>
+        <v>18.3</v>
       </c>
       <c r="J46" t="n">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="K46" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L46" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M46" t="n">
-        <v>28</v>
+        <v>107.8</v>
       </c>
       <c r="N46" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~28 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 624u = ~108 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3137,13 +3137,13 @@
         <v>14</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I47" t="n">
-        <v>46.6</v>
+        <v>41.3</v>
       </c>
       <c r="J47" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="K47" t="n">
         <v>150</v>
@@ -3152,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>49.5</v>
+        <v>44.7</v>
       </c>
       <c r="N47" t="n">
         <v>50</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~50 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~45 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3253,10 +3253,10 @@
         <v>15</v>
       </c>
       <c r="H49" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="I49" t="n">
-        <v>20.1</v>
+        <v>23.4</v>
       </c>
       <c r="J49" t="n">
         <v>39</v>
@@ -3268,24 +3268,24 @@
         <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>20.8</v>
+        <v>24.3</v>
       </c>
       <c r="N49" t="n">
         <v>48</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~21 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 40u = ~24 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3295,55 +3295,55 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14</v>
+        <v>10.58</v>
       </c>
       <c r="E50" t="n">
-        <v>11.2</v>
+        <v>7.06</v>
       </c>
       <c r="F50" t="n">
-        <v>2.8</v>
+        <v>3.53</v>
       </c>
       <c r="G50" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H50" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="I50" t="n">
-        <v>89.3</v>
+        <v>28.8</v>
       </c>
       <c r="J50" t="n">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="K50" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L50" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M50" t="n">
-        <v>21</v>
+        <v>15.6</v>
       </c>
       <c r="N50" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CAUTION - 24u = ~21 wks (overstock); consider ~24u</t>
+          <t>BUY ~12u (2cs) - sells in ~16 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3353,48 +3353,48 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.58</v>
+        <v>14</v>
       </c>
       <c r="E51" t="n">
-        <v>7.06</v>
+        <v>11.2</v>
       </c>
       <c r="F51" t="n">
-        <v>3.53</v>
+        <v>2.8</v>
       </c>
       <c r="G51" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="I51" t="n">
-        <v>35.6</v>
+        <v>89.3</v>
       </c>
       <c r="J51" t="n">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="K51" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L51" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M51" t="n">
-        <v>18.7</v>
+        <v>21</v>
       </c>
       <c r="N51" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 12u = ~19 wks (overstock); consider ~12u</t>
+          <t>CAUTION - 24u = ~21 wks (overstock); consider ~24u</t>
         </is>
       </c>
     </row>
@@ -3427,13 +3427,13 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="I52" t="n">
-        <v>15.6</v>
+        <v>13.5</v>
       </c>
       <c r="J52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K52" t="n">
         <v>624</v>
@@ -3442,17 +3442,17 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>393.6</v>
+        <v>355.6</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~394 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~356 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>171.5</v>
+        <v>168.7</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="J2" t="n">
-        <v>442</v>
+        <v>380</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>932</v>
+        <v>970</v>
       </c>
       <c r="M2" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~932u (466cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~970u (485cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -588,10 +588,10 @@
         <v>52</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -643,13 +643,13 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="I4" t="n">
         <v>6.7</v>
       </c>
       <c r="J4" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -664,7 +664,7 @@
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>21.7</v>
+        <v>22.7</v>
       </c>
       <c r="I5" t="n">
-        <v>10.8</v>
+        <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>18</v>
+        <v>17.2</v>
       </c>
       <c r="I6" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -774,13 +774,13 @@
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I7" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J7" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -838,7 +838,7 @@
         <v>42</v>
       </c>
       <c r="O7" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -875,13 +875,13 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I8" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J8" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -896,7 +896,7 @@
         <v>44</v>
       </c>
       <c r="O8" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -933,13 +933,13 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I9" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J9" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -954,7 +954,7 @@
         <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
         <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>13.8</v>
+        <v>13.5</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
         <v>69</v>
@@ -1006,13 +1006,13 @@
         <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N10" t="n">
         <v>44</v>
       </c>
       <c r="O10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1049,13 +1049,13 @@
         <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="J11" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
@@ -1070,7 +1070,7 @@
         <v>50</v>
       </c>
       <c r="O11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="I12" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J12" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K12" t="n">
         <v>624</v>
@@ -1122,7 +1122,7 @@
         <v>624</v>
       </c>
       <c r="M12" t="n">
-        <v>27</v>
+        <v>27.2</v>
       </c>
       <c r="N12" t="n">
         <v>45</v>
@@ -1165,10 +1165,10 @@
         <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="J13" t="n">
         <v>55</v>
@@ -1186,7 +1186,7 @@
         <v>50</v>
       </c>
       <c r="O13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1223,13 +1223,13 @@
         <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="I14" t="n">
         <v>11.3</v>
       </c>
       <c r="J14" t="n">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K14" t="n">
         <v>624</v>
@@ -1238,7 +1238,7 @@
         <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>39.9</v>
+        <v>40.4</v>
       </c>
       <c r="N14" t="n">
         <v>45</v>
@@ -1281,10 +1281,10 @@
         <v>17</v>
       </c>
       <c r="H15" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>24</v>
@@ -1293,10 +1293,10 @@
         <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="M15" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="N15" t="n">
         <v>45</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~66u (11cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~60u (10cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="I16" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K16" t="n">
         <v>624</v>
@@ -1354,7 +1354,7 @@
         <v>624</v>
       </c>
       <c r="M16" t="n">
-        <v>42</v>
+        <v>42.3</v>
       </c>
       <c r="N16" t="n">
         <v>45</v>
@@ -1400,7 +1400,7 @@
         <v>9.6</v>
       </c>
       <c r="I17" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="J17" t="n">
         <v>60</v>
@@ -1455,13 +1455,13 @@
         <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="I18" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="J18" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K18" t="n">
         <v>624</v>
@@ -1470,17 +1470,17 @@
         <v>624</v>
       </c>
       <c r="M18" t="n">
-        <v>49</v>
+        <v>48.4</v>
       </c>
       <c r="N18" t="n">
         <v>45</v>
       </c>
       <c r="O18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1513,22 +1513,22 @@
         <v>22</v>
       </c>
       <c r="H19" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M19" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N19" t="n">
         <v>46</v>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
@@ -1571,22 +1571,22 @@
         <v>24</v>
       </c>
       <c r="H20" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="J20" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
         <v>45</v>
@@ -1596,14 +1596,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,55 +1613,55 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G21" t="n">
         <v>20</v>
       </c>
-      <c r="E21" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="G21" t="n">
-        <v>17</v>
-      </c>
       <c r="H21" t="n">
-        <v>5.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>15.8</v>
+        <v>4.1</v>
       </c>
       <c r="J21" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="N21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O21" t="n">
         <v>18</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,55 +1671,55 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>10.5</v>
       </c>
       <c r="E22" t="n">
-        <v>8.4</v>
+        <v>9.06</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>8.6</v>
+        <v>11.9</v>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>13.6</v>
       </c>
       <c r="J22" t="n">
-        <v>39</v>
+        <v>164</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L22" t="n">
-        <v>30</v>
+        <v>624</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>52.4</v>
       </c>
       <c r="N22" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
+          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,38 +1729,38 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.03</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>9.15</v>
+        <v>16.67</v>
       </c>
       <c r="F23" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>19.4</v>
+        <v>5</v>
       </c>
       <c r="I23" t="n">
-        <v>9.1</v>
+        <v>16.7</v>
       </c>
       <c r="J23" t="n">
-        <v>178</v>
+        <v>84</v>
       </c>
       <c r="K23" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="M23" t="n">
-        <v>32.1</v>
+        <v>0.6</v>
       </c>
       <c r="N23" t="n">
         <v>46</v>
@@ -1770,14 +1770,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~32 wks (overstock); consider ~624u</t>
+          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,29 +1787,29 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.5</v>
+        <v>10.03</v>
       </c>
       <c r="E24" t="n">
-        <v>9.06</v>
+        <v>9.15</v>
       </c>
       <c r="F24" t="n">
-        <v>1.44</v>
+        <v>0.88</v>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H24" t="n">
-        <v>11.6</v>
+        <v>18.5</v>
       </c>
       <c r="I24" t="n">
-        <v>14.2</v>
+        <v>9.5</v>
       </c>
       <c r="J24" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K24" t="n">
         <v>624</v>
@@ -1818,24 +1818,24 @@
         <v>624</v>
       </c>
       <c r="M24" t="n">
-        <v>53.8</v>
+        <v>33.8</v>
       </c>
       <c r="N24" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~54 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~34 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,55 +1845,55 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.03</v>
+        <v>9.33</v>
       </c>
       <c r="E25" t="n">
-        <v>9.15</v>
+        <v>8.01</v>
       </c>
       <c r="F25" t="n">
-        <v>0.88</v>
+        <v>1.32</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>18</v>
+        <v>11.3</v>
       </c>
       <c r="I25" t="n">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="J25" t="n">
-        <v>201</v>
+        <v>69</v>
       </c>
       <c r="K25" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L25" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M25" t="n">
-        <v>34.7</v>
+        <v>13.3</v>
       </c>
       <c r="N25" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~35 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.67</v>
+        <v>10.03</v>
       </c>
       <c r="E26" t="n">
-        <v>13.34</v>
+        <v>9.15</v>
       </c>
       <c r="F26" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
       <c r="I26" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="J26" t="n">
-        <v>34</v>
+        <v>195</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7</v>
+        <v>35.6</v>
       </c>
       <c r="N26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O26" t="n">
         <v>15</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~36 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,48 +1961,48 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9.33</v>
+        <v>16.67</v>
       </c>
       <c r="E27" t="n">
-        <v>8.01</v>
+        <v>13.34</v>
       </c>
       <c r="F27" t="n">
-        <v>1.32</v>
+        <v>3.33</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>11.5</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>10.1</v>
+        <v>7.4</v>
       </c>
       <c r="J27" t="n">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="K27" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>13</v>
+        <v>0.7</v>
       </c>
       <c r="N27" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O27" t="n">
         <v>15</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
+          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -2035,13 +2035,13 @@
         <v>9</v>
       </c>
       <c r="H28" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="I28" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="J28" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K28" t="n">
         <v>624</v>
@@ -2050,7 +2050,7 @@
         <v>624</v>
       </c>
       <c r="M28" t="n">
-        <v>41.8</v>
+        <v>41.6</v>
       </c>
       <c r="N28" t="n">
         <v>46</v>
@@ -2093,13 +2093,13 @@
         <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I29" t="n">
-        <v>13.5</v>
+        <v>12.7</v>
       </c>
       <c r="J29" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K29" t="n">
         <v>208</v>
@@ -2108,7 +2108,7 @@
         <v>208</v>
       </c>
       <c r="M29" t="n">
-        <v>41.8</v>
+        <v>40.5</v>
       </c>
       <c r="N29" t="n">
         <v>44</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~42 wks (overstock); consider ~208u</t>
+          <t>CAUTION - 208u = ~40 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
@@ -2209,10 +2209,10 @@
         <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="I31" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J31" t="n">
         <v>156</v>
@@ -2224,7 +2224,7 @@
         <v>84</v>
       </c>
       <c r="M31" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="N31" t="n">
         <v>44</v>
@@ -2299,7 +2299,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>10.5</v>
       </c>
       <c r="E33" t="n">
-        <v>8.4</v>
+        <v>9.06</v>
       </c>
       <c r="F33" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H33" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="I33" t="n">
-        <v>13.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L33" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3</v>
+        <v>91.3</v>
       </c>
       <c r="N33" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O33" t="n">
         <v>10</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~91 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2371,44 +2371,44 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="E34" t="n">
-        <v>9.06</v>
+        <v>18.02</v>
       </c>
       <c r="F34" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="G34" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H34" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="I34" t="n">
-        <v>8.699999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="J34" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="K34" t="n">
-        <v>624</v>
+        <v>40</v>
       </c>
       <c r="L34" t="n">
-        <v>624</v>
+        <v>40</v>
       </c>
       <c r="M34" t="n">
-        <v>89.5</v>
+        <v>8.1</v>
       </c>
       <c r="N34" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O34" t="n">
         <v>10</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~90 wks (overstock); consider ~624u</t>
+          <t>BUY ~40u (10cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2441,13 +2441,13 @@
         <v>20</v>
       </c>
       <c r="H35" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I35" t="n">
-        <v>17.5</v>
+        <v>16.8</v>
       </c>
       <c r="J35" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K35" t="n">
         <v>6</v>
@@ -2473,7 +2473,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,55 +2483,55 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G36" t="n">
         <v>20</v>
       </c>
-      <c r="E36" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G36" t="n">
-        <v>10</v>
-      </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I36" t="n">
-        <v>13.1</v>
+        <v>20.6</v>
       </c>
       <c r="J36" t="n">
-        <v>88</v>
+        <v>138</v>
       </c>
       <c r="K36" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>8</v>
+        <v>1.3</v>
       </c>
       <c r="N36" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O36" t="n">
         <v>10</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~8 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,29 +2541,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E37" t="n">
-        <v>8.68</v>
+        <v>8.4</v>
       </c>
       <c r="F37" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G37" t="n">
         <v>20</v>
       </c>
       <c r="H37" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I37" t="n">
-        <v>20.1</v>
+        <v>13.3</v>
       </c>
       <c r="J37" t="n">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="K37" t="n">
         <v>6</v>
@@ -2572,17 +2572,17 @@
         <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N37" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -2615,13 +2615,13 @@
         <v>24</v>
       </c>
       <c r="H38" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I38" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="J38" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
@@ -2636,7 +2636,7 @@
         <v>45</v>
       </c>
       <c r="O38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -2673,13 +2673,13 @@
         <v>22</v>
       </c>
       <c r="H39" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I39" t="n">
-        <v>13.4</v>
+        <v>13.3</v>
       </c>
       <c r="J39" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K39" t="n">
         <v>6</v>
@@ -2694,7 +2694,7 @@
         <v>46</v>
       </c>
       <c r="O39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -2731,13 +2731,13 @@
         <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K40" t="n">
         <v>84</v>
@@ -2746,7 +2746,7 @@
         <v>84</v>
       </c>
       <c r="M40" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="N40" t="n">
         <v>44</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
+          <t>BUY ~84u (14cs) - sells in ~9 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2789,10 +2789,10 @@
         <v>11</v>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I41" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="J41" t="n">
         <v>106</v>
@@ -2804,7 +2804,7 @@
         <v>150</v>
       </c>
       <c r="M41" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N41" t="n">
         <v>55</v>
@@ -2847,13 +2847,13 @@
         <v>7</v>
       </c>
       <c r="H42" t="n">
-        <v>8.1</v>
+        <v>8.5</v>
       </c>
       <c r="I42" t="n">
-        <v>13.7</v>
+        <v>12.7</v>
       </c>
       <c r="J42" t="n">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K42" t="n">
         <v>84</v>
@@ -2862,13 +2862,13 @@
         <v>84</v>
       </c>
       <c r="M42" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="N42" t="n">
         <v>44</v>
       </c>
       <c r="O42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,48 +2889,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>10.85</v>
       </c>
       <c r="E43" t="n">
-        <v>9.82</v>
+        <v>8.68</v>
       </c>
       <c r="F43" t="n">
-        <v>1.18</v>
+        <v>2.17</v>
       </c>
       <c r="G43" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="I43" t="n">
-        <v>21.5</v>
+        <v>27.1</v>
       </c>
       <c r="J43" t="n">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="K43" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L43" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>30</v>
+        <v>2.2</v>
       </c>
       <c r="N43" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O43" t="n">
         <v>6</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~30 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2963,10 +2963,10 @@
         <v>11</v>
       </c>
       <c r="H44" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I44" t="n">
-        <v>22.3</v>
+        <v>23.2</v>
       </c>
       <c r="J44" t="n">
         <v>100</v>
@@ -2978,7 +2978,7 @@
         <v>150</v>
       </c>
       <c r="M44" t="n">
-        <v>30.9</v>
+        <v>32.1</v>
       </c>
       <c r="N44" t="n">
         <v>45</v>
@@ -2988,14 +2988,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~31 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~32 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3005,48 +3005,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>8.68</v>
+        <v>9.82</v>
       </c>
       <c r="F45" t="n">
-        <v>2.17</v>
+        <v>1.18</v>
       </c>
       <c r="G45" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H45" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="I45" t="n">
-        <v>27.1</v>
+        <v>20.8</v>
       </c>
       <c r="J45" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="K45" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L45" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M45" t="n">
-        <v>2.2</v>
+        <v>29.2</v>
       </c>
       <c r="N45" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O45" t="n">
         <v>6</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
+          <t>CAUTION - 150u = ~29 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3079,13 +3079,13 @@
         <v>9</v>
       </c>
       <c r="H46" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I46" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="J46" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K46" t="n">
         <v>624</v>
@@ -3094,7 +3094,7 @@
         <v>624</v>
       </c>
       <c r="M46" t="n">
-        <v>107.8</v>
+        <v>110.5</v>
       </c>
       <c r="N46" t="n">
         <v>46</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~108 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~110 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3137,10 +3137,10 @@
         <v>14</v>
       </c>
       <c r="H47" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="I47" t="n">
-        <v>41.3</v>
+        <v>43.6</v>
       </c>
       <c r="J47" t="n">
         <v>160</v>
@@ -3152,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>44.7</v>
+        <v>47.1</v>
       </c>
       <c r="N47" t="n">
         <v>50</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~45 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~47 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3195,10 +3195,10 @@
         <v>11</v>
       </c>
       <c r="H48" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>16.6</v>
+        <v>20</v>
       </c>
       <c r="J48" t="n">
         <v>85</v>
@@ -3210,7 +3210,7 @@
         <v>150</v>
       </c>
       <c r="M48" t="n">
-        <v>41.9</v>
+        <v>50.5</v>
       </c>
       <c r="N48" t="n">
         <v>45</v>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~42 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~50 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3427,10 +3427,10 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="I52" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="J52" t="n">
         <v>24</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>355.6</v>
+        <v>361.9</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~356 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~362 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>168.7</v>
+        <v>169.5</v>
       </c>
       <c r="I2" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J2" t="n">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="M2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~970u (485cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~990u (495cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>52</v>
+        <v>52.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -606,7 +606,7 @@
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="I4" t="n">
-        <v>6.7</v>
+        <v>7.6</v>
       </c>
       <c r="J4" t="n">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="M4" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~36u (18cs) - sells in ~2 wks</t>
+          <t>BUY ~20u (10cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="J5" t="n">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="J6" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -817,10 +817,10 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J7" t="n">
         <v>83</v>
@@ -838,7 +838,7 @@
         <v>42</v>
       </c>
       <c r="O7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
         <v>83</v>
@@ -896,7 +896,7 @@
         <v>44</v>
       </c>
       <c r="O8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J9" t="n">
         <v>83</v>
@@ -954,7 +954,7 @@
         <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -994,10 +994,10 @@
         <v>13.5</v>
       </c>
       <c r="I10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J10" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K10" t="n">
         <v>24</v>
@@ -1049,13 +1049,13 @@
         <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="J11" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
@@ -1070,7 +1070,7 @@
         <v>50</v>
       </c>
       <c r="O11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>23</v>
+        <v>23.7</v>
       </c>
       <c r="I12" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J12" t="n">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="K12" t="n">
         <v>624</v>
@@ -1122,17 +1122,17 @@
         <v>624</v>
       </c>
       <c r="M12" t="n">
-        <v>27.2</v>
+        <v>26.3</v>
       </c>
       <c r="N12" t="n">
         <v>45</v>
       </c>
       <c r="O12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~27 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1223,13 +1223,13 @@
         <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="I14" t="n">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="J14" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="K14" t="n">
         <v>624</v>
@@ -1238,13 +1238,13 @@
         <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>40.4</v>
+        <v>39.6</v>
       </c>
       <c r="N14" t="n">
         <v>45</v>
       </c>
       <c r="O14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1284,19 +1284,19 @@
         <v>10.5</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
         <v>6</v>
       </c>
       <c r="L15" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="M15" t="n">
-        <v>5.7</v>
+        <v>6.3</v>
       </c>
       <c r="N15" t="n">
         <v>45</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~60u (10cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~66u (11cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J16" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="K16" t="n">
         <v>624</v>
@@ -1354,7 +1354,7 @@
         <v>624</v>
       </c>
       <c r="M16" t="n">
-        <v>42.3</v>
+        <v>42.6</v>
       </c>
       <c r="N16" t="n">
         <v>45</v>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1397,13 +1397,13 @@
         <v>17</v>
       </c>
       <c r="H17" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="I17" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K17" t="n">
         <v>6</v>
@@ -1458,10 +1458,10 @@
         <v>12.9</v>
       </c>
       <c r="I18" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K18" t="n">
         <v>624</v>
@@ -1516,10 +1516,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
@@ -1545,7 +1545,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,38 +1555,38 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8.67</v>
+        <v>10.5</v>
       </c>
       <c r="E20" t="n">
-        <v>6.57</v>
+        <v>9.06</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="H20" t="n">
-        <v>8.699999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="I20" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="J20" t="n">
-        <v>36</v>
+        <v>161</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L20" t="n">
-        <v>36</v>
+        <v>624</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>51</v>
       </c>
       <c r="N20" t="n">
         <v>45</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
+          <t>CAUTION - 624u = ~51 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1632,10 +1632,10 @@
         <v>8.699999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
@@ -1661,7 +1661,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,55 +1671,55 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>8.67</v>
       </c>
       <c r="E22" t="n">
-        <v>9.06</v>
+        <v>6.57</v>
       </c>
       <c r="F22" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H22" t="n">
-        <v>11.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>13.6</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>164</v>
+        <v>35</v>
       </c>
       <c r="K22" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>624</v>
+        <v>36</v>
       </c>
       <c r="M22" t="n">
-        <v>52.4</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
         <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
+          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,38 +1729,38 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>10.03</v>
       </c>
       <c r="E23" t="n">
-        <v>16.67</v>
+        <v>9.15</v>
       </c>
       <c r="F23" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G23" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>18.8</v>
       </c>
       <c r="I23" t="n">
-        <v>16.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>84</v>
+        <v>175</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L23" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6</v>
+        <v>33.2</v>
       </c>
       <c r="N23" t="n">
         <v>46</v>
@@ -1770,14 +1770,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~33 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,55 +1787,55 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.03</v>
+        <v>20</v>
       </c>
       <c r="E24" t="n">
-        <v>9.15</v>
+        <v>16.67</v>
       </c>
       <c r="F24" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H24" t="n">
-        <v>18.5</v>
+        <v>5.1</v>
       </c>
       <c r="I24" t="n">
-        <v>9.5</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>177</v>
+        <v>83</v>
       </c>
       <c r="K24" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L24" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
-        <v>33.8</v>
+        <v>0.6</v>
       </c>
       <c r="N24" t="n">
         <v>46</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~34 wks (overstock); consider ~624u</t>
+          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,55 +1845,55 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>9.33</v>
+        <v>10.03</v>
       </c>
       <c r="E25" t="n">
-        <v>8.01</v>
+        <v>9.15</v>
       </c>
       <c r="F25" t="n">
-        <v>1.32</v>
+        <v>0.88</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>11.3</v>
+        <v>18.4</v>
       </c>
       <c r="I25" t="n">
         <v>10.2</v>
       </c>
       <c r="J25" t="n">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="K25" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L25" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M25" t="n">
-        <v>13.3</v>
+        <v>34</v>
       </c>
       <c r="N25" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~34 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.03</v>
+        <v>16.67</v>
       </c>
       <c r="E26" t="n">
-        <v>9.15</v>
+        <v>13.34</v>
       </c>
       <c r="F26" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H26" t="n">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="I26" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="J26" t="n">
-        <v>195</v>
+        <v>34</v>
       </c>
       <c r="K26" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L26" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="M26" t="n">
-        <v>35.6</v>
+        <v>0.7</v>
       </c>
       <c r="N26" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O26" t="n">
         <v>15</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~36 wks (overstock); consider ~624u</t>
+          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,48 +1961,48 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.67</v>
+        <v>9.33</v>
       </c>
       <c r="E27" t="n">
-        <v>13.34</v>
+        <v>8.01</v>
       </c>
       <c r="F27" t="n">
-        <v>3.33</v>
+        <v>1.32</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>4.5</v>
+        <v>11.2</v>
       </c>
       <c r="I27" t="n">
-        <v>7.4</v>
+        <v>10.3</v>
       </c>
       <c r="J27" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>150</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7</v>
+        <v>13.4</v>
       </c>
       <c r="N27" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O27" t="n">
         <v>15</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2035,13 +2035,13 @@
         <v>9</v>
       </c>
       <c r="H28" t="n">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="I28" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="J28" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K28" t="n">
         <v>624</v>
@@ -2050,7 +2050,7 @@
         <v>624</v>
       </c>
       <c r="M28" t="n">
-        <v>41.6</v>
+        <v>41.2</v>
       </c>
       <c r="N28" t="n">
         <v>46</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~41 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2093,13 +2093,13 @@
         <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I29" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="J29" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K29" t="n">
         <v>208</v>
@@ -2108,7 +2108,7 @@
         <v>208</v>
       </c>
       <c r="M29" t="n">
-        <v>40.5</v>
+        <v>39.2</v>
       </c>
       <c r="N29" t="n">
         <v>44</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~40 wks (overstock); consider ~208u</t>
+          <t>CAUTION - 208u = ~39 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
@@ -2209,7 +2209,7 @@
         <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="I31" t="n">
         <v>9.9</v>
@@ -2241,7 +2241,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,55 +2251,55 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E32" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F32" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G32" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="I32" t="n">
-        <v>21.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="K32" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L32" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M32" t="n">
-        <v>1.2</v>
+        <v>91.3</v>
       </c>
       <c r="N32" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>CAUTION - 624u = ~91 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D33" t="n">
         <v>10.5</v>
       </c>
       <c r="E33" t="n">
-        <v>9.06</v>
+        <v>8.4</v>
       </c>
       <c r="F33" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="I33" t="n">
-        <v>8.800000000000001</v>
+        <v>12.9</v>
       </c>
       <c r="J33" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K33" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L33" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M33" t="n">
-        <v>91.3</v>
+        <v>1.3</v>
       </c>
       <c r="N33" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O33" t="n">
         <v>10</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~91 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,48 +2367,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D34" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G34" t="n">
         <v>20</v>
       </c>
-      <c r="E34" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G34" t="n">
-        <v>10</v>
-      </c>
       <c r="H34" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I34" t="n">
-        <v>13.2</v>
+        <v>21.7</v>
       </c>
       <c r="J34" t="n">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="K34" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L34" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>8.1</v>
+        <v>1.3</v>
       </c>
       <c r="N34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O34" t="n">
         <v>10</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~8 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2444,10 +2444,10 @@
         <v>4.7</v>
       </c>
       <c r="I35" t="n">
-        <v>16.8</v>
+        <v>17.9</v>
       </c>
       <c r="J35" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K35" t="n">
         <v>6</v>
@@ -2473,7 +2473,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,55 +2483,55 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.85</v>
+        <v>20</v>
       </c>
       <c r="E36" t="n">
-        <v>8.68</v>
+        <v>18.02</v>
       </c>
       <c r="F36" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="G36" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H36" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="I36" t="n">
-        <v>20.6</v>
+        <v>12.8</v>
       </c>
       <c r="J36" t="n">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="K36" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L36" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>1.3</v>
+        <v>7.9</v>
       </c>
       <c r="N36" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O36" t="n">
         <v>10</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~40u (10cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,29 +2541,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E37" t="n">
-        <v>8.4</v>
+        <v>8.68</v>
       </c>
       <c r="F37" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="G37" t="n">
         <v>20</v>
       </c>
       <c r="H37" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I37" t="n">
-        <v>13.3</v>
+        <v>22.5</v>
       </c>
       <c r="J37" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="K37" t="n">
         <v>6</v>
@@ -2575,14 +2575,14 @@
         <v>1.3</v>
       </c>
       <c r="N37" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2615,13 +2615,13 @@
         <v>24</v>
       </c>
       <c r="H38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I38" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="J38" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
@@ -2636,7 +2636,7 @@
         <v>45</v>
       </c>
       <c r="O38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -2673,13 +2673,13 @@
         <v>22</v>
       </c>
       <c r="H39" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I39" t="n">
-        <v>13.3</v>
+        <v>12.9</v>
       </c>
       <c r="J39" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K39" t="n">
         <v>6</v>
@@ -2694,7 +2694,7 @@
         <v>46</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2715,55 +2715,55 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E40" t="n">
-        <v>11.2</v>
+        <v>9.82</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="G40" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H40" t="n">
-        <v>9.5</v>
+        <v>7.3</v>
       </c>
       <c r="I40" t="n">
-        <v>9.300000000000001</v>
+        <v>14.3</v>
       </c>
       <c r="J40" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="K40" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L40" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M40" t="n">
-        <v>8.9</v>
+        <v>20.6</v>
       </c>
       <c r="N40" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~9 wks (cooling)</t>
+          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,48 +2773,48 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E41" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F41" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G41" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>6.9</v>
+        <v>9.6</v>
       </c>
       <c r="I41" t="n">
-        <v>15.3</v>
+        <v>9.1</v>
       </c>
       <c r="J41" t="n">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="K41" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L41" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M41" t="n">
-        <v>21.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="O41" t="n">
         <v>8</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~22 wks (overstock); consider ~150u</t>
+          <t>BUY ~84u (14cs) - sells in ~9 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2847,13 +2847,13 @@
         <v>7</v>
       </c>
       <c r="H42" t="n">
-        <v>8.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>12.7</v>
+        <v>12.1</v>
       </c>
       <c r="J42" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K42" t="n">
         <v>84</v>
@@ -2862,7 +2862,7 @@
         <v>84</v>
       </c>
       <c r="M42" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="N42" t="n">
         <v>44</v>
@@ -2879,7 +2879,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,55 +2889,55 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>8.68</v>
+        <v>9.82</v>
       </c>
       <c r="F43" t="n">
-        <v>2.17</v>
+        <v>1.18</v>
       </c>
       <c r="G43" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H43" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="I43" t="n">
-        <v>27.1</v>
+        <v>22.1</v>
       </c>
       <c r="J43" t="n">
         <v>99</v>
       </c>
       <c r="K43" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L43" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M43" t="n">
-        <v>2.2</v>
+        <v>30.9</v>
       </c>
       <c r="N43" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O43" t="n">
         <v>6</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
+          <t>CAUTION - 150u = ~31 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2947,7 +2947,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -2963,13 +2963,13 @@
         <v>11</v>
       </c>
       <c r="H44" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>23.2</v>
+        <v>21.1</v>
       </c>
       <c r="J44" t="n">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="K44" t="n">
         <v>150</v>
@@ -2978,24 +2978,24 @@
         <v>150</v>
       </c>
       <c r="M44" t="n">
-        <v>32.1</v>
+        <v>29.9</v>
       </c>
       <c r="N44" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O44" t="n">
         <v>6</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~32 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~30 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3005,48 +3005,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>10.85</v>
       </c>
       <c r="E45" t="n">
-        <v>9.82</v>
+        <v>8.68</v>
       </c>
       <c r="F45" t="n">
-        <v>1.18</v>
+        <v>2.17</v>
       </c>
       <c r="G45" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>5.1</v>
+        <v>2.4</v>
       </c>
       <c r="I45" t="n">
-        <v>20.8</v>
+        <v>34.3</v>
       </c>
       <c r="J45" t="n">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="K45" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>29.2</v>
+        <v>2.5</v>
       </c>
       <c r="N45" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~29 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
         <v>3.2</v>
       </c>
       <c r="I47" t="n">
-        <v>43.6</v>
+        <v>44</v>
       </c>
       <c r="J47" t="n">
         <v>160</v>
@@ -3152,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>47.1</v>
+        <v>47.5</v>
       </c>
       <c r="N47" t="n">
         <v>50</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~47 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~48 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3198,10 +3198,10 @@
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="J48" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K48" t="n">
         <v>150</v>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,13 +527,13 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>169.5</v>
+        <v>168.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="J2" t="n">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
@@ -542,13 +542,13 @@
         <v>990</v>
       </c>
       <c r="M2" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>52.5</v>
+        <v>52.4</v>
       </c>
       <c r="I3" t="n">
         <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="I4" t="n">
         <v>7.6</v>
       </c>
       <c r="J4" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~20u (10cs) - sells in ~1 wks</t>
+          <t>BUY ~18u (9cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -704,10 +704,10 @@
         <v>22.8</v>
       </c>
       <c r="I5" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
         <v>7.9</v>
       </c>
       <c r="J6" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -780,7 +780,7 @@
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="J7" t="n">
         <v>83</v>
@@ -838,7 +838,7 @@
         <v>42</v>
       </c>
       <c r="O7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="J8" t="n">
         <v>83</v>
@@ -896,7 +896,7 @@
         <v>44</v>
       </c>
       <c r="O8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="J9" t="n">
         <v>83</v>
@@ -954,7 +954,7 @@
         <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
         <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J10" t="n">
         <v>68</v>
@@ -1006,13 +1006,13 @@
         <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N10" t="n">
         <v>44</v>
       </c>
       <c r="O10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>10.1</v>
@@ -1107,13 +1107,13 @@
         <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>23.7</v>
+        <v>24.4</v>
       </c>
       <c r="I12" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="K12" t="n">
         <v>624</v>
@@ -1122,13 +1122,13 @@
         <v>624</v>
       </c>
       <c r="M12" t="n">
-        <v>26.3</v>
+        <v>25.6</v>
       </c>
       <c r="N12" t="n">
         <v>45</v>
       </c>
       <c r="O12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1165,13 +1165,13 @@
         <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
@@ -1186,7 +1186,7 @@
         <v>50</v>
       </c>
       <c r="O13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1223,13 +1223,13 @@
         <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>15.8</v>
+        <v>16.3</v>
       </c>
       <c r="I14" t="n">
-        <v>10.9</v>
+        <v>10.3</v>
       </c>
       <c r="J14" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="K14" t="n">
         <v>624</v>
@@ -1238,7 +1238,7 @@
         <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>39.6</v>
+        <v>38.2</v>
       </c>
       <c r="N14" t="n">
         <v>45</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~38 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="I16" t="n">
         <v>3.6</v>
       </c>
       <c r="J16" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K16" t="n">
         <v>624</v>
@@ -1354,7 +1354,7 @@
         <v>624</v>
       </c>
       <c r="M16" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="N16" t="n">
         <v>45</v>
@@ -1371,7 +1371,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1381,55 +1381,55 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E17" t="n">
-        <v>9.9</v>
+        <v>9.06</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G17" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>9.5</v>
+        <v>13.2</v>
       </c>
       <c r="I17" t="n">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="J17" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L17" t="n">
-        <v>18</v>
+        <v>624</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9</v>
+        <v>47.2</v>
       </c>
       <c r="N17" t="n">
         <v>45</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~47 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,38 +1439,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>9.06</v>
+        <v>9.9</v>
       </c>
       <c r="F18" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>12.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I18" t="n">
+        <v>9</v>
+      </c>
+      <c r="J18" t="n">
+        <v>59</v>
+      </c>
+      <c r="K18" t="n">
         <v>6</v>
       </c>
-      <c r="J18" t="n">
-        <v>78</v>
-      </c>
-      <c r="K18" t="n">
-        <v>624</v>
-      </c>
       <c r="L18" t="n">
-        <v>624</v>
+        <v>18</v>
       </c>
       <c r="M18" t="n">
-        <v>48.4</v>
+        <v>1.9</v>
       </c>
       <c r="N18" t="n">
         <v>45</v>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
+          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1571,13 +1571,13 @@
         <v>14</v>
       </c>
       <c r="H20" t="n">
-        <v>12.2</v>
+        <v>12.5</v>
       </c>
       <c r="I20" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="J20" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K20" t="n">
         <v>624</v>
@@ -1586,7 +1586,7 @@
         <v>624</v>
       </c>
       <c r="M20" t="n">
-        <v>51</v>
+        <v>50.1</v>
       </c>
       <c r="N20" t="n">
         <v>45</v>
@@ -1596,14 +1596,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~51 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,48 +1613,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>8.4</v>
+        <v>16.67</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>3.33</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>8.699999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>15.4</v>
       </c>
       <c r="J21" t="n">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O21" t="n">
         <v>18</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
+          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,55 +1729,55 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.03</v>
+        <v>10.5</v>
       </c>
       <c r="E23" t="n">
-        <v>9.15</v>
+        <v>8.4</v>
       </c>
       <c r="F23" t="n">
-        <v>0.88</v>
+        <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H23" t="n">
-        <v>18.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>9.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
-        <v>175</v>
+        <v>35</v>
       </c>
       <c r="K23" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>624</v>
+        <v>36</v>
       </c>
       <c r="M23" t="n">
-        <v>33.2</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~33 wks (overstock); consider ~624u</t>
+          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,38 +1787,38 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>20</v>
+        <v>10.03</v>
       </c>
       <c r="E24" t="n">
-        <v>16.67</v>
+        <v>9.15</v>
       </c>
       <c r="F24" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H24" t="n">
-        <v>5.1</v>
+        <v>19.1</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>8.9</v>
       </c>
       <c r="J24" t="n">
-        <v>83</v>
+        <v>171</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L24" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="M24" t="n">
-        <v>0.6</v>
+        <v>32.6</v>
       </c>
       <c r="N24" t="n">
         <v>46</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~33 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1861,10 +1861,10 @@
         <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>18.4</v>
+        <v>17.9</v>
       </c>
       <c r="I25" t="n">
-        <v>10.2</v>
+        <v>10.5</v>
       </c>
       <c r="J25" t="n">
         <v>190</v>
@@ -1876,7 +1876,7 @@
         <v>624</v>
       </c>
       <c r="M25" t="n">
-        <v>34</v>
+        <v>34.8</v>
       </c>
       <c r="N25" t="n">
         <v>46</v>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~34 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~35 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1919,10 +1919,10 @@
         <v>20</v>
       </c>
       <c r="H26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I26" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="J26" t="n">
         <v>34</v>
@@ -1977,13 +1977,13 @@
         <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="I27" t="n">
-        <v>10.3</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K27" t="n">
         <v>150</v>
@@ -1992,7 +1992,7 @@
         <v>150</v>
       </c>
       <c r="M27" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="N27" t="n">
         <v>50</v>
@@ -2009,7 +2009,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,55 +2019,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.03</v>
+        <v>14</v>
       </c>
       <c r="E28" t="n">
-        <v>9.15</v>
+        <v>11.2</v>
       </c>
       <c r="F28" t="n">
-        <v>0.88</v>
+        <v>2.8</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H28" t="n">
-        <v>15.2</v>
+        <v>4.6</v>
       </c>
       <c r="I28" t="n">
-        <v>10.2</v>
+        <v>7.4</v>
       </c>
       <c r="J28" t="n">
-        <v>157</v>
+        <v>30</v>
       </c>
       <c r="K28" t="n">
-        <v>624</v>
+        <v>24</v>
       </c>
       <c r="L28" t="n">
-        <v>624</v>
+        <v>24</v>
       </c>
       <c r="M28" t="n">
-        <v>41.2</v>
+        <v>5.3</v>
       </c>
       <c r="N28" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O28" t="n">
         <v>13</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~41 wks (overstock); consider ~624u</t>
+          <t>BUY ~24u (4cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2081,51 +2081,51 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>26.52</v>
+        <v>10.03</v>
       </c>
       <c r="E29" t="n">
-        <v>24.2</v>
+        <v>9.15</v>
       </c>
       <c r="F29" t="n">
-        <v>2.33</v>
+        <v>0.88</v>
       </c>
       <c r="G29" t="n">
         <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>5.3</v>
+        <v>15.2</v>
       </c>
       <c r="I29" t="n">
-        <v>12.1</v>
+        <v>10.1</v>
       </c>
       <c r="J29" t="n">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="K29" t="n">
-        <v>208</v>
+        <v>624</v>
       </c>
       <c r="L29" t="n">
-        <v>208</v>
+        <v>624</v>
       </c>
       <c r="M29" t="n">
-        <v>39.2</v>
+        <v>41.2</v>
       </c>
       <c r="N29" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~39 wks (overstock); consider ~208u</t>
+          <t>CAUTION - 624u = ~41 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,38 +2135,38 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
         <v>11.2</v>
       </c>
       <c r="F30" t="n">
-        <v>2.8</v>
+        <v>0.8</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>4.4</v>
+        <v>14.7</v>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>10.6</v>
       </c>
       <c r="J30" t="n">
-        <v>31</v>
+        <v>167</v>
       </c>
       <c r="K30" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="L30" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="M30" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="N30" t="n">
         <v>44</v>
@@ -2176,14 +2176,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2193,38 +2193,38 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>26.52</v>
       </c>
       <c r="E31" t="n">
-        <v>11.2</v>
+        <v>24.2</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8</v>
+        <v>2.33</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H31" t="n">
-        <v>14.6</v>
+        <v>5.3</v>
       </c>
       <c r="I31" t="n">
-        <v>9.9</v>
+        <v>12.2</v>
       </c>
       <c r="J31" t="n">
-        <v>156</v>
+        <v>65</v>
       </c>
       <c r="K31" t="n">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="L31" t="n">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="M31" t="n">
-        <v>5.7</v>
+        <v>39.4</v>
       </c>
       <c r="N31" t="n">
         <v>44</v>
@@ -2234,7 +2234,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
+          <t>CAUTION - 208u = ~39 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
@@ -2267,13 +2267,13 @@
         <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="I32" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J32" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K32" t="n">
         <v>624</v>
@@ -2282,24 +2282,24 @@
         <v>624</v>
       </c>
       <c r="M32" t="n">
-        <v>91.3</v>
+        <v>85</v>
       </c>
       <c r="N32" t="n">
         <v>45</v>
       </c>
       <c r="O32" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~91 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~85 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,38 +2309,38 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="E33" t="n">
-        <v>8.4</v>
+        <v>18.02</v>
       </c>
       <c r="F33" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="I33" t="n">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="J33" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="K33" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L33" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="M33" t="n">
-        <v>1.3</v>
+        <v>7.6</v>
       </c>
       <c r="N33" t="n">
         <v>47</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~40u (10cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2383,10 +2383,10 @@
         <v>20</v>
       </c>
       <c r="H34" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I34" t="n">
-        <v>21.7</v>
+        <v>22.4</v>
       </c>
       <c r="J34" t="n">
         <v>125</v>
@@ -2441,13 +2441,13 @@
         <v>20</v>
       </c>
       <c r="H35" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I35" t="n">
-        <v>17.9</v>
+        <v>18.4</v>
       </c>
       <c r="J35" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K35" t="n">
         <v>6</v>
@@ -2473,7 +2473,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,55 +2483,55 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G36" t="n">
         <v>20</v>
       </c>
-      <c r="E36" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G36" t="n">
-        <v>10</v>
-      </c>
       <c r="H36" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I36" t="n">
-        <v>12.8</v>
+        <v>21.9</v>
       </c>
       <c r="J36" t="n">
-        <v>87</v>
+        <v>149</v>
       </c>
       <c r="K36" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L36" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>7.9</v>
+        <v>1.3</v>
       </c>
       <c r="N36" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O36" t="n">
         <v>10</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~8 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,29 +2541,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E37" t="n">
-        <v>8.68</v>
+        <v>8.4</v>
       </c>
       <c r="F37" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G37" t="n">
         <v>20</v>
       </c>
       <c r="H37" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I37" t="n">
-        <v>22.5</v>
+        <v>13.1</v>
       </c>
       <c r="J37" t="n">
-        <v>150</v>
+        <v>59</v>
       </c>
       <c r="K37" t="n">
         <v>6</v>
@@ -2575,14 +2575,14 @@
         <v>1.3</v>
       </c>
       <c r="N37" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>4.5</v>
       </c>
       <c r="I38" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="J38" t="n">
         <v>59</v>
@@ -2636,7 +2636,7 @@
         <v>45</v>
       </c>
       <c r="O38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -2676,7 +2676,7 @@
         <v>4.5</v>
       </c>
       <c r="I39" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="J39" t="n">
         <v>59</v>
@@ -2694,7 +2694,7 @@
         <v>46</v>
       </c>
       <c r="O39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2715,55 +2715,55 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E40" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F40" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G40" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>7.3</v>
+        <v>9.6</v>
       </c>
       <c r="I40" t="n">
-        <v>14.3</v>
+        <v>10</v>
       </c>
       <c r="J40" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="K40" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L40" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M40" t="n">
-        <v>20.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="O40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
+          <t>BUY ~84u (14cs) - sells in ~9 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,48 +2773,48 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>11.2</v>
+        <v>9.82</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="G41" t="n">
+        <v>11</v>
+      </c>
+      <c r="H41" t="n">
         <v>7</v>
       </c>
-      <c r="H41" t="n">
-        <v>9.6</v>
-      </c>
       <c r="I41" t="n">
-        <v>9.1</v>
+        <v>14.9</v>
       </c>
       <c r="J41" t="n">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="K41" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L41" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M41" t="n">
-        <v>8.800000000000001</v>
+        <v>21.4</v>
       </c>
       <c r="N41" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O41" t="n">
         <v>8</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~9 wks (cooling)</t>
+          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2847,13 +2847,13 @@
         <v>7</v>
       </c>
       <c r="H42" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="J42" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K42" t="n">
         <v>84</v>
@@ -2879,7 +2879,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,48 +2889,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>10.03</v>
       </c>
       <c r="E43" t="n">
-        <v>9.82</v>
+        <v>9.15</v>
       </c>
       <c r="F43" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="G43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>4.9</v>
+        <v>6.3</v>
       </c>
       <c r="I43" t="n">
-        <v>22.1</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K43" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L43" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M43" t="n">
-        <v>30.9</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O43" t="n">
         <v>6</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~31 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 624u = ~99 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2963,13 +2963,13 @@
         <v>11</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I44" t="n">
-        <v>21.1</v>
+        <v>20.3</v>
       </c>
       <c r="J44" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K44" t="n">
         <v>150</v>
@@ -2978,7 +2978,7 @@
         <v>150</v>
       </c>
       <c r="M44" t="n">
-        <v>29.9</v>
+        <v>29</v>
       </c>
       <c r="N44" t="n">
         <v>55</v>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~30 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~29 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3021,13 +3021,13 @@
         <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I45" t="n">
-        <v>34.3</v>
+        <v>33.7</v>
       </c>
       <c r="J45" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K45" t="n">
         <v>6</v>
@@ -3036,7 +3036,7 @@
         <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="N45" t="n">
         <v>46</v>
@@ -3053,7 +3053,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,48 +3063,48 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F46" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="I46" t="n">
-        <v>18.6</v>
+        <v>23.9</v>
       </c>
       <c r="J46" t="n">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="K46" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L46" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M46" t="n">
-        <v>110.5</v>
+        <v>33.4</v>
       </c>
       <c r="N46" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O46" t="n">
         <v>5</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~110 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 150u = ~33 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3137,10 +3137,10 @@
         <v>14</v>
       </c>
       <c r="H47" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>44</v>
+        <v>45.7</v>
       </c>
       <c r="J47" t="n">
         <v>160</v>
@@ -3152,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>47.5</v>
+        <v>49.5</v>
       </c>
       <c r="N47" t="n">
         <v>50</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~48 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~50 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3427,10 +3427,10 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="I52" t="n">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="J52" t="n">
         <v>24</v>
@@ -3442,17 +3442,17 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>361.9</v>
+        <v>393.6</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
       </c>
       <c r="O52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~362 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~394 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>168.5</v>
+        <v>162.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>359</v>
+        <v>413</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>990</v>
+        <v>884</v>
       </c>
       <c r="M2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~990u (495cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~884u (442cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>52.4</v>
+        <v>53.4</v>
       </c>
       <c r="I3" t="n">
         <v>4.1</v>
       </c>
       <c r="J3" t="n">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,10 +643,10 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>18.1</v>
+        <v>19.1</v>
       </c>
       <c r="I4" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J4" t="n">
         <v>127</v>
@@ -655,20 +655,20 @@
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~18u (9cs) - sells in ~1 wks</t>
+          <t>BUY ~28u (14cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>22.8</v>
+        <v>20.9</v>
       </c>
       <c r="I5" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="J5" t="n">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -716,13 +716,13 @@
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -762,10 +762,10 @@
         <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="J6" t="n">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -817,13 +817,13 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I7" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="J7" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -832,13 +832,13 @@
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N7" t="n">
         <v>42</v>
       </c>
       <c r="O7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -875,13 +875,13 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I8" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="J8" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -890,13 +890,13 @@
         <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N8" t="n">
         <v>44</v>
       </c>
       <c r="O8" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -933,13 +933,13 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>7.3</v>
       </c>
       <c r="I9" t="n">
-        <v>10.2</v>
+        <v>10.9</v>
       </c>
       <c r="J9" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -948,13 +948,13 @@
         <v>2</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N9" t="n">
         <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -991,32 +991,32 @@
         <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>13.2</v>
+        <v>12.4</v>
       </c>
       <c r="I10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J10" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="K10" t="n">
         <v>24</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N10" t="n">
         <v>44</v>
       </c>
       <c r="O10" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~42u (7cs) - sells in ~3 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~3 wks</t>
         </is>
       </c>
     </row>
@@ -1049,13 +1049,13 @@
         <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I11" t="n">
-        <v>10.1</v>
+        <v>9.6</v>
       </c>
       <c r="J11" t="n">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="K11" t="n">
         <v>2</v>
@@ -1070,7 +1070,7 @@
         <v>50</v>
       </c>
       <c r="O11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>24.4</v>
+        <v>23.7</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="J12" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K12" t="n">
         <v>624</v>
@@ -1122,13 +1122,13 @@
         <v>624</v>
       </c>
       <c r="M12" t="n">
-        <v>25.6</v>
+        <v>26.3</v>
       </c>
       <c r="N12" t="n">
         <v>45</v>
       </c>
       <c r="O12" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1165,32 +1165,32 @@
         <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>6.2</v>
+        <v>6.7</v>
       </c>
       <c r="I13" t="n">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J13" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="N13" t="n">
         <v>50</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1223,13 +1223,13 @@
         <v>14</v>
       </c>
       <c r="H14" t="n">
-        <v>16.3</v>
+        <v>17.9</v>
       </c>
       <c r="I14" t="n">
-        <v>10.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="K14" t="n">
         <v>624</v>
@@ -1238,24 +1238,24 @@
         <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>38.2</v>
+        <v>34.8</v>
       </c>
       <c r="N14" t="n">
         <v>45</v>
       </c>
       <c r="O14" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~38 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~35 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,55 +1265,55 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E15" t="n">
-        <v>9.9</v>
+        <v>9.06</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G15" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>10.5</v>
+        <v>14.9</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="J15" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="K15" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L15" t="n">
-        <v>66</v>
+        <v>624</v>
       </c>
       <c r="M15" t="n">
-        <v>6.3</v>
+        <v>42</v>
       </c>
       <c r="N15" t="n">
         <v>45</v>
       </c>
       <c r="O15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~66u (11cs) - sells in ~6 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1323,48 +1323,48 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>9.06</v>
+        <v>9.9</v>
       </c>
       <c r="F16" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>14.6</v>
+        <v>9.1</v>
       </c>
       <c r="I16" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="K16" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>624</v>
+        <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>42.8</v>
+        <v>5.9</v>
       </c>
       <c r="N16" t="n">
         <v>45</v>
       </c>
       <c r="O16" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>BUY ~54u (9cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1397,13 +1397,13 @@
         <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="I17" t="n">
-        <v>5.6</v>
+        <v>8.5</v>
       </c>
       <c r="J17" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="K17" t="n">
         <v>624</v>
@@ -1412,24 +1412,24 @@
         <v>624</v>
       </c>
       <c r="M17" t="n">
-        <v>47.2</v>
+        <v>48.7</v>
       </c>
       <c r="N17" t="n">
         <v>45</v>
       </c>
       <c r="O17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~47 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,55 +1439,55 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>10.03</v>
       </c>
       <c r="E18" t="n">
-        <v>9.9</v>
+        <v>9.15</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>0.88</v>
       </c>
       <c r="G18" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H18" t="n">
-        <v>9.199999999999999</v>
+        <v>20.3</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>8.1</v>
       </c>
       <c r="J18" t="n">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L18" t="n">
+        <v>624</v>
+      </c>
+      <c r="M18" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="N18" t="n">
+        <v>46</v>
+      </c>
+      <c r="O18" t="n">
         <v>18</v>
       </c>
-      <c r="M18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N18" t="n">
-        <v>45</v>
-      </c>
-      <c r="O18" t="n">
-        <v>19</v>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~31 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,55 +1497,55 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9.67</v>
+        <v>10.5</v>
       </c>
       <c r="E19" t="n">
-        <v>7.57</v>
+        <v>9.06</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>8.699999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="I19" t="n">
-        <v>4</v>
+        <v>11.5</v>
       </c>
       <c r="J19" t="n">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L19" t="n">
-        <v>36</v>
+        <v>624</v>
       </c>
       <c r="M19" t="n">
-        <v>4.1</v>
+        <v>50</v>
       </c>
       <c r="N19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O19" t="n">
         <v>18</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
+          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,48 +1555,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>9.9</v>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>12.5</v>
+        <v>7.9</v>
       </c>
       <c r="I20" t="n">
-        <v>12.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>159</v>
+        <v>55</v>
       </c>
       <c r="K20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>50.1</v>
+        <v>1.5</v>
       </c>
       <c r="N20" t="n">
         <v>45</v>
       </c>
       <c r="O20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
+          <t>BUY ~12u (2cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1629,13 +1629,13 @@
         <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="I21" t="n">
-        <v>15.4</v>
+        <v>17.5</v>
       </c>
       <c r="J21" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
@@ -1650,7 +1650,7 @@
         <v>46</v>
       </c>
       <c r="O21" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1687,39 +1687,39 @@
         <v>24</v>
       </c>
       <c r="H22" t="n">
-        <v>8.699999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J22" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K22" t="n">
         <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
         <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
+          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,55 +1729,55 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.5</v>
+        <v>10.03</v>
       </c>
       <c r="E23" t="n">
-        <v>8.4</v>
+        <v>9.15</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1</v>
+        <v>0.88</v>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>8.699999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>35</v>
+        <v>179</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L23" t="n">
-        <v>36</v>
+        <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>34.1</v>
       </c>
       <c r="N23" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
+          <t>CAUTION - 624u = ~34 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,55 +1787,55 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.03</v>
+        <v>9.67</v>
       </c>
       <c r="E24" t="n">
-        <v>9.15</v>
+        <v>7.57</v>
       </c>
       <c r="F24" t="n">
-        <v>0.88</v>
+        <v>2.1</v>
       </c>
       <c r="G24" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>19.1</v>
+        <v>7.6</v>
       </c>
       <c r="I24" t="n">
-        <v>8.9</v>
+        <v>4.5</v>
       </c>
       <c r="J24" t="n">
-        <v>171</v>
+        <v>34</v>
       </c>
       <c r="K24" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>624</v>
+        <v>30</v>
       </c>
       <c r="M24" t="n">
-        <v>32.6</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
         <v>46</v>
       </c>
       <c r="O24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~33 wks (overstock); consider ~624u</t>
+          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,55 +1845,55 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.03</v>
+        <v>10.5</v>
       </c>
       <c r="E25" t="n">
-        <v>9.15</v>
+        <v>8.4</v>
       </c>
       <c r="F25" t="n">
-        <v>0.88</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>17.9</v>
+        <v>7.6</v>
       </c>
       <c r="I25" t="n">
-        <v>10.5</v>
+        <v>4.5</v>
       </c>
       <c r="J25" t="n">
-        <v>190</v>
+        <v>34</v>
       </c>
       <c r="K25" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>624</v>
+        <v>30</v>
       </c>
       <c r="M25" t="n">
-        <v>34.8</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O25" t="n">
         <v>16</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~35 wks (overstock); consider ~624u</t>
+          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,48 +1903,48 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.67</v>
+        <v>10.03</v>
       </c>
       <c r="E26" t="n">
-        <v>13.34</v>
+        <v>9.15</v>
       </c>
       <c r="F26" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>4.4</v>
+        <v>15.5</v>
       </c>
       <c r="I26" t="n">
-        <v>7.7</v>
+        <v>9.4</v>
       </c>
       <c r="J26" t="n">
-        <v>34</v>
+        <v>148</v>
       </c>
       <c r="K26" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7</v>
+        <v>40.2</v>
       </c>
       <c r="N26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1977,13 +1977,13 @@
         <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>11.4</v>
+        <v>10.5</v>
       </c>
       <c r="I27" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J27" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K27" t="n">
         <v>150</v>
@@ -1992,17 +1992,17 @@
         <v>150</v>
       </c>
       <c r="M27" t="n">
-        <v>13.2</v>
+        <v>14.2</v>
       </c>
       <c r="N27" t="n">
         <v>50</v>
       </c>
       <c r="O27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2035,13 +2035,13 @@
         <v>20</v>
       </c>
       <c r="H28" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I28" t="n">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="J28" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K28" t="n">
         <v>24</v>
@@ -2050,7 +2050,7 @@
         <v>24</v>
       </c>
       <c r="M28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="N28" t="n">
         <v>44</v>
@@ -2067,7 +2067,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.03</v>
+        <v>16.67</v>
       </c>
       <c r="E29" t="n">
-        <v>9.15</v>
+        <v>13.34</v>
       </c>
       <c r="F29" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>15.2</v>
+        <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>10.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>155</v>
+        <v>33</v>
       </c>
       <c r="K29" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="M29" t="n">
-        <v>41.2</v>
+        <v>0.8</v>
       </c>
       <c r="N29" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O29" t="n">
         <v>13</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~41 wks (overstock); consider ~624u</t>
+          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>10.85</v>
       </c>
       <c r="E30" t="n">
-        <v>11.2</v>
+        <v>8.68</v>
       </c>
       <c r="F30" t="n">
-        <v>0.8</v>
+        <v>2.17</v>
       </c>
       <c r="G30" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H30" t="n">
-        <v>14.7</v>
+        <v>5.5</v>
       </c>
       <c r="I30" t="n">
-        <v>10.6</v>
+        <v>19</v>
       </c>
       <c r="J30" t="n">
-        <v>167</v>
+        <v>150</v>
       </c>
       <c r="K30" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O30" t="n">
         <v>12</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2193,38 +2193,38 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>26.52</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>24.2</v>
+        <v>11.2</v>
       </c>
       <c r="F31" t="n">
-        <v>2.33</v>
+        <v>0.8</v>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H31" t="n">
-        <v>5.3</v>
+        <v>14.9</v>
       </c>
       <c r="I31" t="n">
-        <v>12.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>65</v>
+        <v>156</v>
       </c>
       <c r="K31" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="L31" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="M31" t="n">
-        <v>39.4</v>
+        <v>5.7</v>
       </c>
       <c r="N31" t="n">
         <v>44</v>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~39 wks (overstock); consider ~208u</t>
+          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,55 +2251,55 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.5</v>
+        <v>26.52</v>
       </c>
       <c r="E32" t="n">
-        <v>9.06</v>
+        <v>24.2</v>
       </c>
       <c r="F32" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="G32" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>7.3</v>
+        <v>5</v>
       </c>
       <c r="I32" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="J32" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="K32" t="n">
-        <v>624</v>
+        <v>208</v>
       </c>
       <c r="L32" t="n">
-        <v>624</v>
+        <v>208</v>
       </c>
       <c r="M32" t="n">
-        <v>85</v>
+        <v>41.6</v>
       </c>
       <c r="N32" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~85 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 208u = ~42 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2313,51 +2313,51 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="E33" t="n">
-        <v>18.02</v>
+        <v>9.06</v>
       </c>
       <c r="F33" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="G33" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H33" t="n">
-        <v>5.3</v>
+        <v>7.7</v>
       </c>
       <c r="I33" t="n">
-        <v>12</v>
+        <v>8.1</v>
       </c>
       <c r="J33" t="n">
-        <v>85</v>
+        <v>63</v>
       </c>
       <c r="K33" t="n">
-        <v>40</v>
+        <v>624</v>
       </c>
       <c r="L33" t="n">
-        <v>40</v>
+        <v>624</v>
       </c>
       <c r="M33" t="n">
-        <v>7.6</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~8 wks (cooling)</t>
+          <t>CAUTION - 624u = ~81 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,48 +2367,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.85</v>
+        <v>20</v>
       </c>
       <c r="E34" t="n">
-        <v>8.68</v>
+        <v>18.02</v>
       </c>
       <c r="F34" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="G34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H34" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="I34" t="n">
-        <v>22.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="K34" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L34" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="M34" t="n">
-        <v>1.3</v>
+        <v>6.9</v>
       </c>
       <c r="N34" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O34" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~40u (10cs) - sells in ~7 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2441,13 +2441,13 @@
         <v>20</v>
       </c>
       <c r="H35" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>18.4</v>
+        <v>16.4</v>
       </c>
       <c r="J35" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="K35" t="n">
         <v>6</v>
@@ -2456,13 +2456,13 @@
         <v>6</v>
       </c>
       <c r="M35" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="N35" t="n">
         <v>46</v>
       </c>
       <c r="O35" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,29 +2483,29 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E36" t="n">
-        <v>8.68</v>
+        <v>8.4</v>
       </c>
       <c r="F36" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G36" t="n">
         <v>20</v>
       </c>
       <c r="H36" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I36" t="n">
-        <v>21.9</v>
+        <v>12.5</v>
       </c>
       <c r="J36" t="n">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="K36" t="n">
         <v>6</v>
@@ -2514,24 +2514,24 @@
         <v>6</v>
       </c>
       <c r="M36" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N36" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,29 +2541,29 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E37" t="n">
-        <v>8.4</v>
+        <v>8.68</v>
       </c>
       <c r="F37" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="G37" t="n">
         <v>20</v>
       </c>
       <c r="H37" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="I37" t="n">
-        <v>13.1</v>
+        <v>26.5</v>
       </c>
       <c r="J37" t="n">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="K37" t="n">
         <v>6</v>
@@ -2572,17 +2572,17 @@
         <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="N37" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O37" t="n">
         <v>9</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2615,13 +2615,13 @@
         <v>24</v>
       </c>
       <c r="H38" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I38" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="J38" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
@@ -2630,7 +2630,7 @@
         <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N38" t="n">
         <v>45</v>
@@ -2673,13 +2673,13 @@
         <v>22</v>
       </c>
       <c r="H39" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I39" t="n">
-        <v>13.1</v>
+        <v>12.5</v>
       </c>
       <c r="J39" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K39" t="n">
         <v>6</v>
@@ -2688,7 +2688,7 @@
         <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N39" t="n">
         <v>46</v>
@@ -2705,7 +2705,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2731,13 +2731,13 @@
         <v>7</v>
       </c>
       <c r="H40" t="n">
-        <v>9.6</v>
+        <v>10.2</v>
       </c>
       <c r="I40" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="J40" t="n">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="K40" t="n">
         <v>84</v>
@@ -2746,7 +2746,7 @@
         <v>84</v>
       </c>
       <c r="M40" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N40" t="n">
         <v>44</v>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~9 wks (cooling)</t>
+          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2789,13 +2789,13 @@
         <v>11</v>
       </c>
       <c r="H41" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I41" t="n">
-        <v>14.9</v>
+        <v>13.3</v>
       </c>
       <c r="J41" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K41" t="n">
         <v>150</v>
@@ -2804,7 +2804,7 @@
         <v>150</v>
       </c>
       <c r="M41" t="n">
-        <v>21.4</v>
+        <v>20.8</v>
       </c>
       <c r="N41" t="n">
         <v>55</v>
@@ -2821,7 +2821,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2847,13 +2847,13 @@
         <v>7</v>
       </c>
       <c r="H42" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="I42" t="n">
-        <v>12.6</v>
+        <v>8.9</v>
       </c>
       <c r="J42" t="n">
-        <v>157</v>
+        <v>128</v>
       </c>
       <c r="K42" t="n">
         <v>84</v>
@@ -2862,24 +2862,24 @@
         <v>84</v>
       </c>
       <c r="M42" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="N42" t="n">
         <v>44</v>
       </c>
       <c r="O42" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~10 wks (cooling)</t>
+          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,48 +2889,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.03</v>
+        <v>14</v>
       </c>
       <c r="E43" t="n">
-        <v>9.15</v>
+        <v>11.2</v>
       </c>
       <c r="F43" t="n">
-        <v>0.88</v>
+        <v>2.8</v>
       </c>
       <c r="G43" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>6.3</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>48.7</v>
       </c>
       <c r="J43" t="n">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="K43" t="n">
-        <v>624</v>
+        <v>24</v>
       </c>
       <c r="L43" t="n">
-        <v>624</v>
+        <v>24</v>
       </c>
       <c r="M43" t="n">
-        <v>99.09999999999999</v>
+        <v>12</v>
       </c>
       <c r="N43" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O43" t="n">
         <v>6</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~99 wks (overstock); consider ~624u</t>
+          <t>BUY ~24u (4cs) - sells in ~12 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2963,13 +2963,13 @@
         <v>11</v>
       </c>
       <c r="H44" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I44" t="n">
-        <v>20.3</v>
+        <v>19.9</v>
       </c>
       <c r="J44" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K44" t="n">
         <v>150</v>
@@ -2978,7 +2978,7 @@
         <v>150</v>
       </c>
       <c r="M44" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="N44" t="n">
         <v>55</v>
@@ -2995,7 +2995,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3005,55 +3005,55 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.85</v>
+        <v>10.03</v>
       </c>
       <c r="E45" t="n">
-        <v>8.68</v>
+        <v>9.15</v>
       </c>
       <c r="F45" t="n">
-        <v>2.17</v>
+        <v>0.88</v>
       </c>
       <c r="G45" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H45" t="n">
-        <v>2.5</v>
+        <v>6.9</v>
       </c>
       <c r="I45" t="n">
-        <v>33.7</v>
+        <v>13.7</v>
       </c>
       <c r="J45" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="K45" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L45" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M45" t="n">
-        <v>2.4</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N45" t="n">
         <v>46</v>
       </c>
       <c r="O45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
+          <t>CAUTION - 624u = ~91 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,55 +3063,55 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>10.85</v>
       </c>
       <c r="E46" t="n">
-        <v>9.82</v>
+        <v>8.68</v>
       </c>
       <c r="F46" t="n">
-        <v>1.18</v>
+        <v>2.17</v>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H46" t="n">
-        <v>4.5</v>
+        <v>2.6</v>
       </c>
       <c r="I46" t="n">
-        <v>23.9</v>
+        <v>34.6</v>
       </c>
       <c r="J46" t="n">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="K46" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L46" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M46" t="n">
-        <v>33.4</v>
+        <v>2.3</v>
       </c>
       <c r="N46" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~33 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3121,29 +3121,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9.33</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>8.01</v>
+        <v>9.82</v>
       </c>
       <c r="F47" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="G47" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="I47" t="n">
-        <v>45.7</v>
+        <v>22.4</v>
       </c>
       <c r="J47" t="n">
-        <v>160</v>
+        <v>96</v>
       </c>
       <c r="K47" t="n">
         <v>150</v>
@@ -3152,24 +3152,24 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>49.5</v>
+        <v>32.3</v>
       </c>
       <c r="N47" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~50 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~32 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
+          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3183,25 +3183,25 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>9.33</v>
       </c>
       <c r="E48" t="n">
-        <v>9.82</v>
+        <v>8.01</v>
       </c>
       <c r="F48" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="G48" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="I48" t="n">
-        <v>21.4</v>
+        <v>49.1</v>
       </c>
       <c r="J48" t="n">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="K48" t="n">
         <v>150</v>
@@ -3210,17 +3210,17 @@
         <v>150</v>
       </c>
       <c r="M48" t="n">
-        <v>50.5</v>
+        <v>53.8</v>
       </c>
       <c r="N48" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O48" t="n">
         <v>4</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~50 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~54 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3256,10 +3256,10 @@
         <v>1.6</v>
       </c>
       <c r="I49" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="J49" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K49" t="n">
         <v>40</v>
@@ -3268,7 +3268,7 @@
         <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>24.3</v>
+        <v>25.5</v>
       </c>
       <c r="N49" t="n">
         <v>48</v>
@@ -3278,14 +3278,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~24 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 40u = ~26 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
+          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3299,51 +3299,51 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.58</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>7.06</v>
+        <v>9.82</v>
       </c>
       <c r="F50" t="n">
-        <v>3.53</v>
+        <v>1.18</v>
       </c>
       <c r="G50" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="I50" t="n">
-        <v>28.8</v>
+        <v>25.3</v>
       </c>
       <c r="J50" t="n">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="K50" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="L50" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="M50" t="n">
-        <v>15.6</v>
+        <v>61</v>
       </c>
       <c r="N50" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~16 wks (cooling)</t>
+          <t>CAUTION - 150u = ~61 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3353,48 +3353,48 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>14</v>
+        <v>10.58</v>
       </c>
       <c r="E51" t="n">
-        <v>11.2</v>
+        <v>7.06</v>
       </c>
       <c r="F51" t="n">
-        <v>2.8</v>
+        <v>3.53</v>
       </c>
       <c r="G51" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H51" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>89.3</v>
+        <v>29.7</v>
       </c>
       <c r="J51" t="n">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="K51" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L51" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M51" t="n">
-        <v>21</v>
+        <v>16.1</v>
       </c>
       <c r="N51" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 24u = ~21 wks (overstock); consider ~24u</t>
+          <t>CAUTION - 12u = ~16 wks (overstock); consider ~12u</t>
         </is>
       </c>
     </row>
@@ -3427,13 +3427,13 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="I52" t="n">
-        <v>15</v>
+        <v>17.2</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K52" t="n">
         <v>624</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>393.6</v>
+        <v>471.4</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~394 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~471 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,19 +527,19 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>162.1</v>
+        <v>162.6</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>884</v>
+        <v>898</v>
       </c>
       <c r="M2" t="n">
         <v>5.5</v>
@@ -548,11 +548,11 @@
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~884u (442cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~898u (449cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,32 +585,32 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>53.4</v>
+        <v>54</v>
       </c>
       <c r="I3" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
       </c>
       <c r="L3" t="n">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="M3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BUY ~208u (104cs) - sells in ~4 wks</t>
+          <t>BUY ~218u (109cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
@@ -643,22 +643,22 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J4" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="M4" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~28u (14cs) - sells in ~2 wks</t>
+          <t>BUY ~30u (15cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="J5" t="n">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="I6" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J6" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -780,7 +780,7 @@
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -820,10 +820,10 @@
         <v>7.3</v>
       </c>
       <c r="I7" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="J7" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -878,10 +878,10 @@
         <v>7.3</v>
       </c>
       <c r="I8" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="J8" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -936,10 +936,10 @@
         <v>7.3</v>
       </c>
       <c r="I9" t="n">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="J9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -991,22 +991,22 @@
         <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="I10" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="K10" t="n">
         <v>24</v>
       </c>
       <c r="L10" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N10" t="n">
         <v>44</v>
@@ -1016,14 +1016,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~3 wks</t>
+          <t>BUY ~42u (7cs) - sells in ~3 wks</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1033,55 +1033,55 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.7</v>
+        <v>10.5</v>
       </c>
       <c r="E11" t="n">
-        <v>21.7</v>
+        <v>9.06</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>8.5</v>
+        <v>24.6</v>
       </c>
       <c r="I11" t="n">
-        <v>9.6</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2</v>
+        <v>25.3</v>
       </c>
       <c r="N11" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1091,55 +1091,55 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.5</v>
+        <v>25.7</v>
       </c>
       <c r="E12" t="n">
-        <v>9.06</v>
+        <v>21.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>23.7</v>
+        <v>8.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4.8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="K12" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>26.3</v>
+        <v>0.2</v>
       </c>
       <c r="N12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O12" t="n">
         <v>34</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,55 +1149,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25.7</v>
+        <v>10.5</v>
       </c>
       <c r="E13" t="n">
-        <v>21.7</v>
+        <v>9.06</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H13" t="n">
-        <v>6.7</v>
+        <v>19.5</v>
       </c>
       <c r="I13" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="J13" t="n">
-        <v>49</v>
+        <v>139</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9</v>
+        <v>32</v>
       </c>
       <c r="N13" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~32 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,48 +1207,48 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10.5</v>
+        <v>25.7</v>
       </c>
       <c r="E14" t="n">
-        <v>9.06</v>
+        <v>21.7</v>
       </c>
       <c r="F14" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H14" t="n">
-        <v>17.9</v>
+        <v>6.7</v>
       </c>
       <c r="I14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J14" t="n">
-        <v>149</v>
+        <v>49</v>
       </c>
       <c r="K14" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>34.8</v>
+        <v>0.9</v>
       </c>
       <c r="N14" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~35 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1284,10 +1284,10 @@
         <v>14.9</v>
       </c>
       <c r="I15" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K15" t="n">
         <v>624</v>
@@ -1313,7 +1313,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1323,38 +1323,38 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E16" t="n">
-        <v>9.9</v>
+        <v>9.06</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>9.1</v>
+        <v>12.9</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>8.4</v>
       </c>
       <c r="J16" t="n">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L16" t="n">
-        <v>54</v>
+        <v>624</v>
       </c>
       <c r="M16" t="n">
-        <v>5.9</v>
+        <v>48.3</v>
       </c>
       <c r="N16" t="n">
         <v>45</v>
@@ -1364,14 +1364,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUY ~54u (9cs) - sells in ~6 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1397,13 +1397,13 @@
         <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="I17" t="n">
-        <v>8.5</v>
+        <v>10.8</v>
       </c>
       <c r="J17" t="n">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="K17" t="n">
         <v>624</v>
@@ -1412,24 +1412,24 @@
         <v>624</v>
       </c>
       <c r="M17" t="n">
-        <v>48.7</v>
+        <v>48.3</v>
       </c>
       <c r="N17" t="n">
         <v>45</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,55 +1439,55 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.03</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
-        <v>9.15</v>
+        <v>9.9</v>
       </c>
       <c r="F18" t="n">
-        <v>0.88</v>
+        <v>2.1</v>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>20.3</v>
+        <v>9.1</v>
       </c>
       <c r="I18" t="n">
-        <v>8.1</v>
+        <v>2.8</v>
       </c>
       <c r="J18" t="n">
-        <v>166</v>
+        <v>19</v>
       </c>
       <c r="K18" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>624</v>
+        <v>60</v>
       </c>
       <c r="M18" t="n">
-        <v>30.7</v>
+        <v>6.6</v>
       </c>
       <c r="N18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~31 wks (overstock); consider ~624u</t>
+          <t>BUY ~60u (10cs) - sells in ~7 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,29 +1497,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.5</v>
+        <v>10.03</v>
       </c>
       <c r="E19" t="n">
-        <v>9.06</v>
+        <v>9.15</v>
       </c>
       <c r="F19" t="n">
-        <v>1.44</v>
+        <v>0.88</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>12.5</v>
+        <v>20.2</v>
       </c>
       <c r="I19" t="n">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="K19" t="n">
         <v>624</v>
@@ -1528,24 +1528,24 @@
         <v>624</v>
       </c>
       <c r="M19" t="n">
-        <v>50</v>
+        <v>30.9</v>
       </c>
       <c r="N19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O19" t="n">
         <v>18</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~31 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,48 +1555,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>10.03</v>
       </c>
       <c r="E20" t="n">
-        <v>9.9</v>
+        <v>9.15</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1</v>
+        <v>0.88</v>
       </c>
       <c r="G20" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>7.9</v>
+        <v>19</v>
       </c>
       <c r="I20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J20" t="n">
-        <v>55</v>
+        <v>175</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L20" t="n">
-        <v>12</v>
+        <v>624</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5</v>
+        <v>32.9</v>
       </c>
       <c r="N20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O20" t="n">
         <v>17</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~33 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1629,13 +1629,13 @@
         <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>17.5</v>
+        <v>16.7</v>
       </c>
       <c r="J21" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
@@ -1650,7 +1650,7 @@
         <v>46</v>
       </c>
       <c r="O21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
         <v>7.6</v>
       </c>
       <c r="I22" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K22" t="n">
         <v>6</v>
@@ -1719,7 +1719,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,48 +1729,48 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.03</v>
+        <v>12</v>
       </c>
       <c r="E23" t="n">
-        <v>9.15</v>
+        <v>9.9</v>
       </c>
       <c r="F23" t="n">
-        <v>0.88</v>
+        <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
-        <v>18.3</v>
+        <v>7.9</v>
       </c>
       <c r="I23" t="n">
-        <v>9.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="J23" t="n">
-        <v>179</v>
+        <v>55</v>
       </c>
       <c r="K23" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M23" t="n">
-        <v>34.1</v>
+        <v>1.5</v>
       </c>
       <c r="N23" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O23" t="n">
         <v>16</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~34 wks (overstock); consider ~624u</t>
+          <t>BUY ~12u (2cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1806,10 +1806,10 @@
         <v>7.6</v>
       </c>
       <c r="I24" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J24" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K24" t="n">
         <v>6</v>
@@ -1864,10 +1864,10 @@
         <v>7.6</v>
       </c>
       <c r="I25" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K25" t="n">
         <v>6</v>
@@ -1919,13 +1919,13 @@
         <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="I26" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J26" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K26" t="n">
         <v>624</v>
@@ -1934,7 +1934,7 @@
         <v>624</v>
       </c>
       <c r="M26" t="n">
-        <v>40.2</v>
+        <v>39.3</v>
       </c>
       <c r="N26" t="n">
         <v>46</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~39 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1977,10 +1977,10 @@
         <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="I27" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="J27" t="n">
         <v>65</v>
@@ -1992,7 +1992,7 @@
         <v>150</v>
       </c>
       <c r="M27" t="n">
-        <v>14.2</v>
+        <v>14.4</v>
       </c>
       <c r="N27" t="n">
         <v>50</v>
@@ -2009,7 +2009,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,55 +2019,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14</v>
+        <v>16.67</v>
       </c>
       <c r="E28" t="n">
-        <v>11.2</v>
+        <v>13.34</v>
       </c>
       <c r="F28" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="G28" t="n">
         <v>20</v>
       </c>
       <c r="H28" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="I28" t="n">
-        <v>7.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K28" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>5.4</v>
+        <v>0.8</v>
       </c>
       <c r="N28" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O28" t="n">
         <v>13</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="E29" t="n">
-        <v>13.34</v>
+        <v>18.02</v>
       </c>
       <c r="F29" t="n">
-        <v>3.33</v>
+        <v>1.98</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J29" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8</v>
+        <v>6.7</v>
       </c>
       <c r="N29" t="n">
         <v>47</v>
       </c>
       <c r="O29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~40u (10cs) - sells in ~7 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E30" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F30" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H30" t="n">
-        <v>5.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>19</v>
+        <v>7.2</v>
       </c>
       <c r="J30" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O30" t="n">
         <v>12</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>CAUTION - 624u = ~76 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2193,55 +2193,55 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12</v>
+        <v>10.85</v>
       </c>
       <c r="E31" t="n">
-        <v>11.2</v>
+        <v>8.68</v>
       </c>
       <c r="F31" t="n">
-        <v>0.8</v>
+        <v>2.17</v>
       </c>
       <c r="G31" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>14.9</v>
+        <v>5.4</v>
       </c>
       <c r="I31" t="n">
-        <v>9.800000000000001</v>
+        <v>19.3</v>
       </c>
       <c r="J31" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="K31" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O31" t="n">
         <v>12</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,38 +2251,38 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>26.52</v>
+        <v>14</v>
       </c>
       <c r="E32" t="n">
-        <v>24.2</v>
+        <v>11.2</v>
       </c>
       <c r="F32" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="G32" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="I32" t="n">
-        <v>12.5</v>
+        <v>7.2</v>
       </c>
       <c r="J32" t="n">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="K32" t="n">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="L32" t="n">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="M32" t="n">
-        <v>41.6</v>
+        <v>5.4</v>
       </c>
       <c r="N32" t="n">
         <v>44</v>
@@ -2292,14 +2292,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~42 wks (overstock); consider ~208u</t>
+          <t>BUY ~24u (4cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>9.06</v>
+        <v>11.2</v>
       </c>
       <c r="F33" t="n">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>7.7</v>
+        <v>15.1</v>
       </c>
       <c r="I33" t="n">
-        <v>8.1</v>
+        <v>10.2</v>
       </c>
       <c r="J33" t="n">
-        <v>63</v>
+        <v>166</v>
       </c>
       <c r="K33" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="L33" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="M33" t="n">
-        <v>80.59999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="N33" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~81 wks (overstock); consider ~624u</t>
+          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,55 +2367,55 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D34" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="F34" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G34" t="n">
         <v>20</v>
       </c>
-      <c r="E34" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="F34" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G34" t="n">
-        <v>10</v>
-      </c>
       <c r="H34" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>9.699999999999999</v>
+        <v>16.2</v>
       </c>
       <c r="J34" t="n">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="K34" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L34" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>6.9</v>
+        <v>1.2</v>
       </c>
       <c r="N34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O34" t="n">
         <v>11</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~7 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2425,55 +2425,55 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.85</v>
+        <v>26.52</v>
       </c>
       <c r="E35" t="n">
-        <v>8.68</v>
+        <v>24.2</v>
       </c>
       <c r="F35" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="G35" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I35" t="n">
-        <v>16.4</v>
+        <v>13.2</v>
       </c>
       <c r="J35" t="n">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="K35" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="L35" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="M35" t="n">
-        <v>1.2</v>
+        <v>44</v>
       </c>
       <c r="N35" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O35" t="n">
         <v>11</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>CAUTION - 208u = ~44 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,48 +2483,48 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>8.4</v>
+        <v>9.82</v>
       </c>
       <c r="F36" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="G36" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H36" t="n">
-        <v>4.4</v>
+        <v>7.3</v>
       </c>
       <c r="I36" t="n">
-        <v>12.5</v>
+        <v>12.9</v>
       </c>
       <c r="J36" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="K36" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L36" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4</v>
+        <v>20.4</v>
       </c>
       <c r="N36" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="O36" t="n">
         <v>9</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 150u = ~20 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2618,7 @@
         <v>4.4</v>
       </c>
       <c r="I38" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="J38" t="n">
         <v>56</v>
@@ -2676,7 +2676,7 @@
         <v>4.4</v>
       </c>
       <c r="I39" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="J39" t="n">
         <v>56</v>
@@ -2705,7 +2705,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2715,55 +2715,55 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E40" t="n">
-        <v>11.2</v>
+        <v>8.4</v>
       </c>
       <c r="F40" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="G40" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>10.2</v>
+        <v>4.4</v>
       </c>
       <c r="I40" t="n">
-        <v>10.2</v>
+        <v>12.6</v>
       </c>
       <c r="J40" t="n">
-        <v>149</v>
+        <v>56</v>
       </c>
       <c r="K40" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L40" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>8.199999999999999</v>
+        <v>1.4</v>
       </c>
       <c r="N40" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O40" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,48 +2773,48 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E41" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F41" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G41" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>7.2</v>
+        <v>10.2</v>
       </c>
       <c r="I41" t="n">
-        <v>13.3</v>
+        <v>10.3</v>
       </c>
       <c r="J41" t="n">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="K41" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L41" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M41" t="n">
-        <v>20.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="O41" t="n">
         <v>8</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
+          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2847,13 +2847,13 @@
         <v>7</v>
       </c>
       <c r="H42" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="I42" t="n">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K42" t="n">
         <v>84</v>
@@ -2862,7 +2862,7 @@
         <v>84</v>
       </c>
       <c r="M42" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N42" t="n">
         <v>44</v>
@@ -3021,10 +3021,10 @@
         <v>9</v>
       </c>
       <c r="H45" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I45" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="J45" t="n">
         <v>95</v>
@@ -3036,7 +3036,7 @@
         <v>624</v>
       </c>
       <c r="M45" t="n">
-        <v>90.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="N45" t="n">
         <v>46</v>
@@ -3079,10 +3079,10 @@
         <v>20</v>
       </c>
       <c r="H46" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="I46" t="n">
-        <v>34.6</v>
+        <v>36.1</v>
       </c>
       <c r="J46" t="n">
         <v>119</v>
@@ -3094,13 +3094,13 @@
         <v>6</v>
       </c>
       <c r="M46" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="N46" t="n">
         <v>46</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -3137,10 +3137,10 @@
         <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I47" t="n">
-        <v>22.4</v>
+        <v>23.7</v>
       </c>
       <c r="J47" t="n">
         <v>96</v>
@@ -3152,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>32.3</v>
+        <v>34.2</v>
       </c>
       <c r="N47" t="n">
         <v>45</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~32 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~34 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3369,10 +3369,10 @@
         <v>33</v>
       </c>
       <c r="H51" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I51" t="n">
-        <v>29.7</v>
+        <v>34.4</v>
       </c>
       <c r="J51" t="n">
         <v>30</v>
@@ -3384,17 +3384,17 @@
         <v>12</v>
       </c>
       <c r="M51" t="n">
-        <v>16.1</v>
+        <v>18.7</v>
       </c>
       <c r="N51" t="n">
         <v>46</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 12u = ~16 wks (overstock); consider ~12u</t>
+          <t>CAUTION - 12u = ~19 wks (overstock); consider ~12u</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3430,7 @@
         <v>1.3</v>
       </c>
       <c r="I52" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="J52" t="n">
         <v>23</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>471.4</v>
+        <v>482.6</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~471 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~483 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>162.6</v>
+        <v>101</v>
       </c>
       <c r="I2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J2" t="n">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>898</v>
+        <v>392</v>
       </c>
       <c r="M2" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>422</v>
+        <v>262</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~898u (449cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~392u (196cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,32 +585,32 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>54</v>
+        <v>57.7</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
       </c>
       <c r="L3" t="n">
-        <v>218</v>
+        <v>248</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BUY ~218u (109cs) - sells in ~4 wks</t>
+          <t>BUY ~248u (124cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>22.4</v>
       </c>
       <c r="I4" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="M4" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~30u (15cs) - sells in ~2 wks</t>
+          <t>BUY ~58u (29cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>20.5</v>
+        <v>28</v>
       </c>
       <c r="I5" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="J5" t="n">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -716,17 +716,17 @@
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BUY ~40u (20cs) - sells in ~2 wks (cooling)</t>
+          <t>BUY ~40u (20cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>17.3</v>
+        <v>17.9</v>
       </c>
       <c r="I6" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="J6" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -774,13 +774,13 @@
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="J7" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -838,7 +838,7 @@
         <v>42</v>
       </c>
       <c r="O7" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -875,13 +875,13 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="J8" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -896,7 +896,7 @@
         <v>44</v>
       </c>
       <c r="O8" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -933,13 +933,13 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
-        <v>10.7</v>
+        <v>10.5</v>
       </c>
       <c r="J9" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -954,7 +954,7 @@
         <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -975,48 +975,48 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>25.7</v>
       </c>
       <c r="E10" t="n">
-        <v>11.2</v>
+        <v>21.7</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>12.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>9.4</v>
       </c>
       <c r="J10" t="n">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="K10" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3</v>
+        <v>0.2</v>
       </c>
       <c r="N10" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~42u (7cs) - sells in ~3 wks</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
@@ -1049,13 +1049,13 @@
         <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>24.6</v>
+        <v>26.1</v>
       </c>
       <c r="I11" t="n">
         <v>4.3</v>
       </c>
       <c r="J11" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K11" t="n">
         <v>624</v>
@@ -1064,24 +1064,24 @@
         <v>624</v>
       </c>
       <c r="M11" t="n">
-        <v>25.3</v>
+        <v>23.9</v>
       </c>
       <c r="N11" t="n">
         <v>45</v>
       </c>
       <c r="O11" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~24 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1091,55 +1091,55 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>25.7</v>
+        <v>10.5</v>
       </c>
       <c r="E12" t="n">
-        <v>21.7</v>
+        <v>9.06</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>8.6</v>
+        <v>21.2</v>
       </c>
       <c r="I12" t="n">
-        <v>9.300000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="J12" t="n">
-        <v>81</v>
+        <v>141</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2</v>
+        <v>29.4</v>
       </c>
       <c r="N12" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~29 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,55 +1149,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="E13" t="n">
-        <v>9.06</v>
+        <v>11.2</v>
       </c>
       <c r="F13" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>19.5</v>
+        <v>10.7</v>
       </c>
       <c r="I13" t="n">
-        <v>7.1</v>
+        <v>4.3</v>
       </c>
       <c r="J13" t="n">
-        <v>139</v>
+        <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>624</v>
+        <v>24</v>
       </c>
       <c r="L13" t="n">
-        <v>624</v>
+        <v>30</v>
       </c>
       <c r="M13" t="n">
-        <v>32</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~32 wks (overstock); consider ~624u</t>
+          <t>BUY ~30u (5cs) - sells in ~3 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,55 +1207,55 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25.7</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>21.7</v>
+        <v>16.67</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="G14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>6.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>7.3</v>
+        <v>17.4</v>
       </c>
       <c r="J14" t="n">
-        <v>49</v>
+        <v>85</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,55 +1265,55 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.5</v>
+        <v>25.7</v>
       </c>
       <c r="E15" t="n">
-        <v>9.06</v>
+        <v>21.7</v>
       </c>
       <c r="F15" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>14.9</v>
+        <v>7.3</v>
       </c>
       <c r="I15" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="K15" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>42</v>
+        <v>1.7</v>
       </c>
       <c r="N15" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O15" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
+          <t>BUY ~12u (6cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1323,55 +1323,55 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
-        <v>9.06</v>
+        <v>9.9</v>
       </c>
       <c r="F16" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>12.9</v>
+        <v>12</v>
       </c>
       <c r="I16" t="n">
-        <v>8.4</v>
+        <v>2.7</v>
       </c>
       <c r="J16" t="n">
-        <v>109</v>
+        <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="M16" t="n">
-        <v>48.3</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
         <v>45</v>
       </c>
       <c r="O16" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
+          <t>BUY ~84u (14cs) - sells in ~7 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1397,13 +1397,13 @@
         <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>12.9</v>
+        <v>15.7</v>
       </c>
       <c r="I17" t="n">
-        <v>10.8</v>
+        <v>3.4</v>
       </c>
       <c r="J17" t="n">
-        <v>141</v>
+        <v>50</v>
       </c>
       <c r="K17" t="n">
         <v>624</v>
@@ -1412,24 +1412,24 @@
         <v>624</v>
       </c>
       <c r="M17" t="n">
-        <v>48.3</v>
+        <v>39.7</v>
       </c>
       <c r="N17" t="n">
         <v>45</v>
       </c>
       <c r="O17" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1455,39 +1455,39 @@
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>9.1</v>
+        <v>10.2</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8</v>
+        <v>9.5</v>
       </c>
       <c r="J18" t="n">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="M18" t="n">
-        <v>6.6</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
         <v>45</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUY ~60u (10cs) - sells in ~7 wks (rising into season)</t>
+          <t>BUY ~30u (5cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,29 +1497,29 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.03</v>
+        <v>10.5</v>
       </c>
       <c r="E19" t="n">
-        <v>9.15</v>
+        <v>9.06</v>
       </c>
       <c r="F19" t="n">
-        <v>0.88</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>20.2</v>
+        <v>14</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="J19" t="n">
-        <v>164</v>
+        <v>113</v>
       </c>
       <c r="K19" t="n">
         <v>624</v>
@@ -1528,24 +1528,24 @@
         <v>624</v>
       </c>
       <c r="M19" t="n">
-        <v>30.9</v>
+        <v>44.5</v>
       </c>
       <c r="N19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~31 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~44 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,29 +1555,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.03</v>
+        <v>10.5</v>
       </c>
       <c r="E20" t="n">
-        <v>9.15</v>
+        <v>9.06</v>
       </c>
       <c r="F20" t="n">
-        <v>0.88</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>13.8</v>
       </c>
       <c r="I20" t="n">
-        <v>9.1</v>
+        <v>10.9</v>
       </c>
       <c r="J20" t="n">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="K20" t="n">
         <v>624</v>
@@ -1586,24 +1586,24 @@
         <v>624</v>
       </c>
       <c r="M20" t="n">
-        <v>32.9</v>
+        <v>45.1</v>
       </c>
       <c r="N20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O20" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~33 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~45 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1617,51 +1617,51 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="E21" t="n">
-        <v>16.67</v>
+        <v>13.34</v>
       </c>
       <c r="F21" t="n">
         <v>3.33</v>
       </c>
       <c r="G21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="I21" t="n">
-        <v>16.7</v>
+        <v>9</v>
       </c>
       <c r="J21" t="n">
-        <v>85</v>
+        <v>33</v>
       </c>
       <c r="K21" t="n">
         <v>3</v>
       </c>
       <c r="L21" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="N21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~15u (5cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,55 +1671,55 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>8.67</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>6.57</v>
+        <v>11.2</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
+        <v>20</v>
+      </c>
+      <c r="H22" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="I22" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>28</v>
+      </c>
+      <c r="K22" t="n">
         <v>24</v>
-      </c>
-      <c r="H22" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="I22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>33</v>
-      </c>
-      <c r="K22" t="n">
-        <v>6</v>
       </c>
       <c r="L22" t="n">
         <v>30</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="N22" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
+          <t>BUY ~30u (5cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,48 +1729,48 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E23" t="n">
-        <v>9.9</v>
+        <v>18.02</v>
       </c>
       <c r="F23" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>84</v>
+      </c>
+      <c r="K23" t="n">
+        <v>40</v>
+      </c>
+      <c r="L23" t="n">
+        <v>40</v>
+      </c>
+      <c r="M23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>47</v>
+      </c>
+      <c r="O23" t="n">
         <v>17</v>
       </c>
-      <c r="H23" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="I23" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="J23" t="n">
-        <v>55</v>
-      </c>
-      <c r="K23" t="n">
-        <v>6</v>
-      </c>
-      <c r="L23" t="n">
-        <v>12</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N23" t="n">
-        <v>45</v>
-      </c>
-      <c r="O23" t="n">
-        <v>16</v>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
@@ -1803,10 +1803,10 @@
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="I24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J24" t="n">
         <v>33</v>
@@ -1815,20 +1815,20 @@
         <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N24" t="n">
         <v>46</v>
       </c>
       <c r="O24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
@@ -1861,10 +1861,10 @@
         <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J25" t="n">
         <v>33</v>
@@ -1873,27 +1873,27 @@
         <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="N25" t="n">
         <v>47</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~4 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.03</v>
+        <v>8.67</v>
       </c>
       <c r="E26" t="n">
-        <v>9.15</v>
+        <v>6.57</v>
       </c>
       <c r="F26" t="n">
-        <v>0.88</v>
+        <v>2.1</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="H26" t="n">
-        <v>15.9</v>
+        <v>8.1</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>4.4</v>
       </c>
       <c r="J26" t="n">
-        <v>145</v>
+        <v>33</v>
       </c>
       <c r="K26" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>624</v>
+        <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>39.3</v>
+        <v>4.5</v>
       </c>
       <c r="N26" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~39 wks (overstock); consider ~624u</t>
+          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9.33</v>
+        <v>10.85</v>
       </c>
       <c r="E27" t="n">
-        <v>8.01</v>
+        <v>8.68</v>
       </c>
       <c r="F27" t="n">
-        <v>1.32</v>
+        <v>2.17</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>10.4</v>
+        <v>6.8</v>
       </c>
       <c r="I27" t="n">
-        <v>10.4</v>
+        <v>15</v>
       </c>
       <c r="J27" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
-        <v>14.4</v>
+        <v>0.9</v>
       </c>
       <c r="N27" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,55 +2019,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16.67</v>
+        <v>10.85</v>
       </c>
       <c r="E28" t="n">
-        <v>13.34</v>
+        <v>8.68</v>
       </c>
       <c r="F28" t="n">
-        <v>3.33</v>
+        <v>2.17</v>
       </c>
       <c r="G28" t="n">
         <v>20</v>
       </c>
       <c r="H28" t="n">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="I28" t="n">
-        <v>8.300000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="J28" t="n">
-        <v>33</v>
+        <v>150</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="N28" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O28" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2081,44 +2081,44 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>9.33</v>
       </c>
       <c r="E29" t="n">
-        <v>18.02</v>
+        <v>8.01</v>
       </c>
       <c r="F29" t="n">
-        <v>1.98</v>
+        <v>1.32</v>
       </c>
       <c r="G29" t="n">
+        <v>14</v>
+      </c>
+      <c r="H29" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I29" t="n">
         <v>10</v>
       </c>
-      <c r="H29" t="n">
-        <v>6</v>
-      </c>
-      <c r="I29" t="n">
-        <v>9.6</v>
-      </c>
       <c r="J29" t="n">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="M29" t="n">
-        <v>6.7</v>
+        <v>15.8</v>
       </c>
       <c r="N29" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~7 wks (cooling)</t>
+          <t>BUY ~150u (25cs) - sells in ~16 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>14</v>
       </c>
       <c r="H30" t="n">
-        <v>8.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J30" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K30" t="n">
         <v>624</v>
@@ -2166,24 +2166,24 @@
         <v>624</v>
       </c>
       <c r="M30" t="n">
-        <v>75.59999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="N30" t="n">
         <v>45</v>
       </c>
       <c r="O30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~76 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~71 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2209,13 +2209,13 @@
         <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="I31" t="n">
-        <v>19.3</v>
+        <v>26.5</v>
       </c>
       <c r="J31" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="K31" t="n">
         <v>6</v>
@@ -2224,24 +2224,24 @@
         <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>46</v>
       </c>
       <c r="O31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,55 +2251,55 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14</v>
+        <v>10.03</v>
       </c>
       <c r="E32" t="n">
-        <v>11.2</v>
+        <v>9.15</v>
       </c>
       <c r="F32" t="n">
-        <v>2.8</v>
+        <v>0.88</v>
       </c>
       <c r="G32" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>4.4</v>
+        <v>14.6</v>
       </c>
       <c r="I32" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="J32" t="n">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="K32" t="n">
-        <v>24</v>
+        <v>624</v>
       </c>
       <c r="L32" t="n">
-        <v>24</v>
+        <v>624</v>
       </c>
       <c r="M32" t="n">
-        <v>5.4</v>
+        <v>42.7</v>
       </c>
       <c r="N32" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O32" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~5 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>11.2</v>
+        <v>9.82</v>
       </c>
       <c r="F33" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H33" t="n">
-        <v>15.1</v>
+        <v>9</v>
       </c>
       <c r="I33" t="n">
-        <v>10.2</v>
+        <v>18.9</v>
       </c>
       <c r="J33" t="n">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="K33" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L33" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M33" t="n">
-        <v>5.6</v>
+        <v>16.7</v>
       </c>
       <c r="N33" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O33" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
+          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,38 +2367,38 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.85</v>
+        <v>10.03</v>
       </c>
       <c r="E34" t="n">
-        <v>8.68</v>
+        <v>9.15</v>
       </c>
       <c r="F34" t="n">
-        <v>2.17</v>
+        <v>0.88</v>
       </c>
       <c r="G34" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>12.8</v>
       </c>
       <c r="I34" t="n">
-        <v>16.2</v>
+        <v>10.4</v>
       </c>
       <c r="J34" t="n">
-        <v>103</v>
+        <v>190</v>
       </c>
       <c r="K34" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L34" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2</v>
+        <v>48.9</v>
       </c>
       <c r="N34" t="n">
         <v>46</v>
@@ -2408,14 +2408,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2425,38 +2425,38 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>26.52</v>
+        <v>12</v>
       </c>
       <c r="E35" t="n">
-        <v>24.2</v>
+        <v>11.2</v>
       </c>
       <c r="F35" t="n">
-        <v>2.33</v>
+        <v>0.8</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H35" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="I35" t="n">
-        <v>13.2</v>
+        <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>63</v>
+        <v>163</v>
       </c>
       <c r="K35" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="L35" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="M35" t="n">
-        <v>44</v>
+        <v>6.2</v>
       </c>
       <c r="N35" t="n">
         <v>44</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~44 wks (overstock); consider ~208u</t>
+          <t>BUY ~84u (14cs) - sells in ~6 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2499,10 +2499,10 @@
         <v>11</v>
       </c>
       <c r="H36" t="n">
-        <v>7.3</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>12.9</v>
+        <v>13.2</v>
       </c>
       <c r="J36" t="n">
         <v>95</v>
@@ -2514,24 +2514,24 @@
         <v>150</v>
       </c>
       <c r="M36" t="n">
-        <v>20.4</v>
+        <v>16.6</v>
       </c>
       <c r="N36" t="n">
         <v>55</v>
       </c>
       <c r="O36" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~20 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,48 +2541,48 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.85</v>
+        <v>10.03</v>
       </c>
       <c r="E37" t="n">
-        <v>8.68</v>
+        <v>9.15</v>
       </c>
       <c r="F37" t="n">
-        <v>2.17</v>
+        <v>0.88</v>
       </c>
       <c r="G37" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H37" t="n">
-        <v>4</v>
+        <v>11.2</v>
       </c>
       <c r="I37" t="n">
-        <v>26.5</v>
+        <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="K37" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L37" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M37" t="n">
-        <v>1.5</v>
+        <v>55.7</v>
       </c>
       <c r="N37" t="n">
         <v>46</v>
       </c>
       <c r="O37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
+          <t>CAUTION - 624u = ~56 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2615,13 +2615,13 @@
         <v>24</v>
       </c>
       <c r="H38" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I38" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="J38" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
@@ -2630,13 +2630,13 @@
         <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N38" t="n">
         <v>45</v>
       </c>
       <c r="O38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -2673,13 +2673,13 @@
         <v>22</v>
       </c>
       <c r="H39" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I39" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="J39" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K39" t="n">
         <v>6</v>
@@ -2688,13 +2688,13 @@
         <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N39" t="n">
         <v>46</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -2731,13 +2731,13 @@
         <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I40" t="n">
-        <v>12.6</v>
+        <v>12.3</v>
       </c>
       <c r="J40" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K40" t="n">
         <v>6</v>
@@ -2746,13 +2746,13 @@
         <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="N40" t="n">
         <v>47</v>
       </c>
       <c r="O40" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,55 +2773,55 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12</v>
+        <v>10.85</v>
       </c>
       <c r="E41" t="n">
-        <v>11.2</v>
+        <v>8.68</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8</v>
+        <v>2.17</v>
       </c>
       <c r="G41" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>10.2</v>
+        <v>4.2</v>
       </c>
       <c r="I41" t="n">
-        <v>10.3</v>
+        <v>34.3</v>
       </c>
       <c r="J41" t="n">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="K41" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L41" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="M41" t="n">
-        <v>8.300000000000001</v>
+        <v>1.4</v>
       </c>
       <c r="N41" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2831,55 +2831,55 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>11.2</v>
+        <v>9.82</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="G42" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H42" t="n">
-        <v>10.2</v>
+        <v>7.2</v>
       </c>
       <c r="I42" t="n">
-        <v>8.699999999999999</v>
+        <v>22.5</v>
       </c>
       <c r="J42" t="n">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="K42" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L42" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M42" t="n">
-        <v>8.199999999999999</v>
+        <v>20.8</v>
       </c>
       <c r="N42" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O42" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
+          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,55 +2889,55 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14</v>
+        <v>26.52</v>
       </c>
       <c r="E43" t="n">
-        <v>11.2</v>
+        <v>24.2</v>
       </c>
       <c r="F43" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="G43" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="I43" t="n">
-        <v>48.7</v>
+        <v>12.6</v>
       </c>
       <c r="J43" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="K43" t="n">
-        <v>24</v>
+        <v>208</v>
       </c>
       <c r="L43" t="n">
-        <v>24</v>
+        <v>208</v>
       </c>
       <c r="M43" t="n">
-        <v>12</v>
+        <v>60.4</v>
       </c>
       <c r="N43" t="n">
         <v>44</v>
       </c>
       <c r="O43" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~12 wks (rising into season)</t>
+          <t>CAUTION - 208u = ~60 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2947,55 +2947,55 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E44" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F44" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G44" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H44" t="n">
-        <v>5.1</v>
+        <v>10.2</v>
       </c>
       <c r="I44" t="n">
-        <v>19.9</v>
+        <v>8.5</v>
       </c>
       <c r="J44" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="K44" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L44" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M44" t="n">
-        <v>29.2</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N44" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="O44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~29 wks (overstock); consider ~150u</t>
+          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3005,55 +3005,55 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.03</v>
+        <v>12</v>
       </c>
       <c r="E45" t="n">
-        <v>9.15</v>
+        <v>11.2</v>
       </c>
       <c r="F45" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H45" t="n">
-        <v>6.8</v>
+        <v>10.2</v>
       </c>
       <c r="I45" t="n">
-        <v>13.8</v>
+        <v>10.1</v>
       </c>
       <c r="J45" t="n">
-        <v>95</v>
+        <v>147</v>
       </c>
       <c r="K45" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="L45" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="M45" t="n">
-        <v>91.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O45" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~91 wks (overstock); consider ~624u</t>
+          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,55 +3063,55 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.85</v>
+        <v>14</v>
       </c>
       <c r="E46" t="n">
-        <v>8.68</v>
+        <v>11.2</v>
       </c>
       <c r="F46" t="n">
-        <v>2.17</v>
+        <v>2.8</v>
       </c>
       <c r="G46" t="n">
         <v>20</v>
       </c>
       <c r="H46" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="I46" t="n">
-        <v>36.1</v>
+        <v>49.6</v>
       </c>
       <c r="J46" t="n">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="K46" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L46" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M46" t="n">
-        <v>2.4</v>
+        <v>8.5</v>
       </c>
       <c r="N46" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks (cooling)</t>
+          <t>BUY ~24u (4cs) - sells in ~8 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3121,29 +3121,29 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>9.33</v>
       </c>
       <c r="E47" t="n">
-        <v>9.82</v>
+        <v>8.01</v>
       </c>
       <c r="F47" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H47" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I47" t="n">
-        <v>23.7</v>
+        <v>51.3</v>
       </c>
       <c r="J47" t="n">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="K47" t="n">
         <v>150</v>
@@ -3152,24 +3152,24 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>34.2</v>
+        <v>35.3</v>
       </c>
       <c r="N47" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~34 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~35 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
+          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3183,25 +3183,25 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>9.33</v>
+        <v>11</v>
       </c>
       <c r="E48" t="n">
-        <v>8.01</v>
+        <v>9.82</v>
       </c>
       <c r="F48" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="G48" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H48" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="I48" t="n">
-        <v>49.1</v>
+        <v>23.9</v>
       </c>
       <c r="J48" t="n">
-        <v>158</v>
+        <v>88</v>
       </c>
       <c r="K48" t="n">
         <v>150</v>
@@ -3210,17 +3210,17 @@
         <v>150</v>
       </c>
       <c r="M48" t="n">
-        <v>53.8</v>
+        <v>46.1</v>
       </c>
       <c r="N48" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O48" t="n">
         <v>4</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~54 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~46 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3253,13 +3253,13 @@
         <v>15</v>
       </c>
       <c r="H49" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="I49" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="J49" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K49" t="n">
         <v>40</v>
@@ -3268,24 +3268,24 @@
         <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>25.5</v>
+        <v>21.7</v>
       </c>
       <c r="N49" t="n">
         <v>48</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~26 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 40u = ~22 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
+          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3299,51 +3299,51 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>10.58</v>
       </c>
       <c r="E50" t="n">
-        <v>9.82</v>
+        <v>7.06</v>
       </c>
       <c r="F50" t="n">
-        <v>1.18</v>
+        <v>3.53</v>
       </c>
       <c r="G50" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="H50" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="I50" t="n">
-        <v>25.3</v>
+        <v>35.7</v>
       </c>
       <c r="J50" t="n">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="K50" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="L50" t="n">
-        <v>150</v>
+        <v>12</v>
       </c>
       <c r="M50" t="n">
-        <v>61</v>
+        <v>10.2</v>
       </c>
       <c r="N50" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~61 wks (overstock); consider ~150u</t>
+          <t>BUY ~12u (2cs) - sells in ~10 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3353,48 +3353,48 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.58</v>
+        <v>10.03</v>
       </c>
       <c r="E51" t="n">
-        <v>7.06</v>
+        <v>9.15</v>
       </c>
       <c r="F51" t="n">
-        <v>3.53</v>
+        <v>0.88</v>
       </c>
       <c r="G51" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>34.4</v>
+        <v>13.1</v>
       </c>
       <c r="J51" t="n">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="K51" t="n">
-        <v>12</v>
+        <v>624</v>
       </c>
       <c r="L51" t="n">
-        <v>12</v>
+        <v>624</v>
       </c>
       <c r="M51" t="n">
-        <v>18.7</v>
+        <v>125.4</v>
       </c>
       <c r="N51" t="n">
         <v>46</v>
       </c>
       <c r="O51" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 12u = ~19 wks (overstock); consider ~12u</t>
+          <t>CAUTION - 624u = ~125 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="I52" t="n">
         <v>17.6</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>482.6</v>
+        <v>447.4</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~483 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~447 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
         <v>150</v>
       </c>
       <c r="M53" t="n">
-        <v>198.9</v>
+        <v>184.4</v>
       </c>
       <c r="N53" t="n">
         <v>55</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~199 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~184 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
         <v>60</v>
       </c>
       <c r="M59" t="n">
-        <v>205.1</v>
+        <v>190.2</v>
       </c>
       <c r="N59" t="n">
         <v>48</v>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~205 wks (overstock); consider ~60u</t>
+          <t>CAUTION - 60u = ~190 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>101</v>
+        <v>90.5</v>
       </c>
       <c r="I2" t="n">
-        <v>4.6</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>416</v>
+        <v>509</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>392</v>
+        <v>216</v>
       </c>
       <c r="M2" t="n">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~392u (196cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~216u (108cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -585,32 +585,32 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>57.7</v>
+        <v>52.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
       </c>
       <c r="L3" t="n">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BUY ~248u (124cs) - sells in ~4 wks</t>
+          <t>BUY ~208u (104cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>22.4</v>
+        <v>21.4</v>
       </c>
       <c r="I4" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M4" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~58u (29cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~62u (31cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>28</v>
+        <v>25.6</v>
       </c>
       <c r="I5" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="J5" t="n">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -716,17 +716,17 @@
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BUY ~40u (20cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~40u (20cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>17.9</v>
+        <v>16.6</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -774,17 +774,17 @@
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~50u (25cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~50u (25cs) - sells in ~3 wks</t>
         </is>
       </c>
     </row>
@@ -817,13 +817,13 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I7" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="J7" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K7" t="n">
         <v>2</v>
@@ -838,7 +838,7 @@
         <v>42</v>
       </c>
       <c r="O7" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -875,13 +875,13 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="J8" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K8" t="n">
         <v>2</v>
@@ -896,7 +896,7 @@
         <v>44</v>
       </c>
       <c r="O8" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -933,13 +933,13 @@
         <v>22</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="I9" t="n">
-        <v>10.5</v>
+        <v>10.1</v>
       </c>
       <c r="J9" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
@@ -954,7 +954,7 @@
         <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -975,55 +975,55 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.7</v>
+        <v>10.5</v>
       </c>
       <c r="E10" t="n">
-        <v>21.7</v>
+        <v>9.06</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H10" t="n">
-        <v>9.300000000000001</v>
+        <v>24.7</v>
       </c>
       <c r="I10" t="n">
-        <v>9.4</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2</v>
+        <v>25.2</v>
       </c>
       <c r="N10" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O10" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1033,48 +1033,48 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.5</v>
+        <v>25.7</v>
       </c>
       <c r="E11" t="n">
-        <v>9.06</v>
+        <v>21.7</v>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>26.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="K11" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>23.9</v>
+        <v>0.2</v>
       </c>
       <c r="N11" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O11" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~24 wks (overstock); consider ~624u</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
@@ -1107,13 +1107,13 @@
         <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>21.2</v>
+        <v>22.5</v>
       </c>
       <c r="I12" t="n">
-        <v>7.1</v>
+        <v>5.6</v>
       </c>
       <c r="J12" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="K12" t="n">
         <v>624</v>
@@ -1122,17 +1122,17 @@
         <v>624</v>
       </c>
       <c r="M12" t="n">
-        <v>29.4</v>
+        <v>27.7</v>
       </c>
       <c r="N12" t="n">
         <v>45</v>
       </c>
       <c r="O12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~29 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~28 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
         <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>10.7</v>
+        <v>10.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="J13" t="n">
         <v>60</v>
@@ -1177,20 +1177,20 @@
         <v>24</v>
       </c>
       <c r="L13" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="N13" t="n">
         <v>44</v>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~3 wks (cooling)</t>
+          <t>BUY ~24u (4cs) - sells in ~2 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -1226,10 +1226,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>17.4</v>
+        <v>16.8</v>
       </c>
       <c r="J14" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
@@ -1281,32 +1281,32 @@
         <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>7.3</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="J15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N15" t="n">
         <v>50</v>
       </c>
       <c r="O15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~12u (6cs) - sells in ~2 wks</t>
+          <t>BUY ~10u (5cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1339,32 +1339,32 @@
         <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>12</v>
+        <v>11.4</v>
       </c>
       <c r="I16" t="n">
         <v>2.7</v>
       </c>
       <c r="J16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K16" t="n">
         <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="N16" t="n">
         <v>45</v>
       </c>
       <c r="O16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~7 wks (rising into season)</t>
+          <t>BUY ~78u (13cs) - sells in ~7 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1397,13 +1397,13 @@
         <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>15.7</v>
+        <v>15</v>
       </c>
       <c r="I17" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="J17" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="K17" t="n">
         <v>624</v>
@@ -1412,24 +1412,24 @@
         <v>624</v>
       </c>
       <c r="M17" t="n">
-        <v>39.7</v>
+        <v>41.6</v>
       </c>
       <c r="N17" t="n">
         <v>45</v>
       </c>
       <c r="O17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,55 +1439,55 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E18" t="n">
-        <v>9.9</v>
+        <v>9.06</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>10.2</v>
+        <v>13.3</v>
       </c>
       <c r="I18" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="K18" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L18" t="n">
-        <v>30</v>
+        <v>624</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>46.9</v>
       </c>
       <c r="N18" t="n">
         <v>45</v>
       </c>
       <c r="O18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~3 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~47 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,55 +1497,55 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>9.06</v>
+        <v>9.9</v>
       </c>
       <c r="F19" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H19" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="I19" t="n">
-        <v>8.6</v>
+        <v>11.3</v>
       </c>
       <c r="J19" t="n">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="K19" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>624</v>
+        <v>18</v>
       </c>
       <c r="M19" t="n">
-        <v>44.5</v>
+        <v>2.1</v>
       </c>
       <c r="N19" t="n">
         <v>45</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~44 wks (overstock); consider ~624u</t>
+          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1559,51 +1559,51 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>18.02</v>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>13.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>10.9</v>
+        <v>9.1</v>
       </c>
       <c r="J20" t="n">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="K20" t="n">
-        <v>624</v>
+        <v>40</v>
       </c>
       <c r="L20" t="n">
-        <v>624</v>
+        <v>40</v>
       </c>
       <c r="M20" t="n">
-        <v>45.1</v>
+        <v>4.5</v>
       </c>
       <c r="N20" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~45 wks (overstock); consider ~624u</t>
+          <t>BUY ~40u (10cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,55 +1613,55 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16.67</v>
+        <v>10.5</v>
       </c>
       <c r="E21" t="n">
-        <v>13.34</v>
+        <v>9.06</v>
       </c>
       <c r="F21" t="n">
-        <v>3.33</v>
+        <v>1.44</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H21" t="n">
-        <v>5.6</v>
+        <v>12</v>
       </c>
       <c r="I21" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="J21" t="n">
-        <v>33</v>
+        <v>109</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L21" t="n">
-        <v>15</v>
+        <v>624</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7</v>
+        <v>52.1</v>
       </c>
       <c r="N21" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~15u (5cs) - sells in ~3 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,55 +1671,55 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14</v>
+        <v>16.67</v>
       </c>
       <c r="E22" t="n">
-        <v>11.2</v>
+        <v>13.34</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="G22" t="n">
         <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>6.9</v>
+        <v>4.8</v>
       </c>
       <c r="I22" t="n">
-        <v>7.3</v>
+        <v>10.7</v>
       </c>
       <c r="J22" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K22" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L22" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>4.4</v>
+        <v>1.3</v>
       </c>
       <c r="N22" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O22" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~6u (2cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,48 +1729,48 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D23" t="n">
+        <v>14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G23" t="n">
         <v>20</v>
       </c>
-      <c r="E23" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G23" t="n">
-        <v>10</v>
-      </c>
       <c r="H23" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="I23" t="n">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="J23" t="n">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="K23" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="L23" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="M23" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N23" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1803,13 +1803,13 @@
         <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="I24" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K24" t="n">
         <v>6</v>
@@ -1818,24 +1818,24 @@
         <v>36</v>
       </c>
       <c r="M24" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="N24" t="n">
         <v>46</v>
       </c>
       <c r="O24" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,48 +1845,48 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E25" t="n">
-        <v>8.4</v>
+        <v>8.68</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="G25" t="n">
         <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>8.1</v>
+        <v>6.7</v>
       </c>
       <c r="I25" t="n">
-        <v>4.4</v>
+        <v>14.1</v>
       </c>
       <c r="J25" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="K25" t="n">
         <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>4.5</v>
+        <v>0.9</v>
       </c>
       <c r="N25" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O25" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1919,13 +1919,13 @@
         <v>24</v>
       </c>
       <c r="H26" t="n">
-        <v>8.1</v>
+        <v>7.1</v>
       </c>
       <c r="I26" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="K26" t="n">
         <v>6</v>
@@ -1934,24 +1934,24 @@
         <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="N26" t="n">
         <v>45</v>
       </c>
       <c r="O26" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~4 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E27" t="n">
-        <v>8.68</v>
+        <v>8.4</v>
       </c>
       <c r="F27" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G27" t="n">
         <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="I27" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="K27" t="n">
         <v>6</v>
       </c>
       <c r="L27" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="M27" t="n">
-        <v>0.9</v>
+        <v>5.1</v>
       </c>
       <c r="N27" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O27" t="n">
         <v>15</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2038,10 +2038,10 @@
         <v>6.5</v>
       </c>
       <c r="I28" t="n">
-        <v>19.5</v>
+        <v>29.8</v>
       </c>
       <c r="J28" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K28" t="n">
         <v>6</v>
@@ -2060,14 +2060,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9.33</v>
+        <v>10.85</v>
       </c>
       <c r="E29" t="n">
-        <v>8.01</v>
+        <v>8.68</v>
       </c>
       <c r="F29" t="n">
-        <v>1.32</v>
+        <v>2.17</v>
       </c>
       <c r="G29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>150</v>
+      </c>
+      <c r="K29" t="n">
+        <v>6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>46</v>
+      </c>
+      <c r="O29" t="n">
         <v>14</v>
       </c>
-      <c r="H29" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="I29" t="n">
-        <v>10</v>
-      </c>
-      <c r="J29" t="n">
-        <v>64</v>
-      </c>
-      <c r="K29" t="n">
-        <v>150</v>
-      </c>
-      <c r="L29" t="n">
-        <v>150</v>
-      </c>
-      <c r="M29" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="N29" t="n">
-        <v>50</v>
-      </c>
-      <c r="O29" t="n">
-        <v>13</v>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~16 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,29 +2135,29 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.5</v>
+        <v>10.03</v>
       </c>
       <c r="E30" t="n">
-        <v>9.06</v>
+        <v>9.15</v>
       </c>
       <c r="F30" t="n">
-        <v>1.44</v>
+        <v>0.88</v>
       </c>
       <c r="G30" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>8.800000000000001</v>
+        <v>15.2</v>
       </c>
       <c r="I30" t="n">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="J30" t="n">
-        <v>58</v>
+        <v>157</v>
       </c>
       <c r="K30" t="n">
         <v>624</v>
@@ -2166,24 +2166,24 @@
         <v>624</v>
       </c>
       <c r="M30" t="n">
-        <v>71.3</v>
+        <v>41.2</v>
       </c>
       <c r="N30" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O30" t="n">
         <v>13</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~71 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~41 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2193,55 +2193,55 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E31" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F31" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G31" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H31" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="I31" t="n">
-        <v>26.5</v>
+        <v>7.7</v>
       </c>
       <c r="J31" t="n">
-        <v>127</v>
+        <v>66</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>72.8</v>
       </c>
       <c r="N31" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~73 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,48 +2251,48 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.03</v>
+        <v>9.33</v>
       </c>
       <c r="E32" t="n">
-        <v>9.15</v>
+        <v>8.01</v>
       </c>
       <c r="F32" t="n">
-        <v>0.88</v>
+        <v>1.32</v>
       </c>
       <c r="G32" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>14.6</v>
+        <v>8.4</v>
       </c>
       <c r="I32" t="n">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="J32" t="n">
-        <v>167</v>
+        <v>63</v>
       </c>
       <c r="K32" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L32" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M32" t="n">
-        <v>42.7</v>
+        <v>18</v>
       </c>
       <c r="N32" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O32" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2328,10 +2328,10 @@
         <v>9</v>
       </c>
       <c r="I33" t="n">
-        <v>18.9</v>
+        <v>17.2</v>
       </c>
       <c r="J33" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="K33" t="n">
         <v>150</v>
@@ -2340,7 +2340,7 @@
         <v>150</v>
       </c>
       <c r="M33" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N33" t="n">
         <v>55</v>
@@ -2383,13 +2383,13 @@
         <v>9</v>
       </c>
       <c r="H34" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="I34" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="K34" t="n">
         <v>624</v>
@@ -2398,7 +2398,7 @@
         <v>624</v>
       </c>
       <c r="M34" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="N34" t="n">
         <v>46</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2441,13 +2441,13 @@
         <v>7</v>
       </c>
       <c r="H35" t="n">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="K35" t="n">
         <v>84</v>
@@ -2456,7 +2456,7 @@
         <v>84</v>
       </c>
       <c r="M35" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="N35" t="n">
         <v>44</v>
@@ -2499,13 +2499,13 @@
         <v>11</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>13.2</v>
+        <v>12</v>
       </c>
       <c r="J36" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K36" t="n">
         <v>150</v>
@@ -2514,7 +2514,7 @@
         <v>150</v>
       </c>
       <c r="M36" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="N36" t="n">
         <v>55</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~16 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2560,10 +2560,10 @@
         <v>11.2</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="J37" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="K37" t="n">
         <v>624</v>
@@ -2572,7 +2572,7 @@
         <v>624</v>
       </c>
       <c r="M37" t="n">
-        <v>55.7</v>
+        <v>55.6</v>
       </c>
       <c r="N37" t="n">
         <v>46</v>
@@ -2589,7 +2589,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2599,29 +2599,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8.67</v>
+        <v>10.85</v>
       </c>
       <c r="E38" t="n">
-        <v>6.57</v>
+        <v>8.68</v>
       </c>
       <c r="F38" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="G38" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H38" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="I38" t="n">
-        <v>12.3</v>
+        <v>35</v>
       </c>
       <c r="J38" t="n">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
@@ -2630,24 +2630,24 @@
         <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="N38" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,48 +2657,48 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9.67</v>
+        <v>12</v>
       </c>
       <c r="E39" t="n">
-        <v>7.57</v>
+        <v>11.2</v>
       </c>
       <c r="F39" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="G39" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H39" t="n">
-        <v>4.8</v>
+        <v>10.7</v>
       </c>
       <c r="I39" t="n">
-        <v>12.3</v>
+        <v>7.8</v>
       </c>
       <c r="J39" t="n">
-        <v>55</v>
+        <v>119</v>
       </c>
       <c r="K39" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="L39" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="M39" t="n">
-        <v>1.3</v>
+        <v>7.8</v>
       </c>
       <c r="N39" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2731,13 +2731,13 @@
         <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="I40" t="n">
-        <v>12.3</v>
+        <v>8.9</v>
       </c>
       <c r="J40" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="K40" t="n">
         <v>6</v>
@@ -2746,13 +2746,13 @@
         <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N40" t="n">
         <v>47</v>
       </c>
       <c r="O40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,29 +2773,29 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.85</v>
+        <v>9.67</v>
       </c>
       <c r="E41" t="n">
-        <v>8.68</v>
+        <v>7.57</v>
       </c>
       <c r="F41" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G41" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I41" t="n">
-        <v>34.3</v>
+        <v>8.9</v>
       </c>
       <c r="J41" t="n">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="K41" t="n">
         <v>6</v>
@@ -2814,14 +2814,14 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2831,38 +2831,38 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>8.67</v>
       </c>
       <c r="E42" t="n">
-        <v>9.82</v>
+        <v>6.57</v>
       </c>
       <c r="F42" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="G42" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H42" t="n">
-        <v>7.2</v>
+        <v>4.3</v>
       </c>
       <c r="I42" t="n">
-        <v>22.5</v>
+        <v>8.9</v>
       </c>
       <c r="J42" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="K42" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L42" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>20.8</v>
+        <v>1.4</v>
       </c>
       <c r="N42" t="n">
         <v>45</v>
@@ -2872,14 +2872,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,55 +2889,55 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>26.52</v>
+        <v>11</v>
       </c>
       <c r="E43" t="n">
-        <v>24.2</v>
+        <v>9.82</v>
       </c>
       <c r="F43" t="n">
-        <v>2.33</v>
+        <v>1.18</v>
       </c>
       <c r="G43" t="n">
+        <v>11</v>
+      </c>
+      <c r="H43" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>20</v>
+      </c>
+      <c r="J43" t="n">
+        <v>91</v>
+      </c>
+      <c r="K43" t="n">
+        <v>150</v>
+      </c>
+      <c r="L43" t="n">
+        <v>150</v>
+      </c>
+      <c r="M43" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="N43" t="n">
+        <v>45</v>
+      </c>
+      <c r="O43" t="n">
         <v>9</v>
       </c>
-      <c r="H43" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I43" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="J43" t="n">
-        <v>62</v>
-      </c>
-      <c r="K43" t="n">
-        <v>208</v>
-      </c>
-      <c r="L43" t="n">
-        <v>208</v>
-      </c>
-      <c r="M43" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="N43" t="n">
-        <v>44</v>
-      </c>
-      <c r="O43" t="n">
-        <v>8</v>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~60 wks (overstock); consider ~208u</t>
+          <t>CAUTION - 150u = ~20 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2963,13 +2963,13 @@
         <v>7</v>
       </c>
       <c r="H44" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="I44" t="n">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="J44" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="K44" t="n">
         <v>84</v>
@@ -2978,7 +2978,7 @@
         <v>84</v>
       </c>
       <c r="M44" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="N44" t="n">
         <v>44</v>
@@ -2995,7 +2995,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E45" t="n">
         <v>11.2</v>
       </c>
       <c r="F45" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="G45" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>10.2</v>
+        <v>2.8</v>
       </c>
       <c r="I45" t="n">
-        <v>10.1</v>
+        <v>46.8</v>
       </c>
       <c r="J45" t="n">
-        <v>147</v>
+        <v>72</v>
       </c>
       <c r="K45" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="L45" t="n">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="M45" t="n">
-        <v>8.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N45" t="n">
         <v>44</v>
@@ -3046,14 +3046,14 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
+          <t>BUY ~24u (4cs) - sells in ~9 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,48 +3063,48 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D46" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="E46" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G46" t="n">
+        <v>9</v>
+      </c>
+      <c r="H46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I46" t="n">
         <v>14</v>
       </c>
-      <c r="E46" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F46" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G46" t="n">
-        <v>20</v>
-      </c>
-      <c r="H46" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I46" t="n">
-        <v>49.6</v>
-      </c>
       <c r="J46" t="n">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="K46" t="n">
-        <v>24</v>
+        <v>208</v>
       </c>
       <c r="L46" t="n">
-        <v>24</v>
+        <v>208</v>
       </c>
       <c r="M46" t="n">
-        <v>8.5</v>
+        <v>67</v>
       </c>
       <c r="N46" t="n">
         <v>44</v>
       </c>
       <c r="O46" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~8 wks (rising into season)</t>
+          <t>CAUTION - 208u = ~67 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
@@ -3137,13 +3137,13 @@
         <v>14</v>
       </c>
       <c r="H47" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I47" t="n">
-        <v>51.3</v>
+        <v>51.7</v>
       </c>
       <c r="J47" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K47" t="n">
         <v>150</v>
@@ -3152,24 +3152,24 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>35.3</v>
+        <v>37.9</v>
       </c>
       <c r="N47" t="n">
         <v>50</v>
       </c>
       <c r="O47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~35 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~38 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3179,48 +3179,48 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>10.03</v>
       </c>
       <c r="E48" t="n">
-        <v>9.82</v>
+        <v>9.15</v>
       </c>
       <c r="F48" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="G48" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H48" t="n">
-        <v>3.3</v>
+        <v>5.3</v>
       </c>
       <c r="I48" t="n">
-        <v>23.9</v>
+        <v>12.8</v>
       </c>
       <c r="J48" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="K48" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L48" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M48" t="n">
-        <v>46.1</v>
+        <v>118.4</v>
       </c>
       <c r="N48" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~46 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 624u = ~118 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3253,10 +3253,10 @@
         <v>15</v>
       </c>
       <c r="H49" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="I49" t="n">
-        <v>23.2</v>
+        <v>25.2</v>
       </c>
       <c r="J49" t="n">
         <v>40</v>
@@ -3268,24 +3268,24 @@
         <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>21.7</v>
+        <v>25.2</v>
       </c>
       <c r="N49" t="n">
         <v>48</v>
       </c>
       <c r="O49" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~22 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 40u = ~25 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
+          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3299,51 +3299,51 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.58</v>
+        <v>11</v>
       </c>
       <c r="E50" t="n">
-        <v>7.06</v>
+        <v>9.82</v>
       </c>
       <c r="F50" t="n">
-        <v>3.53</v>
+        <v>1.18</v>
       </c>
       <c r="G50" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H50" t="n">
-        <v>1.2</v>
+        <v>2.9</v>
       </c>
       <c r="I50" t="n">
-        <v>35.7</v>
+        <v>25.5</v>
       </c>
       <c r="J50" t="n">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="K50" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="L50" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="M50" t="n">
-        <v>10.2</v>
+        <v>52.4</v>
       </c>
       <c r="N50" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~10 wks (rising into season)</t>
+          <t>CAUTION - 150u = ~52 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3353,48 +3353,48 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.03</v>
+        <v>10.58</v>
       </c>
       <c r="E51" t="n">
-        <v>9.15</v>
+        <v>7.06</v>
       </c>
       <c r="F51" t="n">
-        <v>0.88</v>
+        <v>3.53</v>
       </c>
       <c r="G51" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>0.6</v>
       </c>
       <c r="I51" t="n">
-        <v>13.1</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>93</v>
+        <v>30</v>
       </c>
       <c r="K51" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="L51" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M51" t="n">
-        <v>125.4</v>
+        <v>20.4</v>
       </c>
       <c r="N51" t="n">
         <v>46</v>
       </c>
       <c r="O51" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~125 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 12u = ~20 wks (overstock); consider ~12u</t>
         </is>
       </c>
     </row>
@@ -3430,10 +3430,10 @@
         <v>1.4</v>
       </c>
       <c r="I52" t="n">
-        <v>17.6</v>
+        <v>15.2</v>
       </c>
       <c r="J52" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K52" t="n">
         <v>624</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>447.4</v>
+        <v>431.3</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~447 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~431 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3485,10 +3485,10 @@
         <v>11</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I53" t="n">
-        <v>114.1</v>
+        <v>147.2</v>
       </c>
       <c r="J53" t="n">
         <v>87</v>
@@ -3500,7 +3500,7 @@
         <v>150</v>
       </c>
       <c r="M53" t="n">
-        <v>184.4</v>
+        <v>253.8</v>
       </c>
       <c r="N53" t="n">
         <v>55</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~184 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~254 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3803,13 +3803,13 @@
         <v>9</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I59" t="n">
-        <v>930.5</v>
+        <v>587.1</v>
       </c>
       <c r="J59" t="n">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K59" t="n">
         <v>60</v>
@@ -3818,7 +3818,7 @@
         <v>60</v>
       </c>
       <c r="M59" t="n">
-        <v>190.2</v>
+        <v>128.6</v>
       </c>
       <c r="N59" t="n">
         <v>48</v>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~190 wks (overstock); consider ~60u</t>
+          <t>CAUTION - 60u = ~129 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,19 +527,19 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>90.5</v>
+        <v>86.5</v>
       </c>
       <c r="I2" t="n">
         <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>509</v>
+        <v>499</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="M2" t="n">
         <v>2.4</v>
@@ -548,11 +548,11 @@
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~216u (108cs) - sells in ~2 wks</t>
+          <t>BUY ~208u (104cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>52.1</v>
+        <v>49.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,19 +643,19 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
         <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M4" t="n">
         <v>2.9</v>
@@ -664,11 +664,11 @@
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~62u (31cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~60u (30cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>25.6</v>
+        <v>25.2</v>
       </c>
       <c r="I5" t="n">
         <v>11.6</v>
       </c>
       <c r="J5" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -780,7 +780,7 @@
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -801,48 +801,48 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>26.5</v>
+        <v>10.5</v>
       </c>
       <c r="E7" t="n">
-        <v>21.32</v>
+        <v>9.06</v>
       </c>
       <c r="F7" t="n">
-        <v>5.18</v>
+        <v>1.44</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>7.4</v>
+        <v>24.8</v>
       </c>
       <c r="I7" t="n">
-        <v>10.1</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3</v>
+        <v>25.2</v>
       </c>
       <c r="N7" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -875,10 +875,10 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I8" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="J8" t="n">
         <v>75</v>
@@ -896,7 +896,7 @@
         <v>44</v>
       </c>
       <c r="O8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23.4</v>
+        <v>26.5</v>
       </c>
       <c r="E9" t="n">
-        <v>18.22</v>
+        <v>21.32</v>
       </c>
       <c r="F9" t="n">
         <v>5.18</v>
       </c>
       <c r="G9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="I9" t="n">
-        <v>10.1</v>
+        <v>10.6</v>
       </c>
       <c r="J9" t="n">
         <v>75</v>
@@ -951,10 +951,10 @@
         <v>0.3</v>
       </c>
       <c r="N9" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="O9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -965,7 +965,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -975,48 +975,48 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.5</v>
+        <v>23.4</v>
       </c>
       <c r="E10" t="n">
-        <v>9.06</v>
+        <v>18.22</v>
       </c>
       <c r="F10" t="n">
-        <v>1.44</v>
+        <v>5.18</v>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H10" t="n">
-        <v>24.7</v>
+        <v>7</v>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>10.6</v>
       </c>
       <c r="J10" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="K10" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="M10" t="n">
-        <v>25.2</v>
+        <v>0.3</v>
       </c>
       <c r="N10" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="O10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
@@ -1049,10 +1049,10 @@
         <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="I11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="J11" t="n">
         <v>81</v>
@@ -1064,13 +1064,13 @@
         <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N11" t="n">
         <v>50</v>
       </c>
       <c r="O11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1107,13 +1107,13 @@
         <v>14</v>
       </c>
       <c r="H12" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="I12" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J12" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="K12" t="n">
         <v>624</v>
@@ -1122,7 +1122,7 @@
         <v>624</v>
       </c>
       <c r="M12" t="n">
-        <v>27.7</v>
+        <v>28</v>
       </c>
       <c r="N12" t="n">
         <v>45</v>
@@ -1139,7 +1139,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,48 +1149,48 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14</v>
+        <v>25.7</v>
       </c>
       <c r="E13" t="n">
-        <v>11.2</v>
+        <v>21.7</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H13" t="n">
-        <v>10.2</v>
+        <v>7.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4.5</v>
+        <v>6.4</v>
       </c>
       <c r="J13" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="K13" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M13" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="N13" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O13" t="n">
         <v>29</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~2 wks (cooling)</t>
+          <t>BUY ~12u (6cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -1226,10 +1226,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="J14" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
@@ -1255,7 +1255,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,48 +1265,48 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.7</v>
+        <v>14</v>
       </c>
       <c r="E15" t="n">
-        <v>21.7</v>
+        <v>11.2</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>10.2</v>
       </c>
       <c r="I15" t="n">
-        <v>6.7</v>
+        <v>4.5</v>
       </c>
       <c r="J15" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="L15" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="N15" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O15" t="n">
         <v>28</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~10u (5cs) - sells in ~1 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~2 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="I16" t="n">
         <v>2.7</v>
@@ -1354,13 +1354,13 @@
         <v>78</v>
       </c>
       <c r="M16" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="N16" t="n">
         <v>45</v>
       </c>
       <c r="O16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1397,13 +1397,13 @@
         <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I17" t="n">
         <v>4.4</v>
       </c>
       <c r="J17" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K17" t="n">
         <v>624</v>
@@ -1412,17 +1412,17 @@
         <v>624</v>
       </c>
       <c r="M17" t="n">
-        <v>41.6</v>
+        <v>43</v>
       </c>
       <c r="N17" t="n">
         <v>45</v>
       </c>
       <c r="O17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1455,10 +1455,10 @@
         <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>13.3</v>
+        <v>12.8</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="J18" t="n">
         <v>133</v>
@@ -1470,17 +1470,17 @@
         <v>624</v>
       </c>
       <c r="M18" t="n">
-        <v>46.9</v>
+        <v>48.7</v>
       </c>
       <c r="N18" t="n">
         <v>45</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~47 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
         <v>17</v>
       </c>
       <c r="H19" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="I19" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="J19" t="n">
         <v>54</v>
@@ -1528,7 +1528,7 @@
         <v>18</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N19" t="n">
         <v>45</v>
@@ -1545,7 +1545,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1559,51 +1559,51 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="E20" t="n">
-        <v>18.02</v>
+        <v>9.06</v>
       </c>
       <c r="F20" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H20" t="n">
-        <v>8.800000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="I20" t="n">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="J20" t="n">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="K20" t="n">
-        <v>40</v>
+        <v>624</v>
       </c>
       <c r="L20" t="n">
-        <v>40</v>
+        <v>624</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5</v>
+        <v>51.6</v>
       </c>
       <c r="N20" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O20" t="n">
         <v>17</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~4 wks</t>
+          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1617,51 +1617,51 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>9.06</v>
+        <v>18.02</v>
       </c>
       <c r="F21" t="n">
-        <v>1.44</v>
+        <v>1.98</v>
       </c>
       <c r="G21" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>12</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="K21" t="n">
-        <v>624</v>
+        <v>40</v>
       </c>
       <c r="L21" t="n">
-        <v>624</v>
+        <v>40</v>
       </c>
       <c r="M21" t="n">
-        <v>52.1</v>
+        <v>4.8</v>
       </c>
       <c r="N21" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
+          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,55 +1671,55 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.67</v>
+        <v>14</v>
       </c>
       <c r="E22" t="n">
-        <v>13.34</v>
+        <v>11.2</v>
       </c>
       <c r="F22" t="n">
-        <v>3.33</v>
+        <v>2.8</v>
       </c>
       <c r="G22" t="n">
         <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="I22" t="n">
-        <v>10.7</v>
+        <v>8.6</v>
       </c>
       <c r="J22" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M22" t="n">
-        <v>1.3</v>
+        <v>4.2</v>
       </c>
       <c r="N22" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O22" t="n">
         <v>16</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUY ~6u (2cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~24u (4cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,55 +1729,55 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14</v>
+        <v>16.67</v>
       </c>
       <c r="E23" t="n">
-        <v>11.2</v>
+        <v>13.34</v>
       </c>
       <c r="F23" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="G23" t="n">
         <v>20</v>
       </c>
       <c r="H23" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
-        <v>8.5</v>
+        <v>9.9</v>
       </c>
       <c r="J23" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K23" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>4.2</v>
+        <v>1.3</v>
       </c>
       <c r="N23" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~6u (2cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,55 +1787,55 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9.67</v>
+        <v>10.85</v>
       </c>
       <c r="E24" t="n">
-        <v>7.57</v>
+        <v>8.68</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="G24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
       <c r="I24" t="n">
-        <v>3</v>
+        <v>18.7</v>
       </c>
       <c r="J24" t="n">
-        <v>21</v>
+        <v>150</v>
       </c>
       <c r="K24" t="n">
         <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
-        <v>5.1</v>
+        <v>1</v>
       </c>
       <c r="N24" t="n">
         <v>46</v>
       </c>
       <c r="O24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,48 +1845,48 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.85</v>
+        <v>10.03</v>
       </c>
       <c r="E25" t="n">
-        <v>8.68</v>
+        <v>9.15</v>
       </c>
       <c r="F25" t="n">
-        <v>2.17</v>
+        <v>0.88</v>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>6.7</v>
+        <v>15.5</v>
       </c>
       <c r="I25" t="n">
-        <v>14.1</v>
+        <v>6.9</v>
       </c>
       <c r="J25" t="n">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9</v>
+        <v>40.2</v>
       </c>
       <c r="N25" t="n">
         <v>46</v>
       </c>
       <c r="O25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1919,10 +1919,10 @@
         <v>24</v>
       </c>
       <c r="H26" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="I26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
         <v>21</v>
@@ -1934,17 +1934,17 @@
         <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="N26" t="n">
         <v>45</v>
       </c>
       <c r="O26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
@@ -1977,10 +1977,10 @@
         <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="J27" t="n">
         <v>21</v>
@@ -1992,24 +1992,24 @@
         <v>36</v>
       </c>
       <c r="M27" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="N27" t="n">
         <v>47</v>
       </c>
       <c r="O27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,38 +2019,38 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.85</v>
+        <v>9.67</v>
       </c>
       <c r="E28" t="n">
-        <v>8.68</v>
+        <v>7.57</v>
       </c>
       <c r="F28" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H28" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="I28" t="n">
-        <v>29.8</v>
+        <v>3.2</v>
       </c>
       <c r="J28" t="n">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="K28" t="n">
         <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="N28" t="n">
         <v>46</v>
@@ -2060,14 +2060,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~36u (6cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2093,13 +2093,13 @@
         <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="I29" t="n">
-        <v>18.7</v>
+        <v>29.8</v>
       </c>
       <c r="J29" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K29" t="n">
         <v>6</v>
@@ -2108,7 +2108,7 @@
         <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N29" t="n">
         <v>46</v>
@@ -2118,14 +2118,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,48 +2135,48 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.03</v>
+        <v>10.85</v>
       </c>
       <c r="E30" t="n">
-        <v>9.15</v>
+        <v>8.68</v>
       </c>
       <c r="F30" t="n">
-        <v>0.88</v>
+        <v>2.17</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H30" t="n">
-        <v>15.2</v>
+        <v>6.6</v>
       </c>
       <c r="I30" t="n">
-        <v>7.3</v>
+        <v>14.4</v>
       </c>
       <c r="J30" t="n">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="K30" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>41.2</v>
+        <v>0.9</v>
       </c>
       <c r="N30" t="n">
         <v>46</v>
       </c>
       <c r="O30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~41 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -2209,13 +2209,13 @@
         <v>14</v>
       </c>
       <c r="H31" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="I31" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J31" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K31" t="n">
         <v>624</v>
@@ -2224,7 +2224,7 @@
         <v>624</v>
       </c>
       <c r="M31" t="n">
-        <v>72.8</v>
+        <v>73.8</v>
       </c>
       <c r="N31" t="n">
         <v>45</v>
@@ -2234,14 +2234,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~73 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~74 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,55 +2251,55 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.33</v>
+        <v>10.03</v>
       </c>
       <c r="E32" t="n">
-        <v>8.01</v>
+        <v>9.15</v>
       </c>
       <c r="F32" t="n">
-        <v>1.32</v>
+        <v>0.88</v>
       </c>
       <c r="G32" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="I32" t="n">
-        <v>9.9</v>
+        <v>9.6</v>
       </c>
       <c r="J32" t="n">
-        <v>63</v>
+        <v>177</v>
       </c>
       <c r="K32" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L32" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M32" t="n">
-        <v>18</v>
+        <v>48.2</v>
       </c>
       <c r="N32" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O32" t="n">
         <v>11</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2313,25 +2313,25 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>9.33</v>
       </c>
       <c r="E33" t="n">
-        <v>9.82</v>
+        <v>8.01</v>
       </c>
       <c r="F33" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="G33" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>10.4</v>
       </c>
       <c r="J33" t="n">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="K33" t="n">
         <v>150</v>
@@ -2340,24 +2340,24 @@
         <v>150</v>
       </c>
       <c r="M33" t="n">
-        <v>16.6</v>
+        <v>18.8</v>
       </c>
       <c r="N33" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="O33" t="n">
         <v>11</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,55 +2367,55 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F34" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H34" t="n">
-        <v>12.9</v>
+        <v>8.9</v>
       </c>
       <c r="I34" t="n">
-        <v>9.800000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="J34" t="n">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="K34" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L34" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M34" t="n">
-        <v>48.4</v>
+        <v>16.9</v>
       </c>
       <c r="N34" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O34" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2425,55 +2425,55 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12</v>
+        <v>10.03</v>
       </c>
       <c r="E35" t="n">
-        <v>11.2</v>
+        <v>9.15</v>
       </c>
       <c r="F35" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="G35" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H35" t="n">
-        <v>13.2</v>
+        <v>11.7</v>
       </c>
       <c r="I35" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>156</v>
       </c>
       <c r="K35" t="n">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="L35" t="n">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="M35" t="n">
-        <v>6.3</v>
+        <v>53.2</v>
       </c>
       <c r="N35" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O35" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~6 wks (cooling)</t>
+          <t>CAUTION - 624u = ~53 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,55 +2483,55 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E36" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F36" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G36" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H36" t="n">
-        <v>9.199999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="I36" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="J36" t="n">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="K36" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L36" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M36" t="n">
-        <v>16.4</v>
+        <v>6.7</v>
       </c>
       <c r="N36" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="O36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~16 wks (overstock); consider ~150u</t>
+          <t>BUY ~84u (14cs) - sells in ~7 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,48 +2541,48 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.03</v>
+        <v>12</v>
       </c>
       <c r="E37" t="n">
-        <v>9.15</v>
+        <v>11.2</v>
       </c>
       <c r="F37" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="G37" t="n">
+        <v>7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="I37" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>141</v>
+      </c>
+      <c r="K37" t="n">
+        <v>84</v>
+      </c>
+      <c r="L37" t="n">
+        <v>84</v>
+      </c>
+      <c r="M37" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N37" t="n">
+        <v>44</v>
+      </c>
+      <c r="O37" t="n">
         <v>9</v>
       </c>
-      <c r="H37" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="I37" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="J37" t="n">
-        <v>162</v>
-      </c>
-      <c r="K37" t="n">
-        <v>624</v>
-      </c>
-      <c r="L37" t="n">
-        <v>624</v>
-      </c>
-      <c r="M37" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="N37" t="n">
-        <v>46</v>
-      </c>
-      <c r="O37" t="n">
-        <v>10</v>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~56 wks (overstock); consider ~624u</t>
+          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,48 +2657,48 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12</v>
+        <v>9.67</v>
       </c>
       <c r="E39" t="n">
-        <v>11.2</v>
+        <v>7.57</v>
       </c>
       <c r="F39" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H39" t="n">
-        <v>10.7</v>
+        <v>4.2</v>
       </c>
       <c r="I39" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
-        <v>119</v>
+        <v>38</v>
       </c>
       <c r="K39" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>7.8</v>
+        <v>1.4</v>
       </c>
       <c r="N39" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O39" t="n">
         <v>9</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -2731,10 +2731,10 @@
         <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I40" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
         <v>38</v>
@@ -2763,7 +2763,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,48 +2773,48 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>9.67</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>7.57</v>
+        <v>9.82</v>
       </c>
       <c r="F41" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="G41" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H41" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="I41" t="n">
-        <v>8.9</v>
+        <v>20.4</v>
       </c>
       <c r="J41" t="n">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="K41" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L41" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M41" t="n">
-        <v>1.4</v>
+        <v>20.8</v>
       </c>
       <c r="N41" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O41" t="n">
         <v>9</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2847,10 +2847,10 @@
         <v>24</v>
       </c>
       <c r="H42" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I42" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
         <v>38</v>
@@ -2879,7 +2879,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2905,13 +2905,13 @@
         <v>11</v>
       </c>
       <c r="H43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="J43" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="K43" t="n">
         <v>150</v>
@@ -2920,10 +2920,10 @@
         <v>150</v>
       </c>
       <c r="M43" t="n">
-        <v>20.4</v>
+        <v>19.7</v>
       </c>
       <c r="N43" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O43" t="n">
         <v>9</v>
@@ -2937,7 +2937,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2963,13 +2963,13 @@
         <v>7</v>
       </c>
       <c r="H44" t="n">
-        <v>10.6</v>
+        <v>10.1</v>
       </c>
       <c r="I44" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>142</v>
+        <v>119</v>
       </c>
       <c r="K44" t="n">
         <v>84</v>
@@ -2978,7 +2978,7 @@
         <v>84</v>
       </c>
       <c r="M44" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="N44" t="n">
         <v>44</v>
@@ -2995,7 +2995,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3005,55 +3005,55 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D45" t="n">
+        <v>26.52</v>
+      </c>
+      <c r="E45" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="G45" t="n">
+        <v>9</v>
+      </c>
+      <c r="H45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I45" t="n">
         <v>14</v>
       </c>
-      <c r="E45" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G45" t="n">
-        <v>20</v>
-      </c>
-      <c r="H45" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="I45" t="n">
-        <v>46.8</v>
-      </c>
       <c r="J45" t="n">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="K45" t="n">
-        <v>24</v>
+        <v>208</v>
       </c>
       <c r="L45" t="n">
-        <v>24</v>
+        <v>208</v>
       </c>
       <c r="M45" t="n">
-        <v>8.699999999999999</v>
+        <v>68</v>
       </c>
       <c r="N45" t="n">
         <v>44</v>
       </c>
       <c r="O45" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~9 wks (rising into season)</t>
+          <t>CAUTION - 208u = ~68 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,38 +3063,38 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>26.52</v>
+        <v>14</v>
       </c>
       <c r="E46" t="n">
-        <v>24.2</v>
+        <v>11.2</v>
       </c>
       <c r="F46" t="n">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H46" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="I46" t="n">
-        <v>14</v>
+        <v>51.4</v>
       </c>
       <c r="J46" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="K46" t="n">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="L46" t="n">
-        <v>208</v>
+        <v>24</v>
       </c>
       <c r="M46" t="n">
-        <v>67</v>
+        <v>9.5</v>
       </c>
       <c r="N46" t="n">
         <v>44</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~67 wks (overstock); consider ~208u</t>
+          <t>BUY ~24u (4cs) - sells in ~10 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -3137,10 +3137,10 @@
         <v>14</v>
       </c>
       <c r="H47" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="I47" t="n">
-        <v>51.7</v>
+        <v>54.8</v>
       </c>
       <c r="J47" t="n">
         <v>156</v>
@@ -3152,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>37.9</v>
+        <v>40.2</v>
       </c>
       <c r="N47" t="n">
         <v>50</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~38 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~40 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3195,13 +3195,13 @@
         <v>9</v>
       </c>
       <c r="H48" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I48" t="n">
-        <v>12.8</v>
+        <v>12</v>
       </c>
       <c r="J48" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K48" t="n">
         <v>624</v>
@@ -3210,7 +3210,7 @@
         <v>624</v>
       </c>
       <c r="M48" t="n">
-        <v>118.4</v>
+        <v>114.8</v>
       </c>
       <c r="N48" t="n">
         <v>46</v>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~118 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~115 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3253,13 +3253,13 @@
         <v>15</v>
       </c>
       <c r="H49" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="I49" t="n">
-        <v>25.2</v>
+        <v>22.2</v>
       </c>
       <c r="J49" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K49" t="n">
         <v>40</v>
@@ -3268,7 +3268,7 @@
         <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>25.2</v>
+        <v>23</v>
       </c>
       <c r="N49" t="n">
         <v>48</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~25 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 40u = ~23 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
@@ -3311,10 +3311,10 @@
         <v>11</v>
       </c>
       <c r="H50" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="I50" t="n">
-        <v>25.5</v>
+        <v>26.6</v>
       </c>
       <c r="J50" t="n">
         <v>87</v>
@@ -3326,7 +3326,7 @@
         <v>150</v>
       </c>
       <c r="M50" t="n">
-        <v>52.4</v>
+        <v>54.6</v>
       </c>
       <c r="N50" t="n">
         <v>45</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~52 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~55 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3427,13 +3427,13 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I52" t="n">
-        <v>15.2</v>
+        <v>14.2</v>
       </c>
       <c r="J52" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
         <v>624</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>431.3</v>
+        <v>426.7</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~431 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~427 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
         <v>150</v>
       </c>
       <c r="M53" t="n">
-        <v>253.8</v>
+        <v>256.4</v>
       </c>
       <c r="N53" t="n">
         <v>55</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~254 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~256 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
         <v>60</v>
       </c>
       <c r="M59" t="n">
-        <v>128.6</v>
+        <v>129.9</v>
       </c>
       <c r="N59" t="n">
         <v>48</v>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~129 wks (overstock); consider ~60u</t>
+          <t>CAUTION - 60u = ~130 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,13 +527,13 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>86.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J2" t="n">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
@@ -548,7 +548,7 @@
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -588,10 +588,10 @@
         <v>49.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -646,19 +646,19 @@
         <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="J4" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~60u (30cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~62u (31cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>25.2</v>
+        <v>23.9</v>
       </c>
       <c r="I5" t="n">
-        <v>11.6</v>
+        <v>12.2</v>
       </c>
       <c r="J5" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -716,13 +716,13 @@
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>16.4</v>
+        <v>15.9</v>
       </c>
       <c r="I6" t="n">
         <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -774,13 +774,13 @@
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>24.8</v>
+        <v>24.4</v>
       </c>
       <c r="I7" t="n">
         <v>3.7</v>
       </c>
       <c r="J7" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K7" t="n">
         <v>624</v>
@@ -832,17 +832,17 @@
         <v>624</v>
       </c>
       <c r="M7" t="n">
-        <v>25.2</v>
+        <v>25.6</v>
       </c>
       <c r="N7" t="n">
         <v>45</v>
       </c>
       <c r="O7" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -875,10 +875,10 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I8" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="J8" t="n">
         <v>75</v>
@@ -896,7 +896,7 @@
         <v>44</v>
       </c>
       <c r="O8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -933,10 +933,10 @@
         <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I9" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="J9" t="n">
         <v>75</v>
@@ -954,7 +954,7 @@
         <v>42</v>
       </c>
       <c r="O9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -991,10 +991,10 @@
         <v>22</v>
       </c>
       <c r="H10" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I10" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="J10" t="n">
         <v>75</v>
@@ -1012,7 +1012,7 @@
         <v>51</v>
       </c>
       <c r="O10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1033,55 +1033,55 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.7</v>
+        <v>10.5</v>
       </c>
       <c r="E11" t="n">
-        <v>21.7</v>
+        <v>9.06</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H11" t="n">
-        <v>7.9</v>
+        <v>22.6</v>
       </c>
       <c r="I11" t="n">
-        <v>10.1</v>
+        <v>5.1</v>
       </c>
       <c r="J11" t="n">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3</v>
+        <v>27.6</v>
       </c>
       <c r="N11" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~28 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1091,55 +1091,55 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.5</v>
+        <v>25.7</v>
       </c>
       <c r="E12" t="n">
-        <v>9.06</v>
+        <v>21.7</v>
       </c>
       <c r="F12" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>22.3</v>
+        <v>7.8</v>
       </c>
       <c r="I12" t="n">
-        <v>5.4</v>
+        <v>10.1</v>
       </c>
       <c r="J12" t="n">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="K12" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>28</v>
+        <v>0.3</v>
       </c>
       <c r="N12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~28 wks (overstock); consider ~624u</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,55 +1149,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25.7</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>21.7</v>
+        <v>16.67</v>
       </c>
       <c r="F13" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="G13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H13" t="n">
-        <v>7.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>6.4</v>
+        <v>16.6</v>
       </c>
       <c r="J13" t="n">
+        <v>81</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N13" t="n">
         <v>46</v>
-      </c>
-      <c r="K13" t="n">
-        <v>2</v>
-      </c>
-      <c r="L13" t="n">
-        <v>12</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="N13" t="n">
-        <v>50</v>
       </c>
       <c r="O13" t="n">
         <v>29</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BUY ~12u (6cs) - sells in ~2 wks</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,48 +1207,48 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>25.7</v>
       </c>
       <c r="E14" t="n">
-        <v>16.67</v>
+        <v>21.7</v>
       </c>
       <c r="F14" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H14" t="n">
-        <v>8.800000000000001</v>
+        <v>7.1</v>
       </c>
       <c r="I14" t="n">
-        <v>16.6</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>BUY ~8u (4cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1281,13 +1281,13 @@
         <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K15" t="n">
         <v>24</v>
@@ -1339,10 +1339,10 @@
         <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J16" t="n">
         <v>17</v>
@@ -1351,10 +1351,10 @@
         <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="M16" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="N16" t="n">
         <v>45</v>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUY ~78u (13cs) - sells in ~7 wks (rising into season)</t>
+          <t>BUY ~72u (12cs) - sells in ~7 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1397,13 +1397,13 @@
         <v>14</v>
       </c>
       <c r="H17" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="I17" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K17" t="n">
         <v>624</v>
@@ -1412,7 +1412,7 @@
         <v>624</v>
       </c>
       <c r="M17" t="n">
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="N17" t="n">
         <v>45</v>
@@ -1429,7 +1429,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1455,13 +1455,13 @@
         <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>12.8</v>
+        <v>12.2</v>
       </c>
       <c r="I18" t="n">
-        <v>10.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>133</v>
+        <v>109</v>
       </c>
       <c r="K18" t="n">
         <v>624</v>
@@ -1470,7 +1470,7 @@
         <v>624</v>
       </c>
       <c r="M18" t="n">
-        <v>48.7</v>
+        <v>51.1</v>
       </c>
       <c r="N18" t="n">
         <v>45</v>
@@ -1480,14 +1480,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~51 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,38 +1497,38 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E19" t="n">
-        <v>9.9</v>
+        <v>9.06</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>8.4</v>
+        <v>12.5</v>
       </c>
       <c r="I19" t="n">
-        <v>11.6</v>
+        <v>10.4</v>
       </c>
       <c r="J19" t="n">
-        <v>54</v>
+        <v>132</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L19" t="n">
-        <v>18</v>
+        <v>624</v>
       </c>
       <c r="M19" t="n">
-        <v>2.2</v>
+        <v>50.1</v>
       </c>
       <c r="N19" t="n">
         <v>45</v>
@@ -1538,14 +1538,14 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,38 +1555,38 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>9.9</v>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>12.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>8.6</v>
+        <v>11.7</v>
       </c>
       <c r="J20" t="n">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="K20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>624</v>
+        <v>18</v>
       </c>
       <c r="M20" t="n">
-        <v>51.6</v>
+        <v>2.2</v>
       </c>
       <c r="N20" t="n">
         <v>45</v>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
+          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1687,7 +1687,7 @@
         <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I22" t="n">
         <v>8.6</v>
@@ -1702,7 +1702,7 @@
         <v>24</v>
       </c>
       <c r="M22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="N22" t="n">
         <v>44</v>
@@ -1745,13 +1745,13 @@
         <v>20</v>
       </c>
       <c r="H23" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I23" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K23" t="n">
         <v>3</v>
@@ -1760,13 +1760,13 @@
         <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="N23" t="n">
         <v>47</v>
       </c>
       <c r="O23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1803,13 +1803,13 @@
         <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="I24" t="n">
-        <v>18.7</v>
+        <v>29</v>
       </c>
       <c r="J24" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K24" t="n">
         <v>6</v>
@@ -1818,7 +1818,7 @@
         <v>6</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N24" t="n">
         <v>46</v>
@@ -1828,14 +1828,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,38 +1845,38 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.03</v>
+        <v>10.85</v>
       </c>
       <c r="E25" t="n">
-        <v>9.15</v>
+        <v>8.68</v>
       </c>
       <c r="F25" t="n">
-        <v>0.88</v>
+        <v>2.17</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>15.5</v>
+        <v>6.6</v>
       </c>
       <c r="I25" t="n">
-        <v>6.9</v>
+        <v>13.9</v>
       </c>
       <c r="J25" t="n">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="K25" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>40.2</v>
+        <v>0.9</v>
       </c>
       <c r="N25" t="n">
         <v>46</v>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1922,10 +1922,10 @@
         <v>6.6</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K26" t="n">
         <v>6</v>
@@ -1934,7 +1934,7 @@
         <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="N26" t="n">
         <v>45</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~6 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
@@ -1980,10 +1980,10 @@
         <v>6.6</v>
       </c>
       <c r="I27" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K27" t="n">
         <v>6</v>
@@ -1992,7 +1992,7 @@
         <v>36</v>
       </c>
       <c r="M27" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="N27" t="n">
         <v>47</v>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~6 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
@@ -2038,10 +2038,10 @@
         <v>6.6</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K28" t="n">
         <v>6</v>
@@ -2050,7 +2050,7 @@
         <v>36</v>
       </c>
       <c r="M28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="N28" t="n">
         <v>46</v>
@@ -2060,14 +2060,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~6 wks</t>
+          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2093,13 +2093,13 @@
         <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>6.5</v>
+        <v>6.1</v>
       </c>
       <c r="I29" t="n">
-        <v>29.8</v>
+        <v>19.2</v>
       </c>
       <c r="J29" t="n">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K29" t="n">
         <v>6</v>
@@ -2108,24 +2108,24 @@
         <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
         <v>46</v>
       </c>
       <c r="O29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,48 +2135,48 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.85</v>
+        <v>10.03</v>
       </c>
       <c r="E30" t="n">
-        <v>8.68</v>
+        <v>9.15</v>
       </c>
       <c r="F30" t="n">
-        <v>2.17</v>
+        <v>0.88</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>6.6</v>
+        <v>14.6</v>
       </c>
       <c r="I30" t="n">
-        <v>14.4</v>
+        <v>7.2</v>
       </c>
       <c r="J30" t="n">
-        <v>97</v>
+        <v>151</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9</v>
+        <v>42.7</v>
       </c>
       <c r="N30" t="n">
         <v>46</v>
       </c>
       <c r="O30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2212,10 +2212,10 @@
         <v>8.5</v>
       </c>
       <c r="I31" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J31" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K31" t="n">
         <v>624</v>
@@ -2224,7 +2224,7 @@
         <v>624</v>
       </c>
       <c r="M31" t="n">
-        <v>73.8</v>
+        <v>73.7</v>
       </c>
       <c r="N31" t="n">
         <v>45</v>
@@ -2267,13 +2267,13 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="I32" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J32" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="K32" t="n">
         <v>624</v>
@@ -2282,17 +2282,17 @@
         <v>624</v>
       </c>
       <c r="M32" t="n">
-        <v>48.2</v>
+        <v>47.3</v>
       </c>
       <c r="N32" t="n">
         <v>46</v>
       </c>
       <c r="O32" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~47 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2328,10 +2328,10 @@
         <v>8</v>
       </c>
       <c r="I33" t="n">
-        <v>10.4</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K33" t="n">
         <v>150</v>
@@ -2357,7 +2357,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2383,13 +2383,13 @@
         <v>11</v>
       </c>
       <c r="H34" t="n">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>12.1</v>
+        <v>18.1</v>
       </c>
       <c r="J34" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="K34" t="n">
         <v>150</v>
@@ -2398,7 +2398,7 @@
         <v>150</v>
       </c>
       <c r="M34" t="n">
-        <v>16.9</v>
+        <v>18.3</v>
       </c>
       <c r="N34" t="n">
         <v>55</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2441,13 +2441,13 @@
         <v>9</v>
       </c>
       <c r="H35" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="I35" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J35" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="K35" t="n">
         <v>624</v>
@@ -2456,7 +2456,7 @@
         <v>624</v>
       </c>
       <c r="M35" t="n">
-        <v>53.2</v>
+        <v>52.9</v>
       </c>
       <c r="N35" t="n">
         <v>46</v>
@@ -2499,13 +2499,13 @@
         <v>7</v>
       </c>
       <c r="H36" t="n">
-        <v>12.6</v>
+        <v>12.8</v>
       </c>
       <c r="I36" t="n">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
       <c r="J36" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K36" t="n">
         <v>84</v>
@@ -2514,7 +2514,7 @@
         <v>84</v>
       </c>
       <c r="M36" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="N36" t="n">
         <v>44</v>
@@ -2531,7 +2531,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,55 +2541,55 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E37" t="n">
-        <v>11.2</v>
+        <v>9.82</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="G37" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>10.6</v>
+        <v>8.6</v>
       </c>
       <c r="I37" t="n">
-        <v>9.300000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="J37" t="n">
-        <v>141</v>
+        <v>90</v>
       </c>
       <c r="K37" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L37" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M37" t="n">
-        <v>7.9</v>
+        <v>17.4</v>
       </c>
       <c r="N37" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
+          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2599,29 +2599,29 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>10.85</v>
+        <v>8.67</v>
       </c>
       <c r="E38" t="n">
-        <v>8.68</v>
+        <v>6.57</v>
       </c>
       <c r="F38" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G38" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H38" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I38" t="n">
-        <v>35</v>
+        <v>8.5</v>
       </c>
       <c r="J38" t="n">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
@@ -2630,17 +2630,17 @@
         <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="N38" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O38" t="n">
         <v>9</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -2673,13 +2673,13 @@
         <v>22</v>
       </c>
       <c r="H39" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J39" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K39" t="n">
         <v>6</v>
@@ -2731,13 +2731,13 @@
         <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="J40" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K40" t="n">
         <v>6</v>
@@ -2763,7 +2763,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,55 +2773,55 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E41" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F41" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G41" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>7.2</v>
+        <v>9.9</v>
       </c>
       <c r="I41" t="n">
-        <v>20.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="K41" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L41" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M41" t="n">
-        <v>20.8</v>
+        <v>8.5</v>
       </c>
       <c r="N41" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O41" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
+          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2831,55 +2831,55 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8.67</v>
+        <v>12</v>
       </c>
       <c r="E42" t="n">
-        <v>6.57</v>
+        <v>11.2</v>
       </c>
       <c r="F42" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="G42" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H42" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="J42" t="n">
-        <v>38</v>
+        <v>141</v>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="L42" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="M42" t="n">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="N42" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -2905,13 +2905,13 @@
         <v>11</v>
       </c>
       <c r="H43" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="I43" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="J43" t="n">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="K43" t="n">
         <v>150</v>
@@ -2920,24 +2920,24 @@
         <v>150</v>
       </c>
       <c r="M43" t="n">
-        <v>19.7</v>
+        <v>21</v>
       </c>
       <c r="N43" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O43" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~20 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2947,48 +2947,48 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12</v>
+        <v>10.85</v>
       </c>
       <c r="E44" t="n">
-        <v>11.2</v>
+        <v>8.68</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8</v>
+        <v>2.17</v>
       </c>
       <c r="G44" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>10.1</v>
+        <v>3.9</v>
       </c>
       <c r="I44" t="n">
-        <v>8.199999999999999</v>
+        <v>34.7</v>
       </c>
       <c r="J44" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="K44" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L44" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>8.300000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="N44" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O44" t="n">
         <v>8</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -3021,10 +3021,10 @@
         <v>9</v>
       </c>
       <c r="H45" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I45" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="J45" t="n">
         <v>61</v>
@@ -3036,7 +3036,7 @@
         <v>208</v>
       </c>
       <c r="M45" t="n">
-        <v>68</v>
+        <v>68.5</v>
       </c>
       <c r="N45" t="n">
         <v>44</v>
@@ -3079,10 +3079,10 @@
         <v>20</v>
       </c>
       <c r="H46" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="I46" t="n">
-        <v>51.4</v>
+        <v>57.1</v>
       </c>
       <c r="J46" t="n">
         <v>72</v>
@@ -3094,17 +3094,17 @@
         <v>24</v>
       </c>
       <c r="M46" t="n">
-        <v>9.5</v>
+        <v>10.6</v>
       </c>
       <c r="N46" t="n">
         <v>44</v>
       </c>
       <c r="O46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~10 wks (rising into season)</t>
+          <t>BUY ~24u (4cs) - sells in ~11 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -3140,7 +3140,7 @@
         <v>3.7</v>
       </c>
       <c r="I47" t="n">
-        <v>54.8</v>
+        <v>55.4</v>
       </c>
       <c r="J47" t="n">
         <v>156</v>
@@ -3152,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>40.2</v>
+        <v>40.6</v>
       </c>
       <c r="N47" t="n">
         <v>50</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~40 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~41 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3195,13 +3195,13 @@
         <v>9</v>
       </c>
       <c r="H48" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="J48" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K48" t="n">
         <v>624</v>
@@ -3210,7 +3210,7 @@
         <v>624</v>
       </c>
       <c r="M48" t="n">
-        <v>114.8</v>
+        <v>113.3</v>
       </c>
       <c r="N48" t="n">
         <v>46</v>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~115 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~113 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
         <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="N49" t="n">
         <v>48</v>
@@ -3314,7 +3314,7 @@
         <v>2.7</v>
       </c>
       <c r="I50" t="n">
-        <v>26.6</v>
+        <v>26.9</v>
       </c>
       <c r="J50" t="n">
         <v>87</v>
@@ -3326,7 +3326,7 @@
         <v>150</v>
       </c>
       <c r="M50" t="n">
-        <v>54.6</v>
+        <v>55.1</v>
       </c>
       <c r="N50" t="n">
         <v>45</v>
@@ -3427,10 +3427,10 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="I52" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="J52" t="n">
         <v>21</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>426.7</v>
+        <v>440.4</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~427 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~440 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
         <v>150</v>
       </c>
       <c r="M53" t="n">
-        <v>256.4</v>
+        <v>259.1</v>
       </c>
       <c r="N53" t="n">
         <v>55</v>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~256 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~259 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3818,7 +3818,7 @@
         <v>60</v>
       </c>
       <c r="M59" t="n">
-        <v>129.9</v>
+        <v>131.3</v>
       </c>
       <c r="N59" t="n">
         <v>48</v>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~130 wks (overstock); consider ~60u</t>
+          <t>CAUTION - 60u = ~131 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>85.09999999999999</v>
+        <v>161.2</v>
       </c>
       <c r="I2" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>487</v>
+        <v>445</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>208</v>
+        <v>846</v>
       </c>
       <c r="M2" t="n">
-        <v>2.4</v>
+        <v>5.2</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>221</v>
+        <v>419</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~208u (104cs) - sells in ~2 wks</t>
+          <t>BUY ~846u (423cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>49.7</v>
+        <v>45.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,17 +600,17 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>186</v>
+        <v>169</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BUY ~208u (104cs) - sells in ~4 wks</t>
+          <t>BUY ~208u (104cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>21</v>
+        <v>21.7</v>
       </c>
       <c r="I4" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~62u (31cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~74u (37cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>23.9</v>
+        <v>28.9</v>
       </c>
       <c r="I5" t="n">
-        <v>12.2</v>
+        <v>11.2</v>
       </c>
       <c r="J5" t="n">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -716,24 +716,24 @@
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BUY ~40u (20cs) - sells in ~2 wks</t>
+          <t>BUY ~40u (20cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Clrty Variety 10mg THC 12pk 12oz can</t>
+          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -743,55 +743,55 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29.5</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>25.54</v>
+        <v>11.2</v>
       </c>
       <c r="F6" t="n">
-        <v>3.96</v>
+        <v>2.8</v>
       </c>
       <c r="G6" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>15.9</v>
+        <v>23.8</v>
       </c>
       <c r="I6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>57</v>
+      </c>
+      <c r="K6" t="n">
+        <v>24</v>
+      </c>
+      <c r="L6" t="n">
+        <v>138</v>
+      </c>
+      <c r="M6" t="n">
         <v>5.8</v>
       </c>
-      <c r="J6" t="n">
-        <v>91</v>
-      </c>
-      <c r="K6" t="n">
-        <v>50</v>
-      </c>
-      <c r="L6" t="n">
-        <v>50</v>
-      </c>
-      <c r="M6" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N6" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O6" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~50u (25cs) - sells in ~3 wks</t>
+          <t>BUY ~138u (23cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
+          <t>Clrty Variety 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -805,51 +805,51 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.5</v>
+        <v>29.5</v>
       </c>
       <c r="E7" t="n">
-        <v>9.06</v>
+        <v>25.54</v>
       </c>
       <c r="F7" t="n">
-        <v>1.44</v>
+        <v>3.96</v>
       </c>
       <c r="G7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>24.4</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="K7" t="n">
-        <v>624</v>
+        <v>50</v>
       </c>
       <c r="L7" t="n">
-        <v>624</v>
+        <v>50</v>
       </c>
       <c r="M7" t="n">
-        <v>25.6</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
+          <t>BUY ~50u (25cs) - sells in ~3 wks</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -859,55 +859,55 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.9</v>
+        <v>10.5</v>
       </c>
       <c r="E8" t="n">
-        <v>20.72</v>
+        <v>9.06</v>
       </c>
       <c r="F8" t="n">
-        <v>5.18</v>
+        <v>1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>6.8</v>
+        <v>25.4</v>
       </c>
       <c r="I8" t="n">
-        <v>10.7</v>
+        <v>2.9</v>
       </c>
       <c r="J8" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3</v>
+        <v>24.6</v>
       </c>
       <c r="N8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -917,55 +917,55 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>26.5</v>
+        <v>10.85</v>
       </c>
       <c r="E9" t="n">
-        <v>21.32</v>
+        <v>8.68</v>
       </c>
       <c r="F9" t="n">
-        <v>5.18</v>
+        <v>2.17</v>
       </c>
       <c r="G9" t="n">
         <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>6.8</v>
+        <v>16.2</v>
       </c>
       <c r="I9" t="n">
-        <v>10.7</v>
+        <v>16.3</v>
       </c>
       <c r="J9" t="n">
-        <v>75</v>
+        <v>147</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N9" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O9" t="n">
         <v>35</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -975,55 +975,55 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23.4</v>
+        <v>10.03</v>
       </c>
       <c r="E10" t="n">
-        <v>18.22</v>
+        <v>9.15</v>
       </c>
       <c r="F10" t="n">
-        <v>5.18</v>
+        <v>0.88</v>
       </c>
       <c r="G10" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>6.8</v>
+        <v>38.1</v>
       </c>
       <c r="I10" t="n">
-        <v>10.7</v>
+        <v>6.7</v>
       </c>
       <c r="J10" t="n">
-        <v>75</v>
+        <v>141</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3</v>
+        <v>16.4</v>
       </c>
       <c r="N10" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="O10" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~16 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1033,29 +1033,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.5</v>
+        <v>10.03</v>
       </c>
       <c r="E11" t="n">
-        <v>9.06</v>
+        <v>9.15</v>
       </c>
       <c r="F11" t="n">
-        <v>1.44</v>
+        <v>0.88</v>
       </c>
       <c r="G11" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>22.6</v>
+        <v>36.4</v>
       </c>
       <c r="I11" t="n">
-        <v>5.1</v>
+        <v>8.5</v>
       </c>
       <c r="J11" t="n">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="K11" t="n">
         <v>624</v>
@@ -1064,17 +1064,17 @@
         <v>624</v>
       </c>
       <c r="M11" t="n">
-        <v>27.6</v>
+        <v>17.1</v>
       </c>
       <c r="N11" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~28 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~17 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1107,13 +1107,13 @@
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I12" t="n">
-        <v>10.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1128,7 +1128,7 @@
         <v>50</v>
       </c>
       <c r="O12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,55 +1149,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="E13" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="G13" t="n">
         <v>20</v>
       </c>
-      <c r="E13" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="G13" t="n">
-        <v>17</v>
-      </c>
       <c r="H13" t="n">
-        <v>8.800000000000001</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>16.6</v>
+        <v>11.5</v>
       </c>
       <c r="J13" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
         <v>0.3</v>
       </c>
       <c r="N13" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O13" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,55 +1207,55 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="E14" t="n">
-        <v>21.7</v>
+        <v>20.72</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>5.18</v>
       </c>
       <c r="G14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H14" t="n">
-        <v>7.1</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="J14" t="n">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="K14" t="n">
         <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O14" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUY ~8u (4cs) - sells in ~1 wks</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,55 +1265,55 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14</v>
+        <v>23.4</v>
       </c>
       <c r="E15" t="n">
-        <v>11.2</v>
+        <v>18.22</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8</v>
+        <v>5.18</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4</v>
+        <v>11.5</v>
       </c>
       <c r="J15" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="K15" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="N15" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O15" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~2 wks (cooling)</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1323,55 +1323,55 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E16" t="n">
-        <v>9.9</v>
+        <v>16.67</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>3.33</v>
       </c>
       <c r="G16" t="n">
         <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>2.8</v>
+        <v>15.3</v>
       </c>
       <c r="J16" t="n">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>72</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>6.6</v>
+        <v>0.3</v>
       </c>
       <c r="N16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O16" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUY ~72u (12cs) - sells in ~7 wks (rising into season)</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1381,29 +1381,29 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.5</v>
+        <v>10.03</v>
       </c>
       <c r="E17" t="n">
-        <v>9.06</v>
+        <v>9.15</v>
       </c>
       <c r="F17" t="n">
-        <v>1.44</v>
+        <v>0.88</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>14.4</v>
+        <v>32.4</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>70</v>
+        <v>148</v>
       </c>
       <c r="K17" t="n">
         <v>624</v>
@@ -1412,24 +1412,24 @@
         <v>624</v>
       </c>
       <c r="M17" t="n">
-        <v>43.4</v>
+        <v>19.2</v>
       </c>
       <c r="N17" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O17" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,55 +1439,55 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.5</v>
+        <v>25.7</v>
       </c>
       <c r="E18" t="n">
-        <v>9.06</v>
+        <v>21.7</v>
       </c>
       <c r="F18" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>12.2</v>
+        <v>6.2</v>
       </c>
       <c r="I18" t="n">
-        <v>8.699999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="J18" t="n">
-        <v>109</v>
+        <v>47</v>
       </c>
       <c r="K18" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>624</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>51.1</v>
+        <v>0.6</v>
       </c>
       <c r="N18" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O18" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~51 wks (overstock); consider ~624u</t>
+          <t>BUY ~4u (2cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,55 +1497,55 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>9.06</v>
+        <v>11.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>12.5</v>
+        <v>30</v>
       </c>
       <c r="I19" t="n">
-        <v>10.4</v>
+        <v>8.5</v>
       </c>
       <c r="J19" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K19" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="L19" t="n">
-        <v>624</v>
+        <v>102</v>
       </c>
       <c r="M19" t="n">
-        <v>50.1</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O19" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
+          <t>BUY ~102u (17cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1571,39 +1571,39 @@
         <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>8.300000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="I20" t="n">
-        <v>11.7</v>
+        <v>4.6</v>
       </c>
       <c r="J20" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="M20" t="n">
-        <v>2.2</v>
+        <v>5.9</v>
       </c>
       <c r="N20" t="n">
         <v>45</v>
       </c>
       <c r="O20" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~66u (11cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,55 +1613,55 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D21" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="F21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G21" t="n">
         <v>20</v>
       </c>
-      <c r="E21" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G21" t="n">
-        <v>10</v>
-      </c>
       <c r="H21" t="n">
-        <v>8.300000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="I21" t="n">
-        <v>9.699999999999999</v>
+        <v>13.3</v>
       </c>
       <c r="J21" t="n">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="K21" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>4.8</v>
+        <v>0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,48 +1671,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G22" t="n">
         <v>14</v>
       </c>
-      <c r="E22" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G22" t="n">
-        <v>20</v>
-      </c>
       <c r="H22" t="n">
-        <v>5.6</v>
+        <v>14.3</v>
       </c>
       <c r="I22" t="n">
-        <v>8.6</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
-        <v>27</v>
+        <v>81</v>
       </c>
       <c r="K22" t="n">
-        <v>24</v>
+        <v>624</v>
       </c>
       <c r="L22" t="n">
-        <v>24</v>
+        <v>624</v>
       </c>
       <c r="M22" t="n">
-        <v>4.3</v>
+        <v>43.6</v>
       </c>
       <c r="N22" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~4 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~44 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1745,10 +1745,10 @@
         <v>20</v>
       </c>
       <c r="H23" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="I23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J23" t="n">
         <v>31</v>
@@ -1757,27 +1757,27 @@
         <v>3</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="N23" t="n">
         <v>47</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUY ~6u (2cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~18u (6cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,55 +1787,55 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.85</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>8.68</v>
+        <v>11.2</v>
       </c>
       <c r="F24" t="n">
-        <v>2.17</v>
+        <v>0.8</v>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>6.5</v>
+        <v>24.2</v>
       </c>
       <c r="I24" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="J24" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="L24" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="M24" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O24" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,55 +1845,55 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E25" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F25" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>6.6</v>
+        <v>13.5</v>
       </c>
       <c r="I25" t="n">
-        <v>13.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M25" t="n">
-        <v>0.9</v>
+        <v>46.1</v>
       </c>
       <c r="N25" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O25" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~46 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>8.67</v>
+        <v>26.52</v>
       </c>
       <c r="E26" t="n">
-        <v>6.57</v>
+        <v>24.2</v>
       </c>
       <c r="F26" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="G26" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>14.7</v>
       </c>
       <c r="J26" t="n">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>208</v>
       </c>
       <c r="M26" t="n">
-        <v>5.4</v>
+        <v>27.4</v>
       </c>
       <c r="N26" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O26" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
+          <t>CAUTION - 208u = ~27 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>10.5</v>
       </c>
       <c r="E27" t="n">
-        <v>8.4</v>
+        <v>9.06</v>
       </c>
       <c r="F27" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L27" t="n">
-        <v>36</v>
+        <v>624</v>
       </c>
       <c r="M27" t="n">
-        <v>5.4</v>
+        <v>52.1</v>
       </c>
       <c r="N27" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
+          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,55 +2019,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9.67</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>7.57</v>
+        <v>9.9</v>
       </c>
       <c r="F28" t="n">
         <v>2.1</v>
       </c>
       <c r="G28" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H28" t="n">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>11.5</v>
       </c>
       <c r="J28" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="K28" t="n">
         <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="M28" t="n">
-        <v>5.4</v>
+        <v>2.2</v>
       </c>
       <c r="N28" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~5 wks</t>
+          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2093,13 +2093,13 @@
         <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>6.1</v>
+        <v>7.8</v>
       </c>
       <c r="I29" t="n">
-        <v>19.2</v>
+        <v>26.9</v>
       </c>
       <c r="J29" t="n">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="K29" t="n">
         <v>6</v>
@@ -2108,24 +2108,24 @@
         <v>6</v>
       </c>
       <c r="M29" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="N29" t="n">
         <v>46</v>
       </c>
       <c r="O29" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.03</v>
+        <v>10.85</v>
       </c>
       <c r="E30" t="n">
-        <v>9.15</v>
+        <v>8.68</v>
       </c>
       <c r="F30" t="n">
-        <v>0.88</v>
+        <v>2.17</v>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H30" t="n">
-        <v>14.6</v>
+        <v>7.2</v>
       </c>
       <c r="I30" t="n">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="J30" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="K30" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>42.7</v>
+        <v>0.8</v>
       </c>
       <c r="N30" t="n">
         <v>46</v>
       </c>
       <c r="O30" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2197,51 +2197,51 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.5</v>
+        <v>9.33</v>
       </c>
       <c r="E31" t="n">
-        <v>9.06</v>
+        <v>8.01</v>
       </c>
       <c r="F31" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="G31" t="n">
         <v>14</v>
       </c>
       <c r="H31" t="n">
-        <v>8.5</v>
+        <v>10.6</v>
       </c>
       <c r="I31" t="n">
-        <v>7.4</v>
+        <v>10.2</v>
       </c>
       <c r="J31" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="K31" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L31" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M31" t="n">
-        <v>73.7</v>
+        <v>14.1</v>
       </c>
       <c r="N31" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~74 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,55 +2251,55 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.03</v>
+        <v>20</v>
       </c>
       <c r="E32" t="n">
-        <v>9.15</v>
+        <v>18.02</v>
       </c>
       <c r="F32" t="n">
-        <v>0.88</v>
+        <v>1.98</v>
       </c>
       <c r="G32" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H32" t="n">
-        <v>13.2</v>
+        <v>6.9</v>
       </c>
       <c r="I32" t="n">
-        <v>9.5</v>
+        <v>11.8</v>
       </c>
       <c r="J32" t="n">
-        <v>179</v>
+        <v>88</v>
       </c>
       <c r="K32" t="n">
-        <v>624</v>
+        <v>40</v>
       </c>
       <c r="L32" t="n">
-        <v>624</v>
+        <v>40</v>
       </c>
       <c r="M32" t="n">
-        <v>47.3</v>
+        <v>5.8</v>
       </c>
       <c r="N32" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~47 wks (overstock); consider ~624u</t>
+          <t>BUY ~40u (10cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9.33</v>
+        <v>10.03</v>
       </c>
       <c r="E33" t="n">
-        <v>8.01</v>
+        <v>9.15</v>
       </c>
       <c r="F33" t="n">
-        <v>1.32</v>
+        <v>0.88</v>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>14.6</v>
       </c>
       <c r="I33" t="n">
-        <v>10</v>
+        <v>10.9</v>
       </c>
       <c r="J33" t="n">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="K33" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L33" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M33" t="n">
-        <v>18.8</v>
+        <v>42.9</v>
       </c>
       <c r="N33" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O33" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,55 +2367,55 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E34" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F34" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G34" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>8.199999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="I34" t="n">
-        <v>18.1</v>
+        <v>7.5</v>
       </c>
       <c r="J34" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="K34" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L34" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M34" t="n">
-        <v>18.3</v>
+        <v>5.7</v>
       </c>
       <c r="N34" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="O34" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
+          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2425,55 +2425,55 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E35" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F35" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H35" t="n">
-        <v>11.8</v>
+        <v>10.1</v>
       </c>
       <c r="I35" t="n">
-        <v>9.1</v>
+        <v>12.3</v>
       </c>
       <c r="J35" t="n">
-        <v>154</v>
+        <v>85</v>
       </c>
       <c r="K35" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L35" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M35" t="n">
-        <v>52.9</v>
+        <v>14.8</v>
       </c>
       <c r="N35" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O35" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~53 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,55 +2483,55 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G36" t="n">
+        <v>20</v>
+      </c>
+      <c r="H36" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J36" t="n">
+        <v>20</v>
+      </c>
+      <c r="K36" t="n">
+        <v>6</v>
+      </c>
+      <c r="L36" t="n">
+        <v>30</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="N36" t="n">
+        <v>47</v>
+      </c>
+      <c r="O36" t="n">
         <v>12</v>
       </c>
-      <c r="E36" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G36" t="n">
-        <v>7</v>
-      </c>
-      <c r="H36" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="I36" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="J36" t="n">
-        <v>155</v>
-      </c>
-      <c r="K36" t="n">
-        <v>84</v>
-      </c>
-      <c r="L36" t="n">
-        <v>84</v>
-      </c>
-      <c r="M36" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="N36" t="n">
-        <v>44</v>
-      </c>
-      <c r="O36" t="n">
-        <v>10</v>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~7 wks (cooling)</t>
+          <t>BUY ~30u (5cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,55 +2541,55 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>8.67</v>
       </c>
       <c r="E37" t="n">
-        <v>9.82</v>
+        <v>6.57</v>
       </c>
       <c r="F37" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="G37" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H37" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="I37" t="n">
-        <v>12.5</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L37" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="M37" t="n">
-        <v>17.4</v>
+        <v>5.2</v>
       </c>
       <c r="N37" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
+          <t>BUY ~30u (5cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2603,51 +2603,51 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>8.67</v>
+        <v>9.67</v>
       </c>
       <c r="E38" t="n">
-        <v>6.57</v>
+        <v>7.57</v>
       </c>
       <c r="F38" t="n">
         <v>2.1</v>
       </c>
       <c r="G38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H38" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="I38" t="n">
-        <v>8.5</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="M38" t="n">
-        <v>1.4</v>
+        <v>5.2</v>
       </c>
       <c r="N38" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O38" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~30u (5cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,55 +2657,55 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9.67</v>
+        <v>10.5</v>
       </c>
       <c r="E39" t="n">
-        <v>7.57</v>
+        <v>9.06</v>
       </c>
       <c r="F39" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G39" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H39" t="n">
-        <v>4.3</v>
+        <v>8.6</v>
       </c>
       <c r="I39" t="n">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
       <c r="J39" t="n">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="K39" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L39" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M39" t="n">
-        <v>1.4</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~73 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2715,55 +2715,55 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="E40" t="n">
-        <v>8.4</v>
+        <v>11.2</v>
       </c>
       <c r="F40" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="G40" t="n">
         <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I40" t="n">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="K40" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L40" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M40" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="N40" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O40" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,55 +2773,55 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E41" t="n">
-        <v>11.2</v>
+        <v>9.82</v>
       </c>
       <c r="F41" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="G41" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H41" t="n">
-        <v>9.9</v>
+        <v>8</v>
       </c>
       <c r="I41" t="n">
-        <v>8.199999999999999</v>
+        <v>16.9</v>
       </c>
       <c r="J41" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="K41" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L41" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M41" t="n">
-        <v>8.5</v>
+        <v>18.8</v>
       </c>
       <c r="N41" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O41" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
+          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2831,55 +2831,55 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12</v>
+        <v>8.67</v>
       </c>
       <c r="E42" t="n">
-        <v>11.2</v>
+        <v>6.57</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="G42" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="H42" t="n">
-        <v>10.5</v>
+        <v>3.7</v>
       </c>
       <c r="I42" t="n">
-        <v>9.4</v>
+        <v>9.1</v>
       </c>
       <c r="J42" t="n">
-        <v>141</v>
+        <v>36</v>
       </c>
       <c r="K42" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L42" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>8</v>
+        <v>1.6</v>
       </c>
       <c r="N42" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O42" t="n">
         <v>8</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~8 wks (cooling)</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,55 +2889,55 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11</v>
+        <v>9.67</v>
       </c>
       <c r="E43" t="n">
-        <v>9.82</v>
+        <v>7.57</v>
       </c>
       <c r="F43" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="G43" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H43" t="n">
-        <v>7.1</v>
+        <v>3.7</v>
       </c>
       <c r="I43" t="n">
-        <v>20</v>
+        <v>9.1</v>
       </c>
       <c r="J43" t="n">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="K43" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L43" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>21</v>
+        <v>1.6</v>
       </c>
       <c r="N43" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O43" t="n">
         <v>8</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~21 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2947,29 +2947,29 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E44" t="n">
-        <v>8.68</v>
+        <v>8.4</v>
       </c>
       <c r="F44" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G44" t="n">
         <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I44" t="n">
-        <v>34.7</v>
+        <v>9.1</v>
       </c>
       <c r="J44" t="n">
-        <v>116</v>
+        <v>36</v>
       </c>
       <c r="K44" t="n">
         <v>6</v>
@@ -2978,24 +2978,24 @@
         <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="N44" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O44" t="n">
         <v>8</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3005,55 +3005,55 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>26.52</v>
+        <v>11</v>
       </c>
       <c r="E45" t="n">
-        <v>24.2</v>
+        <v>9.82</v>
       </c>
       <c r="F45" t="n">
-        <v>2.33</v>
+        <v>1.18</v>
       </c>
       <c r="G45" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>5.6</v>
       </c>
       <c r="I45" t="n">
-        <v>14.1</v>
+        <v>18.9</v>
       </c>
       <c r="J45" t="n">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="K45" t="n">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="L45" t="n">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="M45" t="n">
-        <v>68.5</v>
+        <v>26.8</v>
       </c>
       <c r="N45" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O45" t="n">
         <v>7</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~68 wks (overstock); consider ~208u</t>
+          <t>CAUTION - 150u = ~27 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
+          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,55 +3063,55 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D46" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="E46" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G46" t="n">
         <v>14</v>
       </c>
-      <c r="E46" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F46" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G46" t="n">
-        <v>20</v>
-      </c>
       <c r="H46" t="n">
-        <v>2.3</v>
+        <v>3.9</v>
       </c>
       <c r="I46" t="n">
-        <v>57.1</v>
+        <v>59</v>
       </c>
       <c r="J46" t="n">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="K46" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="L46" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="M46" t="n">
-        <v>10.6</v>
+        <v>38.1</v>
       </c>
       <c r="N46" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~11 wks (rising into season)</t>
+          <t>CAUTION - 150u = ~38 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
+          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3125,25 +3125,25 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>9.33</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>8.01</v>
+        <v>9.82</v>
       </c>
       <c r="F47" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="G47" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="I47" t="n">
-        <v>55.4</v>
+        <v>29.4</v>
       </c>
       <c r="J47" t="n">
-        <v>156</v>
+        <v>87</v>
       </c>
       <c r="K47" t="n">
         <v>150</v>
@@ -3152,24 +3152,24 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>40.6</v>
+        <v>64.8</v>
       </c>
       <c r="N47" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~41 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~65 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3179,48 +3179,48 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.03</v>
+        <v>10.58</v>
       </c>
       <c r="E48" t="n">
-        <v>9.15</v>
+        <v>7.06</v>
       </c>
       <c r="F48" t="n">
-        <v>0.88</v>
+        <v>3.53</v>
       </c>
       <c r="G48" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H48" t="n">
-        <v>5.5</v>
+        <v>0.8</v>
       </c>
       <c r="I48" t="n">
-        <v>11.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="K48" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="L48" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M48" t="n">
-        <v>113.3</v>
+        <v>15.9</v>
       </c>
       <c r="N48" t="n">
         <v>46</v>
       </c>
       <c r="O48" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~113 wks (overstock); consider ~624u</t>
+          <t>BUY ~12u (2cs) - sells in ~16 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -3253,13 +3253,13 @@
         <v>15</v>
       </c>
       <c r="H49" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="I49" t="n">
-        <v>22.2</v>
+        <v>25.4</v>
       </c>
       <c r="J49" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K49" t="n">
         <v>40</v>
@@ -3268,7 +3268,7 @@
         <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>23.2</v>
+        <v>25.2</v>
       </c>
       <c r="N49" t="n">
         <v>48</v>
@@ -3278,14 +3278,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~23 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 40u = ~25 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
+          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3295,55 +3295,55 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E50" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F50" t="n">
-        <v>1.18</v>
+        <v>2.8</v>
       </c>
       <c r="G50" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H50" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="I50" t="n">
-        <v>26.9</v>
+        <v>46.8</v>
       </c>
       <c r="J50" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K50" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="L50" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="M50" t="n">
-        <v>55.1</v>
+        <v>19.6</v>
       </c>
       <c r="N50" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~55 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 24u = ~20 wks (overstock); consider ~24u</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
+          <t>Clrty SodaPot Blue Ginger 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3357,44 +3357,44 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.58</v>
+        <v>11</v>
       </c>
       <c r="E51" t="n">
-        <v>7.06</v>
+        <v>9.82</v>
       </c>
       <c r="F51" t="n">
-        <v>3.53</v>
+        <v>1.18</v>
       </c>
       <c r="G51" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I51" t="n">
-        <v>71.40000000000001</v>
+        <v>155.4</v>
       </c>
       <c r="J51" t="n">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="K51" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="L51" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="M51" t="n">
-        <v>20.4</v>
+        <v>285.9</v>
       </c>
       <c r="N51" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 12u = ~20 wks (overstock); consider ~12u</t>
+          <t>CAUTION - 150u = ~286 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3427,10 +3427,10 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="I52" t="n">
-        <v>14.5</v>
+        <v>17.3</v>
       </c>
       <c r="J52" t="n">
         <v>21</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>440.4</v>
+        <v>549</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,14 +3452,14 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~440 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~549 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Blue Ginger 10mg 4pk 12oz can</t>
+          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3473,44 +3473,38 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="E53" t="n">
-        <v>9.82</v>
+        <v>9.06</v>
       </c>
       <c r="F53" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="G53" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="I53" t="n">
-        <v>147.2</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L53" t="n">
-        <v>150</v>
-      </c>
-      <c r="M53" t="n">
-        <v>259.1</v>
+        <v>624</v>
       </c>
       <c r="N53" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~259 wks (overstock); consider ~150u</t>
+          <t>SKIP - not selling (any quantity would sit)</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3797,7 @@
         <v>9</v>
       </c>
       <c r="H59" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I59" t="n">
         <v>587.1</v>
@@ -3818,7 +3812,7 @@
         <v>60</v>
       </c>
       <c r="M59" t="n">
-        <v>131.3</v>
+        <v>137.2</v>
       </c>
       <c r="N59" t="n">
         <v>48</v>
@@ -3828,7 +3822,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~131 wks (overstock); consider ~60u</t>
+          <t>CAUTION - 60u = ~137 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>161.2</v>
+        <v>162.8</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>846</v>
+        <v>878</v>
       </c>
       <c r="M2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~846u (423cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~878u (439cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>45.2</v>
+        <v>44.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>21.7</v>
+        <v>22.1</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="M4" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~74u (37cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~82u (41cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>28.9</v>
+        <v>28.1</v>
       </c>
       <c r="I5" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="J5" t="n">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I7" t="n">
         <v>5.2</v>
       </c>
       <c r="J7" t="n">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K7" t="n">
         <v>50</v>
@@ -832,24 +832,24 @@
         <v>50</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
         <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BUY ~50u (25cs) - sells in ~3 wks</t>
+          <t>BUY ~50u (25cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -859,55 +859,55 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E8" t="n">
-        <v>9.06</v>
+        <v>8.68</v>
       </c>
       <c r="F8" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>25.4</v>
+        <v>17.7</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9</v>
+        <v>14.4</v>
       </c>
       <c r="J8" t="n">
-        <v>79</v>
+        <v>142</v>
       </c>
       <c r="K8" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>24.6</v>
+        <v>0.3</v>
       </c>
       <c r="N8" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -917,48 +917,48 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E9" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F9" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>16.2</v>
+        <v>25.7</v>
       </c>
       <c r="I9" t="n">
-        <v>16.3</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
-        <v>147</v>
+        <v>75</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4</v>
+        <v>24.2</v>
       </c>
       <c r="N9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O9" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~24 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -991,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>38.1</v>
+        <v>40.1</v>
       </c>
       <c r="I10" t="n">
-        <v>6.7</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="K10" t="n">
         <v>624</v>
@@ -1006,17 +1006,17 @@
         <v>624</v>
       </c>
       <c r="M10" t="n">
-        <v>16.4</v>
+        <v>15.6</v>
       </c>
       <c r="N10" t="n">
         <v>46</v>
       </c>
       <c r="O10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~16 wks (overstock); consider ~624u</t>
+          <t>BUY ~624u (104cs) - sells in ~16 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1049,13 +1049,13 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>36.4</v>
+        <v>37</v>
       </c>
       <c r="I11" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="K11" t="n">
         <v>624</v>
@@ -1064,13 +1064,13 @@
         <v>624</v>
       </c>
       <c r="M11" t="n">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="N11" t="n">
         <v>46</v>
       </c>
       <c r="O11" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1091,29 +1091,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="E12" t="n">
-        <v>21.7</v>
+        <v>20.72</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>5.18</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>7.9</v>
+        <v>6.2</v>
       </c>
       <c r="I12" t="n">
-        <v>9.300000000000001</v>
+        <v>10.9</v>
       </c>
       <c r="J12" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1125,7 +1125,7 @@
         <v>0.3</v>
       </c>
       <c r="N12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O12" t="n">
         <v>32</v>
@@ -1165,13 +1165,13 @@
         <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I13" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="J13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
@@ -1186,7 +1186,7 @@
         <v>42</v>
       </c>
       <c r="O13" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1211,25 +1211,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25.9</v>
+        <v>23.4</v>
       </c>
       <c r="E14" t="n">
-        <v>20.72</v>
+        <v>18.22</v>
       </c>
       <c r="F14" t="n">
         <v>5.18</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I14" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="J14" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K14" t="n">
         <v>2</v>
@@ -1241,10 +1241,10 @@
         <v>0.3</v>
       </c>
       <c r="N14" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,29 +1265,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23.4</v>
+        <v>25.7</v>
       </c>
       <c r="E15" t="n">
-        <v>18.22</v>
+        <v>21.7</v>
       </c>
       <c r="F15" t="n">
-        <v>5.18</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="I15" t="n">
-        <v>11.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
@@ -1299,7 +1299,7 @@
         <v>0.3</v>
       </c>
       <c r="N15" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O15" t="n">
         <v>31</v>
@@ -1342,7 +1342,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="J16" t="n">
         <v>79</v>
@@ -1397,10 +1397,10 @@
         <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>32.4</v>
+        <v>31.6</v>
       </c>
       <c r="I17" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J17" t="n">
         <v>148</v>
@@ -1412,17 +1412,17 @@
         <v>624</v>
       </c>
       <c r="M17" t="n">
-        <v>19.2</v>
+        <v>19.8</v>
       </c>
       <c r="N17" t="n">
         <v>46</v>
       </c>
       <c r="O17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~20 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
         <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="I18" t="n">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J18" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M18" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="N18" t="n">
         <v>50</v>
       </c>
       <c r="O18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUY ~4u (2cs) - sells in ~1 wks</t>
+          <t>BUY ~8u (4cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1513,13 +1513,13 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="I19" t="n">
         <v>8.5</v>
       </c>
       <c r="J19" t="n">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="K19" t="n">
         <v>84</v>
@@ -1574,7 +1574,7 @@
         <v>11.2</v>
       </c>
       <c r="I20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J20" t="n">
         <v>29</v>
@@ -1592,7 +1592,7 @@
         <v>45</v>
       </c>
       <c r="O20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -1629,13 +1629,13 @@
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="I21" t="n">
-        <v>13.3</v>
+        <v>12.5</v>
       </c>
       <c r="J21" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
@@ -1650,7 +1650,7 @@
         <v>46</v>
       </c>
       <c r="O21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1702,13 +1702,13 @@
         <v>624</v>
       </c>
       <c r="M22" t="n">
-        <v>43.6</v>
+        <v>43.8</v>
       </c>
       <c r="N22" t="n">
         <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -1803,13 +1803,13 @@
         <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>24.2</v>
+        <v>25.6</v>
       </c>
       <c r="I24" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J24" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="K24" t="n">
         <v>84</v>
@@ -1818,17 +1818,17 @@
         <v>84</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="N24" t="n">
         <v>44</v>
       </c>
       <c r="O24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1861,13 +1861,13 @@
         <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="I25" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K25" t="n">
         <v>624</v>
@@ -1876,7 +1876,7 @@
         <v>624</v>
       </c>
       <c r="M25" t="n">
-        <v>46.1</v>
+        <v>46.6</v>
       </c>
       <c r="N25" t="n">
         <v>45</v>
@@ -1886,7 +1886,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~46 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~47 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1919,13 +1919,13 @@
         <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="I26" t="n">
-        <v>14.7</v>
+        <v>13.9</v>
       </c>
       <c r="J26" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K26" t="n">
         <v>208</v>
@@ -1934,7 +1934,7 @@
         <v>208</v>
       </c>
       <c r="M26" t="n">
-        <v>27.4</v>
+        <v>26.3</v>
       </c>
       <c r="N26" t="n">
         <v>44</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~27 wks (overstock); consider ~208u</t>
+          <t>CAUTION - 208u = ~26 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
@@ -1977,13 +1977,13 @@
         <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="I27" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="J27" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K27" t="n">
         <v>624</v>
@@ -1992,7 +1992,7 @@
         <v>624</v>
       </c>
       <c r="M27" t="n">
-        <v>52.1</v>
+        <v>54</v>
       </c>
       <c r="N27" t="n">
         <v>45</v>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~54 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2035,13 +2035,13 @@
         <v>17</v>
       </c>
       <c r="H28" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="J28" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K28" t="n">
         <v>6</v>
@@ -2093,13 +2093,13 @@
         <v>20</v>
       </c>
       <c r="H29" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="I29" t="n">
-        <v>26.9</v>
+        <v>26.2</v>
       </c>
       <c r="J29" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K29" t="n">
         <v>6</v>
@@ -2151,13 +2151,13 @@
         <v>20</v>
       </c>
       <c r="H30" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="I30" t="n">
-        <v>29</v>
+        <v>27.4</v>
       </c>
       <c r="J30" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="K30" t="n">
         <v>6</v>
@@ -2209,13 +2209,13 @@
         <v>14</v>
       </c>
       <c r="H31" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="I31" t="n">
         <v>10.2</v>
       </c>
       <c r="J31" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K31" t="n">
         <v>150</v>
@@ -2224,7 +2224,7 @@
         <v>150</v>
       </c>
       <c r="M31" t="n">
-        <v>14.1</v>
+        <v>14.4</v>
       </c>
       <c r="N31" t="n">
         <v>50</v>
@@ -2267,13 +2267,13 @@
         <v>10</v>
       </c>
       <c r="H32" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="I32" t="n">
-        <v>11.8</v>
+        <v>11</v>
       </c>
       <c r="J32" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K32" t="n">
         <v>40</v>
@@ -2282,7 +2282,7 @@
         <v>40</v>
       </c>
       <c r="M32" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="N32" t="n">
         <v>47</v>
@@ -2299,7 +2299,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.03</v>
+        <v>12</v>
       </c>
       <c r="E33" t="n">
-        <v>9.15</v>
+        <v>11.2</v>
       </c>
       <c r="F33" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H33" t="n">
-        <v>14.6</v>
+        <v>16.9</v>
       </c>
       <c r="I33" t="n">
-        <v>10.9</v>
+        <v>5.9</v>
       </c>
       <c r="J33" t="n">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="K33" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="L33" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="M33" t="n">
-        <v>42.9</v>
+        <v>5</v>
       </c>
       <c r="N33" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>BUY ~84u (14cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,48 +2367,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12</v>
+        <v>10.03</v>
       </c>
       <c r="E34" t="n">
-        <v>11.2</v>
+        <v>9.15</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
         <v>14.9</v>
       </c>
       <c r="I34" t="n">
-        <v>7.5</v>
+        <v>10.4</v>
       </c>
       <c r="J34" t="n">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="K34" t="n">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="L34" t="n">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="M34" t="n">
-        <v>5.7</v>
+        <v>41.8</v>
       </c>
       <c r="N34" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
+          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2441,13 +2441,13 @@
         <v>11</v>
       </c>
       <c r="H35" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="I35" t="n">
-        <v>12.3</v>
+        <v>12.1</v>
       </c>
       <c r="J35" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K35" t="n">
         <v>150</v>
@@ -2456,7 +2456,7 @@
         <v>150</v>
       </c>
       <c r="M35" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="N35" t="n">
         <v>55</v>
@@ -2499,10 +2499,10 @@
         <v>20</v>
       </c>
       <c r="H36" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J36" t="n">
         <v>20</v>
@@ -2511,10 +2511,10 @@
         <v>6</v>
       </c>
       <c r="L36" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M36" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="N36" t="n">
         <v>47</v>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~5 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
@@ -2557,10 +2557,10 @@
         <v>24</v>
       </c>
       <c r="H37" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J37" t="n">
         <v>20</v>
@@ -2569,10 +2569,10 @@
         <v>6</v>
       </c>
       <c r="L37" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M37" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="N37" t="n">
         <v>45</v>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~5 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
@@ -2615,10 +2615,10 @@
         <v>22</v>
       </c>
       <c r="H38" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J38" t="n">
         <v>20</v>
@@ -2627,10 +2627,10 @@
         <v>6</v>
       </c>
       <c r="L38" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M38" t="n">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="N38" t="n">
         <v>46</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~5 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
@@ -2676,10 +2676,10 @@
         <v>8.6</v>
       </c>
       <c r="I39" t="n">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="J39" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K39" t="n">
         <v>624</v>
@@ -2688,7 +2688,7 @@
         <v>624</v>
       </c>
       <c r="M39" t="n">
-        <v>72.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="N39" t="n">
         <v>45</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~73 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~72 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2789,13 +2789,13 @@
         <v>11</v>
       </c>
       <c r="H41" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>16.9</v>
+        <v>16.3</v>
       </c>
       <c r="J41" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K41" t="n">
         <v>150</v>
@@ -2804,17 +2804,17 @@
         <v>150</v>
       </c>
       <c r="M41" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="N41" t="n">
         <v>55</v>
       </c>
       <c r="O41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
         <v>3.7</v>
       </c>
       <c r="I42" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J42" t="n">
         <v>36</v>
@@ -2908,7 +2908,7 @@
         <v>3.7</v>
       </c>
       <c r="I43" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J43" t="n">
         <v>36</v>
@@ -2966,7 +2966,7 @@
         <v>3.7</v>
       </c>
       <c r="I44" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J44" t="n">
         <v>36</v>
@@ -3021,13 +3021,13 @@
         <v>11</v>
       </c>
       <c r="H45" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="I45" t="n">
-        <v>18.9</v>
+        <v>19.2</v>
       </c>
       <c r="J45" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K45" t="n">
         <v>150</v>
@@ -3036,17 +3036,17 @@
         <v>150</v>
       </c>
       <c r="M45" t="n">
-        <v>26.8</v>
+        <v>27.5</v>
       </c>
       <c r="N45" t="n">
         <v>45</v>
       </c>
       <c r="O45" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~27 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~28 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3079,10 +3079,10 @@
         <v>14</v>
       </c>
       <c r="H46" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="I46" t="n">
-        <v>59</v>
+        <v>62.3</v>
       </c>
       <c r="J46" t="n">
         <v>156</v>
@@ -3094,7 +3094,7 @@
         <v>150</v>
       </c>
       <c r="M46" t="n">
-        <v>38.1</v>
+        <v>40.3</v>
       </c>
       <c r="N46" t="n">
         <v>50</v>
@@ -3104,14 +3104,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~38 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~40 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
+          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3125,44 +3125,44 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>13.45</v>
       </c>
       <c r="E47" t="n">
-        <v>9.82</v>
+        <v>11.47</v>
       </c>
       <c r="F47" t="n">
-        <v>1.18</v>
+        <v>1.97</v>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H47" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="I47" t="n">
-        <v>29.4</v>
+        <v>20.1</v>
       </c>
       <c r="J47" t="n">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="L47" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="M47" t="n">
-        <v>64.8</v>
+        <v>21</v>
       </c>
       <c r="N47" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~65 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 40u = ~21 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
+          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3241,44 +3241,44 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.45</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>11.47</v>
+        <v>9.82</v>
       </c>
       <c r="F49" t="n">
-        <v>1.97</v>
+        <v>1.18</v>
       </c>
       <c r="G49" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H49" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="I49" t="n">
-        <v>25.4</v>
+        <v>22.8</v>
       </c>
       <c r="J49" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="K49" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="L49" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="M49" t="n">
-        <v>25.2</v>
+        <v>52.6</v>
       </c>
       <c r="N49" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~25 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 150u = ~53 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3369,13 +3369,13 @@
         <v>11</v>
       </c>
       <c r="H51" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>155.4</v>
+        <v>94.2</v>
       </c>
       <c r="J51" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K51" t="n">
         <v>150</v>
@@ -3384,7 +3384,7 @@
         <v>150</v>
       </c>
       <c r="M51" t="n">
-        <v>285.9</v>
+        <v>177.5</v>
       </c>
       <c r="N51" t="n">
         <v>55</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~286 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~178 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>162.8</v>
+        <v>157.6</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>878</v>
+        <v>842</v>
       </c>
       <c r="M2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>423</v>
+        <v>409</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~878u (439cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~842u (421cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>44.7</v>
+        <v>43.6</v>
       </c>
       <c r="I3" t="n">
         <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="J4" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~82u (41cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~64u (32cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>28.1</v>
+        <v>27.4</v>
       </c>
       <c r="I5" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="J5" t="n">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -716,17 +716,17 @@
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BUY ~40u (20cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~40u (20cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -759,10 +759,10 @@
         <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>23.8</v>
+        <v>23.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J6" t="n">
         <v>57</v>
@@ -771,20 +771,20 @@
         <v>24</v>
       </c>
       <c r="L6" t="n">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="M6" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="N6" t="n">
         <v>44</v>
       </c>
       <c r="O6" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~138u (23cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~132u (22cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -817,13 +817,13 @@
         <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="I7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K7" t="n">
         <v>50</v>
@@ -832,13 +832,13 @@
         <v>50</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N7" t="n">
         <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -875,32 +875,32 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>17.7</v>
+        <v>18.3</v>
       </c>
       <c r="I8" t="n">
-        <v>14.4</v>
+        <v>13.5</v>
       </c>
       <c r="J8" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="N8" t="n">
         <v>46</v>
       </c>
       <c r="O8" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>BUY ~12u (2cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -933,13 +933,13 @@
         <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J9" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="K9" t="n">
         <v>624</v>
@@ -991,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="I10" t="n">
         <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K10" t="n">
         <v>624</v>
@@ -1006,7 +1006,7 @@
         <v>624</v>
       </c>
       <c r="M10" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="N10" t="n">
         <v>46</v>
@@ -1049,13 +1049,13 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>37</v>
+        <v>35.9</v>
       </c>
       <c r="I11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="K11" t="n">
         <v>624</v>
@@ -1064,13 +1064,13 @@
         <v>624</v>
       </c>
       <c r="M11" t="n">
-        <v>16.8</v>
+        <v>17.4</v>
       </c>
       <c r="N11" t="n">
         <v>46</v>
       </c>
       <c r="O11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1107,10 +1107,10 @@
         <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="I12" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="J12" t="n">
         <v>72</v>
@@ -1128,7 +1128,7 @@
         <v>44</v>
       </c>
       <c r="O12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="I13" t="n">
-        <v>10.9</v>
+        <v>11.7</v>
       </c>
       <c r="J13" t="n">
         <v>72</v>
@@ -1186,7 +1186,7 @@
         <v>42</v>
       </c>
       <c r="O13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,29 +1207,29 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>23.4</v>
+        <v>25.7</v>
       </c>
       <c r="E14" t="n">
-        <v>18.22</v>
+        <v>21.7</v>
       </c>
       <c r="F14" t="n">
-        <v>5.18</v>
+        <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="H14" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="I14" t="n">
-        <v>10.9</v>
+        <v>9.6</v>
       </c>
       <c r="J14" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K14" t="n">
         <v>2</v>
@@ -1241,10 +1241,10 @@
         <v>0.3</v>
       </c>
       <c r="N14" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="O14" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,29 +1265,29 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.7</v>
+        <v>23.4</v>
       </c>
       <c r="E15" t="n">
-        <v>21.7</v>
+        <v>18.22</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>5.18</v>
       </c>
       <c r="G15" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="H15" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="I15" t="n">
-        <v>9.300000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="J15" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
@@ -1299,10 +1299,10 @@
         <v>0.3</v>
       </c>
       <c r="N15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O15" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1339,10 +1339,10 @@
         <v>17</v>
       </c>
       <c r="H16" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>15.4</v>
+        <v>16.5</v>
       </c>
       <c r="J16" t="n">
         <v>79</v>
@@ -1354,13 +1354,13 @@
         <v>3</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N16" t="n">
         <v>46</v>
       </c>
       <c r="O16" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1397,13 +1397,13 @@
         <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>31.6</v>
+        <v>30.9</v>
       </c>
       <c r="I17" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J17" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K17" t="n">
         <v>624</v>
@@ -1412,13 +1412,13 @@
         <v>624</v>
       </c>
       <c r="M17" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="N17" t="n">
         <v>46</v>
       </c>
       <c r="O17" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1455,13 +1455,13 @@
         <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J18" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -1470,7 +1470,7 @@
         <v>8</v>
       </c>
       <c r="M18" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="N18" t="n">
         <v>50</v>
@@ -1513,32 +1513,32 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>29.8</v>
+        <v>28.2</v>
       </c>
       <c r="I19" t="n">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
       <c r="J19" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K19" t="n">
         <v>84</v>
       </c>
       <c r="L19" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
         <v>44</v>
       </c>
       <c r="O19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUY ~102u (17cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~90u (15cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1571,10 +1571,10 @@
         <v>17</v>
       </c>
       <c r="H20" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="I20" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>29</v>
@@ -1583,20 +1583,20 @@
         <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="M20" t="n">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="N20" t="n">
         <v>45</v>
       </c>
       <c r="O20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~66u (11cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~54u (9cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1629,10 +1629,10 @@
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>9.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="J21" t="n">
         <v>99</v>
@@ -1650,7 +1650,7 @@
         <v>46</v>
       </c>
       <c r="O21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1687,13 +1687,13 @@
         <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>14.3</v>
+        <v>13.7</v>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>81</v>
+        <v>129</v>
       </c>
       <c r="K22" t="n">
         <v>624</v>
@@ -1702,7 +1702,7 @@
         <v>624</v>
       </c>
       <c r="M22" t="n">
-        <v>43.8</v>
+        <v>45.6</v>
       </c>
       <c r="N22" t="n">
         <v>45</v>
@@ -1712,14 +1712,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~44 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~46 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,48 +1729,48 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.67</v>
+        <v>10.5</v>
       </c>
       <c r="E23" t="n">
-        <v>13.34</v>
+        <v>9.06</v>
       </c>
       <c r="F23" t="n">
-        <v>3.33</v>
+        <v>1.44</v>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>6</v>
+        <v>13.6</v>
       </c>
       <c r="I23" t="n">
-        <v>9.4</v>
+        <v>6.8</v>
       </c>
       <c r="J23" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="K23" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L23" t="n">
-        <v>18</v>
+        <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="N23" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUY ~18u (6cs) - sells in ~3 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~46 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1803,13 +1803,13 @@
         <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>25.6</v>
+        <v>24.1</v>
       </c>
       <c r="I24" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="K24" t="n">
         <v>84</v>
@@ -1818,24 +1818,24 @@
         <v>84</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
         <v>44</v>
       </c>
       <c r="O24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,55 +1845,55 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.5</v>
+        <v>26.52</v>
       </c>
       <c r="E25" t="n">
-        <v>9.06</v>
+        <v>24.2</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="G25" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>13.4</v>
+        <v>7.6</v>
       </c>
       <c r="I25" t="n">
-        <v>8.800000000000001</v>
+        <v>14.4</v>
       </c>
       <c r="J25" t="n">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="K25" t="n">
-        <v>624</v>
+        <v>208</v>
       </c>
       <c r="L25" t="n">
-        <v>624</v>
+        <v>208</v>
       </c>
       <c r="M25" t="n">
-        <v>46.6</v>
+        <v>27.2</v>
       </c>
       <c r="N25" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~47 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 208u = ~27 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26.52</v>
+        <v>10.85</v>
       </c>
       <c r="E26" t="n">
-        <v>24.2</v>
+        <v>8.68</v>
       </c>
       <c r="F26" t="n">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H26" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>13.9</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="K26" t="n">
-        <v>208</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>208</v>
+        <v>6</v>
       </c>
       <c r="M26" t="n">
-        <v>26.3</v>
+        <v>0.7</v>
       </c>
       <c r="N26" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O26" t="n">
         <v>18</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~26 wks (overstock); consider ~208u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.5</v>
+        <v>16.67</v>
       </c>
       <c r="E27" t="n">
-        <v>9.06</v>
+        <v>13.34</v>
       </c>
       <c r="F27" t="n">
-        <v>1.44</v>
+        <v>3.33</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H27" t="n">
-        <v>11.6</v>
+        <v>5.2</v>
       </c>
       <c r="I27" t="n">
-        <v>9</v>
+        <v>10.7</v>
       </c>
       <c r="J27" t="n">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="K27" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L27" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M27" t="n">
-        <v>54</v>
+        <v>2.3</v>
       </c>
       <c r="N27" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O27" t="n">
         <v>17</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~54 wks (overstock); consider ~624u</t>
+          <t>BUY ~12u (4cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,55 +2019,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>10.85</v>
       </c>
       <c r="E28" t="n">
-        <v>9.9</v>
+        <v>8.68</v>
       </c>
       <c r="F28" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="G28" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H28" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="I28" t="n">
-        <v>11.2</v>
+        <v>26.4</v>
       </c>
       <c r="J28" t="n">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="K28" t="n">
         <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M28" t="n">
-        <v>2.2</v>
+        <v>0.8</v>
       </c>
       <c r="N28" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O28" t="n">
         <v>17</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.85</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>8.68</v>
+        <v>9.9</v>
       </c>
       <c r="F29" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="I29" t="n">
-        <v>26.2</v>
+        <v>11.3</v>
       </c>
       <c r="J29" t="n">
-        <v>115</v>
+        <v>51</v>
       </c>
       <c r="K29" t="n">
         <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="N29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O29" t="n">
         <v>17</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E30" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F30" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H30" t="n">
-        <v>7.5</v>
+        <v>11.2</v>
       </c>
       <c r="I30" t="n">
-        <v>27.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8</v>
+        <v>55.9</v>
       </c>
       <c r="N30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O30" t="n">
         <v>16</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~56 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2197,51 +2197,51 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.33</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
-        <v>8.01</v>
+        <v>18.02</v>
       </c>
       <c r="F31" t="n">
-        <v>1.32</v>
+        <v>1.98</v>
       </c>
       <c r="G31" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H31" t="n">
-        <v>10.4</v>
+        <v>7.2</v>
       </c>
       <c r="I31" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="J31" t="n">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="K31" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="L31" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="M31" t="n">
-        <v>14.4</v>
+        <v>5.5</v>
       </c>
       <c r="N31" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O31" t="n">
         <v>14</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
+          <t>BUY ~40u (10cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2255,51 +2255,51 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>9.33</v>
       </c>
       <c r="E32" t="n">
-        <v>18.02</v>
+        <v>8.01</v>
       </c>
       <c r="F32" t="n">
-        <v>1.98</v>
+        <v>1.32</v>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>7.2</v>
+        <v>10.2</v>
       </c>
       <c r="I32" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="J32" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="K32" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="L32" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="M32" t="n">
-        <v>5.5</v>
+        <v>14.8</v>
       </c>
       <c r="N32" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~6 wks</t>
+          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E33" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G33" t="n">
+        <v>14</v>
+      </c>
+      <c r="H33" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>70</v>
+      </c>
+      <c r="K33" t="n">
+        <v>624</v>
+      </c>
+      <c r="L33" t="n">
+        <v>624</v>
+      </c>
+      <c r="M33" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="N33" t="n">
+        <v>45</v>
+      </c>
+      <c r="O33" t="n">
         <v>12</v>
       </c>
-      <c r="E33" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G33" t="n">
-        <v>7</v>
-      </c>
-      <c r="H33" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="I33" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J33" t="n">
-        <v>106</v>
-      </c>
-      <c r="K33" t="n">
-        <v>84</v>
-      </c>
-      <c r="L33" t="n">
-        <v>84</v>
-      </c>
-      <c r="M33" t="n">
-        <v>5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>44</v>
-      </c>
-      <c r="O33" t="n">
-        <v>14</v>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~5 wks</t>
+          <t>CAUTION - 624u = ~74 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,55 +2367,55 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.03</v>
+        <v>12</v>
       </c>
       <c r="E34" t="n">
-        <v>9.15</v>
+        <v>11.2</v>
       </c>
       <c r="F34" t="n">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="G34" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H34" t="n">
-        <v>14.9</v>
+        <v>15.3</v>
       </c>
       <c r="I34" t="n">
-        <v>10.4</v>
+        <v>6.4</v>
       </c>
       <c r="J34" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="K34" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="L34" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="M34" t="n">
-        <v>41.8</v>
+        <v>5.5</v>
       </c>
       <c r="N34" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
+          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2425,55 +2425,55 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>10.03</v>
       </c>
       <c r="E35" t="n">
-        <v>9.82</v>
+        <v>9.15</v>
       </c>
       <c r="F35" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="G35" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H35" t="n">
-        <v>10.2</v>
+        <v>14.2</v>
       </c>
       <c r="I35" t="n">
-        <v>12.1</v>
+        <v>10.9</v>
       </c>
       <c r="J35" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K35" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L35" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M35" t="n">
-        <v>14.7</v>
+        <v>44</v>
       </c>
       <c r="N35" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O35" t="n">
         <v>12</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~44 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,48 +2483,48 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>8.4</v>
+        <v>9.82</v>
       </c>
       <c r="F36" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="G36" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H36" t="n">
-        <v>5.5</v>
+        <v>10.1</v>
       </c>
       <c r="I36" t="n">
-        <v>3.4</v>
+        <v>12.1</v>
       </c>
       <c r="J36" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="K36" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L36" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="M36" t="n">
-        <v>4.4</v>
+        <v>14.9</v>
       </c>
       <c r="N36" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="O36" t="n">
         <v>12</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~4 wks</t>
+          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2545,44 +2545,44 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8.67</v>
+        <v>10.5</v>
       </c>
       <c r="E37" t="n">
-        <v>6.57</v>
+        <v>8.4</v>
       </c>
       <c r="F37" t="n">
         <v>2.1</v>
       </c>
       <c r="G37" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H37" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I37" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K37" t="n">
         <v>6</v>
       </c>
       <c r="L37" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M37" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="N37" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~4 wks</t>
+          <t>BUY ~12u (2cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -2615,39 +2615,39 @@
         <v>22</v>
       </c>
       <c r="H38" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="I38" t="n">
-        <v>3.4</v>
+        <v>5.9</v>
       </c>
       <c r="J38" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K38" t="n">
         <v>6</v>
       </c>
       <c r="L38" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M38" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="N38" t="n">
         <v>46</v>
       </c>
       <c r="O38" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~4 wks</t>
+          <t>BUY ~12u (2cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,48 +2657,48 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.5</v>
+        <v>8.67</v>
       </c>
       <c r="E39" t="n">
-        <v>9.06</v>
+        <v>6.57</v>
       </c>
       <c r="F39" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H39" t="n">
-        <v>8.6</v>
+        <v>5.1</v>
       </c>
       <c r="I39" t="n">
-        <v>6.9</v>
+        <v>5.9</v>
       </c>
       <c r="J39" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="K39" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M39" t="n">
-        <v>72.3</v>
+        <v>2.4</v>
       </c>
       <c r="N39" t="n">
         <v>45</v>
       </c>
       <c r="O39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~72 wks (overstock); consider ~624u</t>
+          <t>BUY ~12u (2cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -2731,10 +2731,10 @@
         <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="I40" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="J40" t="n">
         <v>27</v>
@@ -2746,7 +2746,7 @@
         <v>24</v>
       </c>
       <c r="M40" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="N40" t="n">
         <v>44</v>
@@ -2789,10 +2789,10 @@
         <v>11</v>
       </c>
       <c r="H41" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="I41" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="J41" t="n">
         <v>104</v>
@@ -2804,7 +2804,7 @@
         <v>150</v>
       </c>
       <c r="M41" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="N41" t="n">
         <v>55</v>
@@ -2847,13 +2847,13 @@
         <v>24</v>
       </c>
       <c r="H42" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I42" t="n">
-        <v>9.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="J42" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K42" t="n">
         <v>6</v>
@@ -2862,13 +2862,13 @@
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N42" t="n">
         <v>45</v>
       </c>
       <c r="O42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -2905,13 +2905,13 @@
         <v>22</v>
       </c>
       <c r="H43" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I43" t="n">
-        <v>9.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="J43" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K43" t="n">
         <v>6</v>
@@ -2920,13 +2920,13 @@
         <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N43" t="n">
         <v>46</v>
       </c>
       <c r="O43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -2963,13 +2963,13 @@
         <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="I44" t="n">
-        <v>9.199999999999999</v>
+        <v>14.2</v>
       </c>
       <c r="J44" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="K44" t="n">
         <v>6</v>
@@ -2978,13 +2978,13 @@
         <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="N44" t="n">
         <v>47</v>
       </c>
       <c r="O44" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -3137,10 +3137,10 @@
         <v>15</v>
       </c>
       <c r="H47" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I47" t="n">
-        <v>20.1</v>
+        <v>21.6</v>
       </c>
       <c r="J47" t="n">
         <v>41</v>
@@ -3152,7 +3152,7 @@
         <v>40</v>
       </c>
       <c r="M47" t="n">
-        <v>21</v>
+        <v>22.5</v>
       </c>
       <c r="N47" t="n">
         <v>48</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~21 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 40u = ~22 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
@@ -3256,10 +3256,10 @@
         <v>2.9</v>
       </c>
       <c r="I49" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="J49" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K49" t="n">
         <v>150</v>
@@ -3430,10 +3430,10 @@
         <v>1.1</v>
       </c>
       <c r="I52" t="n">
-        <v>17.3</v>
+        <v>20.6</v>
       </c>
       <c r="J52" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K52" t="n">
         <v>624</v>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>157.6</v>
+        <v>154.5</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
-        <v>419</v>
+        <v>492</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>842</v>
+        <v>744</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~842u (421cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~744u (372cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>43.6</v>
+        <v>42.6</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>21.1</v>
+        <v>19.8</v>
       </c>
       <c r="I4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~64u (32cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~58u (29cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>27.4</v>
+        <v>26.9</v>
       </c>
       <c r="I5" t="n">
-        <v>11.7</v>
+        <v>11.5</v>
       </c>
       <c r="J5" t="n">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>23.3</v>
+        <v>22.7</v>
       </c>
       <c r="I6" t="n">
         <v>4.4</v>
       </c>
       <c r="J6" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K6" t="n">
         <v>24</v>
@@ -774,13 +774,13 @@
         <v>132</v>
       </c>
       <c r="M6" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="N6" t="n">
         <v>44</v>
       </c>
       <c r="O6" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>13</v>
       </c>
       <c r="H7" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J7" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="K7" t="n">
         <v>50</v>
@@ -832,13 +832,13 @@
         <v>50</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N7" t="n">
         <v>48</v>
       </c>
       <c r="O7" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -875,22 +875,22 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="I8" t="n">
-        <v>13.5</v>
+        <v>12.9</v>
       </c>
       <c r="J8" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>46</v>
@@ -900,7 +900,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~18u (3cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -933,13 +933,13 @@
         <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>25.8</v>
+        <v>25.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="J9" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="K9" t="n">
         <v>624</v>
@@ -948,17 +948,17 @@
         <v>624</v>
       </c>
       <c r="M9" t="n">
-        <v>24.2</v>
+        <v>24.7</v>
       </c>
       <c r="N9" t="n">
         <v>45</v>
       </c>
       <c r="O9" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~24 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -991,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>40.2</v>
+        <v>38.6</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="K10" t="n">
         <v>624</v>
@@ -1006,17 +1006,17 @@
         <v>624</v>
       </c>
       <c r="M10" t="n">
-        <v>15.5</v>
+        <v>16.2</v>
       </c>
       <c r="N10" t="n">
         <v>46</v>
       </c>
       <c r="O10" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~624u (104cs) - sells in ~16 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~16 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1052,10 +1052,10 @@
         <v>35.9</v>
       </c>
       <c r="I11" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="K11" t="n">
         <v>624</v>
@@ -1081,7 +1081,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1091,29 +1091,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>25.9</v>
+        <v>25.7</v>
       </c>
       <c r="E12" t="n">
-        <v>20.72</v>
+        <v>21.7</v>
       </c>
       <c r="F12" t="n">
-        <v>5.18</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>5.7</v>
+        <v>7.6</v>
       </c>
       <c r="I12" t="n">
-        <v>11.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1125,10 +1125,10 @@
         <v>0.3</v>
       </c>
       <c r="N12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,55 +1149,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.5</v>
+        <v>10.03</v>
       </c>
       <c r="E13" t="n">
-        <v>21.32</v>
+        <v>9.15</v>
       </c>
       <c r="F13" t="n">
-        <v>5.18</v>
+        <v>0.88</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>5.7</v>
+        <v>32.2</v>
       </c>
       <c r="I13" t="n">
-        <v>11.7</v>
+        <v>7.8</v>
       </c>
       <c r="J13" t="n">
-        <v>72</v>
+        <v>140</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3</v>
+        <v>19.4</v>
       </c>
       <c r="N13" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,48 +1207,48 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>25.7</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>21.7</v>
+        <v>16.67</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="G14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I14" t="n">
-        <v>9.6</v>
+        <v>16.6</v>
       </c>
       <c r="J14" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N14" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1269,22 +1269,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23.4</v>
+        <v>26.5</v>
       </c>
       <c r="E15" t="n">
-        <v>18.22</v>
+        <v>21.32</v>
       </c>
       <c r="F15" t="n">
         <v>5.18</v>
       </c>
       <c r="G15" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>11.7</v>
+        <v>13.6</v>
       </c>
       <c r="J15" t="n">
         <v>72</v>
@@ -1296,13 +1296,13 @@
         <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="N15" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1323,55 +1323,55 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>23.4</v>
       </c>
       <c r="E16" t="n">
-        <v>16.67</v>
+        <v>18.22</v>
       </c>
       <c r="F16" t="n">
-        <v>3.33</v>
+        <v>5.18</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>8.199999999999999</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>16.5</v>
+        <v>13.6</v>
       </c>
       <c r="J16" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>0.4</v>
       </c>
       <c r="N16" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="O16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1381,48 +1381,48 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.03</v>
+        <v>25.9</v>
       </c>
       <c r="E17" t="n">
-        <v>9.15</v>
+        <v>20.72</v>
       </c>
       <c r="F17" t="n">
-        <v>0.88</v>
+        <v>5.18</v>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>30.9</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>8.5</v>
+        <v>13.6</v>
       </c>
       <c r="J17" t="n">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="K17" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>20.2</v>
+        <v>0.4</v>
       </c>
       <c r="N17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~20 wks (overstock); consider ~624u</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
         <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I18" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>50</v>
       </c>
       <c r="O18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUY ~8u (4cs) - sells in ~1 wks</t>
+          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1513,39 +1513,39 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>28.2</v>
+        <v>27.5</v>
       </c>
       <c r="I19" t="n">
-        <v>8.9</v>
+        <v>11.1</v>
       </c>
       <c r="J19" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="K19" t="n">
         <v>84</v>
       </c>
       <c r="L19" t="n">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N19" t="n">
         <v>44</v>
       </c>
       <c r="O19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUY ~90u (15cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,55 +1555,55 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G20" t="n">
+        <v>20</v>
+      </c>
+      <c r="H20" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="I20" t="n">
         <v>12</v>
       </c>
-      <c r="E20" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="G20" t="n">
-        <v>17</v>
-      </c>
-      <c r="H20" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="I20" t="n">
-        <v>5.1</v>
-      </c>
       <c r="J20" t="n">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>5.3</v>
+        <v>0.6</v>
       </c>
       <c r="N20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~54u (9cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,48 +1613,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.85</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>8.68</v>
+        <v>9.9</v>
       </c>
       <c r="F21" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>9.300000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="I21" t="n">
-        <v>13.3</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
-        <v>99</v>
+        <v>28</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6</v>
+        <v>5.4</v>
       </c>
       <c r="N21" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~54u (9cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1687,13 +1687,13 @@
         <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="I22" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="K22" t="n">
         <v>624</v>
@@ -1702,7 +1702,7 @@
         <v>624</v>
       </c>
       <c r="M22" t="n">
-        <v>45.6</v>
+        <v>45.9</v>
       </c>
       <c r="N22" t="n">
         <v>45</v>
@@ -1745,13 +1745,13 @@
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>13.6</v>
+        <v>12.5</v>
       </c>
       <c r="I23" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="J23" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K23" t="n">
         <v>624</v>
@@ -1760,17 +1760,17 @@
         <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>46</v>
+        <v>50.1</v>
       </c>
       <c r="N23" t="n">
         <v>45</v>
       </c>
       <c r="O23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~46 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1803,13 +1803,13 @@
         <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>24.1</v>
+        <v>23</v>
       </c>
       <c r="I24" t="n">
-        <v>8.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="J24" t="n">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="K24" t="n">
         <v>84</v>
@@ -1818,13 +1818,13 @@
         <v>84</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
         <v>44</v>
       </c>
       <c r="O24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,55 +1845,55 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.52</v>
+        <v>10.85</v>
       </c>
       <c r="E25" t="n">
-        <v>24.2</v>
+        <v>8.68</v>
       </c>
       <c r="F25" t="n">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="I25" t="n">
-        <v>14.4</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="K25" t="n">
-        <v>208</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>208</v>
+        <v>6</v>
       </c>
       <c r="M25" t="n">
-        <v>27.2</v>
+        <v>0.7</v>
       </c>
       <c r="N25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O25" t="n">
         <v>18</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~27 wks (overstock); consider ~208u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.85</v>
+        <v>26.52</v>
       </c>
       <c r="E26" t="n">
-        <v>8.68</v>
+        <v>24.2</v>
       </c>
       <c r="F26" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H26" t="n">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>14.7</v>
       </c>
       <c r="J26" t="n">
-        <v>114</v>
+        <v>60</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="L26" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7</v>
+        <v>28.4</v>
       </c>
       <c r="N26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 208u = ~28 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,48 +1961,48 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16.67</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>13.34</v>
+        <v>9.9</v>
       </c>
       <c r="F27" t="n">
-        <v>3.33</v>
+        <v>2.1</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H27" t="n">
-        <v>5.2</v>
+        <v>7.9</v>
       </c>
       <c r="I27" t="n">
-        <v>10.7</v>
+        <v>11.1</v>
       </c>
       <c r="J27" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M27" t="n">
         <v>2.3</v>
       </c>
       <c r="N27" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O27" t="n">
         <v>17</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~12u (4cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2035,13 +2035,13 @@
         <v>20</v>
       </c>
       <c r="H28" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="I28" t="n">
-        <v>26.4</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="K28" t="n">
         <v>6</v>
@@ -2056,7 +2056,7 @@
         <v>46</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E29" t="n">
-        <v>9.9</v>
+        <v>9.06</v>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G29" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>8.1</v>
+        <v>10.7</v>
       </c>
       <c r="I29" t="n">
-        <v>11.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J29" t="n">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L29" t="n">
-        <v>18</v>
+        <v>624</v>
       </c>
       <c r="M29" t="n">
-        <v>2.2</v>
+        <v>58.1</v>
       </c>
       <c r="N29" t="n">
         <v>45</v>
       </c>
       <c r="O29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~58 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.5</v>
+        <v>16.67</v>
       </c>
       <c r="E30" t="n">
-        <v>9.06</v>
+        <v>13.34</v>
       </c>
       <c r="F30" t="n">
-        <v>1.44</v>
+        <v>3.33</v>
       </c>
       <c r="G30" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H30" t="n">
-        <v>11.2</v>
+        <v>4.6</v>
       </c>
       <c r="I30" t="n">
-        <v>9.300000000000001</v>
+        <v>12</v>
       </c>
       <c r="J30" t="n">
-        <v>111</v>
+        <v>31</v>
       </c>
       <c r="K30" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>624</v>
+        <v>9</v>
       </c>
       <c r="M30" t="n">
-        <v>55.9</v>
+        <v>1.9</v>
       </c>
       <c r="N30" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~56 wks (overstock); consider ~624u</t>
+          <t>BUY ~9u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2197,51 +2197,51 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>20</v>
+        <v>9.33</v>
       </c>
       <c r="E31" t="n">
-        <v>18.02</v>
+        <v>8.01</v>
       </c>
       <c r="F31" t="n">
-        <v>1.98</v>
+        <v>1.32</v>
       </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H31" t="n">
-        <v>7.2</v>
+        <v>10.3</v>
       </c>
       <c r="I31" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>86</v>
+        <v>56</v>
       </c>
       <c r="K31" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="L31" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="M31" t="n">
-        <v>5.5</v>
+        <v>14.6</v>
       </c>
       <c r="N31" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="O31" t="n">
         <v>14</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~6 wks</t>
+          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2255,51 +2255,51 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.33</v>
+        <v>20</v>
       </c>
       <c r="E32" t="n">
-        <v>8.01</v>
+        <v>18.02</v>
       </c>
       <c r="F32" t="n">
-        <v>1.32</v>
+        <v>1.98</v>
       </c>
       <c r="G32" t="n">
+        <v>10</v>
+      </c>
+      <c r="H32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="J32" t="n">
+        <v>83</v>
+      </c>
+      <c r="K32" t="n">
+        <v>40</v>
+      </c>
+      <c r="L32" t="n">
+        <v>40</v>
+      </c>
+      <c r="M32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>47</v>
+      </c>
+      <c r="O32" t="n">
         <v>14</v>
       </c>
-      <c r="H32" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="I32" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J32" t="n">
-        <v>59</v>
-      </c>
-      <c r="K32" t="n">
-        <v>150</v>
-      </c>
-      <c r="L32" t="n">
-        <v>150</v>
-      </c>
-      <c r="M32" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="N32" t="n">
-        <v>50</v>
-      </c>
-      <c r="O32" t="n">
-        <v>13</v>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
+          <t>BUY ~40u (10cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,29 +2309,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.5</v>
+        <v>10.03</v>
       </c>
       <c r="E33" t="n">
-        <v>9.06</v>
+        <v>9.15</v>
       </c>
       <c r="F33" t="n">
-        <v>1.44</v>
+        <v>0.88</v>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>8.5</v>
+        <v>15.5</v>
       </c>
       <c r="I33" t="n">
-        <v>7.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="K33" t="n">
         <v>624</v>
@@ -2340,24 +2340,24 @@
         <v>624</v>
       </c>
       <c r="M33" t="n">
-        <v>73.7</v>
+        <v>40.2</v>
       </c>
       <c r="N33" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~74 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,55 +2367,55 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E34" t="n">
-        <v>11.2</v>
+        <v>9.06</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8</v>
+        <v>1.44</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H34" t="n">
-        <v>15.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>6.4</v>
+        <v>7.1</v>
       </c>
       <c r="J34" t="n">
-        <v>105</v>
+        <v>66</v>
       </c>
       <c r="K34" t="n">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="L34" t="n">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="M34" t="n">
-        <v>5.5</v>
+        <v>71.2</v>
       </c>
       <c r="N34" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
+          <t>CAUTION - 624u = ~71 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2425,55 +2425,55 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E35" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F35" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G35" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H35" t="n">
-        <v>14.2</v>
+        <v>10.2</v>
       </c>
       <c r="I35" t="n">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="J35" t="n">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="K35" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L35" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M35" t="n">
-        <v>44</v>
+        <v>14.7</v>
       </c>
       <c r="N35" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O35" t="n">
         <v>12</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~44 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,48 +2483,48 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>12</v>
+      </c>
+      <c r="E36" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G36" t="n">
+        <v>7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>14</v>
+      </c>
+      <c r="I36" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J36" t="n">
+        <v>147</v>
+      </c>
+      <c r="K36" t="n">
+        <v>84</v>
+      </c>
+      <c r="L36" t="n">
+        <v>84</v>
+      </c>
+      <c r="M36" t="n">
+        <v>6</v>
+      </c>
+      <c r="N36" t="n">
+        <v>44</v>
+      </c>
+      <c r="O36" t="n">
         <v>11</v>
       </c>
-      <c r="E36" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G36" t="n">
-        <v>11</v>
-      </c>
-      <c r="H36" t="n">
-        <v>10.1</v>
-      </c>
-      <c r="I36" t="n">
-        <v>12.1</v>
-      </c>
-      <c r="J36" t="n">
-        <v>83</v>
-      </c>
-      <c r="K36" t="n">
-        <v>150</v>
-      </c>
-      <c r="L36" t="n">
-        <v>150</v>
-      </c>
-      <c r="M36" t="n">
-        <v>14.9</v>
-      </c>
-      <c r="N36" t="n">
-        <v>55</v>
-      </c>
-      <c r="O36" t="n">
-        <v>12</v>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
@@ -2545,22 +2545,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>10.5</v>
+        <v>8.67</v>
       </c>
       <c r="E37" t="n">
-        <v>8.4</v>
+        <v>6.57</v>
       </c>
       <c r="F37" t="n">
         <v>2.1</v>
       </c>
       <c r="G37" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H37" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="I37" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="J37" t="n">
         <v>32</v>
@@ -2569,20 +2569,20 @@
         <v>6</v>
       </c>
       <c r="L37" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M37" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="N37" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O37" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~2 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -2615,10 +2615,10 @@
         <v>22</v>
       </c>
       <c r="H38" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="I38" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="J38" t="n">
         <v>32</v>
@@ -2627,27 +2627,27 @@
         <v>6</v>
       </c>
       <c r="L38" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="N38" t="n">
         <v>46</v>
       </c>
       <c r="O38" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~2 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,55 +2657,55 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8.67</v>
+        <v>11</v>
       </c>
       <c r="E39" t="n">
-        <v>6.57</v>
+        <v>9.82</v>
       </c>
       <c r="F39" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="G39" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H39" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="I39" t="n">
-        <v>5.9</v>
+        <v>16.8</v>
       </c>
       <c r="J39" t="n">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="K39" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L39" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="M39" t="n">
-        <v>2.4</v>
+        <v>18.8</v>
       </c>
       <c r="N39" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O39" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~2 wks</t>
+          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2715,55 +2715,55 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="E40" t="n">
-        <v>11.2</v>
+        <v>8.4</v>
       </c>
       <c r="F40" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="G40" t="n">
         <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="I40" t="n">
-        <v>10.3</v>
+        <v>7</v>
       </c>
       <c r="J40" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K40" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L40" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="N40" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O40" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,55 +2773,55 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E41" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F41" t="n">
-        <v>1.18</v>
+        <v>2.8</v>
       </c>
       <c r="G41" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>8.1</v>
+        <v>3.2</v>
       </c>
       <c r="I41" t="n">
-        <v>16.5</v>
+        <v>12.4</v>
       </c>
       <c r="J41" t="n">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="K41" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="L41" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="M41" t="n">
-        <v>18.5</v>
+        <v>7.5</v>
       </c>
       <c r="N41" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="O41" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
+          <t>BUY ~24u (4cs) - sells in ~8 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2831,38 +2831,38 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8.67</v>
+        <v>11</v>
       </c>
       <c r="E42" t="n">
-        <v>6.57</v>
+        <v>9.82</v>
       </c>
       <c r="F42" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="G42" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H42" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
       <c r="I42" t="n">
-        <v>14.2</v>
+        <v>18.3</v>
       </c>
       <c r="J42" t="n">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="K42" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L42" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M42" t="n">
-        <v>1.7</v>
+        <v>26.8</v>
       </c>
       <c r="N42" t="n">
         <v>45</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
+          <t>CAUTION - 150u = ~27 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2893,22 +2893,22 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>9.67</v>
+        <v>8.67</v>
       </c>
       <c r="E43" t="n">
-        <v>7.57</v>
+        <v>6.57</v>
       </c>
       <c r="F43" t="n">
         <v>2.1</v>
       </c>
       <c r="G43" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H43" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="I43" t="n">
-        <v>14.2</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
         <v>53</v>
@@ -2920,13 +2920,13 @@
         <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N43" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O43" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
         <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="I44" t="n">
-        <v>14.2</v>
+        <v>17</v>
       </c>
       <c r="J44" t="n">
         <v>53</v>
@@ -2978,13 +2978,13 @@
         <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="N44" t="n">
         <v>47</v>
       </c>
       <c r="O44" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3005,48 +3005,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11</v>
+        <v>9.67</v>
       </c>
       <c r="E45" t="n">
-        <v>9.82</v>
+        <v>7.57</v>
       </c>
       <c r="F45" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="G45" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H45" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="I45" t="n">
-        <v>19.2</v>
+        <v>17</v>
       </c>
       <c r="J45" t="n">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="K45" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L45" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>27.5</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O45" t="n">
         <v>6</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~28 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -3082,10 +3082,10 @@
         <v>3.7</v>
       </c>
       <c r="I46" t="n">
-        <v>62.3</v>
+        <v>63.9</v>
       </c>
       <c r="J46" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="K46" t="n">
         <v>150</v>
@@ -3094,7 +3094,7 @@
         <v>150</v>
       </c>
       <c r="M46" t="n">
-        <v>40.3</v>
+        <v>40.8</v>
       </c>
       <c r="N46" t="n">
         <v>50</v>
@@ -3104,14 +3104,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~40 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~41 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
+          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3125,51 +3125,51 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.45</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>11.47</v>
+        <v>9.82</v>
       </c>
       <c r="F47" t="n">
-        <v>1.97</v>
+        <v>1.18</v>
       </c>
       <c r="G47" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="I47" t="n">
-        <v>21.6</v>
+        <v>20.1</v>
       </c>
       <c r="J47" t="n">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="K47" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="L47" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>22.5</v>
+        <v>48.1</v>
       </c>
       <c r="N47" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O47" t="n">
         <v>4</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~22 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 150u = ~48 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3179,55 +3179,55 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.58</v>
+        <v>14</v>
       </c>
       <c r="E48" t="n">
-        <v>7.06</v>
+        <v>11.2</v>
       </c>
       <c r="F48" t="n">
-        <v>3.53</v>
+        <v>2.8</v>
       </c>
       <c r="G48" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="H48" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="I48" t="n">
-        <v>71.40000000000001</v>
+        <v>41.7</v>
       </c>
       <c r="J48" t="n">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="K48" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L48" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M48" t="n">
-        <v>15.9</v>
+        <v>17.7</v>
       </c>
       <c r="N48" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~16 wks (rising into season)</t>
+          <t>CAUTION - 24u = ~18 wks (overstock); consider ~24u</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
+          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3241,51 +3241,51 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>13.45</v>
       </c>
       <c r="E49" t="n">
-        <v>9.82</v>
+        <v>11.47</v>
       </c>
       <c r="F49" t="n">
-        <v>1.18</v>
+        <v>1.97</v>
       </c>
       <c r="G49" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H49" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="I49" t="n">
-        <v>22.5</v>
+        <v>22</v>
       </c>
       <c r="J49" t="n">
-        <v>82</v>
+        <v>41</v>
       </c>
       <c r="K49" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="L49" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>52.6</v>
+        <v>22.9</v>
       </c>
       <c r="N49" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~53 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 40u = ~23 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3295,48 +3295,48 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>14</v>
+        <v>10.58</v>
       </c>
       <c r="E50" t="n">
-        <v>11.2</v>
+        <v>7.06</v>
       </c>
       <c r="F50" t="n">
-        <v>2.8</v>
+        <v>3.53</v>
       </c>
       <c r="G50" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="H50" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="I50" t="n">
-        <v>46.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="K50" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L50" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M50" t="n">
-        <v>19.6</v>
+        <v>15.9</v>
       </c>
       <c r="N50" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CAUTION - 24u = ~20 wks (overstock); consider ~24u</t>
+          <t>BUY ~12u (2cs) - sells in ~16 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -3369,10 +3369,10 @@
         <v>11</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I51" t="n">
-        <v>94.2</v>
+        <v>111.5</v>
       </c>
       <c r="J51" t="n">
         <v>85</v>
@@ -3384,7 +3384,7 @@
         <v>150</v>
       </c>
       <c r="M51" t="n">
-        <v>177.5</v>
+        <v>210.1</v>
       </c>
       <c r="N51" t="n">
         <v>55</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~178 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~210 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3427,13 +3427,13 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="I52" t="n">
-        <v>20.6</v>
+        <v>18.2</v>
       </c>
       <c r="J52" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K52" t="n">
         <v>624</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>549</v>
+        <v>503.7</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~549 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~504 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3797,13 +3797,13 @@
         <v>9</v>
       </c>
       <c r="H59" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I59" t="n">
-        <v>587.1</v>
+        <v>548.4</v>
       </c>
       <c r="J59" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K59" t="n">
         <v>60</v>
@@ -3812,7 +3812,7 @@
         <v>60</v>
       </c>
       <c r="M59" t="n">
-        <v>137.2</v>
+        <v>128.7</v>
       </c>
       <c r="N59" t="n">
         <v>48</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~137 wks (overstock); consider ~60u</t>
+          <t>CAUTION - 60u = ~129 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,13 +527,13 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>154.5</v>
+        <v>153.4</v>
       </c>
       <c r="I2" t="n">
         <v>5.7</v>
       </c>
       <c r="J2" t="n">
-        <v>492</v>
+        <v>485</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
@@ -548,7 +548,7 @@
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J3" t="n">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -606,7 +606,7 @@
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>19.8</v>
+        <v>20.8</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="M4" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~58u (29cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~72u (36cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>26.9</v>
+        <v>27.3</v>
       </c>
       <c r="I5" t="n">
-        <v>11.5</v>
+        <v>11.1</v>
       </c>
       <c r="J5" t="n">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
+          <t>Clrty Variety 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -743,55 +743,55 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14</v>
+        <v>29.5</v>
       </c>
       <c r="E6" t="n">
-        <v>11.2</v>
+        <v>25.54</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8</v>
+        <v>3.96</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>22.7</v>
+        <v>14.6</v>
       </c>
       <c r="I6" t="n">
         <v>4.4</v>
       </c>
       <c r="J6" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="K6" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="N6" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~132u (22cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~50u (25cs) - sells in ~3 wks</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Clrty Variety 10mg THC 12pk 12oz can</t>
+          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -801,48 +801,48 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29.5</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
-        <v>25.54</v>
+        <v>11.2</v>
       </c>
       <c r="F7" t="n">
-        <v>3.96</v>
+        <v>2.8</v>
       </c>
       <c r="G7" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>14.4</v>
+        <v>19.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="J7" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="K7" t="n">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="L7" t="n">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="M7" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="N7" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="O7" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BUY ~50u (25cs) - sells in ~4 wks</t>
+          <t>BUY ~102u (17cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -878,7 +878,7 @@
         <v>18.5</v>
       </c>
       <c r="I8" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="J8" t="n">
         <v>133</v>
@@ -933,13 +933,13 @@
         <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="I9" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="J9" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="K9" t="n">
         <v>624</v>
@@ -948,7 +948,7 @@
         <v>624</v>
       </c>
       <c r="M9" t="n">
-        <v>24.7</v>
+        <v>25</v>
       </c>
       <c r="N9" t="n">
         <v>45</v>
@@ -991,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>38.6</v>
+        <v>38.4</v>
       </c>
       <c r="I10" t="n">
         <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K10" t="n">
         <v>624</v>
@@ -1006,7 +1006,7 @@
         <v>624</v>
       </c>
       <c r="M10" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="N10" t="n">
         <v>46</v>
@@ -1052,10 +1052,10 @@
         <v>35.9</v>
       </c>
       <c r="I11" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="J11" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="K11" t="n">
         <v>624</v>
@@ -1107,13 +1107,13 @@
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
       <c r="I12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1165,13 +1165,13 @@
         <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>32.2</v>
+        <v>30.9</v>
       </c>
       <c r="I13" t="n">
-        <v>7.8</v>
+        <v>8.5</v>
       </c>
       <c r="J13" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="K13" t="n">
         <v>624</v>
@@ -1180,17 +1180,17 @@
         <v>624</v>
       </c>
       <c r="M13" t="n">
-        <v>19.4</v>
+        <v>20.2</v>
       </c>
       <c r="N13" t="n">
         <v>46</v>
       </c>
       <c r="O13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~20 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1223,10 +1223,10 @@
         <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I14" t="n">
-        <v>16.6</v>
+        <v>17.5</v>
       </c>
       <c r="J14" t="n">
         <v>82</v>
@@ -1244,7 +1244,7 @@
         <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,48 +1265,48 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="E15" t="n">
-        <v>21.32</v>
+        <v>21.7</v>
       </c>
       <c r="F15" t="n">
-        <v>5.18</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="I15" t="n">
-        <v>13.6</v>
+        <v>6.9</v>
       </c>
       <c r="J15" t="n">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N15" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>BUY ~4u (2cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I16" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="J16" t="n">
         <v>72</v>
@@ -1360,7 +1360,7 @@
         <v>51</v>
       </c>
       <c r="O16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I17" t="n">
-        <v>13.6</v>
+        <v>13.8</v>
       </c>
       <c r="J17" t="n">
         <v>72</v>
@@ -1418,7 +1418,7 @@
         <v>44</v>
       </c>
       <c r="O17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,48 +1439,48 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>25.7</v>
+        <v>26.5</v>
       </c>
       <c r="E18" t="n">
-        <v>21.7</v>
+        <v>21.32</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>5.18</v>
       </c>
       <c r="G18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H18" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>13.8</v>
       </c>
       <c r="J18" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N18" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="O18" t="n">
         <v>25</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
@@ -1513,13 +1513,13 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>27.5</v>
+        <v>27.2</v>
       </c>
       <c r="I19" t="n">
-        <v>11.1</v>
+        <v>12.9</v>
       </c>
       <c r="J19" t="n">
-        <v>170</v>
+        <v>194</v>
       </c>
       <c r="K19" t="n">
         <v>84</v>
@@ -1571,13 +1571,13 @@
         <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>12.9</v>
       </c>
       <c r="J20" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="K20" t="n">
         <v>6</v>
@@ -1592,7 +1592,7 @@
         <v>46</v>
       </c>
       <c r="O20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
         <v>17</v>
       </c>
       <c r="H21" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
         <v>28</v>
@@ -1644,17 +1644,17 @@
         <v>54</v>
       </c>
       <c r="M21" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="N21" t="n">
         <v>45</v>
       </c>
       <c r="O21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~54u (9cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~54u (9cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1687,13 +1687,13 @@
         <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="I22" t="n">
-        <v>8.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="J22" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="K22" t="n">
         <v>624</v>
@@ -1702,13 +1702,13 @@
         <v>624</v>
       </c>
       <c r="M22" t="n">
-        <v>45.9</v>
+        <v>46.4</v>
       </c>
       <c r="N22" t="n">
         <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -1745,13 +1745,13 @@
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="I23" t="n">
-        <v>7.3</v>
+        <v>6.7</v>
       </c>
       <c r="J23" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K23" t="n">
         <v>624</v>
@@ -1760,17 +1760,17 @@
         <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>50.1</v>
+        <v>47.8</v>
       </c>
       <c r="N23" t="n">
         <v>45</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1803,13 +1803,13 @@
         <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="I24" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="J24" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K24" t="n">
         <v>84</v>
@@ -1818,13 +1818,13 @@
         <v>84</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
         <v>44</v>
       </c>
       <c r="O24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -1861,10 +1861,10 @@
         <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>24.3</v>
       </c>
       <c r="J25" t="n">
         <v>112</v>
@@ -1893,7 +1893,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26.52</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>24.2</v>
+        <v>9.9</v>
       </c>
       <c r="F26" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="G26" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H26" t="n">
-        <v>7.3</v>
+        <v>8</v>
       </c>
       <c r="I26" t="n">
-        <v>14.7</v>
+        <v>10.8</v>
       </c>
       <c r="J26" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K26" t="n">
-        <v>208</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>208</v>
+        <v>18</v>
       </c>
       <c r="M26" t="n">
-        <v>28.4</v>
+        <v>2.2</v>
       </c>
       <c r="N26" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O26" t="n">
         <v>17</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~28 wks (overstock); consider ~208u</t>
+          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E27" t="n">
-        <v>9.9</v>
+        <v>9.06</v>
       </c>
       <c r="F27" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G27" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>7.9</v>
+        <v>11.4</v>
       </c>
       <c r="I27" t="n">
-        <v>11.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L27" t="n">
-        <v>18</v>
+        <v>624</v>
       </c>
       <c r="M27" t="n">
-        <v>2.3</v>
+        <v>55</v>
       </c>
       <c r="N27" t="n">
         <v>45</v>
       </c>
       <c r="O27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~55 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,55 +2019,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.85</v>
+        <v>16.67</v>
       </c>
       <c r="E28" t="n">
-        <v>8.68</v>
+        <v>13.34</v>
       </c>
       <c r="F28" t="n">
-        <v>2.17</v>
+        <v>3.33</v>
       </c>
       <c r="G28" t="n">
         <v>20</v>
       </c>
       <c r="H28" t="n">
-        <v>7.2</v>
+        <v>4.7</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>11.4</v>
       </c>
       <c r="J28" t="n">
-        <v>150</v>
+        <v>30</v>
       </c>
       <c r="K28" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="N28" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O28" t="n">
         <v>16</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~9u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.5</v>
+        <v>26.52</v>
       </c>
       <c r="E29" t="n">
-        <v>9.06</v>
+        <v>24.2</v>
       </c>
       <c r="F29" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="G29" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H29" t="n">
-        <v>10.7</v>
+        <v>7.1</v>
       </c>
       <c r="I29" t="n">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="J29" t="n">
-        <v>106</v>
+        <v>59</v>
       </c>
       <c r="K29" t="n">
-        <v>624</v>
+        <v>208</v>
       </c>
       <c r="L29" t="n">
-        <v>624</v>
+        <v>208</v>
       </c>
       <c r="M29" t="n">
-        <v>58.1</v>
+        <v>29.4</v>
       </c>
       <c r="N29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~58 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 208u = ~29 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>16.67</v>
+        <v>10.85</v>
       </c>
       <c r="E30" t="n">
-        <v>13.34</v>
+        <v>8.68</v>
       </c>
       <c r="F30" t="n">
-        <v>3.33</v>
+        <v>2.17</v>
       </c>
       <c r="G30" t="n">
         <v>20</v>
       </c>
       <c r="H30" t="n">
-        <v>4.6</v>
+        <v>7.1</v>
       </c>
       <c r="I30" t="n">
-        <v>12</v>
+        <v>28.3</v>
       </c>
       <c r="J30" t="n">
-        <v>31</v>
+        <v>150</v>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="N30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O30" t="n">
         <v>15</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~9u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2197,51 +2197,51 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.33</v>
+        <v>20</v>
       </c>
       <c r="E31" t="n">
-        <v>8.01</v>
+        <v>18.02</v>
       </c>
       <c r="F31" t="n">
-        <v>1.32</v>
+        <v>1.98</v>
       </c>
       <c r="G31" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H31" t="n">
-        <v>10.3</v>
+        <v>7.2</v>
       </c>
       <c r="I31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="J31" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="K31" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="L31" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="M31" t="n">
-        <v>14.6</v>
+        <v>5.5</v>
       </c>
       <c r="N31" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="O31" t="n">
         <v>14</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
+          <t>BUY ~40u (10cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,55 +2251,55 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>20</v>
+        <v>10.03</v>
       </c>
       <c r="E32" t="n">
-        <v>18.02</v>
+        <v>9.15</v>
       </c>
       <c r="F32" t="n">
-        <v>1.98</v>
+        <v>0.88</v>
       </c>
       <c r="G32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>7.2</v>
+        <v>15.5</v>
       </c>
       <c r="I32" t="n">
-        <v>10.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K32" t="n">
-        <v>40</v>
+        <v>624</v>
       </c>
       <c r="L32" t="n">
-        <v>40</v>
+        <v>624</v>
       </c>
       <c r="M32" t="n">
-        <v>5.5</v>
+        <v>40.4</v>
       </c>
       <c r="N32" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O32" t="n">
         <v>14</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~6 wks</t>
+          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,48 +2309,48 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F33" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H33" t="n">
-        <v>15.5</v>
+        <v>10.7</v>
       </c>
       <c r="I33" t="n">
-        <v>9.199999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="J33" t="n">
         <v>79</v>
       </c>
       <c r="K33" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L33" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M33" t="n">
-        <v>40.2</v>
+        <v>14</v>
       </c>
       <c r="N33" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2383,13 +2383,13 @@
         <v>14</v>
       </c>
       <c r="H34" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I34" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="J34" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K34" t="n">
         <v>624</v>
@@ -2398,7 +2398,7 @@
         <v>624</v>
       </c>
       <c r="M34" t="n">
-        <v>71.2</v>
+        <v>70</v>
       </c>
       <c r="N34" t="n">
         <v>45</v>
@@ -2408,14 +2408,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~71 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~70 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2429,25 +2429,25 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>9.33</v>
       </c>
       <c r="E35" t="n">
-        <v>9.82</v>
+        <v>8.01</v>
       </c>
       <c r="F35" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="G35" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>10.2</v>
+        <v>9.9</v>
       </c>
       <c r="I35" t="n">
-        <v>11.6</v>
+        <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="K35" t="n">
         <v>150</v>
@@ -2456,13 +2456,13 @@
         <v>150</v>
       </c>
       <c r="M35" t="n">
-        <v>14.7</v>
+        <v>15.1</v>
       </c>
       <c r="N35" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="O35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         <v>7</v>
       </c>
       <c r="H36" t="n">
-        <v>14</v>
+        <v>13.8</v>
       </c>
       <c r="I36" t="n">
-        <v>9.800000000000001</v>
+        <v>11.6</v>
       </c>
       <c r="J36" t="n">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="K36" t="n">
         <v>84</v>
@@ -2514,7 +2514,7 @@
         <v>84</v>
       </c>
       <c r="M36" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="N36" t="n">
         <v>44</v>
@@ -2531,7 +2531,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,48 +2541,48 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>8.67</v>
+        <v>11</v>
       </c>
       <c r="E37" t="n">
-        <v>6.57</v>
+        <v>9.82</v>
       </c>
       <c r="F37" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="G37" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>4.3</v>
+        <v>8.1</v>
       </c>
       <c r="I37" t="n">
-        <v>7</v>
+        <v>16.4</v>
       </c>
       <c r="J37" t="n">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="K37" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L37" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M37" t="n">
-        <v>1.4</v>
+        <v>18.6</v>
       </c>
       <c r="N37" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2615,10 +2615,10 @@
         <v>22</v>
       </c>
       <c r="H38" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I38" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J38" t="n">
         <v>32</v>
@@ -2647,7 +2647,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,48 +2657,48 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11</v>
+        <v>8.67</v>
       </c>
       <c r="E39" t="n">
-        <v>9.82</v>
+        <v>6.57</v>
       </c>
       <c r="F39" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H39" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="I39" t="n">
-        <v>16.8</v>
+        <v>7.1</v>
       </c>
       <c r="J39" t="n">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="K39" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>18.8</v>
+        <v>1.4</v>
       </c>
       <c r="N39" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O39" t="n">
         <v>9</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -2731,10 +2731,10 @@
         <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I40" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J40" t="n">
         <v>32</v>
@@ -2789,10 +2789,10 @@
         <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="I41" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="J41" t="n">
         <v>27</v>
@@ -2804,7 +2804,7 @@
         <v>24</v>
       </c>
       <c r="M41" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="N41" t="n">
         <v>44</v>
@@ -2847,13 +2847,13 @@
         <v>11</v>
       </c>
       <c r="H42" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I42" t="n">
-        <v>18.3</v>
+        <v>17.5</v>
       </c>
       <c r="J42" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="K42" t="n">
         <v>150</v>
@@ -2862,7 +2862,7 @@
         <v>150</v>
       </c>
       <c r="M42" t="n">
-        <v>26.8</v>
+        <v>26.1</v>
       </c>
       <c r="N42" t="n">
         <v>45</v>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~27 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~26 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
         <v>2.9</v>
       </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="J43" t="n">
         <v>53</v>
@@ -2920,7 +2920,7 @@
         <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="N43" t="n">
         <v>45</v>
@@ -2966,7 +2966,7 @@
         <v>2.9</v>
       </c>
       <c r="I44" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="J44" t="n">
         <v>53</v>
@@ -2978,7 +2978,7 @@
         <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="N44" t="n">
         <v>47</v>
@@ -3024,7 +3024,7 @@
         <v>2.9</v>
       </c>
       <c r="I45" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="J45" t="n">
         <v>53</v>
@@ -3036,7 +3036,7 @@
         <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="N45" t="n">
         <v>46</v>
@@ -3079,13 +3079,13 @@
         <v>14</v>
       </c>
       <c r="H46" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I46" t="n">
-        <v>63.9</v>
+        <v>60.1</v>
       </c>
       <c r="J46" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K46" t="n">
         <v>150</v>
@@ -3094,7 +3094,7 @@
         <v>150</v>
       </c>
       <c r="M46" t="n">
-        <v>40.8</v>
+        <v>38.6</v>
       </c>
       <c r="N46" t="n">
         <v>50</v>
@@ -3104,7 +3104,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~41 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~39 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3137,13 +3137,13 @@
         <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I47" t="n">
-        <v>20.1</v>
+        <v>19.5</v>
       </c>
       <c r="J47" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K47" t="n">
         <v>150</v>
@@ -3152,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>48.1</v>
+        <v>47.1</v>
       </c>
       <c r="N47" t="n">
         <v>45</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~48 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~47 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3797,10 +3797,10 @@
         <v>9</v>
       </c>
       <c r="H59" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="I59" t="n">
-        <v>548.4</v>
+        <v>731.2</v>
       </c>
       <c r="J59" t="n">
         <v>273</v>
@@ -3812,7 +3812,7 @@
         <v>60</v>
       </c>
       <c r="M59" t="n">
-        <v>128.7</v>
+        <v>171.5</v>
       </c>
       <c r="N59" t="n">
         <v>48</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~129 wks (overstock); consider ~60u</t>
+          <t>CAUTION - 60u = ~172 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>153.4</v>
+        <v>159.2</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
-        <v>485</v>
+        <v>457</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>744</v>
+        <v>818</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~744u (372cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~818u (409cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>42.8</v>
+        <v>43.1</v>
       </c>
       <c r="I3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J4" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="M4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~72u (36cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~80u (40cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>27.3</v>
+        <v>27.8</v>
       </c>
       <c r="I5" t="n">
-        <v>11.1</v>
+        <v>11.6</v>
       </c>
       <c r="J5" t="n">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -716,17 +716,17 @@
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BUY ~40u (20cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~40u (20cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -759,10 +759,10 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
         <v>70</v>
@@ -774,17 +774,17 @@
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~50u (25cs) - sells in ~3 wks</t>
+          <t>BUY ~50u (25cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>19.2</v>
+        <v>18.9</v>
       </c>
       <c r="I7" t="n">
         <v>5.1</v>
@@ -832,13 +832,13 @@
         <v>102</v>
       </c>
       <c r="M7" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="N7" t="n">
         <v>44</v>
       </c>
       <c r="O7" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -875,32 +875,32 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>18.5</v>
+        <v>19.4</v>
       </c>
       <c r="I8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J8" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="M8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N8" t="n">
         <v>46</v>
       </c>
       <c r="O8" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BUY ~18u (3cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~24u (4cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -933,13 +933,13 @@
         <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>24.9</v>
+        <v>25.6</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="K9" t="n">
         <v>624</v>
@@ -948,17 +948,17 @@
         <v>624</v>
       </c>
       <c r="M9" t="n">
-        <v>25</v>
+        <v>24.4</v>
       </c>
       <c r="N9" t="n">
         <v>45</v>
       </c>
       <c r="O9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~24 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -991,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K10" t="n">
         <v>624</v>
@@ -1006,7 +1006,7 @@
         <v>624</v>
       </c>
       <c r="M10" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N10" t="n">
         <v>46</v>
@@ -1049,13 +1049,13 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>35.9</v>
+        <v>36.3</v>
       </c>
       <c r="I11" t="n">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J11" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="K11" t="n">
         <v>624</v>
@@ -1064,7 +1064,7 @@
         <v>624</v>
       </c>
       <c r="M11" t="n">
-        <v>17.4</v>
+        <v>17.2</v>
       </c>
       <c r="N11" t="n">
         <v>46</v>
@@ -1107,13 +1107,13 @@
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1122,13 +1122,13 @@
         <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N12" t="n">
         <v>50</v>
       </c>
       <c r="O12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
         <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>30.9</v>
+        <v>32.7</v>
       </c>
       <c r="I13" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
         <v>145</v>
@@ -1180,17 +1180,17 @@
         <v>624</v>
       </c>
       <c r="M13" t="n">
-        <v>20.2</v>
+        <v>19.1</v>
       </c>
       <c r="N13" t="n">
         <v>46</v>
       </c>
       <c r="O13" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~20 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1223,13 +1223,13 @@
         <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>17.5</v>
+        <v>15.3</v>
       </c>
       <c r="J14" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K14" t="n">
         <v>3</v>
@@ -1238,13 +1238,13 @@
         <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="n">
         <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1281,10 +1281,10 @@
         <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="I15" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J15" t="n">
         <v>46</v>
@@ -1293,10 +1293,10 @@
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>50</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~4u (2cs) - sells in ~1 wks</t>
+          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="J16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
@@ -1397,13 +1397,13 @@
         <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="J17" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K17" t="n">
         <v>2</v>
@@ -1455,13 +1455,13 @@
         <v>20</v>
       </c>
       <c r="H18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="J18" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -1513,13 +1513,13 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="I19" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="J19" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="K19" t="n">
         <v>84</v>
@@ -1545,7 +1545,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,55 +1555,55 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E20" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F20" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H20" t="n">
-        <v>9.800000000000001</v>
+        <v>14.6</v>
       </c>
       <c r="I20" t="n">
-        <v>12.9</v>
+        <v>8.4</v>
       </c>
       <c r="J20" t="n">
-        <v>101</v>
+        <v>131</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6</v>
+        <v>42.9</v>
       </c>
       <c r="N20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O20" t="n">
         <v>21</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,55 +1613,55 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>10.85</v>
       </c>
       <c r="E21" t="n">
-        <v>9.9</v>
+        <v>8.68</v>
       </c>
       <c r="F21" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="G21" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>13.7</v>
       </c>
       <c r="J21" t="n">
-        <v>28</v>
+        <v>107</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>5.6</v>
+        <v>0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~54u (9cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,48 +1671,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E22" t="n">
-        <v>9.06</v>
+        <v>9.9</v>
       </c>
       <c r="F22" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H22" t="n">
-        <v>13.4</v>
+        <v>9.4</v>
       </c>
       <c r="I22" t="n">
-        <v>9.6</v>
+        <v>5.3</v>
       </c>
       <c r="J22" t="n">
-        <v>138</v>
+        <v>28</v>
       </c>
       <c r="K22" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>624</v>
+        <v>48</v>
       </c>
       <c r="M22" t="n">
-        <v>46.4</v>
+        <v>5.1</v>
       </c>
       <c r="N22" t="n">
         <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~46 wks (overstock); consider ~624u</t>
+          <t>BUY ~48u (8cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1745,13 +1745,13 @@
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="I23" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="J23" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="K23" t="n">
         <v>624</v>
@@ -1760,7 +1760,7 @@
         <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="N23" t="n">
         <v>45</v>
@@ -1803,13 +1803,13 @@
         <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="I24" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="J24" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K24" t="n">
         <v>84</v>
@@ -1818,7 +1818,7 @@
         <v>84</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
         <v>44</v>
@@ -1861,13 +1861,13 @@
         <v>20</v>
       </c>
       <c r="H25" t="n">
-        <v>8.300000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I25" t="n">
-        <v>24.3</v>
+        <v>23.2</v>
       </c>
       <c r="J25" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K25" t="n">
         <v>6</v>
@@ -1882,7 +1882,7 @@
         <v>46</v>
       </c>
       <c r="O25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,38 +1903,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E26" t="n">
-        <v>9.9</v>
+        <v>9.06</v>
       </c>
       <c r="F26" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G26" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H26" t="n">
-        <v>8</v>
+        <v>11.9</v>
       </c>
       <c r="I26" t="n">
-        <v>10.8</v>
+        <v>7.6</v>
       </c>
       <c r="J26" t="n">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L26" t="n">
-        <v>18</v>
+        <v>624</v>
       </c>
       <c r="M26" t="n">
-        <v>2.2</v>
+        <v>52.3</v>
       </c>
       <c r="N26" t="n">
         <v>45</v>
@@ -1944,14 +1944,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>9.06</v>
+        <v>9.9</v>
       </c>
       <c r="F27" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H27" t="n">
-        <v>11.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>8.300000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="J27" t="n">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="K27" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L27" t="n">
-        <v>624</v>
+        <v>24</v>
       </c>
       <c r="M27" t="n">
-        <v>55</v>
+        <v>2.9</v>
       </c>
       <c r="N27" t="n">
         <v>45</v>
       </c>
       <c r="O27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~55 wks (overstock); consider ~624u</t>
+          <t>BUY ~24u (4cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,55 +2019,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>16.67</v>
+        <v>26.52</v>
       </c>
       <c r="E28" t="n">
-        <v>13.34</v>
+        <v>24.2</v>
       </c>
       <c r="F28" t="n">
-        <v>3.33</v>
+        <v>2.33</v>
       </c>
       <c r="G28" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H28" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="I28" t="n">
-        <v>11.4</v>
+        <v>14.1</v>
       </c>
       <c r="J28" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>208</v>
       </c>
       <c r="L28" t="n">
-        <v>9</v>
+        <v>208</v>
       </c>
       <c r="M28" t="n">
-        <v>1.9</v>
+        <v>28.1</v>
       </c>
       <c r="N28" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~9u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 208u = ~28 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>26.52</v>
+        <v>16.67</v>
       </c>
       <c r="E29" t="n">
-        <v>24.2</v>
+        <v>13.34</v>
       </c>
       <c r="F29" t="n">
-        <v>2.33</v>
+        <v>3.33</v>
       </c>
       <c r="G29" t="n">
+        <v>20</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J29" t="n">
+        <v>30</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3</v>
+      </c>
+      <c r="L29" t="n">
         <v>9</v>
       </c>
-      <c r="H29" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="I29" t="n">
-        <v>15</v>
-      </c>
-      <c r="J29" t="n">
-        <v>59</v>
-      </c>
-      <c r="K29" t="n">
-        <v>208</v>
-      </c>
-      <c r="L29" t="n">
-        <v>208</v>
-      </c>
       <c r="M29" t="n">
-        <v>29.4</v>
+        <v>1.9</v>
       </c>
       <c r="N29" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O29" t="n">
         <v>16</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~29 wks (overstock); consider ~208u</t>
+          <t>BUY ~9u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.85</v>
+        <v>20</v>
       </c>
       <c r="E30" t="n">
-        <v>8.68</v>
+        <v>18.02</v>
       </c>
       <c r="F30" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H30" t="n">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
       <c r="I30" t="n">
-        <v>28.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>0.8</v>
+        <v>5.3</v>
       </c>
       <c r="N30" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O30" t="n">
         <v>15</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2193,55 +2193,55 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D31" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G31" t="n">
         <v>20</v>
       </c>
-      <c r="E31" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G31" t="n">
-        <v>10</v>
-      </c>
       <c r="H31" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I31" t="n">
-        <v>10.7</v>
+        <v>28.3</v>
       </c>
       <c r="J31" t="n">
-        <v>83</v>
+        <v>149</v>
       </c>
       <c r="K31" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>5.5</v>
+        <v>0.9</v>
       </c>
       <c r="N31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~6 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,55 +2251,55 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.03</v>
+        <v>9.33</v>
       </c>
       <c r="E32" t="n">
-        <v>9.15</v>
+        <v>8.01</v>
       </c>
       <c r="F32" t="n">
-        <v>0.88</v>
+        <v>1.32</v>
       </c>
       <c r="G32" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>15.5</v>
+        <v>10.8</v>
       </c>
       <c r="I32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="K32" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L32" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M32" t="n">
-        <v>40.4</v>
+        <v>13.9</v>
       </c>
       <c r="N32" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O32" t="n">
         <v>14</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>10.03</v>
       </c>
       <c r="E33" t="n">
-        <v>9.82</v>
+        <v>9.15</v>
       </c>
       <c r="F33" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="G33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>10.7</v>
+        <v>16.1</v>
       </c>
       <c r="I33" t="n">
-        <v>10.9</v>
+        <v>8.6</v>
       </c>
       <c r="J33" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K33" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L33" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M33" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="N33" t="n">
+        <v>46</v>
+      </c>
+      <c r="O33" t="n">
         <v>14</v>
       </c>
-      <c r="N33" t="n">
-        <v>55</v>
-      </c>
-      <c r="O33" t="n">
-        <v>13</v>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~39 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2371,51 +2371,51 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>9.06</v>
+        <v>9.82</v>
       </c>
       <c r="F34" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="G34" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H34" t="n">
-        <v>8.9</v>
+        <v>11</v>
       </c>
       <c r="I34" t="n">
-        <v>6.8</v>
+        <v>10.1</v>
       </c>
       <c r="J34" t="n">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="K34" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L34" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M34" t="n">
-        <v>70</v>
+        <v>13.6</v>
       </c>
       <c r="N34" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O34" t="n">
         <v>13</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~70 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2429,44 +2429,44 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9.33</v>
+        <v>10.5</v>
       </c>
       <c r="E35" t="n">
-        <v>8.01</v>
+        <v>9.06</v>
       </c>
       <c r="F35" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="G35" t="n">
         <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="J35" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="K35" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L35" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M35" t="n">
-        <v>15.1</v>
+        <v>67.5</v>
       </c>
       <c r="N35" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O35" t="n">
         <v>13</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~68 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2505,7 +2505,7 @@
         <v>11.6</v>
       </c>
       <c r="J36" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="K36" t="n">
         <v>84</v>
@@ -2557,13 +2557,13 @@
         <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="I37" t="n">
-        <v>16.4</v>
+        <v>14.3</v>
       </c>
       <c r="J37" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K37" t="n">
         <v>150</v>
@@ -2572,7 +2572,7 @@
         <v>150</v>
       </c>
       <c r="M37" t="n">
-        <v>18.6</v>
+        <v>16.9</v>
       </c>
       <c r="N37" t="n">
         <v>55</v>
@@ -2582,14 +2582,14 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2599,55 +2599,55 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9.67</v>
+        <v>11</v>
       </c>
       <c r="E38" t="n">
-        <v>7.57</v>
+        <v>9.82</v>
       </c>
       <c r="F38" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="G38" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H38" t="n">
-        <v>4.2</v>
+        <v>6.7</v>
       </c>
       <c r="I38" t="n">
-        <v>7.1</v>
+        <v>13.9</v>
       </c>
       <c r="J38" t="n">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="K38" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M38" t="n">
-        <v>1.4</v>
+        <v>22.2</v>
       </c>
       <c r="N38" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O38" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>CAUTION - 150u = ~22 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,48 +2657,48 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>8.67</v>
+        <v>14</v>
       </c>
       <c r="E39" t="n">
-        <v>6.57</v>
+        <v>11.2</v>
       </c>
       <c r="F39" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="G39" t="n">
+        <v>20</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>27</v>
+      </c>
+      <c r="K39" t="n">
         <v>24</v>
       </c>
-      <c r="H39" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I39" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="J39" t="n">
-        <v>32</v>
-      </c>
-      <c r="K39" t="n">
-        <v>6</v>
-      </c>
       <c r="L39" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M39" t="n">
-        <v>1.4</v>
+        <v>8</v>
       </c>
       <c r="N39" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~8 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2731,10 +2731,10 @@
         <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="I40" t="n">
-        <v>7.1</v>
+        <v>8.5</v>
       </c>
       <c r="J40" t="n">
         <v>32</v>
@@ -2746,24 +2746,24 @@
         <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="N40" t="n">
         <v>47</v>
       </c>
       <c r="O40" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,55 +2773,55 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>8.67</v>
       </c>
       <c r="E41" t="n">
-        <v>11.2</v>
+        <v>6.57</v>
       </c>
       <c r="F41" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="G41" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H41" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="I41" t="n">
-        <v>12.6</v>
+        <v>8.5</v>
       </c>
       <c r="J41" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K41" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L41" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M41" t="n">
-        <v>7.6</v>
+        <v>1.7</v>
       </c>
       <c r="N41" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O41" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~8 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2831,48 +2831,48 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11</v>
+        <v>9.67</v>
       </c>
       <c r="E42" t="n">
-        <v>9.82</v>
+        <v>7.57</v>
       </c>
       <c r="F42" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="G42" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H42" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="I42" t="n">
-        <v>17.5</v>
+        <v>8.5</v>
       </c>
       <c r="J42" t="n">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="K42" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L42" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>26.1</v>
+        <v>1.7</v>
       </c>
       <c r="N42" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O42" t="n">
         <v>7</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~26 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -2908,10 +2908,10 @@
         <v>2.9</v>
       </c>
       <c r="I43" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="J43" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K43" t="n">
         <v>6</v>
@@ -2966,10 +2966,10 @@
         <v>2.9</v>
       </c>
       <c r="I44" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="J44" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K44" t="n">
         <v>6</v>
@@ -3024,10 +3024,10 @@
         <v>2.9</v>
       </c>
       <c r="I45" t="n">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="J45" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K45" t="n">
         <v>6</v>
@@ -3079,13 +3079,13 @@
         <v>14</v>
       </c>
       <c r="H46" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="I46" t="n">
-        <v>60.1</v>
+        <v>53</v>
       </c>
       <c r="J46" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K46" t="n">
         <v>150</v>
@@ -3094,17 +3094,17 @@
         <v>150</v>
       </c>
       <c r="M46" t="n">
-        <v>38.6</v>
+        <v>34.5</v>
       </c>
       <c r="N46" t="n">
         <v>50</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~39 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~34 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3427,13 +3427,13 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="I52" t="n">
-        <v>18.2</v>
+        <v>15.4</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K52" t="n">
         <v>624</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>503.7</v>
+        <v>446</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~504 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~446 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,19 +527,19 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>159.2</v>
+        <v>157.2</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J2" t="n">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>818</v>
+        <v>800</v>
       </c>
       <c r="M2" t="n">
         <v>5.1</v>
@@ -548,11 +548,11 @@
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~818u (409cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~800u (400cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>43.1</v>
+        <v>40.6</v>
       </c>
       <c r="I3" t="n">
         <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="I4" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="M4" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~80u (40cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~92u (46cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>27.8</v>
+        <v>26.5</v>
       </c>
       <c r="I5" t="n">
-        <v>11.6</v>
+        <v>12.1</v>
       </c>
       <c r="J5" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -716,17 +716,17 @@
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BUY ~40u (20cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~40u (20cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>14.4</v>
+        <v>13.5</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J6" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -774,13 +774,13 @@
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -801,55 +801,55 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>10.85</v>
       </c>
       <c r="E7" t="n">
-        <v>11.2</v>
+        <v>8.68</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="G7" t="n">
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="I7" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="J7" t="n">
-        <v>54</v>
+        <v>124</v>
       </c>
       <c r="K7" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="M7" t="n">
-        <v>5.4</v>
+        <v>1.6</v>
       </c>
       <c r="N7" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O7" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BUY ~102u (17cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~30u (5cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -859,48 +859,48 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.85</v>
+        <v>14</v>
       </c>
       <c r="E8" t="n">
-        <v>8.68</v>
+        <v>11.2</v>
       </c>
       <c r="F8" t="n">
-        <v>2.17</v>
+        <v>2.8</v>
       </c>
       <c r="G8" t="n">
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>19.4</v>
+        <v>13</v>
       </c>
       <c r="I8" t="n">
-        <v>12.5</v>
+        <v>7.1</v>
       </c>
       <c r="J8" t="n">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L8" t="n">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O8" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~54u (9cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -933,13 +933,13 @@
         <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>25.6</v>
+        <v>24</v>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J9" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="K9" t="n">
         <v>624</v>
@@ -948,17 +948,17 @@
         <v>624</v>
       </c>
       <c r="M9" t="n">
-        <v>24.4</v>
+        <v>26</v>
       </c>
       <c r="N9" t="n">
         <v>45</v>
       </c>
       <c r="O9" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~24 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -991,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>38.6</v>
+        <v>37.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K10" t="n">
         <v>624</v>
@@ -1006,17 +1006,17 @@
         <v>624</v>
       </c>
       <c r="M10" t="n">
-        <v>16.2</v>
+        <v>16.6</v>
       </c>
       <c r="N10" t="n">
         <v>46</v>
       </c>
       <c r="O10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~16 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~17 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1049,10 +1049,10 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>36.3</v>
+        <v>35.1</v>
       </c>
       <c r="I11" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="J11" t="n">
         <v>152</v>
@@ -1064,17 +1064,17 @@
         <v>624</v>
       </c>
       <c r="M11" t="n">
-        <v>17.2</v>
+        <v>17.8</v>
       </c>
       <c r="N11" t="n">
         <v>46</v>
       </c>
       <c r="O11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~17 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~18 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1107,13 +1107,13 @@
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I12" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1122,13 +1122,13 @@
         <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="N12" t="n">
         <v>50</v>
       </c>
       <c r="O12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,55 +1149,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.03</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>9.15</v>
+        <v>16.67</v>
       </c>
       <c r="F13" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H13" t="n">
-        <v>32.7</v>
+        <v>8.5</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>15.5</v>
       </c>
       <c r="J13" t="n">
-        <v>145</v>
+        <v>77</v>
       </c>
       <c r="K13" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>19.1</v>
+        <v>0.4</v>
       </c>
       <c r="N13" t="n">
         <v>46</v>
       </c>
       <c r="O13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,55 +1207,55 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>10.03</v>
       </c>
       <c r="E14" t="n">
-        <v>16.67</v>
+        <v>9.15</v>
       </c>
       <c r="F14" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G14" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>8.800000000000001</v>
+        <v>31.1</v>
       </c>
       <c r="I14" t="n">
-        <v>15.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>79</v>
+        <v>144</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>20.1</v>
       </c>
       <c r="N14" t="n">
         <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~20 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,48 +1265,48 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.7</v>
+        <v>26.5</v>
       </c>
       <c r="E15" t="n">
-        <v>21.7</v>
+        <v>21.32</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>5.18</v>
       </c>
       <c r="G15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>6.3</v>
+        <v>4.8</v>
       </c>
       <c r="I15" t="n">
-        <v>6.8</v>
+        <v>13.4</v>
       </c>
       <c r="J15" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N15" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="O15" t="n">
         <v>25</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="J16" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
@@ -1400,10 +1400,10 @@
         <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>13.9</v>
+        <v>13.4</v>
       </c>
       <c r="J17" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K17" t="n">
         <v>2</v>
@@ -1429,7 +1429,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,29 +1439,29 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="E18" t="n">
-        <v>21.32</v>
+        <v>21.7</v>
       </c>
       <c r="F18" t="n">
-        <v>5.18</v>
+        <v>4</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="I18" t="n">
-        <v>13.9</v>
+        <v>7.4</v>
       </c>
       <c r="J18" t="n">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
@@ -1470,13 +1470,13 @@
         <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="N18" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="O18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1513,13 +1513,13 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>27.1</v>
+        <v>24.7</v>
       </c>
       <c r="I19" t="n">
-        <v>12.6</v>
+        <v>13.6</v>
       </c>
       <c r="J19" t="n">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="K19" t="n">
         <v>84</v>
@@ -1528,13 +1528,13 @@
         <v>84</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
         <v>44</v>
       </c>
       <c r="O19" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,55 +1555,55 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>8.68</v>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>14.6</v>
+        <v>9</v>
       </c>
       <c r="I20" t="n">
-        <v>8.4</v>
+        <v>14.4</v>
       </c>
       <c r="J20" t="n">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="K20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>42.9</v>
+        <v>0.7</v>
       </c>
       <c r="N20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,48 +1613,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E21" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F21" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H21" t="n">
-        <v>9.800000000000001</v>
+        <v>13.3</v>
       </c>
       <c r="I21" t="n">
-        <v>13.7</v>
+        <v>8.9</v>
       </c>
       <c r="J21" t="n">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6</v>
+        <v>46.8</v>
       </c>
       <c r="N21" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~47 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1687,10 +1687,10 @@
         <v>17</v>
       </c>
       <c r="H22" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="J22" t="n">
         <v>28</v>
@@ -1699,20 +1699,20 @@
         <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M22" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="N22" t="n">
         <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUY ~48u (8cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~42u (7cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1745,13 +1745,13 @@
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="I23" t="n">
-        <v>6.5</v>
+        <v>6.7</v>
       </c>
       <c r="J23" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="K23" t="n">
         <v>624</v>
@@ -1760,24 +1760,24 @@
         <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>47.6</v>
+        <v>50.5</v>
       </c>
       <c r="N23" t="n">
         <v>45</v>
       </c>
       <c r="O23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,55 +1787,55 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>10.85</v>
       </c>
       <c r="E24" t="n">
-        <v>11.2</v>
+        <v>8.68</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8</v>
+        <v>2.17</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>23.7</v>
+        <v>8.5</v>
       </c>
       <c r="I24" t="n">
-        <v>10.3</v>
+        <v>23.3</v>
       </c>
       <c r="J24" t="n">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="K24" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>0.7</v>
       </c>
       <c r="N24" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,55 +1845,55 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.85</v>
+        <v>26.52</v>
       </c>
       <c r="E25" t="n">
-        <v>8.68</v>
+        <v>24.2</v>
       </c>
       <c r="F25" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H25" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="I25" t="n">
-        <v>23.2</v>
+        <v>14.1</v>
       </c>
       <c r="J25" t="n">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="L25" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7</v>
+        <v>28.1</v>
       </c>
       <c r="N25" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 208u = ~28 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,38 +1903,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>9.06</v>
+        <v>9.9</v>
       </c>
       <c r="F26" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H26" t="n">
-        <v>11.9</v>
+        <v>8.1</v>
       </c>
       <c r="I26" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="J26" t="n">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="K26" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>624</v>
+        <v>24</v>
       </c>
       <c r="M26" t="n">
-        <v>52.3</v>
+        <v>2.9</v>
       </c>
       <c r="N26" t="n">
         <v>45</v>
@@ -1944,14 +1944,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
+          <t>BUY ~24u (4cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D27" t="n">
         <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="F27" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="G27" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>8.199999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="I27" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="J27" t="n">
-        <v>47</v>
+        <v>176</v>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="L27" t="n">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="M27" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O27" t="n">
         <v>17</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,48 +2019,48 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>26.52</v>
+        <v>10.5</v>
       </c>
       <c r="E28" t="n">
-        <v>24.2</v>
+        <v>9.06</v>
       </c>
       <c r="F28" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H28" t="n">
-        <v>7.4</v>
+        <v>10.9</v>
       </c>
       <c r="I28" t="n">
-        <v>14.1</v>
+        <v>8</v>
       </c>
       <c r="J28" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="K28" t="n">
-        <v>208</v>
+        <v>624</v>
       </c>
       <c r="L28" t="n">
-        <v>208</v>
+        <v>624</v>
       </c>
       <c r="M28" t="n">
-        <v>28.1</v>
+        <v>57.4</v>
       </c>
       <c r="N28" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~28 wks (overstock); consider ~208u</t>
+          <t>CAUTION - 624u = ~57 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2096,19 +2096,19 @@
         <v>4.7</v>
       </c>
       <c r="I29" t="n">
-        <v>11.4</v>
+        <v>10.7</v>
       </c>
       <c r="J29" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K29" t="n">
         <v>3</v>
       </c>
       <c r="L29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="M29" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="N29" t="n">
         <v>47</v>
@@ -2118,7 +2118,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~9u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~12u (4cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>10</v>
       </c>
       <c r="H30" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I30" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J30" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="K30" t="n">
         <v>40</v>
@@ -2166,13 +2166,13 @@
         <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="N30" t="n">
         <v>47</v>
       </c>
       <c r="O30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -2209,13 +2209,13 @@
         <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="I31" t="n">
-        <v>28.3</v>
+        <v>29.2</v>
       </c>
       <c r="J31" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K31" t="n">
         <v>6</v>
@@ -2267,13 +2267,13 @@
         <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="I32" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J32" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K32" t="n">
         <v>150</v>
@@ -2282,7 +2282,7 @@
         <v>150</v>
       </c>
       <c r="M32" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
       </c>
       <c r="N32" t="n">
         <v>50</v>
@@ -2325,13 +2325,13 @@
         <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>16.1</v>
+        <v>15.5</v>
       </c>
       <c r="I33" t="n">
         <v>8.6</v>
       </c>
       <c r="J33" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K33" t="n">
         <v>624</v>
@@ -2340,7 +2340,7 @@
         <v>624</v>
       </c>
       <c r="M33" t="n">
-        <v>38.8</v>
+        <v>40.3</v>
       </c>
       <c r="N33" t="n">
         <v>46</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~39 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2383,10 +2383,10 @@
         <v>11</v>
       </c>
       <c r="H34" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="I34" t="n">
         <v>11</v>
-      </c>
-      <c r="I34" t="n">
-        <v>10.1</v>
       </c>
       <c r="J34" t="n">
         <v>76</v>
@@ -2398,17 +2398,17 @@
         <v>150</v>
       </c>
       <c r="M34" t="n">
-        <v>13.6</v>
+        <v>14.7</v>
       </c>
       <c r="N34" t="n">
         <v>55</v>
       </c>
       <c r="O34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2441,13 +2441,13 @@
         <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>9.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="J35" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="K35" t="n">
         <v>624</v>
@@ -2456,17 +2456,17 @@
         <v>624</v>
       </c>
       <c r="M35" t="n">
-        <v>67.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>45</v>
       </c>
       <c r="O35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~68 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~75 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2499,13 +2499,13 @@
         <v>7</v>
       </c>
       <c r="H36" t="n">
-        <v>13.8</v>
+        <v>12.6</v>
       </c>
       <c r="I36" t="n">
-        <v>11.6</v>
+        <v>12.3</v>
       </c>
       <c r="J36" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="K36" t="n">
         <v>84</v>
@@ -2514,17 +2514,17 @@
         <v>84</v>
       </c>
       <c r="M36" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
       <c r="N36" t="n">
         <v>44</v>
       </c>
       <c r="O36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~6 wks</t>
+          <t>BUY ~84u (14cs) - sells in ~7 wks</t>
         </is>
       </c>
     </row>
@@ -2557,13 +2557,13 @@
         <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>8.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>14.3</v>
+        <v>14.1</v>
       </c>
       <c r="J37" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="K37" t="n">
         <v>150</v>
@@ -2572,7 +2572,7 @@
         <v>150</v>
       </c>
       <c r="M37" t="n">
-        <v>16.9</v>
+        <v>18.3</v>
       </c>
       <c r="N37" t="n">
         <v>55</v>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2615,13 +2615,13 @@
         <v>11</v>
       </c>
       <c r="H38" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="I38" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="J38" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K38" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         <v>150</v>
       </c>
       <c r="M38" t="n">
-        <v>22.2</v>
+        <v>22.9</v>
       </c>
       <c r="N38" t="n">
         <v>45</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~22 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~23 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
         <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>13.1</v>
+        <v>13.4</v>
       </c>
       <c r="J39" t="n">
         <v>27</v>
@@ -2688,7 +2688,7 @@
         <v>24</v>
       </c>
       <c r="M39" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="N39" t="n">
         <v>44</v>
@@ -2731,13 +2731,13 @@
         <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I40" t="n">
         <v>8.5</v>
       </c>
       <c r="J40" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K40" t="n">
         <v>6</v>
@@ -2746,7 +2746,7 @@
         <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N40" t="n">
         <v>47</v>
@@ -2789,13 +2789,13 @@
         <v>24</v>
       </c>
       <c r="H41" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I41" t="n">
         <v>8.5</v>
       </c>
       <c r="J41" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K41" t="n">
         <v>6</v>
@@ -2804,7 +2804,7 @@
         <v>6</v>
       </c>
       <c r="M41" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N41" t="n">
         <v>45</v>
@@ -2847,13 +2847,13 @@
         <v>22</v>
       </c>
       <c r="H42" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="I42" t="n">
         <v>8.5</v>
       </c>
       <c r="J42" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K42" t="n">
         <v>6</v>
@@ -2862,7 +2862,7 @@
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="N42" t="n">
         <v>46</v>
@@ -2908,10 +2908,10 @@
         <v>2.9</v>
       </c>
       <c r="I43" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="J43" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K43" t="n">
         <v>6</v>
@@ -2966,10 +2966,10 @@
         <v>2.9</v>
       </c>
       <c r="I44" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="J44" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K44" t="n">
         <v>6</v>
@@ -3024,10 +3024,10 @@
         <v>2.9</v>
       </c>
       <c r="I45" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="J45" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K45" t="n">
         <v>6</v>
@@ -3079,13 +3079,13 @@
         <v>14</v>
       </c>
       <c r="H46" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="I46" t="n">
-        <v>53</v>
+        <v>48.9</v>
       </c>
       <c r="J46" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K46" t="n">
         <v>150</v>
@@ -3094,7 +3094,7 @@
         <v>150</v>
       </c>
       <c r="M46" t="n">
-        <v>34.5</v>
+        <v>32.3</v>
       </c>
       <c r="N46" t="n">
         <v>50</v>
@@ -3104,14 +3104,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~34 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~32 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
+          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3125,44 +3125,44 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>13.45</v>
       </c>
       <c r="E47" t="n">
-        <v>9.82</v>
+        <v>11.47</v>
       </c>
       <c r="F47" t="n">
-        <v>1.18</v>
+        <v>1.97</v>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H47" t="n">
-        <v>3.2</v>
+        <v>1.8</v>
       </c>
       <c r="I47" t="n">
-        <v>19.5</v>
+        <v>20.2</v>
       </c>
       <c r="J47" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="K47" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="L47" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="M47" t="n">
-        <v>47.1</v>
+        <v>22.1</v>
       </c>
       <c r="N47" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O47" t="n">
         <v>4</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~47 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 40u = ~22 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
@@ -3195,13 +3195,13 @@
         <v>20</v>
       </c>
       <c r="H48" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="I48" t="n">
-        <v>41.7</v>
+        <v>37.5</v>
       </c>
       <c r="J48" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K48" t="n">
         <v>24</v>
@@ -3210,7 +3210,7 @@
         <v>24</v>
       </c>
       <c r="M48" t="n">
-        <v>17.7</v>
+        <v>16.2</v>
       </c>
       <c r="N48" t="n">
         <v>44</v>
@@ -3220,14 +3220,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 24u = ~18 wks (overstock); consider ~24u</t>
+          <t>CAUTION - 24u = ~16 wks (overstock); consider ~24u</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
+          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3241,44 +3241,44 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.45</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>11.47</v>
+        <v>9.82</v>
       </c>
       <c r="F49" t="n">
-        <v>1.97</v>
+        <v>1.18</v>
       </c>
       <c r="G49" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H49" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>20.4</v>
       </c>
       <c r="J49" t="n">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="K49" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="L49" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="M49" t="n">
-        <v>22.9</v>
+        <v>51.5</v>
       </c>
       <c r="N49" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~23 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 150u = ~52 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3369,10 +3369,10 @@
         <v>11</v>
       </c>
       <c r="H51" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I51" t="n">
-        <v>111.5</v>
+        <v>143.8</v>
       </c>
       <c r="J51" t="n">
         <v>85</v>
@@ -3384,7 +3384,7 @@
         <v>150</v>
       </c>
       <c r="M51" t="n">
-        <v>210.1</v>
+        <v>270.9</v>
       </c>
       <c r="N51" t="n">
         <v>55</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~210 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~271 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3427,13 +3427,13 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="I52" t="n">
-        <v>15.4</v>
+        <v>11.6</v>
       </c>
       <c r="J52" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K52" t="n">
         <v>624</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>446</v>
+        <v>369.1</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~446 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~369 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>157.2</v>
+        <v>155.9</v>
       </c>
       <c r="I2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>459</v>
+        <v>489</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>800</v>
+        <v>760</v>
       </c>
       <c r="M2" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~800u (400cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~760u (380cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>40.6</v>
+        <v>39.9</v>
       </c>
       <c r="I3" t="n">
         <v>3.7</v>
       </c>
       <c r="J3" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>21.6</v>
       </c>
       <c r="I4" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>26.5</v>
+        <v>26.2</v>
       </c>
       <c r="I5" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="J5" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>13.5</v>
+        <v>13.9</v>
       </c>
       <c r="I6" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -774,13 +774,13 @@
         <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="I7" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="J7" t="n">
         <v>124</v>
@@ -829,10 +829,10 @@
         <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="M7" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="N7" t="n">
         <v>46</v>
@@ -842,7 +842,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~24u (4cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -875,10 +875,10 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="I8" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="J8" t="n">
         <v>51</v>
@@ -890,7 +890,7 @@
         <v>54</v>
       </c>
       <c r="M8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="N8" t="n">
         <v>44</v>
@@ -933,13 +933,13 @@
         <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>24</v>
+        <v>24.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K9" t="n">
         <v>624</v>
@@ -948,13 +948,13 @@
         <v>624</v>
       </c>
       <c r="M9" t="n">
-        <v>26</v>
+        <v>25.5</v>
       </c>
       <c r="N9" t="n">
         <v>45</v>
       </c>
       <c r="O9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -991,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K10" t="n">
         <v>624</v>
@@ -1006,7 +1006,7 @@
         <v>624</v>
       </c>
       <c r="M10" t="n">
-        <v>16.6</v>
+        <v>16.9</v>
       </c>
       <c r="N10" t="n">
         <v>46</v>
@@ -1023,7 +1023,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1037,51 +1037,51 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.03</v>
+        <v>25.7</v>
       </c>
       <c r="E11" t="n">
-        <v>9.15</v>
+        <v>21.7</v>
       </c>
       <c r="F11" t="n">
-        <v>0.88</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>35.1</v>
+        <v>8.1</v>
       </c>
       <c r="I11" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>152</v>
+        <v>69</v>
       </c>
       <c r="K11" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="M11" t="n">
-        <v>17.8</v>
+        <v>0.2</v>
       </c>
       <c r="N11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~18 wks (overstock); consider ~624u</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1095,51 +1095,51 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>25.7</v>
+        <v>10.03</v>
       </c>
       <c r="E12" t="n">
-        <v>21.7</v>
+        <v>9.15</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>0.88</v>
       </c>
       <c r="G12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>7.8</v>
+        <v>34.4</v>
       </c>
       <c r="I12" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="J12" t="n">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="K12" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="M12" t="n">
-        <v>0.3</v>
+        <v>18.1</v>
       </c>
       <c r="N12" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~18 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,55 +1149,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>10.03</v>
       </c>
       <c r="E13" t="n">
-        <v>16.67</v>
+        <v>9.15</v>
       </c>
       <c r="F13" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>8.5</v>
+        <v>33.2</v>
       </c>
       <c r="I13" t="n">
-        <v>15.5</v>
+        <v>7.4</v>
       </c>
       <c r="J13" t="n">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4</v>
+        <v>18.8</v>
       </c>
       <c r="N13" t="n">
         <v>46</v>
       </c>
       <c r="O13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,48 +1207,48 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10.03</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>9.15</v>
+        <v>16.67</v>
       </c>
       <c r="F14" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>31.1</v>
+        <v>8.4</v>
       </c>
       <c r="I14" t="n">
-        <v>8.300000000000001</v>
+        <v>15.6</v>
       </c>
       <c r="J14" t="n">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="K14" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>20.1</v>
+        <v>0.4</v>
       </c>
       <c r="N14" t="n">
         <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~20 wks (overstock); consider ~624u</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1281,13 +1281,13 @@
         <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>13.4</v>
+        <v>12.6</v>
       </c>
       <c r="J15" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
@@ -1302,7 +1302,7 @@
         <v>42</v>
       </c>
       <c r="O15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>13.4</v>
+        <v>12.6</v>
       </c>
       <c r="J16" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
@@ -1360,7 +1360,7 @@
         <v>51</v>
       </c>
       <c r="O16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1397,13 +1397,13 @@
         <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>13.4</v>
+        <v>12.6</v>
       </c>
       <c r="J17" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K17" t="n">
         <v>2</v>
@@ -1418,7 +1418,7 @@
         <v>44</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1455,39 +1455,39 @@
         <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="I18" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="J18" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="N18" t="n">
         <v>50</v>
       </c>
       <c r="O18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,55 +1497,55 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>10.85</v>
       </c>
       <c r="E19" t="n">
-        <v>11.2</v>
+        <v>8.68</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8</v>
+        <v>2.17</v>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>24.7</v>
+        <v>9.5</v>
       </c>
       <c r="I19" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="J19" t="n">
-        <v>186</v>
+        <v>102</v>
       </c>
       <c r="K19" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>0.6</v>
       </c>
       <c r="N19" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O19" t="n">
         <v>20</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,55 +1555,55 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E20" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F20" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H20" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="I20" t="n">
         <v>9</v>
       </c>
-      <c r="I20" t="n">
-        <v>14.4</v>
-      </c>
       <c r="J20" t="n">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7</v>
+        <v>47.5</v>
       </c>
       <c r="N20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,55 +1613,55 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E21" t="n">
-        <v>9.06</v>
+        <v>11.2</v>
       </c>
       <c r="F21" t="n">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="G21" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H21" t="n">
-        <v>13.3</v>
+        <v>24.1</v>
       </c>
       <c r="I21" t="n">
-        <v>8.9</v>
+        <v>13.9</v>
       </c>
       <c r="J21" t="n">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="K21" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="L21" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="M21" t="n">
-        <v>46.8</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O21" t="n">
         <v>19</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~47 wks (overstock); consider ~624u</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1687,22 +1687,22 @@
         <v>17</v>
       </c>
       <c r="H22" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I22" t="n">
-        <v>5.9</v>
+        <v>9.6</v>
       </c>
       <c r="J22" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="K22" t="n">
         <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="M22" t="n">
-        <v>4.9</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
         <v>45</v>
@@ -1712,14 +1712,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUY ~42u (7cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~24u (4cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,48 +1729,48 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.5</v>
+        <v>26.52</v>
       </c>
       <c r="E23" t="n">
-        <v>9.06</v>
+        <v>24.2</v>
       </c>
       <c r="F23" t="n">
-        <v>1.44</v>
+        <v>2.33</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H23" t="n">
-        <v>12.4</v>
+        <v>7.7</v>
       </c>
       <c r="I23" t="n">
-        <v>6.7</v>
+        <v>13.3</v>
       </c>
       <c r="J23" t="n">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="K23" t="n">
-        <v>624</v>
+        <v>208</v>
       </c>
       <c r="L23" t="n">
-        <v>624</v>
+        <v>208</v>
       </c>
       <c r="M23" t="n">
-        <v>50.5</v>
+        <v>27</v>
       </c>
       <c r="N23" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O23" t="n">
         <v>18</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 208u = ~27 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
@@ -1803,13 +1803,13 @@
         <v>20</v>
       </c>
       <c r="H24" t="n">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>23.3</v>
+        <v>25.2</v>
       </c>
       <c r="J24" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="K24" t="n">
         <v>6</v>
@@ -1835,7 +1835,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,38 +1845,38 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.52</v>
+        <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>24.2</v>
+        <v>11.2</v>
       </c>
       <c r="F25" t="n">
-        <v>2.33</v>
+        <v>0.8</v>
       </c>
       <c r="G25" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>7.4</v>
+        <v>21.8</v>
       </c>
       <c r="I25" t="n">
-        <v>14.1</v>
+        <v>10.8</v>
       </c>
       <c r="J25" t="n">
-        <v>58</v>
+        <v>175</v>
       </c>
       <c r="K25" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="L25" t="n">
-        <v>208</v>
+        <v>84</v>
       </c>
       <c r="M25" t="n">
-        <v>28.1</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
         <v>44</v>
@@ -1886,14 +1886,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~28 wks (overstock); consider ~208u</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1919,22 +1919,22 @@
         <v>17</v>
       </c>
       <c r="H26" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>10.2</v>
+        <v>6.1</v>
       </c>
       <c r="J26" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="K26" t="n">
         <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="M26" t="n">
-        <v>2.9</v>
+        <v>5.1</v>
       </c>
       <c r="N26" t="n">
         <v>45</v>
@@ -1944,14 +1944,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~42u (7cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,48 +1961,48 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E27" t="n">
-        <v>11.2</v>
+        <v>9.06</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8</v>
+        <v>1.44</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>21.6</v>
+        <v>12.1</v>
       </c>
       <c r="I27" t="n">
-        <v>11</v>
+        <v>6.8</v>
       </c>
       <c r="J27" t="n">
-        <v>176</v>
+        <v>88</v>
       </c>
       <c r="K27" t="n">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="L27" t="n">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>51.6</v>
       </c>
       <c r="N27" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O27" t="n">
         <v>17</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2035,13 +2035,13 @@
         <v>14</v>
       </c>
       <c r="H28" t="n">
-        <v>10.9</v>
+        <v>11.1</v>
       </c>
       <c r="I28" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="J28" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K28" t="n">
         <v>624</v>
@@ -2050,7 +2050,7 @@
         <v>624</v>
       </c>
       <c r="M28" t="n">
-        <v>57.4</v>
+        <v>56.1</v>
       </c>
       <c r="N28" t="n">
         <v>45</v>
@@ -2060,14 +2060,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~57 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~56 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,38 +2077,38 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="E29" t="n">
-        <v>13.34</v>
+        <v>18.02</v>
       </c>
       <c r="F29" t="n">
-        <v>3.33</v>
+        <v>1.98</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H29" t="n">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="I29" t="n">
-        <v>10.7</v>
+        <v>8.4</v>
       </c>
       <c r="J29" t="n">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="K29" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="L29" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="M29" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
         <v>47</v>
@@ -2118,14 +2118,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~12u (4cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D30" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G30" t="n">
         <v>20</v>
       </c>
-      <c r="E30" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G30" t="n">
-        <v>10</v>
-      </c>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I30" t="n">
-        <v>8.4</v>
+        <v>27.9</v>
       </c>
       <c r="J30" t="n">
-        <v>73</v>
+        <v>146</v>
       </c>
       <c r="K30" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="N30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2193,48 +2193,48 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.85</v>
+        <v>16.67</v>
       </c>
       <c r="E31" t="n">
-        <v>8.68</v>
+        <v>13.34</v>
       </c>
       <c r="F31" t="n">
-        <v>2.17</v>
+        <v>3.33</v>
       </c>
       <c r="G31" t="n">
         <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="I31" t="n">
-        <v>29.2</v>
+        <v>11.2</v>
       </c>
       <c r="J31" t="n">
-        <v>148</v>
+        <v>28</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="N31" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O31" t="n">
         <v>15</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~9u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2267,13 +2267,13 @@
         <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="I32" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="J32" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="K32" t="n">
         <v>150</v>
@@ -2282,7 +2282,7 @@
         <v>150</v>
       </c>
       <c r="M32" t="n">
-        <v>14.2</v>
+        <v>13.7</v>
       </c>
       <c r="N32" t="n">
         <v>50</v>
@@ -2383,10 +2383,10 @@
         <v>11</v>
       </c>
       <c r="H34" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="I34" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="J34" t="n">
         <v>76</v>
@@ -2398,7 +2398,7 @@
         <v>150</v>
       </c>
       <c r="M34" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="N34" t="n">
         <v>55</v>
@@ -2441,13 +2441,13 @@
         <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I35" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K35" t="n">
         <v>624</v>
@@ -2456,7 +2456,7 @@
         <v>624</v>
       </c>
       <c r="M35" t="n">
-        <v>74.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="N35" t="n">
         <v>45</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~75 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~77 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2557,10 +2557,10 @@
         <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I37" t="n">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="J37" t="n">
         <v>90</v>
@@ -2572,17 +2572,17 @@
         <v>150</v>
       </c>
       <c r="M37" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="N37" t="n">
         <v>55</v>
       </c>
       <c r="O37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2615,13 +2615,13 @@
         <v>11</v>
       </c>
       <c r="H38" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I38" t="n">
-        <v>14</v>
+        <v>12.8</v>
       </c>
       <c r="J38" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K38" t="n">
         <v>150</v>
@@ -2630,7 +2630,7 @@
         <v>150</v>
       </c>
       <c r="M38" t="n">
-        <v>22.9</v>
+        <v>21.6</v>
       </c>
       <c r="N38" t="n">
         <v>45</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~23 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~22 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2731,10 +2731,10 @@
         <v>20</v>
       </c>
       <c r="H40" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I40" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
         <v>30</v>
@@ -2746,7 +2746,7 @@
         <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N40" t="n">
         <v>47</v>
@@ -2789,10 +2789,10 @@
         <v>24</v>
       </c>
       <c r="H41" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I41" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J41" t="n">
         <v>30</v>
@@ -2804,7 +2804,7 @@
         <v>6</v>
       </c>
       <c r="M41" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N41" t="n">
         <v>45</v>
@@ -2847,10 +2847,10 @@
         <v>22</v>
       </c>
       <c r="H42" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="I42" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
         <v>30</v>
@@ -2862,7 +2862,7 @@
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="N42" t="n">
         <v>46</v>
@@ -2905,10 +2905,10 @@
         <v>24</v>
       </c>
       <c r="H43" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I43" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="J43" t="n">
         <v>50</v>
@@ -2963,10 +2963,10 @@
         <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I44" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="J44" t="n">
         <v>50</v>
@@ -3021,10 +3021,10 @@
         <v>22</v>
       </c>
       <c r="H45" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I45" t="n">
-        <v>16.4</v>
+        <v>16.6</v>
       </c>
       <c r="J45" t="n">
         <v>50</v>
@@ -3079,10 +3079,10 @@
         <v>14</v>
       </c>
       <c r="H46" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>48.9</v>
+        <v>57.2</v>
       </c>
       <c r="J46" t="n">
         <v>153</v>
@@ -3094,17 +3094,17 @@
         <v>150</v>
       </c>
       <c r="M46" t="n">
-        <v>32.3</v>
+        <v>37.7</v>
       </c>
       <c r="N46" t="n">
         <v>50</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~32 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~38 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3311,10 +3311,10 @@
         <v>33</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="I50" t="n">
-        <v>71.40000000000001</v>
+        <v>107.1</v>
       </c>
       <c r="J50" t="n">
         <v>30</v>
@@ -3326,17 +3326,17 @@
         <v>12</v>
       </c>
       <c r="M50" t="n">
-        <v>15.9</v>
+        <v>23.8</v>
       </c>
       <c r="N50" t="n">
         <v>46</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~16 wks (rising into season)</t>
+          <t>CAUTION - 12u = ~24 wks (overstock); consider ~12u</t>
         </is>
       </c>
     </row>
@@ -3427,10 +3427,10 @@
         <v>9</v>
       </c>
       <c r="H52" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="I52" t="n">
-        <v>11.6</v>
+        <v>12.6</v>
       </c>
       <c r="J52" t="n">
         <v>21</v>
@@ -3442,7 +3442,7 @@
         <v>624</v>
       </c>
       <c r="M52" t="n">
-        <v>369.1</v>
+        <v>400.2</v>
       </c>
       <c r="N52" t="n">
         <v>46</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~369 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~400 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>155.9</v>
+        <v>156.8</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="M2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~760u (380cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~748u (374cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>39.9</v>
+        <v>37.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,17 +600,17 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BUY ~208u (104cs) - sells in ~5 wks</t>
+          <t>BUY ~208u (104cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>21.6</v>
+        <v>23.3</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>81</v>
+        <v>61</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~92u (46cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~126u (63cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>26.2</v>
+        <v>27.8</v>
       </c>
       <c r="I5" t="n">
-        <v>12.2</v>
+        <v>10.3</v>
       </c>
       <c r="J5" t="n">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -716,17 +716,17 @@
         <v>40</v>
       </c>
       <c r="M5" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BUY ~40u (20cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~40u (20cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -759,22 +759,22 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="M6" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
@@ -784,7 +784,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~50u (25cs) - sells in ~4 wks</t>
+          <t>BUY ~64u (32cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
@@ -817,39 +817,39 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>18.3</v>
+        <v>16.8</v>
       </c>
       <c r="I7" t="n">
-        <v>12.2</v>
+        <v>13.1</v>
       </c>
       <c r="J7" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="K7" t="n">
         <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M7" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="N7" t="n">
         <v>46</v>
       </c>
       <c r="O7" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~18u (3cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -859,48 +859,48 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>25.7</v>
       </c>
       <c r="E8" t="n">
-        <v>11.2</v>
+        <v>21.7</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>12.8</v>
+        <v>8.4</v>
       </c>
       <c r="I8" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J8" t="n">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="K8" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>4.2</v>
+        <v>0.7</v>
       </c>
       <c r="N8" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BUY ~54u (9cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -933,13 +933,13 @@
         <v>14</v>
       </c>
       <c r="H9" t="n">
-        <v>24.5</v>
+        <v>23.6</v>
       </c>
       <c r="I9" t="n">
         <v>2.6</v>
       </c>
       <c r="J9" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K9" t="n">
         <v>624</v>
@@ -948,13 +948,13 @@
         <v>624</v>
       </c>
       <c r="M9" t="n">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="N9" t="n">
         <v>45</v>
       </c>
       <c r="O9" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -991,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>37</v>
+        <v>36.1</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="J10" t="n">
-        <v>123</v>
+        <v>157</v>
       </c>
       <c r="K10" t="n">
         <v>624</v>
@@ -1006,13 +1006,13 @@
         <v>624</v>
       </c>
       <c r="M10" t="n">
-        <v>16.9</v>
+        <v>17.3</v>
       </c>
       <c r="N10" t="n">
         <v>46</v>
       </c>
       <c r="O10" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1033,48 +1033,48 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.7</v>
+        <v>14</v>
       </c>
       <c r="E11" t="n">
-        <v>21.7</v>
+        <v>11.2</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="I11" t="n">
         <v>8.1</v>
       </c>
-      <c r="I11" t="n">
-        <v>8</v>
-      </c>
       <c r="J11" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2</v>
+        <v>3.8</v>
       </c>
       <c r="N11" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>BUY ~42u (7cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1107,13 +1107,13 @@
         <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>34.4</v>
+        <v>33.9</v>
       </c>
       <c r="I12" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="J12" t="n">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="K12" t="n">
         <v>624</v>
@@ -1122,7 +1122,7 @@
         <v>624</v>
       </c>
       <c r="M12" t="n">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="N12" t="n">
         <v>46</v>
@@ -1139,7 +1139,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,38 +1149,38 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.03</v>
+        <v>20</v>
       </c>
       <c r="E13" t="n">
-        <v>9.15</v>
+        <v>16.67</v>
       </c>
       <c r="F13" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H13" t="n">
-        <v>33.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>7.4</v>
+        <v>14.7</v>
       </c>
       <c r="J13" t="n">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="K13" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>18.8</v>
+        <v>0.3</v>
       </c>
       <c r="N13" t="n">
         <v>46</v>
@@ -1190,14 +1190,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,38 +1207,38 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>10.03</v>
       </c>
       <c r="E14" t="n">
-        <v>16.67</v>
+        <v>9.15</v>
       </c>
       <c r="F14" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G14" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>8.4</v>
+        <v>32.3</v>
       </c>
       <c r="I14" t="n">
-        <v>15.6</v>
+        <v>7.5</v>
       </c>
       <c r="J14" t="n">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4</v>
+        <v>19.3</v>
       </c>
       <c r="N14" t="n">
         <v>46</v>
@@ -1248,14 +1248,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,48 +1265,48 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26.5</v>
+        <v>25.7</v>
       </c>
       <c r="E15" t="n">
-        <v>21.32</v>
+        <v>21.7</v>
       </c>
       <c r="F15" t="n">
-        <v>5.18</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>7.1</v>
       </c>
       <c r="I15" t="n">
-        <v>12.6</v>
+        <v>4.6</v>
       </c>
       <c r="J15" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="N15" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>BUY ~22u (11cs) - sells in ~3 wks</t>
         </is>
       </c>
     </row>
@@ -1327,25 +1327,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>23.4</v>
+        <v>25.9</v>
       </c>
       <c r="E16" t="n">
-        <v>18.22</v>
+        <v>20.72</v>
       </c>
       <c r="F16" t="n">
         <v>5.18</v>
       </c>
       <c r="G16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H16" t="n">
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>12.6</v>
+        <v>11.1</v>
       </c>
       <c r="J16" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
@@ -1357,7 +1357,7 @@
         <v>0.4</v>
       </c>
       <c r="N16" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="O16" t="n">
         <v>26</v>
@@ -1385,25 +1385,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>25.9</v>
+        <v>23.4</v>
       </c>
       <c r="E17" t="n">
-        <v>20.72</v>
+        <v>18.22</v>
       </c>
       <c r="F17" t="n">
         <v>5.18</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H17" t="n">
         <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>12.6</v>
+        <v>11.1</v>
       </c>
       <c r="J17" t="n">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="K17" t="n">
         <v>2</v>
@@ -1415,7 +1415,7 @@
         <v>0.4</v>
       </c>
       <c r="N17" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O17" t="n">
         <v>26</v>
@@ -1429,7 +1429,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,48 +1439,48 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>25.7</v>
+        <v>26.5</v>
       </c>
       <c r="E18" t="n">
-        <v>21.7</v>
+        <v>21.32</v>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>5.18</v>
       </c>
       <c r="G18" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H18" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>6.7</v>
+        <v>11.1</v>
       </c>
       <c r="J18" t="n">
-        <v>44</v>
+        <v>60</v>
       </c>
       <c r="K18" t="n">
         <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="N18" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="O18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
@@ -1513,13 +1513,13 @@
         <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="I19" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="J19" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
@@ -1534,7 +1534,7 @@
         <v>46</v>
       </c>
       <c r="O19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,55 +1555,55 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>8.68</v>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>13.1</v>
+        <v>8.6</v>
       </c>
       <c r="I20" t="n">
-        <v>9</v>
+        <v>23.4</v>
       </c>
       <c r="J20" t="n">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="K20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>47.5</v>
+        <v>0.7</v>
       </c>
       <c r="N20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O20" t="n">
         <v>19</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~48 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,38 +1613,38 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>26.52</v>
       </c>
       <c r="E21" t="n">
-        <v>11.2</v>
+        <v>24.2</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8</v>
+        <v>2.33</v>
       </c>
       <c r="G21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>24.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>13.9</v>
+        <v>11.5</v>
       </c>
       <c r="J21" t="n">
-        <v>186</v>
+        <v>53</v>
       </c>
       <c r="K21" t="n">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="L21" t="n">
-        <v>84</v>
+        <v>208</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>25</v>
       </c>
       <c r="N21" t="n">
         <v>44</v>
@@ -1654,14 +1654,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>CAUTION - 208u = ~25 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,55 +1671,55 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E22" t="n">
-        <v>9.9</v>
+        <v>9.06</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>8.4</v>
+        <v>13.4</v>
       </c>
       <c r="I22" t="n">
-        <v>9.6</v>
+        <v>8.5</v>
       </c>
       <c r="J22" t="n">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L22" t="n">
-        <v>24</v>
+        <v>624</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>46.5</v>
       </c>
       <c r="N22" t="n">
         <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~3 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~46 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,55 +1729,55 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>26.52</v>
+        <v>9.33</v>
       </c>
       <c r="E23" t="n">
-        <v>24.2</v>
+        <v>8.01</v>
       </c>
       <c r="F23" t="n">
-        <v>2.33</v>
+        <v>1.32</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>7.7</v>
+        <v>12.5</v>
       </c>
       <c r="I23" t="n">
-        <v>13.3</v>
+        <v>5.8</v>
       </c>
       <c r="J23" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="K23" t="n">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="L23" t="n">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="M23" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="N23" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~27 wks (overstock); consider ~208u</t>
+          <t>BUY ~150u (25cs) - sells in ~12 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,55 +1787,55 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E24" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F24" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>8.300000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="I24" t="n">
-        <v>25.2</v>
+        <v>9</v>
       </c>
       <c r="J24" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L24" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7</v>
+        <v>53.3</v>
       </c>
       <c r="N24" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~53 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,55 +1845,55 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H25" t="n">
-        <v>21.8</v>
+        <v>7.9</v>
       </c>
       <c r="I25" t="n">
-        <v>10.8</v>
+        <v>5.7</v>
       </c>
       <c r="J25" t="n">
-        <v>175</v>
+        <v>25</v>
       </c>
       <c r="K25" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L25" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>5.3</v>
       </c>
       <c r="N25" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O25" t="n">
         <v>17</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~42u (7cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="F26" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="G26" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>8.199999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="I26" t="n">
-        <v>6.1</v>
+        <v>16.6</v>
       </c>
       <c r="J26" t="n">
-        <v>28</v>
+        <v>179</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="L26" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="M26" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="N26" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~42u (7cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1977,13 +1977,13 @@
         <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>12.1</v>
+        <v>11.2</v>
       </c>
       <c r="I27" t="n">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="J27" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K27" t="n">
         <v>624</v>
@@ -1992,24 +1992,24 @@
         <v>624</v>
       </c>
       <c r="M27" t="n">
-        <v>51.6</v>
+        <v>55.9</v>
       </c>
       <c r="N27" t="n">
         <v>45</v>
       </c>
       <c r="O27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~56 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,55 +2019,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>9.06</v>
+        <v>9.9</v>
       </c>
       <c r="F28" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="G28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H28" t="n">
-        <v>11.1</v>
+        <v>7</v>
       </c>
       <c r="I28" t="n">
-        <v>7.5</v>
+        <v>11.3</v>
       </c>
       <c r="J28" t="n">
-        <v>89</v>
+        <v>44</v>
       </c>
       <c r="K28" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M28" t="n">
-        <v>56.1</v>
+        <v>1.7</v>
       </c>
       <c r="N28" t="n">
         <v>45</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~56 wks (overstock); consider ~624u</t>
+          <t>BUY ~12u (2cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>18.02</v>
+        <v>11.2</v>
       </c>
       <c r="F29" t="n">
-        <v>1.98</v>
+        <v>0.8</v>
       </c>
       <c r="G29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>8</v>
+        <v>19.2</v>
       </c>
       <c r="I29" t="n">
-        <v>8.4</v>
+        <v>11.9</v>
       </c>
       <c r="J29" t="n">
-        <v>72</v>
+        <v>170</v>
       </c>
       <c r="K29" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="L29" t="n">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.85</v>
+        <v>20</v>
       </c>
       <c r="E30" t="n">
-        <v>8.68</v>
+        <v>18.02</v>
       </c>
       <c r="F30" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H30" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I30" t="n">
-        <v>27.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>146</v>
+        <v>65</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>0.9</v>
+        <v>5.4</v>
       </c>
       <c r="N30" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O30" t="n">
         <v>15</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2193,55 +2193,55 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.67</v>
+        <v>10.85</v>
       </c>
       <c r="E31" t="n">
-        <v>13.34</v>
+        <v>8.68</v>
       </c>
       <c r="F31" t="n">
-        <v>3.33</v>
+        <v>2.17</v>
       </c>
       <c r="G31" t="n">
         <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="I31" t="n">
-        <v>11.2</v>
+        <v>29.1</v>
       </c>
       <c r="J31" t="n">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="N31" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~9u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,55 +2251,55 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.33</v>
+        <v>16.67</v>
       </c>
       <c r="E32" t="n">
-        <v>8.01</v>
+        <v>13.34</v>
       </c>
       <c r="F32" t="n">
-        <v>1.32</v>
+        <v>3.33</v>
       </c>
       <c r="G32" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>10.9</v>
+        <v>4.3</v>
       </c>
       <c r="I32" t="n">
-        <v>7.7</v>
+        <v>11.3</v>
       </c>
       <c r="J32" t="n">
+        <v>27</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>9</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N32" t="n">
         <v>47</v>
-      </c>
-      <c r="K32" t="n">
-        <v>150</v>
-      </c>
-      <c r="L32" t="n">
-        <v>150</v>
-      </c>
-      <c r="M32" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="N32" t="n">
-        <v>50</v>
       </c>
       <c r="O32" t="n">
         <v>14</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
+          <t>BUY ~9u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F33" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H33" t="n">
-        <v>15.5</v>
+        <v>10.8</v>
       </c>
       <c r="I33" t="n">
-        <v>8.6</v>
+        <v>9.1</v>
       </c>
       <c r="J33" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="K33" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L33" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M33" t="n">
-        <v>40.3</v>
+        <v>14</v>
       </c>
       <c r="N33" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O33" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,48 +2367,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>10.03</v>
       </c>
       <c r="E34" t="n">
-        <v>9.82</v>
+        <v>9.15</v>
       </c>
       <c r="F34" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="G34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
-        <v>10.1</v>
+        <v>14.9</v>
       </c>
       <c r="I34" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="J34" t="n">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="K34" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L34" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M34" t="n">
-        <v>14.9</v>
+        <v>41.9</v>
       </c>
       <c r="N34" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2441,13 +2441,13 @@
         <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>7.3</v>
       </c>
       <c r="J35" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K35" t="n">
         <v>624</v>
@@ -2456,7 +2456,7 @@
         <v>624</v>
       </c>
       <c r="M35" t="n">
-        <v>77.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>45</v>
@@ -2466,14 +2466,14 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~77 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~78 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,55 +2483,55 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E36" t="n">
-        <v>11.2</v>
+        <v>9.82</v>
       </c>
       <c r="F36" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="G36" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H36" t="n">
-        <v>12.6</v>
+        <v>8.4</v>
       </c>
       <c r="I36" t="n">
-        <v>12.3</v>
+        <v>12.8</v>
       </c>
       <c r="J36" t="n">
-        <v>165</v>
+        <v>84</v>
       </c>
       <c r="K36" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L36" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M36" t="n">
-        <v>6.7</v>
+        <v>17.8</v>
       </c>
       <c r="N36" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O36" t="n">
         <v>10</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~7 wks</t>
+          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,48 +2541,48 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E37" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F37" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H37" t="n">
-        <v>8</v>
+        <v>11.4</v>
       </c>
       <c r="I37" t="n">
-        <v>14.5</v>
+        <v>13.1</v>
       </c>
       <c r="J37" t="n">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="K37" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L37" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M37" t="n">
-        <v>18.8</v>
+        <v>7.4</v>
       </c>
       <c r="N37" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="O37" t="n">
         <v>9</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
+          <t>BUY ~84u (14cs) - sells in ~7 wks</t>
         </is>
       </c>
     </row>
@@ -2615,13 +2615,13 @@
         <v>11</v>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="I38" t="n">
-        <v>12.8</v>
+        <v>11.2</v>
       </c>
       <c r="J38" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K38" t="n">
         <v>150</v>
@@ -2630,24 +2630,24 @@
         <v>150</v>
       </c>
       <c r="M38" t="n">
-        <v>21.6</v>
+        <v>18.6</v>
       </c>
       <c r="N38" t="n">
         <v>45</v>
       </c>
       <c r="O38" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~22 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,48 +2657,48 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D39" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G39" t="n">
         <v>14</v>
       </c>
-      <c r="E39" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="F39" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="G39" t="n">
-        <v>20</v>
-      </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
       <c r="I39" t="n">
-        <v>13.4</v>
+        <v>15</v>
       </c>
       <c r="J39" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="K39" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="L39" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="M39" t="n">
-        <v>8.1</v>
+        <v>30.9</v>
       </c>
       <c r="N39" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O39" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~8 wks (rising into season)</t>
+          <t>CAUTION - 150u = ~31 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2719,22 +2719,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.5</v>
+        <v>8.67</v>
       </c>
       <c r="E40" t="n">
-        <v>8.4</v>
+        <v>6.57</v>
       </c>
       <c r="F40" t="n">
         <v>2.1</v>
       </c>
       <c r="G40" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H40" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="J40" t="n">
         <v>30</v>
@@ -2746,13 +2746,13 @@
         <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="N40" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="O40" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,55 +2773,55 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8.67</v>
+        <v>14</v>
       </c>
       <c r="E41" t="n">
-        <v>6.57</v>
+        <v>11.2</v>
       </c>
       <c r="F41" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="G41" t="n">
+        <v>20</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>27</v>
+      </c>
+      <c r="K41" t="n">
         <v>24</v>
       </c>
-      <c r="H41" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="I41" t="n">
-        <v>9</v>
-      </c>
-      <c r="J41" t="n">
-        <v>30</v>
-      </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
+        <v>24</v>
+      </c>
+      <c r="M41" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="N41" t="n">
+        <v>44</v>
+      </c>
+      <c r="O41" t="n">
         <v>6</v>
       </c>
-      <c r="L41" t="n">
-        <v>6</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N41" t="n">
-        <v>45</v>
-      </c>
-      <c r="O41" t="n">
-        <v>7</v>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~12 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2835,25 +2835,25 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>9.67</v>
+        <v>8.67</v>
       </c>
       <c r="E42" t="n">
-        <v>7.57</v>
+        <v>6.57</v>
       </c>
       <c r="F42" t="n">
         <v>2.1</v>
       </c>
       <c r="G42" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H42" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>14.9</v>
       </c>
       <c r="J42" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="K42" t="n">
         <v>6</v>
@@ -2862,13 +2862,13 @@
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="N42" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -2893,25 +2893,25 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>8.67</v>
+        <v>10.5</v>
       </c>
       <c r="E43" t="n">
-        <v>6.57</v>
+        <v>8.4</v>
       </c>
       <c r="F43" t="n">
         <v>2.1</v>
       </c>
       <c r="G43" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="I43" t="n">
-        <v>16.6</v>
+        <v>14.9</v>
       </c>
       <c r="J43" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="K43" t="n">
         <v>6</v>
@@ -2923,7 +2923,7 @@
         <v>2.1</v>
       </c>
       <c r="N43" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O43" t="n">
         <v>6</v>
@@ -2937,7 +2937,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2951,25 +2951,25 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.5</v>
+        <v>9.67</v>
       </c>
       <c r="E44" t="n">
-        <v>8.4</v>
+        <v>7.57</v>
       </c>
       <c r="F44" t="n">
         <v>2.1</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H44" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="I44" t="n">
-        <v>16.6</v>
+        <v>10.3</v>
       </c>
       <c r="J44" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K44" t="n">
         <v>6</v>
@@ -2978,10 +2978,10 @@
         <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N44" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O44" t="n">
         <v>6</v>
@@ -2995,7 +2995,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3009,25 +3009,25 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9.67</v>
+        <v>10.5</v>
       </c>
       <c r="E45" t="n">
-        <v>7.57</v>
+        <v>8.4</v>
       </c>
       <c r="F45" t="n">
         <v>2.1</v>
       </c>
       <c r="G45" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="I45" t="n">
-        <v>16.6</v>
+        <v>10.3</v>
       </c>
       <c r="J45" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K45" t="n">
         <v>6</v>
@@ -3036,10 +3036,10 @@
         <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N45" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O45" t="n">
         <v>6</v>
@@ -3053,7 +3053,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,55 +3063,55 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>9.33</v>
+        <v>9.67</v>
       </c>
       <c r="E46" t="n">
-        <v>8.01</v>
+        <v>7.57</v>
       </c>
       <c r="F46" t="n">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="G46" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="I46" t="n">
-        <v>57.2</v>
+        <v>14.9</v>
       </c>
       <c r="J46" t="n">
-        <v>153</v>
+        <v>46</v>
       </c>
       <c r="K46" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L46" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M46" t="n">
-        <v>37.7</v>
+        <v>2.1</v>
       </c>
       <c r="N46" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~38 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
+          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3125,44 +3125,44 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.45</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>11.47</v>
+        <v>9.82</v>
       </c>
       <c r="F47" t="n">
-        <v>1.97</v>
+        <v>1.18</v>
       </c>
       <c r="G47" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>1.8</v>
+        <v>3.6</v>
       </c>
       <c r="I47" t="n">
-        <v>20.2</v>
+        <v>15.3</v>
       </c>
       <c r="J47" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="K47" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="L47" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>22.1</v>
+        <v>41.8</v>
       </c>
       <c r="N47" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O47" t="n">
         <v>4</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~22 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 150u = ~42 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3195,10 +3195,10 @@
         <v>20</v>
       </c>
       <c r="H48" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="I48" t="n">
-        <v>37.5</v>
+        <v>41.9</v>
       </c>
       <c r="J48" t="n">
         <v>73</v>
@@ -3210,7 +3210,7 @@
         <v>24</v>
       </c>
       <c r="M48" t="n">
-        <v>16.2</v>
+        <v>18.1</v>
       </c>
       <c r="N48" t="n">
         <v>44</v>
@@ -3220,14 +3220,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 24u = ~16 wks (overstock); consider ~24u</t>
+          <t>CAUTION - 24u = ~18 wks (overstock); consider ~24u</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
+          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3241,44 +3241,44 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11</v>
+        <v>13.45</v>
       </c>
       <c r="E49" t="n">
-        <v>9.82</v>
+        <v>11.47</v>
       </c>
       <c r="F49" t="n">
-        <v>1.18</v>
+        <v>1.97</v>
       </c>
       <c r="G49" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H49" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="I49" t="n">
-        <v>20.4</v>
+        <v>26.3</v>
       </c>
       <c r="J49" t="n">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="K49" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="L49" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>51.5</v>
+        <v>26.1</v>
       </c>
       <c r="N49" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~52 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 40u = ~26 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Blue Ginger 10mg 4pk 12oz can</t>
+          <t>Stigma Berry Tea 10mg THC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3353,55 +3353,55 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11</v>
+        <v>10.03</v>
       </c>
       <c r="E51" t="n">
-        <v>9.82</v>
+        <v>9.15</v>
       </c>
       <c r="F51" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="G51" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H51" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="I51" t="n">
-        <v>143.8</v>
+        <v>9.1</v>
       </c>
       <c r="J51" t="n">
-        <v>85</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L51" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M51" t="n">
-        <v>270.9</v>
+        <v>337.2</v>
       </c>
       <c r="N51" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~271 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 624u = ~337 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Stigma Berry Tea 10mg THC</t>
+          <t>Clrty SodaPot Blue Ginger 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3411,48 +3411,48 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E52" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F52" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G52" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H52" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="I52" t="n">
-        <v>12.6</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>21</v>
+        <v>83</v>
       </c>
       <c r="K52" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L52" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M52" t="n">
-        <v>400.2</v>
+        <v>171.5</v>
       </c>
       <c r="N52" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O52" t="n">
         <v>1</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~400 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 150u = ~172 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>156.8</v>
+        <v>158</v>
       </c>
       <c r="I2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>748</v>
+        <v>768</v>
       </c>
       <c r="M2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~748u (374cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~768u (384cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>175</v>
+        <v>192</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,19 +643,19 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>23.3</v>
+        <v>22.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M4" t="n">
         <v>5.4</v>
@@ -664,11 +664,11 @@
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~126u (63cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~122u (61cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         <v>10.3</v>
       </c>
       <c r="J5" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -759,13 +759,13 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="I6" t="n">
         <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -817,10 +817,10 @@
         <v>20</v>
       </c>
       <c r="H7" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="I7" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="J7" t="n">
         <v>122</v>
@@ -829,10 +829,10 @@
         <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M7" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="N7" t="n">
         <v>46</v>
@@ -842,14 +842,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BUY ~18u (3cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~12u (2cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -859,55 +859,55 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.7</v>
+        <v>10.5</v>
       </c>
       <c r="E8" t="n">
-        <v>21.7</v>
+        <v>9.06</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="H8" t="n">
-        <v>8.4</v>
+        <v>24.2</v>
       </c>
       <c r="I8" t="n">
-        <v>6.9</v>
+        <v>2.3</v>
       </c>
       <c r="J8" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7</v>
+        <v>25.8</v>
       </c>
       <c r="N8" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O8" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
+          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -917,48 +917,48 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.5</v>
+        <v>25.7</v>
       </c>
       <c r="E9" t="n">
-        <v>9.06</v>
+        <v>21.7</v>
       </c>
       <c r="F9" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>23.6</v>
+        <v>8.4</v>
       </c>
       <c r="I9" t="n">
-        <v>2.6</v>
+        <v>6.9</v>
       </c>
       <c r="J9" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K9" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>26.5</v>
+        <v>0.7</v>
       </c>
       <c r="N9" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -991,13 +991,13 @@
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="I10" t="n">
         <v>7.8</v>
       </c>
       <c r="J10" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K10" t="n">
         <v>624</v>
@@ -1006,7 +1006,7 @@
         <v>624</v>
       </c>
       <c r="M10" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="N10" t="n">
         <v>46</v>
@@ -1139,7 +1139,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,38 +1149,38 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20</v>
+        <v>10.03</v>
       </c>
       <c r="E13" t="n">
-        <v>16.67</v>
+        <v>9.15</v>
       </c>
       <c r="F13" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G13" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>8.699999999999999</v>
+        <v>32.5</v>
       </c>
       <c r="I13" t="n">
-        <v>14.7</v>
+        <v>7.8</v>
       </c>
       <c r="J13" t="n">
-        <v>75</v>
+        <v>140</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="M13" t="n">
-        <v>0.3</v>
+        <v>19.2</v>
       </c>
       <c r="N13" t="n">
         <v>46</v>
@@ -1190,14 +1190,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,48 +1207,48 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10.03</v>
+        <v>20</v>
       </c>
       <c r="E14" t="n">
-        <v>9.15</v>
+        <v>16.67</v>
       </c>
       <c r="F14" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>32.3</v>
+        <v>8.6</v>
       </c>
       <c r="I14" t="n">
-        <v>7.5</v>
+        <v>14.9</v>
       </c>
       <c r="J14" t="n">
-        <v>135</v>
+        <v>75</v>
       </c>
       <c r="K14" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L14" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>19.3</v>
+        <v>0.3</v>
       </c>
       <c r="N14" t="n">
         <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1284,19 +1284,19 @@
         <v>7.1</v>
       </c>
       <c r="I15" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="N15" t="n">
         <v>50</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~22u (11cs) - sells in ~3 wks</t>
+          <t>BUY ~12u (6cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -1513,10 +1513,10 @@
         <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="J19" t="n">
         <v>95</v>
@@ -1545,7 +1545,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,48 +1555,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E20" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F20" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
+        <v>14</v>
+      </c>
+      <c r="H20" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J20" t="n">
+        <v>120</v>
+      </c>
+      <c r="K20" t="n">
+        <v>624</v>
+      </c>
+      <c r="L20" t="n">
+        <v>624</v>
+      </c>
+      <c r="M20" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="N20" t="n">
+        <v>45</v>
+      </c>
+      <c r="O20" t="n">
         <v>20</v>
       </c>
-      <c r="H20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I20" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="J20" t="n">
-        <v>112</v>
-      </c>
-      <c r="K20" t="n">
-        <v>6</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="N20" t="n">
-        <v>46</v>
-      </c>
-      <c r="O20" t="n">
-        <v>19</v>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~46 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,55 +1671,55 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E22" t="n">
-        <v>9.06</v>
+        <v>8.68</v>
       </c>
       <c r="F22" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>13.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>8.5</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="K22" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>46.5</v>
+        <v>0.7</v>
       </c>
       <c r="N22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O22" t="n">
         <v>19</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~46 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1733,51 +1733,51 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>9.33</v>
+        <v>10.5</v>
       </c>
       <c r="E23" t="n">
-        <v>8.01</v>
+        <v>9.06</v>
       </c>
       <c r="F23" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="G23" t="n">
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>12.5</v>
+        <v>12.7</v>
       </c>
       <c r="I23" t="n">
-        <v>5.8</v>
+        <v>7.7</v>
       </c>
       <c r="J23" t="n">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="K23" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L23" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>12</v>
+        <v>49.2</v>
       </c>
       <c r="N23" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~12 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1791,44 +1791,44 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.5</v>
+        <v>9.33</v>
       </c>
       <c r="E24" t="n">
-        <v>9.06</v>
+        <v>8.01</v>
       </c>
       <c r="F24" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="G24" t="n">
         <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>11.7</v>
+        <v>12.5</v>
       </c>
       <c r="I24" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="J24" t="n">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="K24" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L24" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M24" t="n">
-        <v>53.3</v>
+        <v>12</v>
       </c>
       <c r="N24" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O24" t="n">
         <v>17</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~53 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~12 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1977,10 +1977,10 @@
         <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="I27" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J27" t="n">
         <v>87</v>
@@ -1992,7 +1992,7 @@
         <v>624</v>
       </c>
       <c r="M27" t="n">
-        <v>55.9</v>
+        <v>56.3</v>
       </c>
       <c r="N27" t="n">
         <v>45</v>
@@ -2035,22 +2035,22 @@
         <v>17</v>
       </c>
       <c r="H28" t="n">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I28" t="n">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="J28" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K28" t="n">
         <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M28" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="N28" t="n">
         <v>45</v>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2096,10 +2096,10 @@
         <v>19.2</v>
       </c>
       <c r="I29" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="J29" t="n">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K29" t="n">
         <v>84</v>
@@ -2151,13 +2151,13 @@
         <v>10</v>
       </c>
       <c r="H30" t="n">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="I30" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J30" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K30" t="n">
         <v>40</v>
@@ -2166,7 +2166,7 @@
         <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="N30" t="n">
         <v>47</v>
@@ -2209,10 +2209,10 @@
         <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I31" t="n">
-        <v>29.1</v>
+        <v>30.2</v>
       </c>
       <c r="J31" t="n">
         <v>144</v>
@@ -2270,7 +2270,7 @@
         <v>4.3</v>
       </c>
       <c r="I32" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="J32" t="n">
         <v>27</v>
@@ -2325,10 +2325,10 @@
         <v>11</v>
       </c>
       <c r="H33" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="I33" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J33" t="n">
         <v>67</v>
@@ -2383,13 +2383,13 @@
         <v>9</v>
       </c>
       <c r="H34" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="I34" t="n">
-        <v>10.5</v>
+        <v>11.2</v>
       </c>
       <c r="J34" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K34" t="n">
         <v>624</v>
@@ -2398,7 +2398,7 @@
         <v>624</v>
       </c>
       <c r="M34" t="n">
-        <v>41.9</v>
+        <v>42.2</v>
       </c>
       <c r="N34" t="n">
         <v>46</v>
@@ -2441,13 +2441,13 @@
         <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I35" t="n">
         <v>7.3</v>
       </c>
       <c r="J35" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K35" t="n">
         <v>624</v>
@@ -2456,17 +2456,17 @@
         <v>624</v>
       </c>
       <c r="M35" t="n">
-        <v>77.59999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="N35" t="n">
         <v>45</v>
       </c>
       <c r="O35" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~78 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~80 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2499,13 +2499,13 @@
         <v>11</v>
       </c>
       <c r="H36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I36" t="n">
-        <v>12.8</v>
+        <v>12.4</v>
       </c>
       <c r="J36" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K36" t="n">
         <v>150</v>
@@ -2514,7 +2514,7 @@
         <v>150</v>
       </c>
       <c r="M36" t="n">
-        <v>17.8</v>
+        <v>17.4</v>
       </c>
       <c r="N36" t="n">
         <v>55</v>
@@ -2524,14 +2524,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,55 +2541,55 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E37" t="n">
-        <v>11.2</v>
+        <v>9.82</v>
       </c>
       <c r="F37" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="G37" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>11.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>13.1</v>
+        <v>10</v>
       </c>
       <c r="J37" t="n">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="K37" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L37" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M37" t="n">
-        <v>7.4</v>
+        <v>17.3</v>
       </c>
       <c r="N37" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O37" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~7 wks</t>
+          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2599,48 +2599,48 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E38" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F38" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G38" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H38" t="n">
-        <v>8.1</v>
+        <v>11.4</v>
       </c>
       <c r="I38" t="n">
-        <v>11.2</v>
+        <v>13.1</v>
       </c>
       <c r="J38" t="n">
-        <v>75</v>
+        <v>159</v>
       </c>
       <c r="K38" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L38" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M38" t="n">
-        <v>18.6</v>
+        <v>7.4</v>
       </c>
       <c r="N38" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O38" t="n">
         <v>9</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~19 wks (overstock); consider ~150u</t>
+          <t>BUY ~84u (14cs) - sells in ~7 wks</t>
         </is>
       </c>
     </row>
@@ -2676,10 +2676,10 @@
         <v>4.9</v>
       </c>
       <c r="I39" t="n">
-        <v>15</v>
+        <v>15.6</v>
       </c>
       <c r="J39" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K39" t="n">
         <v>150</v>
@@ -2734,7 +2734,7 @@
         <v>2.7</v>
       </c>
       <c r="I40" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="J40" t="n">
         <v>30</v>
@@ -2792,7 +2792,7 @@
         <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="J41" t="n">
         <v>27</v>
@@ -2804,7 +2804,7 @@
         <v>24</v>
       </c>
       <c r="M41" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="N41" t="n">
         <v>44</v>
@@ -2847,10 +2847,10 @@
         <v>24</v>
       </c>
       <c r="H42" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I42" t="n">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
       <c r="J42" t="n">
         <v>46</v>
@@ -2862,7 +2862,7 @@
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N42" t="n">
         <v>45</v>
@@ -2905,10 +2905,10 @@
         <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I43" t="n">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
       <c r="J43" t="n">
         <v>46</v>
@@ -2920,7 +2920,7 @@
         <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N43" t="n">
         <v>47</v>
@@ -2966,7 +2966,7 @@
         <v>2.7</v>
       </c>
       <c r="I44" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="J44" t="n">
         <v>30</v>
@@ -3024,7 +3024,7 @@
         <v>2.7</v>
       </c>
       <c r="I45" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="J45" t="n">
         <v>30</v>
@@ -3079,10 +3079,10 @@
         <v>22</v>
       </c>
       <c r="H46" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="I46" t="n">
-        <v>14.9</v>
+        <v>15.5</v>
       </c>
       <c r="J46" t="n">
         <v>46</v>
@@ -3094,7 +3094,7 @@
         <v>6</v>
       </c>
       <c r="M46" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="N46" t="n">
         <v>46</v>
@@ -3137,13 +3137,13 @@
         <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I47" t="n">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="J47" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K47" t="n">
         <v>150</v>
@@ -3152,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>41.8</v>
+        <v>40.6</v>
       </c>
       <c r="N47" t="n">
         <v>45</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~42 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~41 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3195,10 +3195,10 @@
         <v>20</v>
       </c>
       <c r="H48" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I48" t="n">
-        <v>41.9</v>
+        <v>45.6</v>
       </c>
       <c r="J48" t="n">
         <v>73</v>
@@ -3210,17 +3210,17 @@
         <v>24</v>
       </c>
       <c r="M48" t="n">
-        <v>18.1</v>
+        <v>19.6</v>
       </c>
       <c r="N48" t="n">
         <v>44</v>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 24u = ~18 wks (overstock); consider ~24u</t>
+          <t>CAUTION - 24u = ~20 wks (overstock); consider ~24u</t>
         </is>
       </c>
     </row>
@@ -3253,13 +3253,13 @@
         <v>15</v>
       </c>
       <c r="H49" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="I49" t="n">
-        <v>26.3</v>
+        <v>25.2</v>
       </c>
       <c r="J49" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K49" t="n">
         <v>40</v>
@@ -3268,7 +3268,7 @@
         <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>26.1</v>
+        <v>25.7</v>
       </c>
       <c r="N49" t="n">
         <v>48</v>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>158</v>
+        <v>157.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J2" t="n">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>768</v>
+        <v>784</v>
       </c>
       <c r="M2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~768u (384cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~784u (392cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>37.5</v>
+        <v>37.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -606,7 +606,7 @@
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,19 +643,19 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>22.7</v>
+        <v>22.2</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M4" t="n">
         <v>5.4</v>
@@ -664,11 +664,11 @@
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~122u (61cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~120u (60cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>27.8</v>
+        <v>28.4</v>
       </c>
       <c r="I5" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -759,39 +759,39 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>13.9</v>
+        <v>14.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J6" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="M6" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~64u (32cs) - sells in ~5 wks</t>
+          <t>BUY ~76u (38cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -801,55 +801,55 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E7" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F7" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>16.7</v>
+        <v>25.6</v>
       </c>
       <c r="I7" t="n">
-        <v>13.2</v>
+        <v>1.6</v>
       </c>
       <c r="J7" t="n">
-        <v>122</v>
+        <v>45</v>
       </c>
       <c r="K7" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>624</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7</v>
+        <v>24.4</v>
       </c>
       <c r="N7" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O7" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~24 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daizy's Grape 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -859,55 +859,55 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.5</v>
+        <v>25.7</v>
       </c>
       <c r="E8" t="n">
-        <v>9.06</v>
+        <v>21.7</v>
       </c>
       <c r="F8" t="n">
-        <v>1.44</v>
+        <v>4</v>
       </c>
       <c r="G8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H8" t="n">
-        <v>24.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3</v>
+        <v>6.2</v>
       </c>
       <c r="J8" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K8" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M8" t="n">
-        <v>25.8</v>
+        <v>1.4</v>
       </c>
       <c r="N8" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O8" t="n">
         <v>35</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
+          <t>BUY ~12u (6cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -917,55 +917,55 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25.7</v>
+        <v>10.85</v>
       </c>
       <c r="E9" t="n">
-        <v>21.7</v>
+        <v>8.68</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>2.17</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>8.4</v>
+        <v>16.2</v>
       </c>
       <c r="I9" t="n">
-        <v>6.9</v>
+        <v>13.3</v>
       </c>
       <c r="J9" t="n">
-        <v>62</v>
+        <v>119</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M9" t="n">
         <v>0.7</v>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O9" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>BUY ~6u (3cs) - sells in ~1 wks</t>
+          <t>BUY ~12u (2cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -975,55 +975,55 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.03</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
-        <v>9.15</v>
+        <v>11.2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.88</v>
+        <v>2.8</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>35.9</v>
+        <v>11.8</v>
       </c>
       <c r="I10" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
-        <v>156</v>
+        <v>47</v>
       </c>
       <c r="K10" t="n">
-        <v>624</v>
+        <v>24</v>
       </c>
       <c r="L10" t="n">
-        <v>624</v>
+        <v>48</v>
       </c>
       <c r="M10" t="n">
-        <v>17.4</v>
+        <v>4.1</v>
       </c>
       <c r="N10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~17 wks (overstock); consider ~624u</t>
+          <t>BUY ~48u (8cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1033,55 +1033,55 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14</v>
+        <v>10.03</v>
       </c>
       <c r="E11" t="n">
-        <v>11.2</v>
+        <v>9.15</v>
       </c>
       <c r="F11" t="n">
-        <v>2.8</v>
+        <v>0.88</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>11.1</v>
+        <v>35.2</v>
       </c>
       <c r="I11" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="J11" t="n">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="K11" t="n">
-        <v>24</v>
+        <v>624</v>
       </c>
       <c r="L11" t="n">
-        <v>42</v>
+        <v>624</v>
       </c>
       <c r="M11" t="n">
-        <v>3.8</v>
+        <v>17.7</v>
       </c>
       <c r="N11" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O11" t="n">
         <v>31</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>BUY ~42u (7cs) - sells in ~4 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~18 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1091,55 +1091,55 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.03</v>
+        <v>20</v>
       </c>
       <c r="E12" t="n">
-        <v>9.15</v>
+        <v>16.67</v>
       </c>
       <c r="F12" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>33.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>8.5</v>
+        <v>13.4</v>
       </c>
       <c r="J12" t="n">
-        <v>161</v>
+        <v>72</v>
       </c>
       <c r="K12" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L12" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="M12" t="n">
-        <v>18.4</v>
+        <v>0.3</v>
       </c>
       <c r="N12" t="n">
         <v>46</v>
       </c>
       <c r="O12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~18 wks (overstock); consider ~624u</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1165,13 +1165,13 @@
         <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>32.5</v>
+        <v>34.6</v>
       </c>
       <c r="I13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="K13" t="n">
         <v>624</v>
@@ -1180,24 +1180,24 @@
         <v>624</v>
       </c>
       <c r="M13" t="n">
-        <v>19.2</v>
+        <v>18</v>
       </c>
       <c r="N13" t="n">
         <v>46</v>
       </c>
       <c r="O13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~18 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,38 +1207,38 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20</v>
+        <v>10.03</v>
       </c>
       <c r="E14" t="n">
-        <v>16.67</v>
+        <v>9.15</v>
       </c>
       <c r="F14" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G14" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>8.6</v>
+        <v>33.1</v>
       </c>
       <c r="I14" t="n">
-        <v>14.9</v>
+        <v>7.4</v>
       </c>
       <c r="J14" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="K14" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3</v>
+        <v>18.8</v>
       </c>
       <c r="N14" t="n">
         <v>46</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1281,32 +1281,32 @@
         <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I15" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="J15" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M15" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="N15" t="n">
         <v>50</v>
       </c>
       <c r="O15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~12u (6cs) - sells in ~2 wks</t>
+          <t>BUY ~16u (8cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="J16" t="n">
         <v>60</v>
@@ -1400,7 +1400,7 @@
         <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="J17" t="n">
         <v>60</v>
@@ -1458,7 +1458,7 @@
         <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="J18" t="n">
         <v>60</v>
@@ -1513,13 +1513,13 @@
         <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I19" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="J19" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
@@ -1545,7 +1545,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,48 +1555,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>8.68</v>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>13.7</v>
+        <v>9.5</v>
       </c>
       <c r="I20" t="n">
-        <v>8.199999999999999</v>
+        <v>20.2</v>
       </c>
       <c r="J20" t="n">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="K20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>45.6</v>
+        <v>0.6</v>
       </c>
       <c r="N20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~46 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1629,13 +1629,13 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>8.300000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I21" t="n">
-        <v>11.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="K21" t="n">
         <v>208</v>
@@ -1644,24 +1644,24 @@
         <v>208</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>23.3</v>
       </c>
       <c r="N21" t="n">
         <v>44</v>
       </c>
       <c r="O21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~25 wks (overstock); consider ~208u</t>
+          <t>CAUTION - 208u = ~23 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,48 +1671,48 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E22" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F22" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>8.699999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>6.7</v>
       </c>
       <c r="J22" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7</v>
+        <v>41.9</v>
       </c>
       <c r="N22" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O22" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1745,13 +1745,13 @@
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>12.7</v>
+        <v>11.8</v>
       </c>
       <c r="I23" t="n">
-        <v>7.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K23" t="n">
         <v>624</v>
@@ -1760,24 +1760,24 @@
         <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>49.2</v>
+        <v>53</v>
       </c>
       <c r="N23" t="n">
         <v>45</v>
       </c>
       <c r="O23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~53 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,55 +1787,55 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9.33</v>
+        <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>8.01</v>
+        <v>11.2</v>
       </c>
       <c r="F24" t="n">
-        <v>1.32</v>
+        <v>0.8</v>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H24" t="n">
-        <v>12.5</v>
+        <v>19.5</v>
       </c>
       <c r="I24" t="n">
-        <v>5.6</v>
+        <v>17</v>
       </c>
       <c r="J24" t="n">
-        <v>39</v>
+        <v>184</v>
       </c>
       <c r="K24" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L24" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M24" t="n">
-        <v>12</v>
+        <v>4.3</v>
       </c>
       <c r="N24" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~12 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,55 +1845,55 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>12</v>
       </c>
       <c r="E25" t="n">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="G25" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>7.9</v>
+        <v>19.9</v>
       </c>
       <c r="I25" t="n">
-        <v>5.7</v>
+        <v>10.9</v>
       </c>
       <c r="J25" t="n">
-        <v>25</v>
+        <v>161</v>
       </c>
       <c r="K25" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="L25" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="M25" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="N25" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUY ~42u (7cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,48 +1903,48 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="G26" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H26" t="n">
-        <v>19.4</v>
+        <v>7.5</v>
       </c>
       <c r="I26" t="n">
-        <v>16.6</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>179</v>
+        <v>25</v>
       </c>
       <c r="K26" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="M26" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="N26" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O26" t="n">
         <v>16</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~36u (6cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1977,13 +1977,13 @@
         <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>11.1</v>
+        <v>10.8</v>
       </c>
       <c r="I27" t="n">
         <v>7.4</v>
       </c>
       <c r="J27" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K27" t="n">
         <v>624</v>
@@ -1992,17 +1992,17 @@
         <v>624</v>
       </c>
       <c r="M27" t="n">
-        <v>56.3</v>
+        <v>57.9</v>
       </c>
       <c r="N27" t="n">
         <v>45</v>
       </c>
       <c r="O27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~56 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~58 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2035,13 +2035,13 @@
         <v>17</v>
       </c>
       <c r="H28" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="I28" t="n">
         <v>10.6</v>
       </c>
       <c r="J28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K28" t="n">
         <v>6</v>
@@ -2067,7 +2067,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,48 +2077,48 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>9.33</v>
       </c>
       <c r="E29" t="n">
-        <v>11.2</v>
+        <v>8.01</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H29" t="n">
-        <v>19.2</v>
+        <v>11.5</v>
       </c>
       <c r="I29" t="n">
-        <v>11.8</v>
+        <v>6.1</v>
       </c>
       <c r="J29" t="n">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="K29" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L29" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M29" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="N29" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O29" t="n">
         <v>15</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>10</v>
       </c>
       <c r="H30" t="n">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I30" t="n">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K30" t="n">
         <v>40</v>
@@ -2166,7 +2166,7 @@
         <v>40</v>
       </c>
       <c r="M30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="N30" t="n">
         <v>47</v>
@@ -2209,10 +2209,10 @@
         <v>20</v>
       </c>
       <c r="H31" t="n">
-        <v>6.4</v>
+        <v>6.1</v>
       </c>
       <c r="I31" t="n">
-        <v>30.2</v>
+        <v>31.5</v>
       </c>
       <c r="J31" t="n">
         <v>144</v>
@@ -2224,13 +2224,13 @@
         <v>6</v>
       </c>
       <c r="M31" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N31" t="n">
         <v>46</v>
       </c>
       <c r="O31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -2267,10 +2267,10 @@
         <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="J32" t="n">
         <v>27</v>
@@ -2279,27 +2279,27 @@
         <v>3</v>
       </c>
       <c r="L32" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M32" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="N32" t="n">
         <v>47</v>
       </c>
       <c r="O32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BUY ~9u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~6u (2cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11</v>
+        <v>10.03</v>
       </c>
       <c r="E33" t="n">
-        <v>9.82</v>
+        <v>9.15</v>
       </c>
       <c r="F33" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="G33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>10.7</v>
+        <v>14.8</v>
       </c>
       <c r="I33" t="n">
-        <v>9.199999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="J33" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="K33" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L33" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M33" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="N33" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O33" t="n">
         <v>13</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,48 +2367,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F34" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H34" t="n">
-        <v>14.8</v>
+        <v>10.2</v>
       </c>
       <c r="I34" t="n">
-        <v>11.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="K34" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L34" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M34" t="n">
-        <v>42.2</v>
+        <v>14.6</v>
       </c>
       <c r="N34" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2441,13 +2441,13 @@
         <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>7.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>7.3</v>
+        <v>6.6</v>
       </c>
       <c r="J35" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="K35" t="n">
         <v>624</v>
@@ -2456,24 +2456,24 @@
         <v>624</v>
       </c>
       <c r="M35" t="n">
-        <v>79.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="N35" t="n">
         <v>45</v>
       </c>
       <c r="O35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~80 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~75 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2499,13 +2499,13 @@
         <v>11</v>
       </c>
       <c r="H36" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>12.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K36" t="n">
         <v>150</v>
@@ -2514,13 +2514,13 @@
         <v>150</v>
       </c>
       <c r="M36" t="n">
-        <v>17.4</v>
+        <v>16.6</v>
       </c>
       <c r="N36" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O36" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,7 +2541,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -2557,13 +2557,13 @@
         <v>11</v>
       </c>
       <c r="H37" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I37" t="n">
-        <v>10</v>
+        <v>12.1</v>
       </c>
       <c r="J37" t="n">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="K37" t="n">
         <v>150</v>
@@ -2572,10 +2572,10 @@
         <v>150</v>
       </c>
       <c r="M37" t="n">
-        <v>17.3</v>
+        <v>17.4</v>
       </c>
       <c r="N37" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O37" t="n">
         <v>10</v>
@@ -2615,13 +2615,13 @@
         <v>7</v>
       </c>
       <c r="H38" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="I38" t="n">
         <v>13.1</v>
       </c>
       <c r="J38" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K38" t="n">
         <v>84</v>
@@ -2630,7 +2630,7 @@
         <v>84</v>
       </c>
       <c r="M38" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="N38" t="n">
         <v>44</v>
@@ -2640,7 +2640,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~7 wks</t>
+          <t>BUY ~84u (14cs) - sells in ~8 wks</t>
         </is>
       </c>
     </row>
@@ -2673,10 +2673,10 @@
         <v>14</v>
       </c>
       <c r="H39" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I39" t="n">
-        <v>15.6</v>
+        <v>16.5</v>
       </c>
       <c r="J39" t="n">
         <v>51</v>
@@ -2688,7 +2688,7 @@
         <v>150</v>
       </c>
       <c r="M39" t="n">
-        <v>30.9</v>
+        <v>32.6</v>
       </c>
       <c r="N39" t="n">
         <v>50</v>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~31 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~33 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2731,10 +2731,10 @@
         <v>24</v>
       </c>
       <c r="H40" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="I40" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J40" t="n">
         <v>30</v>
@@ -2746,13 +2746,13 @@
         <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="N40" t="n">
         <v>45</v>
       </c>
       <c r="O40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -2789,10 +2789,10 @@
         <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="I41" t="n">
-        <v>19.7</v>
+        <v>22.5</v>
       </c>
       <c r="J41" t="n">
         <v>27</v>
@@ -2804,17 +2804,17 @@
         <v>24</v>
       </c>
       <c r="M41" t="n">
-        <v>12</v>
+        <v>13.7</v>
       </c>
       <c r="N41" t="n">
         <v>44</v>
       </c>
       <c r="O41" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~12 wks (rising into season)</t>
+          <t>BUY ~24u (4cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2847,10 +2847,10 @@
         <v>24</v>
       </c>
       <c r="H42" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="I42" t="n">
-        <v>15.5</v>
+        <v>16.6</v>
       </c>
       <c r="J42" t="n">
         <v>46</v>
@@ -2862,13 +2862,13 @@
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="N42" t="n">
         <v>45</v>
       </c>
       <c r="O42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -2905,10 +2905,10 @@
         <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="I43" t="n">
-        <v>15.5</v>
+        <v>16.6</v>
       </c>
       <c r="J43" t="n">
         <v>46</v>
@@ -2920,13 +2920,13 @@
         <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="N43" t="n">
         <v>47</v>
       </c>
       <c r="O43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -2963,10 +2963,10 @@
         <v>22</v>
       </c>
       <c r="H44" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="I44" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J44" t="n">
         <v>30</v>
@@ -2978,13 +2978,13 @@
         <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="N44" t="n">
         <v>46</v>
       </c>
       <c r="O44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="I45" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="J45" t="n">
         <v>30</v>
@@ -3036,13 +3036,13 @@
         <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="N45" t="n">
         <v>47</v>
       </c>
       <c r="O45" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -3079,10 +3079,10 @@
         <v>22</v>
       </c>
       <c r="H46" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="I46" t="n">
-        <v>15.5</v>
+        <v>16.6</v>
       </c>
       <c r="J46" t="n">
         <v>46</v>
@@ -3094,13 +3094,13 @@
         <v>6</v>
       </c>
       <c r="M46" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="N46" t="n">
         <v>46</v>
       </c>
       <c r="O46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -3195,10 +3195,10 @@
         <v>20</v>
       </c>
       <c r="H48" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>45.6</v>
+        <v>56.5</v>
       </c>
       <c r="J48" t="n">
         <v>73</v>
@@ -3210,7 +3210,7 @@
         <v>24</v>
       </c>
       <c r="M48" t="n">
-        <v>19.6</v>
+        <v>24.4</v>
       </c>
       <c r="N48" t="n">
         <v>44</v>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 24u = ~20 wks (overstock); consider ~24u</t>
+          <t>CAUTION - 24u = ~24 wks (overstock); consider ~24u</t>
         </is>
       </c>
     </row>
@@ -3253,10 +3253,10 @@
         <v>15</v>
       </c>
       <c r="H49" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I49" t="n">
-        <v>25.2</v>
+        <v>25.7</v>
       </c>
       <c r="J49" t="n">
         <v>42</v>
@@ -3268,7 +3268,7 @@
         <v>40</v>
       </c>
       <c r="M49" t="n">
-        <v>25.7</v>
+        <v>26.1</v>
       </c>
       <c r="N49" t="n">
         <v>48</v>
@@ -3311,10 +3311,10 @@
         <v>33</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="I50" t="n">
-        <v>107.1</v>
+        <v>120.5</v>
       </c>
       <c r="J50" t="n">
         <v>30</v>
@@ -3326,7 +3326,7 @@
         <v>12</v>
       </c>
       <c r="M50" t="n">
-        <v>23.8</v>
+        <v>26.8</v>
       </c>
       <c r="N50" t="n">
         <v>46</v>
@@ -3336,7 +3336,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CAUTION - 12u = ~24 wks (overstock); consider ~12u</t>
+          <t>CAUTION - 12u = ~27 wks (overstock); consider ~12u</t>
         </is>
       </c>
     </row>
@@ -3369,10 +3369,10 @@
         <v>9</v>
       </c>
       <c r="H51" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I51" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J51" t="n">
         <v>18</v>
@@ -3384,7 +3384,7 @@
         <v>624</v>
       </c>
       <c r="M51" t="n">
-        <v>337.2</v>
+        <v>342.5</v>
       </c>
       <c r="N51" t="n">
         <v>46</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~337 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~342 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3427,10 +3427,10 @@
         <v>11</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I52" t="n">
-        <v>88.90000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="J52" t="n">
         <v>83</v>
@@ -3442,7 +3442,7 @@
         <v>150</v>
       </c>
       <c r="M52" t="n">
-        <v>171.5</v>
+        <v>183.8</v>
       </c>
       <c r="N52" t="n">
         <v>55</v>
@@ -3452,7 +3452,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~172 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~184 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,19 +527,19 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>157.4</v>
+        <v>159.3</v>
       </c>
       <c r="I2" t="n">
         <v>5.4</v>
       </c>
       <c r="J2" t="n">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>784</v>
+        <v>802</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -548,11 +548,11 @@
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~784u (392cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~802u (401cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>37.7</v>
+        <v>38.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,17 +600,17 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BUY ~208u (104cs) - sells in ~6 wks</t>
+          <t>BUY ~208u (104cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
@@ -646,19 +646,19 @@
         <v>22.2</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="J4" t="n">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="M4" t="n">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
@@ -668,7 +668,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~120u (60cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~96u (48cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,13 +701,13 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>28.4</v>
+        <v>28.8</v>
       </c>
       <c r="I5" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="J5" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -722,7 +722,7 @@
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -759,10 +759,10 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>14.7</v>
+        <v>14.3</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
         <v>42</v>
@@ -771,7 +771,7 @@
         <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M6" t="n">
         <v>5.2</v>
@@ -780,11 +780,11 @@
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~76u (38cs) - sells in ~5 wks</t>
+          <t>BUY ~74u (37cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
@@ -817,13 +817,13 @@
         <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
-        <v>45</v>
+        <v>62</v>
       </c>
       <c r="K7" t="n">
         <v>624</v>
@@ -832,7 +832,7 @@
         <v>624</v>
       </c>
       <c r="M7" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="N7" t="n">
         <v>45</v>
@@ -849,7 +849,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -859,55 +859,55 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25.7</v>
+        <v>10.85</v>
       </c>
       <c r="E8" t="n">
-        <v>21.7</v>
+        <v>8.68</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>2.17</v>
       </c>
       <c r="G8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>8.699999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="I8" t="n">
-        <v>6.2</v>
+        <v>13.2</v>
       </c>
       <c r="J8" t="n">
-        <v>58</v>
+        <v>123</v>
       </c>
       <c r="K8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>12</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="N8" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BUY ~12u (6cs) - sells in ~1 wks</t>
+          <t>BUY ~12u (2cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Utepils Royal Cherry Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -917,48 +917,48 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.85</v>
+        <v>25.7</v>
       </c>
       <c r="E9" t="n">
-        <v>8.68</v>
+        <v>21.7</v>
       </c>
       <c r="F9" t="n">
-        <v>2.17</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>16.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>13.3</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>119</v>
+        <v>57</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="N9" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O9" t="n">
         <v>35</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~14u (7cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -991,10 +991,10 @@
         <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>11.8</v>
+        <v>10.9</v>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>7.7</v>
       </c>
       <c r="J10" t="n">
         <v>47</v>
@@ -1003,20 +1003,20 @@
         <v>24</v>
       </c>
       <c r="L10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="M10" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N10" t="n">
         <v>44</v>
       </c>
       <c r="O10" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~48u (8cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~42u (7cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1049,13 +1049,13 @@
         <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>35.2</v>
+        <v>34.8</v>
       </c>
       <c r="I11" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K11" t="n">
         <v>624</v>
@@ -1064,7 +1064,7 @@
         <v>624</v>
       </c>
       <c r="M11" t="n">
-        <v>17.7</v>
+        <v>17.9</v>
       </c>
       <c r="N11" t="n">
         <v>46</v>
@@ -1110,10 +1110,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="J12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K12" t="n">
         <v>3</v>
@@ -1165,13 +1165,13 @@
         <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>34.6</v>
+        <v>34.1</v>
       </c>
       <c r="I13" t="n">
         <v>8</v>
       </c>
       <c r="J13" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="K13" t="n">
         <v>624</v>
@@ -1180,7 +1180,7 @@
         <v>624</v>
       </c>
       <c r="M13" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="N13" t="n">
         <v>46</v>
@@ -1223,13 +1223,13 @@
         <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>33.1</v>
+        <v>32.9</v>
       </c>
       <c r="I14" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="J14" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="K14" t="n">
         <v>624</v>
@@ -1238,7 +1238,7 @@
         <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="N14" t="n">
         <v>46</v>
@@ -1339,10 +1339,10 @@
         <v>20</v>
       </c>
       <c r="H16" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="J16" t="n">
         <v>60</v>
@@ -1360,7 +1360,7 @@
         <v>44</v>
       </c>
       <c r="O16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         <v>22</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="J17" t="n">
         <v>60</v>
@@ -1418,7 +1418,7 @@
         <v>51</v>
       </c>
       <c r="O17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1455,10 +1455,10 @@
         <v>20</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="I18" t="n">
-        <v>11.3</v>
+        <v>11.7</v>
       </c>
       <c r="J18" t="n">
         <v>60</v>
@@ -1476,7 +1476,7 @@
         <v>42</v>
       </c>
       <c r="O18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1513,13 +1513,13 @@
         <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="I19" t="n">
-        <v>12.2</v>
+        <v>11.3</v>
       </c>
       <c r="J19" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K19" t="n">
         <v>6</v>
@@ -1534,7 +1534,7 @@
         <v>46</v>
       </c>
       <c r="O19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,55 +1555,55 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.85</v>
+        <v>26.52</v>
       </c>
       <c r="E20" t="n">
-        <v>8.68</v>
+        <v>24.2</v>
       </c>
       <c r="F20" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="G20" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
         <v>9.5</v>
       </c>
       <c r="I20" t="n">
-        <v>20.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6</v>
+        <v>21.8</v>
       </c>
       <c r="N20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 208u = ~22 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,48 +1613,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>26.52</v>
+        <v>10.85</v>
       </c>
       <c r="E21" t="n">
-        <v>24.2</v>
+        <v>8.68</v>
       </c>
       <c r="F21" t="n">
-        <v>2.33</v>
+        <v>2.17</v>
       </c>
       <c r="G21" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="I21" t="n">
-        <v>9.699999999999999</v>
+        <v>21.3</v>
       </c>
       <c r="J21" t="n">
-        <v>48</v>
+        <v>113</v>
       </c>
       <c r="K21" t="n">
-        <v>208</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
-        <v>208</v>
+        <v>6</v>
       </c>
       <c r="M21" t="n">
-        <v>23.3</v>
+        <v>0.6</v>
       </c>
       <c r="N21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O21" t="n">
         <v>21</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~23 wks (overstock); consider ~208u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1687,13 +1687,13 @@
         <v>14</v>
       </c>
       <c r="H22" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="I22" t="n">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J22" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="K22" t="n">
         <v>624</v>
@@ -1702,7 +1702,7 @@
         <v>624</v>
       </c>
       <c r="M22" t="n">
-        <v>41.9</v>
+        <v>43.1</v>
       </c>
       <c r="N22" t="n">
         <v>45</v>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1745,13 +1745,13 @@
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="I23" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J23" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K23" t="n">
         <v>624</v>
@@ -1760,7 +1760,7 @@
         <v>624</v>
       </c>
       <c r="M23" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N23" t="n">
         <v>45</v>
@@ -1770,14 +1770,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~53 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,55 +1787,55 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>12</v>
       </c>
       <c r="E24" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="G24" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="H24" t="n">
-        <v>19.5</v>
+        <v>8</v>
       </c>
       <c r="I24" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J24" t="n">
+        <v>39</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>30</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N24" t="n">
+        <v>45</v>
+      </c>
+      <c r="O24" t="n">
         <v>17</v>
       </c>
-      <c r="J24" t="n">
-        <v>184</v>
-      </c>
-      <c r="K24" t="n">
-        <v>84</v>
-      </c>
-      <c r="L24" t="n">
-        <v>84</v>
-      </c>
-      <c r="M24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N24" t="n">
-        <v>44</v>
-      </c>
-      <c r="O24" t="n">
-        <v>16</v>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~30u (5cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1861,13 +1861,13 @@
         <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="I25" t="n">
-        <v>10.9</v>
+        <v>16.1</v>
       </c>
       <c r="J25" t="n">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="K25" t="n">
         <v>84</v>
@@ -1876,7 +1876,7 @@
         <v>84</v>
       </c>
       <c r="M25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
         <v>44</v>
@@ -1893,7 +1893,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E26" t="n">
-        <v>9.9</v>
+        <v>18.02</v>
       </c>
       <c r="F26" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="G26" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H26" t="n">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="J26" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="K26" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L26" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M26" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="N26" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O26" t="n">
         <v>16</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>9.06</v>
+        <v>11.2</v>
       </c>
       <c r="F27" t="n">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>10.8</v>
+        <v>20.6</v>
       </c>
       <c r="I27" t="n">
-        <v>7.4</v>
+        <v>10.2</v>
       </c>
       <c r="J27" t="n">
-        <v>85</v>
+        <v>156</v>
       </c>
       <c r="K27" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="L27" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="M27" t="n">
-        <v>57.9</v>
+        <v>4.1</v>
       </c>
       <c r="N27" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~58 wks (overstock); consider ~624u</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,55 +2019,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12</v>
+        <v>9.33</v>
       </c>
       <c r="E28" t="n">
-        <v>9.9</v>
+        <v>8.01</v>
       </c>
       <c r="F28" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="G28" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H28" t="n">
-        <v>7.1</v>
+        <v>11.7</v>
       </c>
       <c r="I28" t="n">
-        <v>10.6</v>
+        <v>5.8</v>
       </c>
       <c r="J28" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="K28" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L28" t="n">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="M28" t="n">
-        <v>2.5</v>
+        <v>12.8</v>
       </c>
       <c r="N28" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O28" t="n">
         <v>15</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9.33</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>8.01</v>
+        <v>9.9</v>
       </c>
       <c r="F29" t="n">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="G29" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H29" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="I29" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="J29" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="K29" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L29" t="n">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="M29" t="n">
-        <v>13</v>
+        <v>5.1</v>
       </c>
       <c r="N29" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O29" t="n">
         <v>15</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
+          <t>BUY ~36u (6cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D30" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="G30" t="n">
         <v>20</v>
       </c>
-      <c r="E30" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="F30" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="G30" t="n">
-        <v>10</v>
-      </c>
       <c r="H30" t="n">
-        <v>7.5</v>
+        <v>6.3</v>
       </c>
       <c r="I30" t="n">
-        <v>8.300000000000001</v>
+        <v>31.6</v>
       </c>
       <c r="J30" t="n">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="K30" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="M30" t="n">
-        <v>5.3</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2193,48 +2193,48 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E31" t="n">
-        <v>8.68</v>
+        <v>9.82</v>
       </c>
       <c r="F31" t="n">
-        <v>2.17</v>
+        <v>1.18</v>
       </c>
       <c r="G31" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H31" t="n">
-        <v>6.1</v>
+        <v>10.7</v>
       </c>
       <c r="I31" t="n">
-        <v>31.5</v>
+        <v>8.5</v>
       </c>
       <c r="J31" t="n">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="K31" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L31" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M31" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="N31" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O31" t="n">
         <v>13</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2267,10 +2267,10 @@
         <v>20</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="I32" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="J32" t="n">
         <v>27</v>
@@ -2282,7 +2282,7 @@
         <v>6</v>
       </c>
       <c r="M32" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="N32" t="n">
         <v>47</v>
@@ -2325,13 +2325,13 @@
         <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="I33" t="n">
-        <v>10.8</v>
+        <v>10.6</v>
       </c>
       <c r="J33" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K33" t="n">
         <v>624</v>
@@ -2340,7 +2340,7 @@
         <v>624</v>
       </c>
       <c r="M33" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="N33" t="n">
         <v>46</v>
@@ -2357,7 +2357,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -2383,13 +2383,13 @@
         <v>11</v>
       </c>
       <c r="H34" t="n">
-        <v>10.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>9.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J34" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K34" t="n">
         <v>150</v>
@@ -2398,10 +2398,10 @@
         <v>150</v>
       </c>
       <c r="M34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="N34" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O34" t="n">
         <v>12</v>
@@ -2441,13 +2441,13 @@
         <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="I35" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="K35" t="n">
         <v>624</v>
@@ -2456,7 +2456,7 @@
         <v>624</v>
       </c>
       <c r="M35" t="n">
-        <v>75.3</v>
+        <v>74.7</v>
       </c>
       <c r="N35" t="n">
         <v>45</v>
@@ -2473,7 +2473,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -2499,13 +2499,13 @@
         <v>11</v>
       </c>
       <c r="H36" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="I36" t="n">
-        <v>9.300000000000001</v>
+        <v>12.1</v>
       </c>
       <c r="J36" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="K36" t="n">
         <v>150</v>
@@ -2514,24 +2514,24 @@
         <v>150</v>
       </c>
       <c r="M36" t="n">
-        <v>16.6</v>
+        <v>17.5</v>
       </c>
       <c r="N36" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,55 +2541,55 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E37" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F37" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G37" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H37" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="I37" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="J37" t="n">
-        <v>81</v>
+        <v>154</v>
       </c>
       <c r="K37" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L37" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M37" t="n">
-        <v>17.4</v>
+        <v>7.3</v>
       </c>
       <c r="N37" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="O37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~17 wks (overstock); consider ~150u</t>
+          <t>BUY ~84u (14cs) - sells in ~7 wks</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Wikid Mimosa 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2599,48 +2599,48 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12</v>
+        <v>9.67</v>
       </c>
       <c r="E38" t="n">
-        <v>11.2</v>
+        <v>7.57</v>
       </c>
       <c r="F38" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="G38" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="H38" t="n">
-        <v>11.2</v>
+        <v>2.7</v>
       </c>
       <c r="I38" t="n">
-        <v>13.1</v>
+        <v>15.5</v>
       </c>
       <c r="J38" t="n">
-        <v>157</v>
+        <v>45</v>
       </c>
       <c r="K38" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="L38" t="n">
-        <v>84</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="N38" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O38" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~8 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
         <v>4.6</v>
       </c>
       <c r="I39" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="J39" t="n">
         <v>51</v>
@@ -2688,7 +2688,7 @@
         <v>150</v>
       </c>
       <c r="M39" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="N39" t="n">
         <v>50</v>
@@ -2705,7 +2705,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2731,13 +2731,13 @@
         <v>24</v>
       </c>
       <c r="H40" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="I40" t="n">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="J40" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K40" t="n">
         <v>6</v>
@@ -2746,13 +2746,13 @@
         <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="N40" t="n">
         <v>45</v>
       </c>
       <c r="O40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,55 +2773,55 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="E41" t="n">
-        <v>11.2</v>
+        <v>8.4</v>
       </c>
       <c r="F41" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="G41" t="n">
         <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="I41" t="n">
-        <v>22.5</v>
+        <v>15.5</v>
       </c>
       <c r="J41" t="n">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="K41" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L41" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M41" t="n">
-        <v>13.7</v>
+        <v>2.2</v>
       </c>
       <c r="N41" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~14 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2847,13 +2847,13 @@
         <v>24</v>
       </c>
       <c r="H42" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="I42" t="n">
-        <v>16.6</v>
+        <v>11</v>
       </c>
       <c r="J42" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="K42" t="n">
         <v>6</v>
@@ -2862,7 +2862,7 @@
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="N42" t="n">
         <v>45</v>
@@ -2879,7 +2879,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,48 +2889,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="E43" t="n">
-        <v>8.4</v>
+        <v>11.2</v>
       </c>
       <c r="F43" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="G43" t="n">
         <v>20</v>
       </c>
       <c r="H43" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="I43" t="n">
-        <v>16.6</v>
+        <v>23.1</v>
       </c>
       <c r="J43" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="K43" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L43" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M43" t="n">
-        <v>2.3</v>
+        <v>14.1</v>
       </c>
       <c r="N43" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O43" t="n">
         <v>5</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2951,25 +2951,25 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>9.67</v>
+        <v>10.5</v>
       </c>
       <c r="E44" t="n">
-        <v>7.57</v>
+        <v>8.4</v>
       </c>
       <c r="F44" t="n">
         <v>2.1</v>
       </c>
       <c r="G44" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I44" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J44" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K44" t="n">
         <v>6</v>
@@ -2978,10 +2978,10 @@
         <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="N44" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O44" t="n">
         <v>5</v>
@@ -3009,25 +3009,25 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.5</v>
+        <v>9.67</v>
       </c>
       <c r="E45" t="n">
-        <v>8.4</v>
+        <v>7.57</v>
       </c>
       <c r="F45" t="n">
         <v>2.1</v>
       </c>
       <c r="G45" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H45" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="I45" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J45" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K45" t="n">
         <v>6</v>
@@ -3036,10 +3036,10 @@
         <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="N45" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O45" t="n">
         <v>5</v>
@@ -3053,7 +3053,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,55 +3063,55 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>9.67</v>
+        <v>11</v>
       </c>
       <c r="E46" t="n">
-        <v>7.57</v>
+        <v>9.82</v>
       </c>
       <c r="F46" t="n">
-        <v>2.1</v>
+        <v>1.18</v>
       </c>
       <c r="G46" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="I46" t="n">
-        <v>16.6</v>
+        <v>13.1</v>
       </c>
       <c r="J46" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="K46" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L46" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M46" t="n">
-        <v>2.3</v>
+        <v>37.9</v>
       </c>
       <c r="N46" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O46" t="n">
         <v>5</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
+          <t>CAUTION - 150u = ~38 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
+          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3125,44 +3125,44 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>13.45</v>
       </c>
       <c r="E47" t="n">
-        <v>9.82</v>
+        <v>11.47</v>
       </c>
       <c r="F47" t="n">
-        <v>1.18</v>
+        <v>1.97</v>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H47" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="I47" t="n">
-        <v>14.4</v>
+        <v>22.7</v>
       </c>
       <c r="J47" t="n">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="K47" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="L47" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="M47" t="n">
-        <v>40.6</v>
+        <v>23.7</v>
       </c>
       <c r="N47" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~41 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 40u = ~24 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
+          <t>Stigma Berry Tea 10mg THC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3237,48 +3237,48 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.45</v>
+        <v>10.03</v>
       </c>
       <c r="E49" t="n">
-        <v>11.47</v>
+        <v>9.15</v>
       </c>
       <c r="F49" t="n">
-        <v>1.97</v>
+        <v>0.88</v>
       </c>
       <c r="G49" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H49" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="I49" t="n">
-        <v>25.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="K49" t="n">
-        <v>40</v>
+        <v>624</v>
       </c>
       <c r="L49" t="n">
-        <v>40</v>
+        <v>624</v>
       </c>
       <c r="M49" t="n">
-        <v>26.1</v>
+        <v>342.5</v>
       </c>
       <c r="N49" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="O49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~26 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 624u = ~342 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3343,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Stigma Berry Tea 10mg THC</t>
+          <t>Clrty SodaPot Blue Ginger 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3353,113 +3353,107 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E51" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F51" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G51" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H51" t="n">
-        <v>1.8</v>
+        <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>9.300000000000001</v>
+        <v>98.8</v>
       </c>
       <c r="J51" t="n">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="K51" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L51" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M51" t="n">
-        <v>342.5</v>
+        <v>190.6</v>
       </c>
       <c r="N51" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~342 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 150u = ~191 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Blue Ginger 10mg 4pk 12oz can</t>
+          <t>Green Monke Tropical Citrus 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Beverage</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>12.91 rebate per case</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11</v>
+        <v>10.76</v>
       </c>
       <c r="E52" t="n">
-        <v>9.82</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>1.18</v>
+        <v>2.15</v>
       </c>
       <c r="G52" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H52" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I52" t="n">
-        <v>95.3</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L52" t="n">
-        <v>150</v>
-      </c>
-      <c r="M52" t="n">
-        <v>183.8</v>
+        <v>6</v>
       </c>
       <c r="N52" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~184 wks (overstock); consider ~150u</t>
+          <t>SKIP - not selling (any quantity would sit)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Strawberry Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3615,30 +3609,30 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Green Monke Tropical Citrus 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Blueberry Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Beverage</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>12.91 rebate per case</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.76</v>
+        <v>10.5</v>
       </c>
       <c r="E56" t="n">
-        <v>8.609999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="F56" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="G56" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -3647,13 +3641,13 @@
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L56" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="N56" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -3719,7 +3713,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Daizy's Root Beer 10mg THC 4pk 12oz can</t>
+          <t>Foundry Nation Granddaddy Purple 5MG THC 4PK 12oz can</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3733,45 +3727,51 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.5</v>
+        <v>9.67</v>
       </c>
       <c r="E58" t="n">
-        <v>9.06</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>1.44</v>
+        <v>0.88</v>
       </c>
       <c r="G58" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="I58" t="n">
+        <v>731.2</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>273</v>
       </c>
       <c r="K58" t="n">
-        <v>624</v>
+        <v>60</v>
       </c>
       <c r="L58" t="n">
-        <v>624</v>
+        <v>60</v>
+      </c>
+      <c r="M58" t="n">
+        <v>171.5</v>
       </c>
       <c r="N58" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="O58" t="n">
         <v>0</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>SKIP - not selling (any quantity would sit)</t>
+          <t>CAUTION - 60u = ~172 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Foundry Nation Granddaddy Purple 5MG THC 4PK 12oz can</t>
+          <t>Daizy's Watermelon Lime 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3785,51 +3785,45 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>9.67</v>
+        <v>10.5</v>
       </c>
       <c r="E59" t="n">
-        <v>8.789999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="F59" t="n">
-        <v>0.88</v>
+        <v>1.44</v>
       </c>
       <c r="G59" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I59" t="n">
-        <v>731.2</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>60</v>
+        <v>624</v>
       </c>
       <c r="L59" t="n">
-        <v>60</v>
-      </c>
-      <c r="M59" t="n">
-        <v>171.5</v>
+        <v>624</v>
       </c>
       <c r="N59" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~172 wks (overstock); consider ~60u</t>
+          <t>SKIP - not selling (any quantity would sit)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Daizy's Strawberry Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Root Beer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>159.3</v>
+        <v>132.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>802</v>
+        <v>608</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>414</v>
+        <v>344</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~802u (401cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~608u (304cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>38.2</v>
+        <v>41.9</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J3" t="n">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>22.2</v>
+        <v>27</v>
       </c>
       <c r="I4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J4" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="M4" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~96u (48cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~138u (69cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,32 +701,32 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>28.8</v>
+        <v>36</v>
       </c>
       <c r="I5" t="n">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
       <c r="J5" t="n">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="M5" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BUY ~40u (20cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~70u (35cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -759,10 +759,10 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>14.3</v>
+        <v>15.3</v>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="J6" t="n">
         <v>42</v>
@@ -771,20 +771,20 @@
         <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="M6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~74u (37cs) - sells in ~5 wks</t>
+          <t>BUY ~82u (41cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
@@ -817,13 +817,13 @@
         <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>25.7</v>
+        <v>27.4</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K7" t="n">
         <v>624</v>
@@ -832,17 +832,17 @@
         <v>624</v>
       </c>
       <c r="M7" t="n">
-        <v>24.3</v>
+        <v>22.8</v>
       </c>
       <c r="N7" t="n">
         <v>45</v>
       </c>
       <c r="O7" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~24 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~23 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -875,32 +875,32 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="I8" t="n">
-        <v>13.2</v>
+        <v>12.3</v>
       </c>
       <c r="J8" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7</v>
+        <v>1.4</v>
       </c>
       <c r="N8" t="n">
         <v>46</v>
       </c>
       <c r="O8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BUY ~12u (2cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~24u (4cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -933,32 +933,32 @@
         <v>16</v>
       </c>
       <c r="H9" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="J9" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K9" t="n">
         <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M9" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="N9" t="n">
         <v>50</v>
       </c>
       <c r="O9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>BUY ~14u (7cs) - sells in ~2 wks</t>
+          <t>BUY ~16u (8cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -991,39 +991,39 @@
         <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>10.9</v>
+        <v>11.5</v>
       </c>
       <c r="I10" t="n">
-        <v>7.7</v>
+        <v>7.1</v>
       </c>
       <c r="J10" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="K10" t="n">
         <v>24</v>
       </c>
       <c r="L10" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="M10" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="N10" t="n">
         <v>44</v>
       </c>
       <c r="O10" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~42u (7cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~48u (8cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1033,55 +1033,55 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.03</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>9.15</v>
+        <v>16.67</v>
       </c>
       <c r="F11" t="n">
-        <v>0.88</v>
+        <v>3.33</v>
       </c>
       <c r="G11" t="n">
+        <v>17</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J11" t="n">
+        <v>71</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="I11" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="J11" t="n">
-        <v>148</v>
-      </c>
-      <c r="K11" t="n">
-        <v>624</v>
-      </c>
-      <c r="L11" t="n">
-        <v>624</v>
-      </c>
       <c r="M11" t="n">
-        <v>17.9</v>
+        <v>0.9</v>
       </c>
       <c r="N11" t="n">
         <v>46</v>
       </c>
       <c r="O11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~18 wks (overstock); consider ~624u</t>
+          <t>BUY ~9u (3cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1091,55 +1091,55 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H12" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>42</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L12" t="n">
         <v>20</v>
       </c>
-      <c r="E12" t="n">
-        <v>16.67</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="G12" t="n">
-        <v>17</v>
-      </c>
-      <c r="H12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="J12" t="n">
-        <v>71</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>3</v>
-      </c>
       <c r="M12" t="n">
-        <v>0.3</v>
+        <v>2.6</v>
       </c>
       <c r="N12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O12" t="n">
         <v>31</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>BUY ~20u (10cs) - sells in ~3 wks</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,55 +1149,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.03</v>
+        <v>26.5</v>
       </c>
       <c r="E13" t="n">
-        <v>9.15</v>
+        <v>21.32</v>
       </c>
       <c r="F13" t="n">
-        <v>0.88</v>
+        <v>5.18</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>34.1</v>
+        <v>4.9</v>
       </c>
       <c r="I13" t="n">
-        <v>8</v>
+        <v>12.1</v>
       </c>
       <c r="J13" t="n">
-        <v>151</v>
+        <v>60</v>
       </c>
       <c r="K13" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>18.3</v>
+        <v>0.4</v>
       </c>
       <c r="N13" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O13" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~18 wks (overstock); consider ~624u</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1223,13 +1223,13 @@
         <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>32.9</v>
+        <v>29</v>
       </c>
       <c r="I14" t="n">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
       <c r="J14" t="n">
-        <v>134</v>
+        <v>147</v>
       </c>
       <c r="K14" t="n">
         <v>624</v>
@@ -1238,24 +1238,24 @@
         <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>21.5</v>
       </c>
       <c r="N14" t="n">
         <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~19 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~22 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Stigma Tea Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,48 +1265,48 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.7</v>
+        <v>25.9</v>
       </c>
       <c r="E15" t="n">
-        <v>21.7</v>
+        <v>20.72</v>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>5.18</v>
       </c>
       <c r="G15" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
-        <v>5.6</v>
+        <v>12.1</v>
       </c>
       <c r="J15" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="N15" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O15" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~16u (8cs) - sells in ~2 wks</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
@@ -1327,22 +1327,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.9</v>
+        <v>23.4</v>
       </c>
       <c r="E16" t="n">
-        <v>20.72</v>
+        <v>18.22</v>
       </c>
       <c r="F16" t="n">
         <v>5.18</v>
       </c>
       <c r="G16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I16" t="n">
-        <v>11.7</v>
+        <v>12.1</v>
       </c>
       <c r="J16" t="n">
         <v>60</v>
@@ -1357,10 +1357,10 @@
         <v>0.4</v>
       </c>
       <c r="N16" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="O16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1381,55 +1381,55 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23.4</v>
+        <v>10.85</v>
       </c>
       <c r="E17" t="n">
-        <v>18.22</v>
+        <v>8.68</v>
       </c>
       <c r="F17" t="n">
-        <v>5.18</v>
+        <v>2.17</v>
       </c>
       <c r="G17" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>10.8</v>
       </c>
       <c r="I17" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="J17" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="N17" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="O17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,55 +1439,55 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>26.5</v>
+        <v>10.5</v>
       </c>
       <c r="E18" t="n">
-        <v>21.32</v>
+        <v>9.06</v>
       </c>
       <c r="F18" t="n">
-        <v>5.18</v>
+        <v>1.44</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>4.8</v>
+        <v>15.3</v>
       </c>
       <c r="I18" t="n">
-        <v>11.7</v>
+        <v>6.9</v>
       </c>
       <c r="J18" t="n">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="K18" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>624</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4</v>
+        <v>40.7</v>
       </c>
       <c r="N18" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O18" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 624u = ~41 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,55 +1497,55 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.85</v>
+        <v>26.52</v>
       </c>
       <c r="E19" t="n">
-        <v>8.68</v>
+        <v>24.2</v>
       </c>
       <c r="F19" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>11.3</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6</v>
+        <v>22.5</v>
       </c>
       <c r="N19" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 208u = ~22 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1559,51 +1559,51 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.52</v>
+        <v>10.03</v>
       </c>
       <c r="E20" t="n">
-        <v>24.2</v>
+        <v>9.15</v>
       </c>
       <c r="F20" t="n">
-        <v>2.33</v>
+        <v>0.88</v>
       </c>
       <c r="G20" t="n">
         <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>9.5</v>
+        <v>23.6</v>
       </c>
       <c r="I20" t="n">
-        <v>8.699999999999999</v>
+        <v>7.3</v>
       </c>
       <c r="J20" t="n">
+        <v>132</v>
+      </c>
+      <c r="K20" t="n">
+        <v>624</v>
+      </c>
+      <c r="L20" t="n">
+        <v>624</v>
+      </c>
+      <c r="M20" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="N20" t="n">
         <v>46</v>
       </c>
-      <c r="K20" t="n">
-        <v>208</v>
-      </c>
-      <c r="L20" t="n">
-        <v>208</v>
-      </c>
-      <c r="M20" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>44</v>
-      </c>
       <c r="O20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~22 wks (overstock); consider ~208u</t>
+          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1613,55 +1613,55 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.85</v>
+        <v>20</v>
       </c>
       <c r="E21" t="n">
-        <v>8.68</v>
+        <v>18.02</v>
       </c>
       <c r="F21" t="n">
-        <v>2.17</v>
+        <v>1.98</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="I21" t="n">
-        <v>21.3</v>
+        <v>7</v>
       </c>
       <c r="J21" t="n">
-        <v>113</v>
+        <v>61</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="L21" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O21" t="n">
         <v>21</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~40u (10cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,55 +1671,55 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E22" t="n">
-        <v>9.06</v>
+        <v>8.68</v>
       </c>
       <c r="F22" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="G22" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>14.5</v>
+        <v>9.4</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9</v>
+        <v>27.7</v>
       </c>
       <c r="J22" t="n">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="K22" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>43.1</v>
+        <v>0.6</v>
       </c>
       <c r="N22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,55 +1729,55 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E23" t="n">
-        <v>9.06</v>
+        <v>8.68</v>
       </c>
       <c r="F23" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="G23" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H23" t="n">
-        <v>12</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>7.9</v>
+        <v>21.9</v>
       </c>
       <c r="J23" t="n">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="K23" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>52</v>
+        <v>0.6</v>
       </c>
       <c r="N23" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~52 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,48 +1787,48 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E24" t="n">
-        <v>9.9</v>
+        <v>9.06</v>
       </c>
       <c r="F24" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="G24" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H24" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="I24" t="n">
         <v>8</v>
       </c>
-      <c r="I24" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="J24" t="n">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L24" t="n">
-        <v>30</v>
+        <v>624</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>49.5</v>
       </c>
       <c r="N24" t="n">
         <v>45</v>
       </c>
       <c r="O24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~30u (5cs) - sells in ~4 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1861,13 +1861,13 @@
         <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>20.3</v>
+        <v>20.9</v>
       </c>
       <c r="I25" t="n">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="J25" t="n">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="K25" t="n">
         <v>84</v>
@@ -1876,13 +1876,13 @@
         <v>84</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
         <v>44</v>
       </c>
       <c r="O25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Two Scoops Variety Pack 10mg THC 6pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1907,51 +1907,51 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>18.02</v>
+        <v>9.82</v>
       </c>
       <c r="F26" t="n">
-        <v>1.98</v>
+        <v>1.18</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H26" t="n">
-        <v>7.9</v>
+        <v>13.8</v>
       </c>
       <c r="I26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J26" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="L26" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="M26" t="n">
-        <v>5.1</v>
+        <v>10.8</v>
       </c>
       <c r="N26" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="O26" t="n">
         <v>16</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~5 wks</t>
+          <t>BUY ~150u (25cs) - sells in ~11 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>9.33</v>
       </c>
       <c r="E27" t="n">
-        <v>11.2</v>
+        <v>8.01</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8</v>
+        <v>1.32</v>
       </c>
       <c r="G27" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>20.6</v>
+        <v>11.8</v>
       </c>
       <c r="I27" t="n">
-        <v>10.2</v>
+        <v>5.7</v>
       </c>
       <c r="J27" t="n">
-        <v>156</v>
+        <v>37</v>
       </c>
       <c r="K27" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L27" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M27" t="n">
-        <v>4.1</v>
+        <v>12.8</v>
       </c>
       <c r="N27" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="O27" t="n">
         <v>16</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,55 +2019,55 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>9.33</v>
+        <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>8.01</v>
+        <v>9.9</v>
       </c>
       <c r="F28" t="n">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="G28" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H28" t="n">
-        <v>11.7</v>
+        <v>7.5</v>
       </c>
       <c r="I28" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J28" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="K28" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="M28" t="n">
-        <v>12.8</v>
+        <v>5.6</v>
       </c>
       <c r="N28" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
+          <t>BUY ~42u (7cs) - sells in ~6 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="G29" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>19.7</v>
       </c>
       <c r="I29" t="n">
-        <v>6.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>25</v>
+        <v>149</v>
       </c>
       <c r="K29" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="L29" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="M29" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~36u (6cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.85</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>8.68</v>
+        <v>9.9</v>
       </c>
       <c r="F30" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H30" t="n">
-        <v>6.3</v>
+        <v>7.7</v>
       </c>
       <c r="I30" t="n">
-        <v>31.6</v>
+        <v>9.1</v>
       </c>
       <c r="J30" t="n">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="K30" t="n">
         <v>6</v>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M30" t="n">
-        <v>1</v>
+        <v>3.1</v>
       </c>
       <c r="N30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~24u (4cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2209,13 +2209,13 @@
         <v>11</v>
       </c>
       <c r="H31" t="n">
-        <v>10.7</v>
+        <v>12.2</v>
       </c>
       <c r="I31" t="n">
-        <v>8.5</v>
+        <v>11.7</v>
       </c>
       <c r="J31" t="n">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="K31" t="n">
         <v>150</v>
@@ -2224,24 +2224,24 @@
         <v>150</v>
       </c>
       <c r="M31" t="n">
-        <v>14</v>
+        <v>12.3</v>
       </c>
       <c r="N31" t="n">
         <v>55</v>
       </c>
       <c r="O31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~12 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,55 +2251,55 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16.67</v>
+        <v>10.03</v>
       </c>
       <c r="E32" t="n">
-        <v>13.34</v>
+        <v>9.15</v>
       </c>
       <c r="F32" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G32" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>3.9</v>
+        <v>15.7</v>
       </c>
       <c r="I32" t="n">
-        <v>12.6</v>
+        <v>7.5</v>
       </c>
       <c r="J32" t="n">
-        <v>27</v>
+        <v>145</v>
       </c>
       <c r="K32" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L32" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M32" t="n">
-        <v>1.6</v>
+        <v>39.7</v>
       </c>
       <c r="N32" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O32" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>BUY ~6u (2cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Stigma Peach Iced Tea 10mg THC</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,29 +2309,29 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.03</v>
+        <v>10.5</v>
       </c>
       <c r="E33" t="n">
-        <v>9.15</v>
+        <v>9.06</v>
       </c>
       <c r="F33" t="n">
-        <v>0.88</v>
+        <v>1.44</v>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H33" t="n">
-        <v>15</v>
+        <v>9.1</v>
       </c>
       <c r="I33" t="n">
-        <v>10.6</v>
+        <v>7.7</v>
       </c>
       <c r="J33" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="K33" t="n">
         <v>624</v>
@@ -2340,24 +2340,24 @@
         <v>624</v>
       </c>
       <c r="M33" t="n">
-        <v>41.7</v>
+        <v>68.2</v>
       </c>
       <c r="N33" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O33" t="n">
         <v>13</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~68 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,55 +2367,55 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>16.67</v>
       </c>
       <c r="E34" t="n">
-        <v>9.82</v>
+        <v>13.34</v>
       </c>
       <c r="F34" t="n">
-        <v>1.18</v>
+        <v>3.33</v>
       </c>
       <c r="G34" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H34" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="I34" t="n">
-        <v>8.1</v>
+        <v>12.8</v>
       </c>
       <c r="J34" t="n">
-        <v>66</v>
+        <v>27</v>
       </c>
       <c r="K34" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="L34" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M34" t="n">
-        <v>15.3</v>
+        <v>1.6</v>
       </c>
       <c r="N34" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O34" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~15 wks (rising into season)</t>
+          <t>BUY ~6u (2cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2425,55 +2425,55 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="E35" t="n">
-        <v>9.06</v>
+        <v>9.82</v>
       </c>
       <c r="F35" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="G35" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H35" t="n">
-        <v>8.4</v>
+        <v>11.3</v>
       </c>
       <c r="I35" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J35" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K35" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L35" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M35" t="n">
-        <v>74.7</v>
+        <v>13.2</v>
       </c>
       <c r="N35" t="n">
         <v>45</v>
       </c>
       <c r="O35" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~75 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Stigma Peach Iced Tea 10mg THC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2483,48 +2483,48 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D36" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="E36" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G36" t="n">
+        <v>9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="I36" t="n">
         <v>11</v>
       </c>
-      <c r="E36" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="F36" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G36" t="n">
-        <v>11</v>
-      </c>
-      <c r="H36" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="I36" t="n">
-        <v>12.1</v>
-      </c>
       <c r="J36" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K36" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L36" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M36" t="n">
-        <v>17.5</v>
+        <v>43.3</v>
       </c>
       <c r="N36" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O36" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~18 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2557,13 +2557,13 @@
         <v>7</v>
       </c>
       <c r="H37" t="n">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="I37" t="n">
         <v>12.6</v>
       </c>
       <c r="J37" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K37" t="n">
         <v>84</v>
@@ -2572,24 +2572,24 @@
         <v>84</v>
       </c>
       <c r="M37" t="n">
-        <v>7.3</v>
+        <v>9.9</v>
       </c>
       <c r="N37" t="n">
         <v>44</v>
       </c>
       <c r="O37" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~7 wks</t>
+          <t>BUY ~84u (14cs) - sells in ~10 wks (cooling)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2599,55 +2599,55 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9.67</v>
+        <v>9.33</v>
       </c>
       <c r="E38" t="n">
-        <v>7.57</v>
+        <v>8.01</v>
       </c>
       <c r="F38" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="G38" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H38" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="I38" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="J38" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K38" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M38" t="n">
-        <v>2.2</v>
+        <v>27.5</v>
       </c>
       <c r="N38" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
+          <t>CAUTION - 150u = ~28 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,48 +2657,48 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9.33</v>
+        <v>9.67</v>
       </c>
       <c r="E39" t="n">
-        <v>8.01</v>
+        <v>7.57</v>
       </c>
       <c r="F39" t="n">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H39" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="I39" t="n">
-        <v>16.6</v>
+        <v>16.8</v>
       </c>
       <c r="J39" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="K39" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>32.9</v>
+        <v>2.2</v>
       </c>
       <c r="N39" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O39" t="n">
         <v>6</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~33 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
         <v>2.7</v>
       </c>
       <c r="I40" t="n">
-        <v>15.5</v>
+        <v>16.8</v>
       </c>
       <c r="J40" t="n">
         <v>45</v>
@@ -2763,7 +2763,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,55 +2773,55 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="E41" t="n">
-        <v>8.4</v>
+        <v>11.2</v>
       </c>
       <c r="F41" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="G41" t="n">
         <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="I41" t="n">
-        <v>15.5</v>
+        <v>23.8</v>
       </c>
       <c r="J41" t="n">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="K41" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L41" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M41" t="n">
-        <v>2.2</v>
+        <v>11.7</v>
       </c>
       <c r="N41" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="O41" t="n">
         <v>6</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~12 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2835,25 +2835,25 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8.67</v>
+        <v>10.5</v>
       </c>
       <c r="E42" t="n">
-        <v>6.57</v>
+        <v>8.4</v>
       </c>
       <c r="F42" t="n">
         <v>2.1</v>
       </c>
       <c r="G42" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H42" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="I42" t="n">
-        <v>11</v>
+        <v>16.8</v>
       </c>
       <c r="J42" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="K42" t="n">
         <v>6</v>
@@ -2862,13 +2862,13 @@
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="N42" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O42" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -2879,7 +2879,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2908,10 +2908,10 @@
         <v>1.7</v>
       </c>
       <c r="I43" t="n">
-        <v>23.1</v>
+        <v>56.5</v>
       </c>
       <c r="J43" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="K43" t="n">
         <v>24</v>
@@ -2920,7 +2920,7 @@
         <v>24</v>
       </c>
       <c r="M43" t="n">
-        <v>14.1</v>
+        <v>14.2</v>
       </c>
       <c r="N43" t="n">
         <v>44</v>
@@ -2963,10 +2963,10 @@
         <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="I44" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="J44" t="n">
         <v>29</v>
@@ -2978,7 +2978,7 @@
         <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="N44" t="n">
         <v>47</v>
@@ -3021,10 +3021,10 @@
         <v>22</v>
       </c>
       <c r="H45" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="I45" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="J45" t="n">
         <v>29</v>
@@ -3036,7 +3036,7 @@
         <v>6</v>
       </c>
       <c r="M45" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="N45" t="n">
         <v>46</v>
@@ -3053,7 +3053,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,38 +3063,38 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11</v>
+        <v>8.67</v>
       </c>
       <c r="E46" t="n">
-        <v>9.82</v>
+        <v>6.57</v>
       </c>
       <c r="F46" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="I46" t="n">
-        <v>13.1</v>
+        <v>11.1</v>
       </c>
       <c r="J46" t="n">
-        <v>66</v>
+        <v>29</v>
       </c>
       <c r="K46" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L46" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M46" t="n">
-        <v>37.9</v>
+        <v>2.3</v>
       </c>
       <c r="N46" t="n">
         <v>45</v>
@@ -3104,14 +3104,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~38 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
+          <t>Clrty SodaPot Straw-Nana 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3125,51 +3125,51 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.45</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>11.47</v>
+        <v>9.82</v>
       </c>
       <c r="F47" t="n">
-        <v>1.97</v>
+        <v>1.18</v>
       </c>
       <c r="G47" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="I47" t="n">
-        <v>22.7</v>
+        <v>13.7</v>
       </c>
       <c r="J47" t="n">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="K47" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="L47" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>23.7</v>
+        <v>44.4</v>
       </c>
       <c r="N47" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="O47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~24 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 150u = ~44 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
+          <t>Foundry Nation Soda Variety Pack 5mg THC 6pk 12oz can</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3179,48 +3179,48 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>14</v>
+        <v>13.45</v>
       </c>
       <c r="E48" t="n">
-        <v>11.2</v>
+        <v>11.47</v>
       </c>
       <c r="F48" t="n">
-        <v>2.8</v>
+        <v>1.97</v>
       </c>
       <c r="G48" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="I48" t="n">
-        <v>56.5</v>
+        <v>24.6</v>
       </c>
       <c r="J48" t="n">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="K48" t="n">
+        <v>40</v>
+      </c>
+      <c r="L48" t="n">
+        <v>40</v>
+      </c>
+      <c r="M48" t="n">
         <v>24</v>
       </c>
-      <c r="L48" t="n">
-        <v>24</v>
-      </c>
-      <c r="M48" t="n">
-        <v>24.4</v>
-      </c>
       <c r="N48" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 24u = ~24 wks (overstock); consider ~24u</t>
+          <t>CAUTION - 40u = ~24 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
@@ -3253,7 +3253,7 @@
         <v>9</v>
       </c>
       <c r="H49" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="I49" t="n">
         <v>9.300000000000001</v>
@@ -3268,7 +3268,7 @@
         <v>624</v>
       </c>
       <c r="M49" t="n">
-        <v>342.5</v>
+        <v>320.9</v>
       </c>
       <c r="N49" t="n">
         <v>46</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~342 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~321 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
         <v>150</v>
       </c>
       <c r="M51" t="n">
-        <v>190.6</v>
+        <v>178.6</v>
       </c>
       <c r="N51" t="n">
         <v>55</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~191 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~179 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
         <v>9</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="I58" t="n">
         <v>731.2</v>
@@ -3754,7 +3754,7 @@
         <v>60</v>
       </c>
       <c r="M58" t="n">
-        <v>171.5</v>
+        <v>160.7</v>
       </c>
       <c r="N58" t="n">
         <v>48</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~172 wks (overstock); consider ~60u</t>
+          <t>CAUTION - 60u = ~161 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>132.4</v>
+        <v>123.9</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="J2" t="n">
-        <v>453</v>
+        <v>688</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>608</v>
+        <v>304</v>
       </c>
       <c r="M2" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~608u (304cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~304u (152cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>41.9</v>
+        <v>38.8</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,13 +600,13 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>27</v>
+        <v>25.1</v>
       </c>
       <c r="I4" t="n">
-        <v>4.3</v>
+        <v>6.1</v>
       </c>
       <c r="J4" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>138</v>
+        <v>98</v>
       </c>
       <c r="M4" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~138u (69cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~98u (49cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,19 +701,19 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>36</v>
+        <v>34.5</v>
       </c>
       <c r="I5" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="M5" t="n">
         <v>1.9</v>
@@ -722,11 +722,11 @@
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BUY ~70u (35cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~64u (32cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -759,32 +759,32 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>15.3</v>
+        <v>14.3</v>
       </c>
       <c r="I6" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="J6" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="M6" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~82u (41cs) - sells in ~5 wks</t>
+          <t>BUY ~74u (37cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
@@ -817,13 +817,13 @@
         <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>27.4</v>
+        <v>25.3</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="J7" t="n">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="K7" t="n">
         <v>624</v>
@@ -832,17 +832,17 @@
         <v>624</v>
       </c>
       <c r="M7" t="n">
-        <v>22.8</v>
+        <v>24.6</v>
       </c>
       <c r="N7" t="n">
         <v>45</v>
       </c>
       <c r="O7" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~23 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -875,39 +875,39 @@
         <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>17.6</v>
+        <v>16.6</v>
       </c>
       <c r="I8" t="n">
-        <v>12.3</v>
+        <v>14.9</v>
       </c>
       <c r="J8" t="n">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4</v>
+        <v>0.4</v>
       </c>
       <c r="N8" t="n">
         <v>46</v>
       </c>
       <c r="O8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -917,55 +917,55 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25.7</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>21.7</v>
+        <v>11.2</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="G9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>9</v>
+        <v>11.8</v>
       </c>
       <c r="I9" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="J9" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="M9" t="n">
-        <v>1.8</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="O9" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>BUY ~16u (8cs) - sells in ~2 wks</t>
+          <t>BUY ~54u (9cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sweet Justice Cherry Cola 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -975,55 +975,55 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
-        <v>11.2</v>
+        <v>16.67</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="H10" t="n">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="I10" t="n">
-        <v>7.1</v>
+        <v>14.5</v>
       </c>
       <c r="J10" t="n">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K10" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>4.2</v>
+        <v>0.3</v>
       </c>
       <c r="N10" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O10" t="n">
         <v>32</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~48u (8cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1033,48 +1033,48 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>20</v>
+        <v>25.7</v>
       </c>
       <c r="E11" t="n">
-        <v>16.67</v>
+        <v>21.7</v>
       </c>
       <c r="F11" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H11" t="n">
-        <v>9.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>13.2</v>
+        <v>7.1</v>
       </c>
       <c r="J11" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O11" t="n">
         <v>32</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>BUY ~9u (3cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~8u (4cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1107,32 @@
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I12" t="n">
         <v>5.5</v>
       </c>
       <c r="J12" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="N12" t="n">
         <v>50</v>
       </c>
       <c r="O12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUY ~20u (10cs) - sells in ~3 wks</t>
+          <t>BUY ~18u (9cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -1165,13 +1165,13 @@
         <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="J13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K13" t="n">
         <v>2</v>
@@ -1186,7 +1186,7 @@
         <v>42</v>
       </c>
       <c r="O13" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1223,13 +1223,13 @@
         <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>29</v>
+        <v>26.6</v>
       </c>
       <c r="I14" t="n">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K14" t="n">
         <v>624</v>
@@ -1238,17 +1238,17 @@
         <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>21.5</v>
+        <v>23.5</v>
       </c>
       <c r="N14" t="n">
         <v>46</v>
       </c>
       <c r="O14" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~22 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~24 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1281,13 +1281,13 @@
         <v>20</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="J15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K15" t="n">
         <v>2</v>
@@ -1302,7 +1302,7 @@
         <v>44</v>
       </c>
       <c r="O15" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1339,13 +1339,13 @@
         <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="I16" t="n">
-        <v>12.1</v>
+        <v>12.8</v>
       </c>
       <c r="J16" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="K16" t="n">
         <v>2</v>
@@ -1360,7 +1360,7 @@
         <v>51</v>
       </c>
       <c r="O16" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1371,7 +1371,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1381,55 +1381,55 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.85</v>
+        <v>26.52</v>
       </c>
       <c r="E17" t="n">
-        <v>8.68</v>
+        <v>24.2</v>
       </c>
       <c r="F17" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H17" t="n">
-        <v>10.8</v>
+        <v>9.5</v>
       </c>
       <c r="I17" t="n">
-        <v>11.9</v>
+        <v>8.5</v>
       </c>
       <c r="J17" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="K17" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="L17" t="n">
-        <v>6</v>
+        <v>208</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6</v>
+        <v>21.9</v>
       </c>
       <c r="N17" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 208u = ~22 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Utepils Raspberry 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1439,55 +1439,55 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E18" t="n">
-        <v>9.06</v>
+        <v>8.68</v>
       </c>
       <c r="F18" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H18" t="n">
-        <v>15.3</v>
+        <v>10.1</v>
       </c>
       <c r="I18" t="n">
-        <v>6.9</v>
+        <v>15.2</v>
       </c>
       <c r="J18" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="K18" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L18" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M18" t="n">
-        <v>40.7</v>
+        <v>0.6</v>
       </c>
       <c r="N18" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O18" t="n">
         <v>22</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~41 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,55 +1497,55 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>26.52</v>
+        <v>10.5</v>
       </c>
       <c r="E19" t="n">
-        <v>24.2</v>
+        <v>9.06</v>
       </c>
       <c r="F19" t="n">
-        <v>2.33</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>9.199999999999999</v>
+        <v>14.7</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="K19" t="n">
-        <v>208</v>
+        <v>624</v>
       </c>
       <c r="L19" t="n">
-        <v>208</v>
+        <v>624</v>
       </c>
       <c r="M19" t="n">
-        <v>22.5</v>
+        <v>42.5</v>
       </c>
       <c r="N19" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O19" t="n">
         <v>21</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~22 wks (overstock); consider ~208u</t>
+          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,48 +1555,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.03</v>
+        <v>10.85</v>
       </c>
       <c r="E20" t="n">
-        <v>9.15</v>
+        <v>8.68</v>
       </c>
       <c r="F20" t="n">
-        <v>0.88</v>
+        <v>2.17</v>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>23.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>7.3</v>
+        <v>23.1</v>
       </c>
       <c r="J20" t="n">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="K20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>26.5</v>
+        <v>0.7</v>
       </c>
       <c r="N20" t="n">
         <v>46</v>
       </c>
       <c r="O20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~26 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1629,13 +1629,13 @@
         <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>10.4</v>
+        <v>9.9</v>
       </c>
       <c r="I21" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="J21" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K21" t="n">
         <v>40</v>
@@ -1644,13 +1644,13 @@
         <v>40</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
         <v>47</v>
       </c>
       <c r="O21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,55 +1671,55 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.85</v>
+        <v>10.03</v>
       </c>
       <c r="E22" t="n">
-        <v>8.68</v>
+        <v>9.15</v>
       </c>
       <c r="F22" t="n">
-        <v>2.17</v>
+        <v>0.88</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H22" t="n">
-        <v>9.4</v>
+        <v>21.4</v>
       </c>
       <c r="I22" t="n">
-        <v>27.7</v>
+        <v>6.8</v>
       </c>
       <c r="J22" t="n">
-        <v>145</v>
+        <v>124</v>
       </c>
       <c r="K22" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L22" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6</v>
+        <v>29.2</v>
       </c>
       <c r="N22" t="n">
         <v>46</v>
       </c>
       <c r="O22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~29 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1745,13 +1745,13 @@
         <v>20</v>
       </c>
       <c r="H23" t="n">
-        <v>9.300000000000001</v>
+        <v>9</v>
       </c>
       <c r="I23" t="n">
-        <v>21.9</v>
+        <v>28.9</v>
       </c>
       <c r="J23" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
       <c r="K23" t="n">
         <v>6</v>
@@ -1760,13 +1760,13 @@
         <v>6</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="N23" t="n">
         <v>46</v>
       </c>
       <c r="O23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="E24" t="n">
-        <v>9.06</v>
+        <v>9.82</v>
       </c>
       <c r="F24" t="n">
-        <v>1.44</v>
+        <v>1.18</v>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H24" t="n">
-        <v>12.6</v>
+        <v>14.4</v>
       </c>
       <c r="I24" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="K24" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L24" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M24" t="n">
-        <v>49.5</v>
+        <v>10.4</v>
       </c>
       <c r="N24" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="O24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~50 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~10 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1845,55 +1845,55 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G25" t="n">
+        <v>11</v>
+      </c>
+      <c r="H25" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>60</v>
+      </c>
+      <c r="K25" t="n">
+        <v>150</v>
+      </c>
+      <c r="L25" t="n">
+        <v>150</v>
+      </c>
+      <c r="M25" t="n">
         <v>11.2</v>
       </c>
-      <c r="F25" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G25" t="n">
-        <v>7</v>
-      </c>
-      <c r="H25" t="n">
-        <v>20.9</v>
-      </c>
-      <c r="I25" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="J25" t="n">
-        <v>177</v>
-      </c>
-      <c r="K25" t="n">
-        <v>84</v>
-      </c>
-      <c r="L25" t="n">
-        <v>84</v>
-      </c>
-      <c r="M25" t="n">
-        <v>4</v>
-      </c>
       <c r="N25" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~11 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1903,55 +1903,55 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E26" t="n">
-        <v>9.82</v>
+        <v>9.9</v>
       </c>
       <c r="F26" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="G26" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H26" t="n">
-        <v>13.8</v>
+        <v>7.6</v>
       </c>
       <c r="I26" t="n">
-        <v>7.6</v>
+        <v>10.1</v>
       </c>
       <c r="J26" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K26" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="M26" t="n">
-        <v>10.8</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O26" t="n">
         <v>16</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~11 wks (rising into season)</t>
+          <t>BUY ~24u (4cs) - sells in ~3 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1965,51 +1965,51 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>9.33</v>
+        <v>10.5</v>
       </c>
       <c r="E27" t="n">
-        <v>8.01</v>
+        <v>9.06</v>
       </c>
       <c r="F27" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="G27" t="n">
         <v>14</v>
       </c>
       <c r="H27" t="n">
-        <v>11.8</v>
+        <v>11.3</v>
       </c>
       <c r="I27" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="J27" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="K27" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L27" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M27" t="n">
-        <v>12.8</v>
+        <v>55</v>
       </c>
       <c r="N27" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O27" t="n">
         <v>16</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~55 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2019,48 +2019,48 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D28" t="n">
         <v>12</v>
       </c>
       <c r="E28" t="n">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="F28" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="G28" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>7.5</v>
+        <v>20.5</v>
       </c>
       <c r="I28" t="n">
-        <v>5.3</v>
+        <v>15.1</v>
       </c>
       <c r="J28" t="n">
-        <v>22</v>
+        <v>174</v>
       </c>
       <c r="K28" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="L28" t="n">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="M28" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O28" t="n">
         <v>16</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>BUY ~42u (7cs) - sells in ~6 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2093,13 +2093,13 @@
         <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>19.7</v>
+        <v>18.5</v>
       </c>
       <c r="I29" t="n">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="J29" t="n">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="K29" t="n">
         <v>84</v>
@@ -2108,13 +2108,13 @@
         <v>84</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="N29" t="n">
         <v>44</v>
       </c>
       <c r="O29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lift Bridge Limelon 10mg THC 4pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2135,55 +2135,55 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12</v>
+        <v>9.33</v>
       </c>
       <c r="E30" t="n">
-        <v>9.9</v>
+        <v>8.01</v>
       </c>
       <c r="F30" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="G30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H30" t="n">
-        <v>7.7</v>
+        <v>11</v>
       </c>
       <c r="I30" t="n">
-        <v>9.1</v>
+        <v>6.1</v>
       </c>
       <c r="J30" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="K30" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L30" t="n">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="M30" t="n">
-        <v>3.1</v>
+        <v>13.6</v>
       </c>
       <c r="N30" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Fruit Cup 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2193,55 +2193,55 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>$14.40/cs Rebate paid out by LB at the end of each quarter</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>9.82</v>
+        <v>9.9</v>
       </c>
       <c r="F31" t="n">
-        <v>1.18</v>
+        <v>2.1</v>
       </c>
       <c r="G31" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H31" t="n">
-        <v>12.2</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>11.7</v>
+        <v>5.6</v>
       </c>
       <c r="J31" t="n">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="K31" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L31" t="n">
-        <v>150</v>
+        <v>36</v>
       </c>
       <c r="M31" t="n">
-        <v>12.3</v>
+        <v>5.1</v>
       </c>
       <c r="N31" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~12 wks (rising into season)</t>
+          <t>BUY ~36u (6cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2251,29 +2251,29 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.03</v>
+        <v>10.5</v>
       </c>
       <c r="E32" t="n">
-        <v>9.15</v>
+        <v>9.06</v>
       </c>
       <c r="F32" t="n">
-        <v>0.88</v>
+        <v>1.44</v>
       </c>
       <c r="G32" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>15.7</v>
+        <v>8.9</v>
       </c>
       <c r="I32" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J32" t="n">
-        <v>145</v>
+        <v>67</v>
       </c>
       <c r="K32" t="n">
         <v>624</v>
@@ -2282,24 +2282,24 @@
         <v>624</v>
       </c>
       <c r="M32" t="n">
-        <v>39.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O32" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~40 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~70 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Daizy's Passion Fruit 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.5</v>
+        <v>16.67</v>
       </c>
       <c r="E33" t="n">
-        <v>9.06</v>
+        <v>13.34</v>
       </c>
       <c r="F33" t="n">
-        <v>1.44</v>
+        <v>3.33</v>
       </c>
       <c r="G33" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>9.1</v>
+        <v>3.8</v>
       </c>
       <c r="I33" t="n">
-        <v>7.7</v>
+        <v>12.8</v>
       </c>
       <c r="J33" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="K33" t="n">
-        <v>624</v>
+        <v>3</v>
       </c>
       <c r="L33" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M33" t="n">
-        <v>68.2</v>
+        <v>1.6</v>
       </c>
       <c r="N33" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O33" t="n">
         <v>13</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~68 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (2cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,48 +2367,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>16.67</v>
+        <v>10.03</v>
       </c>
       <c r="E34" t="n">
-        <v>13.34</v>
+        <v>9.15</v>
       </c>
       <c r="F34" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G34" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
-        <v>3.8</v>
+        <v>14.5</v>
       </c>
       <c r="I34" t="n">
-        <v>12.8</v>
+        <v>7.7</v>
       </c>
       <c r="J34" t="n">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L34" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M34" t="n">
-        <v>1.6</v>
+        <v>43.1</v>
       </c>
       <c r="N34" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O34" t="n">
         <v>13</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~6u (2cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2441,13 +2441,13 @@
         <v>11</v>
       </c>
       <c r="H35" t="n">
-        <v>11.3</v>
+        <v>10.7</v>
       </c>
       <c r="I35" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K35" t="n">
         <v>150</v>
@@ -2456,7 +2456,7 @@
         <v>150</v>
       </c>
       <c r="M35" t="n">
-        <v>13.2</v>
+        <v>14</v>
       </c>
       <c r="N35" t="n">
         <v>45</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2499,13 +2499,13 @@
         <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>14.4</v>
+        <v>13.9</v>
       </c>
       <c r="I36" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="J36" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K36" t="n">
         <v>624</v>
@@ -2514,17 +2514,17 @@
         <v>624</v>
       </c>
       <c r="M36" t="n">
-        <v>43.3</v>
+        <v>45</v>
       </c>
       <c r="N36" t="n">
         <v>46</v>
       </c>
       <c r="O36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~45 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2557,13 +2557,13 @@
         <v>7</v>
       </c>
       <c r="H37" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="I37" t="n">
-        <v>12.6</v>
+        <v>12.1</v>
       </c>
       <c r="J37" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K37" t="n">
         <v>84</v>
@@ -2572,7 +2572,7 @@
         <v>84</v>
       </c>
       <c r="M37" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>44</v>
@@ -2615,10 +2615,10 @@
         <v>14</v>
       </c>
       <c r="H38" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="I38" t="n">
-        <v>16.8</v>
+        <v>17.2</v>
       </c>
       <c r="J38" t="n">
         <v>51</v>
@@ -2630,7 +2630,7 @@
         <v>150</v>
       </c>
       <c r="M38" t="n">
-        <v>27.5</v>
+        <v>28</v>
       </c>
       <c r="N38" t="n">
         <v>50</v>
@@ -2673,13 +2673,13 @@
         <v>22</v>
       </c>
       <c r="H39" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="I39" t="n">
-        <v>16.8</v>
+        <v>13.4</v>
       </c>
       <c r="J39" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K39" t="n">
         <v>6</v>
@@ -2688,7 +2688,7 @@
         <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
         <v>46</v>
@@ -2705,7 +2705,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2734,10 +2734,10 @@
         <v>2.7</v>
       </c>
       <c r="I40" t="n">
-        <v>16.8</v>
+        <v>10.1</v>
       </c>
       <c r="J40" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="K40" t="n">
         <v>6</v>
@@ -2763,7 +2763,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2773,48 +2773,48 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="E41" t="n">
-        <v>11.2</v>
+        <v>8.4</v>
       </c>
       <c r="F41" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="G41" t="n">
         <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="I41" t="n">
-        <v>23.8</v>
+        <v>10.1</v>
       </c>
       <c r="J41" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K41" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L41" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M41" t="n">
-        <v>11.7</v>
+        <v>2.2</v>
       </c>
       <c r="N41" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O41" t="n">
         <v>6</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~12 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -2847,13 +2847,13 @@
         <v>20</v>
       </c>
       <c r="H42" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="I42" t="n">
-        <v>16.8</v>
+        <v>13.4</v>
       </c>
       <c r="J42" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="K42" t="n">
         <v>6</v>
@@ -2862,7 +2862,7 @@
         <v>6</v>
       </c>
       <c r="M42" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="N42" t="n">
         <v>47</v>
@@ -2879,7 +2879,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2889,48 +2889,48 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Support with Free cs from SJ</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14</v>
+        <v>8.67</v>
       </c>
       <c r="E43" t="n">
-        <v>11.2</v>
+        <v>6.57</v>
       </c>
       <c r="F43" t="n">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="G43" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H43" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="I43" t="n">
-        <v>56.5</v>
+        <v>13.4</v>
       </c>
       <c r="J43" t="n">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="K43" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L43" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="M43" t="n">
-        <v>14.2</v>
+        <v>2</v>
       </c>
       <c r="N43" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~14 wks (rising into season)</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -2951,25 +2951,25 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.5</v>
+        <v>9.67</v>
       </c>
       <c r="E44" t="n">
-        <v>8.4</v>
+        <v>7.57</v>
       </c>
       <c r="F44" t="n">
         <v>2.1</v>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H44" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="I44" t="n">
-        <v>11.1</v>
+        <v>10.1</v>
       </c>
       <c r="J44" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K44" t="n">
         <v>6</v>
@@ -2978,13 +2978,13 @@
         <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="N44" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O44" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3005,55 +3005,55 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9.67</v>
+        <v>14</v>
       </c>
       <c r="E45" t="n">
-        <v>7.57</v>
+        <v>11.2</v>
       </c>
       <c r="F45" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="G45" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="I45" t="n">
-        <v>11.1</v>
+        <v>21.8</v>
       </c>
       <c r="J45" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K45" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L45" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M45" t="n">
-        <v>2.3</v>
+        <v>13.8</v>
       </c>
       <c r="N45" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O45" t="n">
         <v>5</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
+          <t>BUY ~24u (4cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Dream 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3063,48 +3063,48 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>Support with Free cs from SJ</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>8.67</v>
+        <v>14</v>
       </c>
       <c r="E46" t="n">
-        <v>6.57</v>
+        <v>11.2</v>
       </c>
       <c r="F46" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="G46" t="n">
+        <v>20</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I46" t="n">
+        <v>65.2</v>
+      </c>
+      <c r="J46" t="n">
+        <v>73</v>
+      </c>
+      <c r="K46" t="n">
         <v>24</v>
       </c>
-      <c r="H46" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I46" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="J46" t="n">
-        <v>29</v>
-      </c>
-      <c r="K46" t="n">
-        <v>6</v>
-      </c>
       <c r="L46" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M46" t="n">
-        <v>2.3</v>
+        <v>16.4</v>
       </c>
       <c r="N46" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O46" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
+          <t>CAUTION - 24u = ~16 wks (overstock); consider ~24u</t>
         </is>
       </c>
     </row>
@@ -3137,13 +3137,13 @@
         <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I47" t="n">
-        <v>13.7</v>
+        <v>12.2</v>
       </c>
       <c r="J47" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K47" t="n">
         <v>150</v>
@@ -3152,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>44.4</v>
+        <v>41.5</v>
       </c>
       <c r="N47" t="n">
         <v>45</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~44 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~42 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3195,7 +3195,7 @@
         <v>15</v>
       </c>
       <c r="H48" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="I48" t="n">
         <v>24.6</v>
@@ -3210,7 +3210,7 @@
         <v>40</v>
       </c>
       <c r="M48" t="n">
-        <v>24</v>
+        <v>24.6</v>
       </c>
       <c r="N48" t="n">
         <v>48</v>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~24 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 40u = ~25 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
@@ -3253,10 +3253,10 @@
         <v>9</v>
       </c>
       <c r="H49" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="I49" t="n">
-        <v>9.300000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="J49" t="n">
         <v>18</v>
@@ -3268,7 +3268,7 @@
         <v>624</v>
       </c>
       <c r="M49" t="n">
-        <v>320.9</v>
+        <v>359.8</v>
       </c>
       <c r="N49" t="n">
         <v>46</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~321 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~360 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3372,7 @@
         <v>0.8</v>
       </c>
       <c r="I51" t="n">
-        <v>98.8</v>
+        <v>102.6</v>
       </c>
       <c r="J51" t="n">
         <v>83</v>
@@ -3384,7 +3384,7 @@
         <v>150</v>
       </c>
       <c r="M51" t="n">
-        <v>178.6</v>
+        <v>189.6</v>
       </c>
       <c r="N51" t="n">
         <v>55</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~179 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~190 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3739,10 +3739,10 @@
         <v>9</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="I58" t="n">
-        <v>731.2</v>
+        <v>1170</v>
       </c>
       <c r="J58" t="n">
         <v>273</v>
@@ -3754,7 +3754,7 @@
         <v>60</v>
       </c>
       <c r="M58" t="n">
-        <v>160.7</v>
+        <v>262.9</v>
       </c>
       <c r="N58" t="n">
         <v>48</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~161 wks (overstock); consider ~60u</t>
+          <t>CAUTION - 60u = ~263 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,32 +527,32 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>123.9</v>
+        <v>121.2</v>
       </c>
       <c r="I2" t="n">
         <v>7.8</v>
       </c>
       <c r="J2" t="n">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="M2" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="N2" t="n">
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~304u (152cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~292u (146cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -588,10 +588,10 @@
         <v>38.8</v>
       </c>
       <c r="I3" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J3" t="n">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -643,13 +643,13 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>25.1</v>
+        <v>24.7</v>
       </c>
       <c r="I4" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="J4" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
@@ -658,13 +658,13 @@
         <v>98</v>
       </c>
       <c r="M4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -701,19 +701,19 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="I5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M5" t="n">
         <v>1.9</v>
@@ -726,7 +726,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BUY ~64u (32cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~66u (33cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -759,32 +759,32 @@
         <v>13</v>
       </c>
       <c r="H6" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
         <v>2.9</v>
       </c>
       <c r="J6" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="M6" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
       </c>
       <c r="O6" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~74u (37cs) - sells in ~5 wks</t>
+          <t>BUY ~72u (36cs) - sells in ~5 wks</t>
         </is>
       </c>
     </row>
@@ -817,13 +817,13 @@
         <v>14</v>
       </c>
       <c r="H7" t="n">
-        <v>25.3</v>
+        <v>24.9</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="J7" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K7" t="n">
         <v>624</v>
@@ -832,7 +832,7 @@
         <v>624</v>
       </c>
       <c r="M7" t="n">
-        <v>24.6</v>
+        <v>25</v>
       </c>
       <c r="N7" t="n">
         <v>45</v>
@@ -881,7 +881,7 @@
         <v>14.9</v>
       </c>
       <c r="J8" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
@@ -933,39 +933,39 @@
         <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>11.8</v>
+        <v>12.7</v>
       </c>
       <c r="I9" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="J9" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="K9" t="n">
         <v>24</v>
       </c>
       <c r="L9" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="N9" t="n">
         <v>44</v>
       </c>
       <c r="O9" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>BUY ~54u (9cs) - sells in ~5 wks (rising into season)</t>
+          <t>BUY ~66u (11cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
+          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -975,55 +975,55 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>20</v>
+        <v>25.7</v>
       </c>
       <c r="E10" t="n">
-        <v>16.67</v>
+        <v>21.7</v>
       </c>
       <c r="F10" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>14.5</v>
+        <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="K10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O10" t="n">
         <v>32</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
+          <t>BUY ~8u (4cs) - sells in ~1 wks</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Stigma Tonic Variety Pack 10mg THC 12pk 12oz can</t>
+          <t>oHHo Variety Pack 10mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1033,48 +1033,48 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>25.7</v>
+        <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>21.7</v>
+        <v>16.67</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>7.1</v>
+        <v>14.9</v>
       </c>
       <c r="J11" t="n">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="K11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="N11" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>BUY ~8u (4cs) - sells in ~1 wks</t>
+          <t>BUY ~3u (1cs) - sells in ~0 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1107,10 +1107,10 @@
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
       <c r="I12" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="J12" t="n">
         <v>41</v>
@@ -1119,20 +1119,20 @@
         <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="M12" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="N12" t="n">
         <v>50</v>
       </c>
       <c r="O12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>BUY ~18u (9cs) - sells in ~2 wks</t>
+          <t>BUY ~16u (8cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1165,10 @@
         <v>20</v>
       </c>
       <c r="H13" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="J13" t="n">
         <v>59</v>
@@ -1180,7 +1180,7 @@
         <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="N13" t="n">
         <v>42</v>
@@ -1223,13 +1223,13 @@
         <v>9</v>
       </c>
       <c r="H14" t="n">
-        <v>26.6</v>
+        <v>26.1</v>
       </c>
       <c r="I14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J14" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="K14" t="n">
         <v>624</v>
@@ -1238,7 +1238,7 @@
         <v>624</v>
       </c>
       <c r="M14" t="n">
-        <v>23.5</v>
+        <v>23.9</v>
       </c>
       <c r="N14" t="n">
         <v>46</v>
@@ -1255,7 +1255,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1265,38 +1265,38 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>25.9</v>
+        <v>26.52</v>
       </c>
       <c r="E15" t="n">
-        <v>20.72</v>
+        <v>24.2</v>
       </c>
       <c r="F15" t="n">
-        <v>5.18</v>
+        <v>2.33</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>12.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>208</v>
       </c>
       <c r="L15" t="n">
-        <v>2</v>
+        <v>208</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4</v>
+        <v>21.5</v>
       </c>
       <c r="N15" t="n">
         <v>44</v>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 208u = ~22 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I16" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="J16" t="n">
         <v>59</v>
@@ -1354,7 +1354,7 @@
         <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="N16" t="n">
         <v>51</v>
@@ -1371,7 +1371,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1381,48 +1381,48 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>26.52</v>
+        <v>25.9</v>
       </c>
       <c r="E17" t="n">
-        <v>24.2</v>
+        <v>20.72</v>
       </c>
       <c r="F17" t="n">
-        <v>2.33</v>
+        <v>5.18</v>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>9.5</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>8.5</v>
+        <v>12.9</v>
       </c>
       <c r="J17" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="K17" t="n">
-        <v>208</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>208</v>
+        <v>2</v>
       </c>
       <c r="M17" t="n">
-        <v>21.9</v>
+        <v>0.5</v>
       </c>
       <c r="N17" t="n">
         <v>44</v>
       </c>
       <c r="O17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~22 wks (overstock); consider ~208u</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,55 +1497,55 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E19" t="n">
-        <v>9.06</v>
+        <v>8.68</v>
       </c>
       <c r="F19" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H19" t="n">
-        <v>14.7</v>
+        <v>9.5</v>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>22.2</v>
       </c>
       <c r="J19" t="n">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="K19" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L19" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
-        <v>42.5</v>
+        <v>0.6</v>
       </c>
       <c r="N19" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O19" t="n">
         <v>21</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~42 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,48 +1555,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E20" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F20" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G20" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H20" t="n">
-        <v>9.199999999999999</v>
+        <v>14.4</v>
       </c>
       <c r="I20" t="n">
-        <v>23.1</v>
+        <v>6.6</v>
       </c>
       <c r="J20" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="K20" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7</v>
+        <v>43.3</v>
       </c>
       <c r="N20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1629,13 +1629,13 @@
         <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="J21" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K21" t="n">
         <v>40</v>
@@ -1644,13 +1644,13 @@
         <v>40</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="N21" t="n">
         <v>47</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1687,10 +1687,10 @@
         <v>9</v>
       </c>
       <c r="H22" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="I22" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="J22" t="n">
         <v>124</v>
@@ -1702,7 +1702,7 @@
         <v>624</v>
       </c>
       <c r="M22" t="n">
-        <v>29.2</v>
+        <v>29.5</v>
       </c>
       <c r="N22" t="n">
         <v>46</v>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~29 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~30 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1745,10 +1745,10 @@
         <v>20</v>
       </c>
       <c r="H23" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="I23" t="n">
-        <v>28.9</v>
+        <v>29.1</v>
       </c>
       <c r="J23" t="n">
         <v>144</v>
@@ -1803,13 +1803,13 @@
         <v>11</v>
       </c>
       <c r="H24" t="n">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="I24" t="n">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="J24" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K24" t="n">
         <v>150</v>
@@ -1818,7 +1818,7 @@
         <v>150</v>
       </c>
       <c r="M24" t="n">
-        <v>10.4</v>
+        <v>10.2</v>
       </c>
       <c r="N24" t="n">
         <v>55</v>
@@ -1835,7 +1835,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1849,44 +1849,44 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="E25" t="n">
-        <v>9.82</v>
+        <v>9.06</v>
       </c>
       <c r="F25" t="n">
-        <v>1.18</v>
+        <v>1.44</v>
       </c>
       <c r="G25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>13.3</v>
+        <v>11.2</v>
       </c>
       <c r="I25" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="J25" t="n">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="K25" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L25" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M25" t="n">
-        <v>11.2</v>
+        <v>55.7</v>
       </c>
       <c r="N25" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="O25" t="n">
         <v>16</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~11 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~56 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
         <v>7.6</v>
       </c>
       <c r="I26" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="J26" t="n">
         <v>43</v>
@@ -1931,10 +1931,10 @@
         <v>6</v>
       </c>
       <c r="L26" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="M26" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="N26" t="n">
         <v>45</v>
@@ -1944,14 +1944,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>BUY ~24u (4cs) - sells in ~3 wks (rising into season)</t>
+          <t>BUY ~18u (3cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="E27" t="n">
-        <v>9.06</v>
+        <v>11.2</v>
       </c>
       <c r="F27" t="n">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="G27" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="H27" t="n">
-        <v>11.3</v>
+        <v>20.2</v>
       </c>
       <c r="I27" t="n">
-        <v>8.6</v>
+        <v>15.2</v>
       </c>
       <c r="J27" t="n">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="K27" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="L27" t="n">
-        <v>624</v>
+        <v>84</v>
       </c>
       <c r="M27" t="n">
-        <v>55</v>
+        <v>4.2</v>
       </c>
       <c r="N27" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="O27" t="n">
         <v>16</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~55 wks (overstock); consider ~624u</t>
+          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2035,13 +2035,13 @@
         <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="I28" t="n">
-        <v>15.1</v>
+        <v>9.1</v>
       </c>
       <c r="J28" t="n">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="K28" t="n">
         <v>84</v>
@@ -2050,13 +2050,13 @@
         <v>84</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="N28" t="n">
         <v>44</v>
       </c>
       <c r="O28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,48 +2077,48 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" t="n">
-        <v>11.2</v>
+        <v>9.82</v>
       </c>
       <c r="F29" t="n">
-        <v>0.8</v>
+        <v>1.18</v>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H29" t="n">
-        <v>18.5</v>
+        <v>13.1</v>
       </c>
       <c r="I29" t="n">
-        <v>9.1</v>
+        <v>7.7</v>
       </c>
       <c r="J29" t="n">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="K29" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="L29" t="n">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="M29" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="N29" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="O29" t="n">
         <v>15</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~12 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2151,13 +2151,13 @@
         <v>14</v>
       </c>
       <c r="H30" t="n">
-        <v>11</v>
+        <v>11.3</v>
       </c>
       <c r="I30" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="J30" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K30" t="n">
         <v>150</v>
@@ -2166,7 +2166,7 @@
         <v>150</v>
       </c>
       <c r="M30" t="n">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="N30" t="n">
         <v>50</v>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2267,13 +2267,13 @@
         <v>14</v>
       </c>
       <c r="H32" t="n">
-        <v>8.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
       <c r="J32" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="K32" t="n">
         <v>624</v>
@@ -2282,7 +2282,7 @@
         <v>624</v>
       </c>
       <c r="M32" t="n">
-        <v>70.09999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="N32" t="n">
         <v>45</v>
@@ -2292,14 +2292,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~70 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~68 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pallet Buy 104 Case</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>16.67</v>
+        <v>10.03</v>
       </c>
       <c r="E33" t="n">
-        <v>13.34</v>
+        <v>9.15</v>
       </c>
       <c r="F33" t="n">
-        <v>3.33</v>
+        <v>0.88</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>3.8</v>
+        <v>14.4</v>
       </c>
       <c r="I33" t="n">
-        <v>12.8</v>
+        <v>7.8</v>
       </c>
       <c r="J33" t="n">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="K33" t="n">
-        <v>3</v>
+        <v>624</v>
       </c>
       <c r="L33" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M33" t="n">
-        <v>1.6</v>
+        <v>43.4</v>
       </c>
       <c r="N33" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="O33" t="n">
         <v>13</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>BUY ~6u (2cs) - sells in ~2 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,55 +2367,55 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E34" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F34" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H34" t="n">
-        <v>14.5</v>
+        <v>10.9</v>
       </c>
       <c r="I34" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J34" t="n">
-        <v>142</v>
+        <v>62</v>
       </c>
       <c r="K34" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L34" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M34" t="n">
-        <v>43.1</v>
+        <v>13.8</v>
       </c>
       <c r="N34" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O34" t="n">
         <v>13</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>oHHo Variety Pack 5mg THC 8pk 12oz can</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2425,48 +2425,48 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>Pallet Buy 104 Case</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11</v>
+        <v>16.67</v>
       </c>
       <c r="E35" t="n">
-        <v>9.82</v>
+        <v>13.34</v>
       </c>
       <c r="F35" t="n">
-        <v>1.18</v>
+        <v>3.33</v>
       </c>
       <c r="G35" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="H35" t="n">
-        <v>10.7</v>
+        <v>3.6</v>
       </c>
       <c r="I35" t="n">
-        <v>8.199999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="J35" t="n">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="K35" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>150</v>
+        <v>3</v>
       </c>
       <c r="M35" t="n">
-        <v>14</v>
+        <v>0.8</v>
       </c>
       <c r="N35" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
+          <t>BUY ~3u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2557,13 +2557,13 @@
         <v>7</v>
       </c>
       <c r="H37" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="J37" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="K37" t="n">
         <v>84</v>
@@ -2572,7 +2572,7 @@
         <v>84</v>
       </c>
       <c r="M37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N37" t="n">
         <v>44</v>
@@ -2589,7 +2589,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2599,55 +2599,55 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9.33</v>
+        <v>9.67</v>
       </c>
       <c r="E38" t="n">
-        <v>8.01</v>
+        <v>7.57</v>
       </c>
       <c r="F38" t="n">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="G38" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H38" t="n">
-        <v>5.3</v>
+        <v>3</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>13.4</v>
       </c>
       <c r="J38" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="K38" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L38" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M38" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="N38" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O38" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~28 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,48 +2657,48 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9.67</v>
+        <v>9.33</v>
       </c>
       <c r="E39" t="n">
-        <v>7.57</v>
+        <v>8.01</v>
       </c>
       <c r="F39" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="G39" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H39" t="n">
-        <v>3.1</v>
+        <v>4.8</v>
       </c>
       <c r="I39" t="n">
-        <v>13.4</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K39" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L39" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="N39" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O39" t="n">
         <v>6</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
+          <t>CAUTION - 150u = ~31 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
         <v>6</v>
       </c>
       <c r="M40" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="N40" t="n">
         <v>45</v>
@@ -2804,7 +2804,7 @@
         <v>6</v>
       </c>
       <c r="M41" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="N41" t="n">
         <v>47</v>
@@ -2847,7 +2847,7 @@
         <v>20</v>
       </c>
       <c r="H42" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
         <v>13.4</v>
@@ -2905,7 +2905,7 @@
         <v>24</v>
       </c>
       <c r="H43" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="I43" t="n">
         <v>13.4</v>
@@ -2978,7 +2978,7 @@
         <v>6</v>
       </c>
       <c r="M44" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="N44" t="n">
         <v>46</v>
@@ -3024,7 +3024,7 @@
         <v>1.7</v>
       </c>
       <c r="I45" t="n">
-        <v>21.8</v>
+        <v>22.5</v>
       </c>
       <c r="J45" t="n">
         <v>21</v>
@@ -3036,7 +3036,7 @@
         <v>24</v>
       </c>
       <c r="M45" t="n">
-        <v>13.8</v>
+        <v>14.3</v>
       </c>
       <c r="N45" t="n">
         <v>44</v>
@@ -3137,13 +3137,13 @@
         <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I47" t="n">
-        <v>12.2</v>
+        <v>11.6</v>
       </c>
       <c r="J47" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K47" t="n">
         <v>150</v>
@@ -3152,7 +3152,7 @@
         <v>150</v>
       </c>
       <c r="M47" t="n">
-        <v>41.5</v>
+        <v>40.2</v>
       </c>
       <c r="N47" t="n">
         <v>45</v>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~42 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~40 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3195,13 +3195,13 @@
         <v>15</v>
       </c>
       <c r="H48" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="I48" t="n">
-        <v>24.6</v>
+        <v>21.8</v>
       </c>
       <c r="J48" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K48" t="n">
         <v>40</v>
@@ -3210,7 +3210,7 @@
         <v>40</v>
       </c>
       <c r="M48" t="n">
-        <v>24.6</v>
+        <v>22.8</v>
       </c>
       <c r="N48" t="n">
         <v>48</v>
@@ -3220,14 +3220,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~25 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 40u = ~23 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Stigma Berry Tea 10mg THC</t>
+          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3237,38 +3237,38 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.03</v>
+        <v>10.58</v>
       </c>
       <c r="E49" t="n">
-        <v>9.15</v>
+        <v>7.06</v>
       </c>
       <c r="F49" t="n">
-        <v>0.88</v>
+        <v>3.53</v>
       </c>
       <c r="G49" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H49" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="I49" t="n">
-        <v>10.2</v>
+        <v>120.5</v>
       </c>
       <c r="J49" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K49" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="L49" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M49" t="n">
-        <v>359.8</v>
+        <v>26.8</v>
       </c>
       <c r="N49" t="n">
         <v>46</v>
@@ -3278,14 +3278,14 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~360 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 12u = ~27 wks (overstock); consider ~12u</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
+          <t>Stigma Berry Tea 10mg THC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3295,48 +3295,48 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.58</v>
+        <v>10.03</v>
       </c>
       <c r="E50" t="n">
-        <v>7.06</v>
+        <v>9.15</v>
       </c>
       <c r="F50" t="n">
-        <v>3.53</v>
+        <v>0.88</v>
       </c>
       <c r="G50" t="n">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="I50" t="n">
-        <v>120.5</v>
+        <v>10.2</v>
       </c>
       <c r="J50" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="K50" t="n">
-        <v>12</v>
+        <v>624</v>
       </c>
       <c r="L50" t="n">
-        <v>12</v>
+        <v>624</v>
       </c>
       <c r="M50" t="n">
-        <v>26.8</v>
+        <v>367.7</v>
       </c>
       <c r="N50" t="n">
         <v>46</v>
       </c>
       <c r="O50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CAUTION - 12u = ~27 wks (overstock); consider ~12u</t>
+          <t>CAUTION - 624u = ~368 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
         <v>150</v>
       </c>
       <c r="M51" t="n">
-        <v>189.6</v>
+        <v>193.8</v>
       </c>
       <c r="N51" t="n">
         <v>55</v>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~190 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 150u = ~194 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
         <v>60</v>
       </c>
       <c r="M58" t="n">
-        <v>262.9</v>
+        <v>268.7</v>
       </c>
       <c r="N58" t="n">
         <v>48</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~263 wks (overstock); consider ~60u</t>
+          <t>CAUTION - 60u = ~269 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>

--- a/data/THC Deal Evaluation.xlsx
+++ b/data/THC Deal Evaluation.xlsx
@@ -527,19 +527,19 @@
         <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>121.2</v>
+        <v>118.8</v>
       </c>
       <c r="I2" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J2" t="n">
-        <v>678</v>
+        <v>670</v>
       </c>
       <c r="K2" t="n">
         <v>208</v>
       </c>
       <c r="L2" t="n">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="M2" t="n">
         <v>2.4</v>
@@ -548,11 +548,11 @@
         <v>45</v>
       </c>
       <c r="O2" t="n">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BUY ~292u (146cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~282u (141cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -585,13 +585,13 @@
         <v>13</v>
       </c>
       <c r="H3" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J3" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="K3" t="n">
         <v>208</v>
@@ -600,17 +600,17 @@
         <v>208</v>
       </c>
       <c r="M3" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="N3" t="n">
         <v>46</v>
       </c>
       <c r="O3" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>BUY ~208u (104cs) - sells in ~5 wks</t>
+          <t>BUY ~208u (104cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
@@ -643,32 +643,32 @@
         <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="I4" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="K4" t="n">
         <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="M4" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N4" t="n">
         <v>47</v>
       </c>
       <c r="O4" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>BUY ~98u (49cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~106u (53cs) - sells in ~4 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -701,32 +701,32 @@
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>34.4</v>
+        <v>34.2</v>
       </c>
       <c r="I5" t="n">
-        <v>8.699999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J5" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
       </c>
       <c r="L5" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>46</v>
       </c>
       <c r="O5" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>BUY ~66u (33cs) - sells in ~2 wks (rising into season)</t>
+          <t>BUY ~68u (34cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -762,19 +762,19 @@
         <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
       </c>
       <c r="L6" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="M6" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="N6" t="n">
         <v>48</v>
@@ -784,7 +784,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>BUY ~72u (36cs) - sells in ~5 wks</t>
+          <t>BUY ~84u (42cs) - sells in ~6 wks</t>
         </is>
       </c>
     </row>
@@ -820,10 +820,10 @@
         <v>24.9</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="J7" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="K7" t="n">
         <v>624</v>
@@ -991,32 +991,32 @@
         <v>16</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J10" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K10" t="n">
         <v>2</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="N10" t="n">
         <v>50</v>
       </c>
       <c r="O10" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>BUY ~8u (4cs) - sells in ~1 wks</t>
+          <t>BUY ~12u (6cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -1052,10 +1052,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="J11" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K11" t="n">
         <v>3</v>
@@ -1107,13 +1107,13 @@
         <v>16</v>
       </c>
       <c r="H12" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
@@ -1128,7 +1128,7 @@
         <v>50</v>
       </c>
       <c r="O12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
+          <t>Stigma Variety Pack 10mg THC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1149,55 +1149,55 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>26.5</v>
+        <v>26.52</v>
       </c>
       <c r="E13" t="n">
-        <v>21.32</v>
+        <v>24.2</v>
       </c>
       <c r="F13" t="n">
-        <v>5.18</v>
+        <v>2.33</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>12.9</v>
+        <v>7.9</v>
       </c>
       <c r="J13" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="K13" t="n">
-        <v>2</v>
+        <v>208</v>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>208</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5</v>
+        <v>21.3</v>
       </c>
       <c r="N13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="O13" t="n">
         <v>23</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
+          <t>CAUTION - 208u = ~21 wks (overstock); consider ~208u</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Stigma Lime Seltzer 10mg THC</t>
+          <t>Lift Bridge Big Believer Variety Pack THC 12pk 12oz can</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1207,55 +1207,55 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10.03</v>
+        <v>26.5</v>
       </c>
       <c r="E14" t="n">
-        <v>9.15</v>
+        <v>21.32</v>
       </c>
       <c r="F14" t="n">
-        <v>0.88</v>
+        <v>5.18</v>
       </c>
       <c r="G14" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H14" t="n">
-        <v>26.1</v>
+        <v>4.3</v>
       </c>
       <c r="I14" t="n">
-        <v>7.9</v>
+        <v>13</v>
       </c>
       <c r="J14" t="n">
-        <v>147</v>
+        <v>59</v>
       </c>
       <c r="K14" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>624</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>23.9</v>
+        <v>0.5</v>
       </c>
       <c r="N14" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="O14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~24 wks (overstock); consider ~624u</t>
+          <t>BUY ~2u (1cs) - sells in ~0 wks</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Stigma Variety Pack 10mg THC</t>
+          <t>Stigma Lime Seltzer 10mg THC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1269,44 +1269,44 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>26.52</v>
+        <v>10.03</v>
       </c>
       <c r="E15" t="n">
-        <v>24.2</v>
+        <v>9.15</v>
       </c>
       <c r="F15" t="n">
-        <v>2.33</v>
+        <v>0.88</v>
       </c>
       <c r="G15" t="n">
         <v>9</v>
       </c>
       <c r="H15" t="n">
-        <v>9.699999999999999</v>
+        <v>25.4</v>
       </c>
       <c r="I15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J15" t="n">
-        <v>44</v>
+        <v>147</v>
       </c>
       <c r="K15" t="n">
-        <v>208</v>
+        <v>624</v>
       </c>
       <c r="L15" t="n">
-        <v>208</v>
+        <v>624</v>
       </c>
       <c r="M15" t="n">
-        <v>21.5</v>
+        <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CAUTION - 208u = ~22 wks (overstock); consider ~208u</t>
+          <t>CAUTION - 624u = ~25 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         <v>22</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="J16" t="n">
         <v>59</v>
@@ -1360,7 +1360,7 @@
         <v>51</v>
       </c>
       <c r="O16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1397,10 +1397,10 @@
         <v>20</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
         <v>59</v>
@@ -1418,7 +1418,7 @@
         <v>44</v>
       </c>
       <c r="O17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1458,10 +1458,10 @@
         <v>10.1</v>
       </c>
       <c r="I18" t="n">
-        <v>15.2</v>
+        <v>14.7</v>
       </c>
       <c r="J18" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K18" t="n">
         <v>6</v>
@@ -1487,7 +1487,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1497,55 +1497,55 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.85</v>
+        <v>10.5</v>
       </c>
       <c r="E19" t="n">
-        <v>8.68</v>
+        <v>9.06</v>
       </c>
       <c r="F19" t="n">
-        <v>2.17</v>
+        <v>1.44</v>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>9.5</v>
+        <v>14.4</v>
       </c>
       <c r="I19" t="n">
-        <v>22.2</v>
+        <v>6.5</v>
       </c>
       <c r="J19" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="K19" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="L19" t="n">
-        <v>6</v>
+        <v>624</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6</v>
+        <v>43.2</v>
       </c>
       <c r="N19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O19" t="n">
         <v>21</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Daizy's Orange Cream 10mg THC 4pk 12oz can</t>
+          <t>Utepils Orange Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1555,48 +1555,48 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.5</v>
+        <v>10.85</v>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>8.68</v>
       </c>
       <c r="F20" t="n">
-        <v>1.44</v>
+        <v>2.17</v>
       </c>
       <c r="G20" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="H20" t="n">
-        <v>14.4</v>
+        <v>9.4</v>
       </c>
       <c r="I20" t="n">
-        <v>6.6</v>
+        <v>22.5</v>
       </c>
       <c r="J20" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="K20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L20" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M20" t="n">
-        <v>43.3</v>
+        <v>0.6</v>
       </c>
       <c r="N20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1629,13 +1629,13 @@
         <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="I21" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="J21" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="K21" t="n">
         <v>40</v>
@@ -1644,24 +1644,24 @@
         <v>40</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
         <v>47</v>
       </c>
       <c r="O21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUY ~40u (10cs) - sells in ~4 wks (rising into season)</t>
+          <t>BUY ~40u (10cs) - sells in ~4 wks</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Stigma Club Soda 10mg THC</t>
+          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1671,38 +1671,38 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Case 1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.03</v>
+        <v>10.85</v>
       </c>
       <c r="E22" t="n">
-        <v>9.15</v>
+        <v>8.68</v>
       </c>
       <c r="F22" t="n">
-        <v>0.88</v>
+        <v>2.17</v>
       </c>
       <c r="G22" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="H22" t="n">
-        <v>21.1</v>
+        <v>8.9</v>
       </c>
       <c r="I22" t="n">
-        <v>6.9</v>
+        <v>29.1</v>
       </c>
       <c r="J22" t="n">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="K22" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
-        <v>624</v>
+        <v>6</v>
       </c>
       <c r="M22" t="n">
-        <v>29.5</v>
+        <v>0.7</v>
       </c>
       <c r="N22" t="n">
         <v>46</v>
@@ -1712,14 +1712,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~30 wks (overstock); consider ~624u</t>
+          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Utepils Key Lime Seltzer 10mg THC 4pk 12oz can</t>
+          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1729,55 +1729,55 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Case 1</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="E23" t="n">
-        <v>8.68</v>
+        <v>9.82</v>
       </c>
       <c r="F23" t="n">
-        <v>2.17</v>
+        <v>1.18</v>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="H23" t="n">
-        <v>8.9</v>
+        <v>15.1</v>
       </c>
       <c r="I23" t="n">
-        <v>29.1</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L23" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7</v>
+        <v>10</v>
       </c>
       <c r="N23" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~10 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Clrty Pink Lemonade 10mg THC 4pk 12oz can</t>
+          <t>Stigma Club Soda 10mg THC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1787,55 +1787,55 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>10.03</v>
       </c>
       <c r="E24" t="n">
-        <v>9.82</v>
+        <v>9.15</v>
       </c>
       <c r="F24" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="G24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H24" t="n">
-        <v>14.7</v>
+        <v>19.9</v>
       </c>
       <c r="I24" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J24" t="n">
-        <v>65</v>
+        <v>122</v>
       </c>
       <c r="K24" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L24" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M24" t="n">
-        <v>10.2</v>
+        <v>31.3</v>
       </c>
       <c r="N24" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~10 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~31 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
+          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1849,44 +1849,44 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.5</v>
+        <v>9.33</v>
       </c>
       <c r="E25" t="n">
-        <v>9.06</v>
+        <v>8.01</v>
       </c>
       <c r="F25" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="G25" t="n">
         <v>14</v>
       </c>
       <c r="H25" t="n">
-        <v>11.2</v>
+        <v>11.9</v>
       </c>
       <c r="I25" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>99</v>
+        <v>33</v>
       </c>
       <c r="K25" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L25" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M25" t="n">
-        <v>55.7</v>
+        <v>12.7</v>
       </c>
       <c r="N25" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="O25" t="n">
         <v>16</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~56 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
+          <t>Daizy's Tropical Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1961,55 +1961,55 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FG From Supplier</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="E27" t="n">
+        <v>9.06</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G27" t="n">
+        <v>14</v>
+      </c>
+      <c r="H27" t="n">
         <v>11.2</v>
       </c>
-      <c r="F27" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G27" t="n">
-        <v>7</v>
-      </c>
-      <c r="H27" t="n">
-        <v>20.2</v>
-      </c>
       <c r="I27" t="n">
-        <v>15.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="K27" t="n">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="L27" t="n">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="M27" t="n">
-        <v>4.2</v>
+        <v>55.7</v>
       </c>
       <c r="N27" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O27" t="n">
         <v>16</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>BUY ~84u (14cs) - sells in ~4 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~56 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
+          <t>Wikid Paloma 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2035,13 +2035,13 @@
         <v>7</v>
       </c>
       <c r="H28" t="n">
-        <v>18.5</v>
+        <v>19.8</v>
       </c>
       <c r="I28" t="n">
-        <v>9.1</v>
+        <v>15.6</v>
       </c>
       <c r="J28" t="n">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="K28" t="n">
         <v>84</v>
@@ -2050,13 +2050,13 @@
         <v>84</v>
       </c>
       <c r="M28" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N28" t="n">
         <v>44</v>
       </c>
       <c r="O28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2067,7 +2067,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
+          <t>Wikid Bramble 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2077,55 +2077,55 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FG From Supplier</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E29" t="n">
-        <v>9.82</v>
+        <v>11.2</v>
       </c>
       <c r="F29" t="n">
-        <v>1.18</v>
+        <v>0.8</v>
       </c>
       <c r="G29" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>13.1</v>
+        <v>18.4</v>
       </c>
       <c r="I29" t="n">
-        <v>7.7</v>
+        <v>9</v>
       </c>
       <c r="J29" t="n">
-        <v>58</v>
+        <v>143</v>
       </c>
       <c r="K29" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="L29" t="n">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="M29" t="n">
-        <v>11.5</v>
+        <v>4.6</v>
       </c>
       <c r="N29" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="O29" t="n">
         <v>15</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~12 wks (rising into season)</t>
+          <t>BUY ~84u (14cs) - sells in ~5 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Clrty Black Cherry 5mg THC 4pk 12oz can</t>
+          <t>Clrty Tangerine 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2139,25 +2139,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9.33</v>
+        <v>11</v>
       </c>
       <c r="E30" t="n">
-        <v>8.01</v>
+        <v>9.82</v>
       </c>
       <c r="F30" t="n">
-        <v>1.32</v>
+        <v>1.18</v>
       </c>
       <c r="G30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H30" t="n">
-        <v>11.3</v>
+        <v>13.1</v>
       </c>
       <c r="I30" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="K30" t="n">
         <v>150</v>
@@ -2166,17 +2166,17 @@
         <v>150</v>
       </c>
       <c r="M30" t="n">
-        <v>13.3</v>
+        <v>11.4</v>
       </c>
       <c r="N30" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="O30" t="n">
         <v>15</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~13 wks (rising into season)</t>
+          <t>BUY ~150u (25cs) - sells in ~11 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2209,10 +2209,10 @@
         <v>17</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="I31" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
         <v>22</v>
@@ -2224,13 +2224,13 @@
         <v>36</v>
       </c>
       <c r="M31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="N31" t="n">
         <v>45</v>
       </c>
       <c r="O31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -2270,10 +2270,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K32" t="n">
         <v>624</v>
@@ -2282,7 +2282,7 @@
         <v>624</v>
       </c>
       <c r="M32" t="n">
-        <v>67.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="N32" t="n">
         <v>45</v>
@@ -2299,7 +2299,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Stigma Lemonade Tea 10mg THC</t>
+          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2309,55 +2309,55 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>Direct Buy</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>10.03</v>
+        <v>11</v>
       </c>
       <c r="E33" t="n">
-        <v>9.15</v>
+        <v>9.82</v>
       </c>
       <c r="F33" t="n">
-        <v>0.88</v>
+        <v>1.18</v>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H33" t="n">
-        <v>14.4</v>
+        <v>11</v>
       </c>
       <c r="I33" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="J33" t="n">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="K33" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="L33" t="n">
-        <v>624</v>
+        <v>150</v>
       </c>
       <c r="M33" t="n">
-        <v>43.4</v>
+        <v>13.6</v>
       </c>
       <c r="N33" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="O33" t="n">
         <v>13</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~43 wks (overstock); consider ~624u</t>
+          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CLRTY Watermelon 10mg THC 4pk 12oz can</t>
+          <t>Stigma Lemonade Tea 10mg THC</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2367,48 +2367,48 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Direct Buy</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11</v>
+        <v>10.03</v>
       </c>
       <c r="E34" t="n">
-        <v>9.82</v>
+        <v>9.15</v>
       </c>
       <c r="F34" t="n">
-        <v>1.18</v>
+        <v>0.88</v>
       </c>
       <c r="G34" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
-        <v>10.9</v>
+        <v>13.7</v>
       </c>
       <c r="I34" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J34" t="n">
-        <v>62</v>
+        <v>137</v>
       </c>
       <c r="K34" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L34" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M34" t="n">
-        <v>13.8</v>
+        <v>45.6</v>
       </c>
       <c r="N34" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="O34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>BUY ~150u (25cs) - sells in ~14 wks (rising into season)</t>
+          <t>CAUTION - 624u = ~46 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2441,22 +2441,22 @@
         <v>20</v>
       </c>
       <c r="H35" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="I35" t="n">
-        <v>13.4</v>
+        <v>12.7</v>
       </c>
       <c r="J35" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K35" t="n">
         <v>3</v>
       </c>
       <c r="L35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M35" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="N35" t="n">
         <v>47</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>BUY ~3u (1cs) - sells in ~1 wks (rising into season)</t>
+          <t>BUY ~6u (2cs) - sells in ~2 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -2499,13 +2499,13 @@
         <v>9</v>
       </c>
       <c r="H36" t="n">
-        <v>13.9</v>
+        <v>12.8</v>
       </c>
       <c r="I36" t="n">
         <v>11.3</v>
       </c>
       <c r="J36" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K36" t="n">
         <v>624</v>
@@ -2514,17 +2514,17 @@
         <v>624</v>
       </c>
       <c r="M36" t="n">
-        <v>45</v>
+        <v>48.8</v>
       </c>
       <c r="N36" t="n">
         <v>46</v>
       </c>
       <c r="O36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~45 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 624u = ~49 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -2557,10 +2557,10 @@
         <v>7</v>
       </c>
       <c r="H37" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I37" t="n">
-        <v>11.7</v>
+        <v>11.9</v>
       </c>
       <c r="J37" t="n">
         <v>146</v>
@@ -2572,7 +2572,7 @@
         <v>84</v>
       </c>
       <c r="M37" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="N37" t="n">
         <v>44</v>
@@ -2589,7 +2589,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
+          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2599,55 +2599,55 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lift Bridge Supports to Hit Pricing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>9.67</v>
+        <v>9.33</v>
       </c>
       <c r="E38" t="n">
-        <v>7.57</v>
+        <v>8.01</v>
       </c>
       <c r="F38" t="n">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="G38" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="H38" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="I38" t="n">
-        <v>13.4</v>
+        <v>16.3</v>
       </c>
       <c r="J38" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="K38" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>150</v>
       </c>
       <c r="M38" t="n">
-        <v>2</v>
+        <v>27.8</v>
       </c>
       <c r="N38" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="O38" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
+          <t>CAUTION - 150u = ~28 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Clrty Blue Raz 5mg THC 4pk 12oz can</t>
+          <t>Lift Bridge Believer Float 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2657,48 +2657,48 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Lift Bridge Supports to Hit Pricing</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9.33</v>
+        <v>9.67</v>
       </c>
       <c r="E39" t="n">
-        <v>8.01</v>
+        <v>7.57</v>
       </c>
       <c r="F39" t="n">
-        <v>1.32</v>
+        <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="H39" t="n">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>13.4</v>
       </c>
       <c r="J39" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="K39" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
-        <v>150</v>
+        <v>6</v>
       </c>
       <c r="M39" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="O39" t="n">
         <v>6</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~31 wks (overstock); consider ~150u</t>
+          <t>BUY ~6u (1cs) - sells in ~2 wks</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2731,7 @@
         <v>24</v>
       </c>
       <c r="H40" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I40" t="n">
         <v>10.1</v>
@@ -2789,7 +2789,7 @@
         <v>20</v>
       </c>
       <c r="H41" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I41" t="n">
         <v>10.1</v>
@@ -2963,7 +2963,7 @@
         <v>22</v>
       </c>
       <c r="H44" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I44" t="n">
         <v>10.1</v>
@@ -2995,7 +2995,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3021,13 +3021,13 @@
         <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="I45" t="n">
-        <v>22.5</v>
+        <v>49.6</v>
       </c>
       <c r="J45" t="n">
-        <v>21</v>
+        <v>71</v>
       </c>
       <c r="K45" t="n">
         <v>24</v>
@@ -3036,7 +3036,7 @@
         <v>24</v>
       </c>
       <c r="M45" t="n">
-        <v>14.3</v>
+        <v>13.7</v>
       </c>
       <c r="N45" t="n">
         <v>44</v>
@@ -3053,7 +3053,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sweet Justice Cola Zero Sugar 10mg THC 4pk 12oz can</t>
+          <t>Sweet Justice Island Punch 10mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3079,13 +3079,13 @@
         <v>20</v>
       </c>
       <c r="H46" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="I46" t="n">
-        <v>65.2</v>
+        <v>22.5</v>
       </c>
       <c r="J46" t="n">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="K46" t="n">
         <v>24</v>
@@ -3094,17 +3094,17 @@
         <v>24</v>
       </c>
       <c r="M46" t="n">
-        <v>16.4</v>
+        <v>14.3</v>
       </c>
       <c r="N46" t="n">
         <v>44</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>CAUTION - 24u = ~16 wks (overstock); consider ~24u</t>
+          <t>BUY ~24u (4cs) - sells in ~14 wks (rising into season)</t>
         </is>
       </c>
     </row>
@@ -3195,13 +3195,13 @@
         <v>15</v>
       </c>
       <c r="H48" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="I48" t="n">
-        <v>21.8</v>
+        <v>26</v>
       </c>
       <c r="J48" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K48" t="n">
         <v>40</v>
@@ -3210,7 +3210,7 @@
         <v>40</v>
       </c>
       <c r="M48" t="n">
-        <v>22.8</v>
+        <v>24.9</v>
       </c>
       <c r="N48" t="n">
         <v>48</v>
@@ -3220,14 +3220,14 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>CAUTION - 40u = ~23 wks (overstock); consider ~40u</t>
+          <t>CAUTION - 40u = ~25 wks (overstock); consider ~40u</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
+          <t>Clrty SodaPot Blue Ginger 10mg 4pk 12oz can</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3241,51 +3241,51 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.58</v>
+        <v>11</v>
       </c>
       <c r="E49" t="n">
-        <v>7.06</v>
+        <v>9.82</v>
       </c>
       <c r="F49" t="n">
-        <v>3.53</v>
+        <v>1.18</v>
       </c>
       <c r="G49" t="n">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="I49" t="n">
-        <v>120.5</v>
+        <v>102.6</v>
       </c>
       <c r="J49" t="n">
-        <v>30</v>
+        <v>83</v>
       </c>
       <c r="K49" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="L49" t="n">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="M49" t="n">
-        <v>26.8</v>
+        <v>195.9</v>
       </c>
       <c r="N49" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>CAUTION - 12u = ~27 wks (overstock); consider ~12u</t>
+          <t>CAUTION - 150u = ~196 wks (overstock); consider ~150u</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Stigma Berry Tea 10mg THC</t>
+          <t>Sweet Justice Lemon Ginger 5mg THC 4pk 12oz can</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3295,38 +3295,38 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.03</v>
+        <v>10.58</v>
       </c>
       <c r="E50" t="n">
-        <v>9.15</v>
+        <v>7.06</v>
       </c>
       <c r="F50" t="n">
-        <v>0.88</v>
+        <v>3.53</v>
       </c>
       <c r="G50" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="H50" t="n">
-        <v>1.7</v>
+        <v>0.4</v>
       </c>
       <c r="I50" t="n">
-        <v>10.2</v>
+        <v>137.8</v>
       </c>
       <c r="J50" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="K50" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="L50" t="n">
-        <v>624</v>
+        <v>12</v>
       </c>
       <c r="M50" t="n">
-        <v>367.7</v>
+        <v>30.6</v>
       </c>
       <c r="N50" t="n">
         <v>46</v>
@@ -3336,14 +3336,14 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>CAUTION - 624u = ~368 wks (overstock); consider ~624u</t>
+          <t>CAUTION - 12u = ~31 wks (overstock); consider ~12u</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Clrty SodaPot Blue Ginger 10mg 4pk 12oz can</t>
+          <t>Stigma Berry Tea 10mg THC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3353,48 +3353,48 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>10 Free on 104, 3 from Stigma, 7 from Artisan</t>
         </is>
       </c>
       <c r="D51" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="E51" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G51" t="n">
+        <v>9</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I51" t="n">
         <v>11</v>
       </c>
-      <c r="E51" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="G51" t="n">
-        <v>11</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I51" t="n">
-        <v>102.6</v>
-      </c>
       <c r="J51" t="n">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="L51" t="n">
-        <v>150</v>
+        <v>624</v>
       </c>
       <c r="M51" t="n">
-        <v>193.8</v>
+        <v>403.5</v>
       </c>
       <c r="N51" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="O51" t="n">
         <v>1</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>CAUTION - 150u = ~194 wks (overstock); consider ~150u</t>
+          <t>CAUTION - 624u = ~404 wks (overstock); consider ~624u</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
         <v>60</v>
       </c>
       <c r="M58" t="n">
-        <v>268.7</v>
+        <v>271.6</v>
       </c>
       <c r="N58" t="n">
         <v>48</v>
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>CAUTION - 60u = ~269 wks (overstock); consider ~60u</t>
+          <t>CAUTION - 60u = ~272 wks (overstock); consider ~60u</t>
         </is>
       </c>
     </row>
